--- a/A_FINAL_RESULT/eko_transactions.xlsx
+++ b/A_FINAL_RESULT/eko_transactions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\A_FINAL_RESULT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC284510-0195-415E-9BF8-FAD3C3AFAA58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B9B4239-90E6-4CE9-AFF1-74514A300C00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="11" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ" sheetId="1" r:id="rId1"/>
@@ -43338,6 +43338,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">

--- a/A_FINAL_RESULT/eko_transactions.xlsx
+++ b/A_FINAL_RESULT/eko_transactions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\A_FINAL_RESULT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B9B4239-90E6-4CE9-AFF1-74514A300C00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CAA947F-4CAE-4717-935B-F72CFC6E46AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="35" activeTab="37" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ" sheetId="1" r:id="rId1"/>
@@ -32,9 +32,9 @@
     <sheet name="ДОК ТРАНС ЕООД" sheetId="17" r:id="rId17"/>
     <sheet name="ЕВРО ТРАНС ПРЕМИУМ ЕООД" sheetId="18" r:id="rId18"/>
     <sheet name="ЕВРОУЕЙ СЪРВИЗ ООД" sheetId="19" r:id="rId19"/>
-    <sheet name="ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДС" sheetId="20" r:id="rId20"/>
-    <sheet name="ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ" sheetId="21" r:id="rId21"/>
-    <sheet name="ЗЕМЕДЕЛСКА ТЕХНИКА ООД" sheetId="22" r:id="rId22"/>
+    <sheet name="ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ" sheetId="21" r:id="rId20"/>
+    <sheet name="ЗЕМЕДЕЛСКА ТЕХНИКА ООД" sheetId="22" r:id="rId21"/>
+    <sheet name="ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДС" sheetId="20" r:id="rId22"/>
     <sheet name="ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ" sheetId="23" r:id="rId23"/>
     <sheet name="ИВО ИВАНОВ ЧЗС" sheetId="24" r:id="rId24"/>
     <sheet name="ИВОН СТРОЙ 2015 ЕООД" sheetId="25" r:id="rId25"/>
@@ -58,7 +58,7 @@
     <sheet name="ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ" sheetId="43" r:id="rId43"/>
     <sheet name="Unknown" sheetId="44" r:id="rId44"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -5025,10 +5025,15 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
   <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -5653,8 +5658,18 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
   <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -13323,8 +13338,8 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
-  <dimension ref="A1:M19"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -13370,239 +13385,209 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="B2" t="s">
-        <v>432</v>
+        <v>380</v>
       </c>
       <c r="C2" t="s">
-        <v>602</v>
+        <v>625</v>
       </c>
       <c r="D2" t="s">
-        <v>603</v>
+        <v>626</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>240</v>
       </c>
       <c r="F2">
-        <v>42.976999999999897</v>
+        <v>37.261000000000003</v>
       </c>
       <c r="G2" t="s">
         <v>18</v>
       </c>
-      <c r="H2">
-        <v>1.21</v>
-      </c>
-      <c r="I2">
-        <v>52</v>
-      </c>
       <c r="J2">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="K2">
-        <v>56.3</v>
+        <v>57.01</v>
       </c>
       <c r="L2" t="s">
-        <v>604</v>
+        <v>627</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>15671</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>432</v>
       </c>
       <c r="C3" t="s">
-        <v>605</v>
+        <v>628</v>
       </c>
       <c r="D3" t="s">
-        <v>606</v>
+        <v>629</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>240</v>
       </c>
       <c r="F3">
-        <v>40.137</v>
+        <v>26.707999999999899</v>
       </c>
       <c r="G3" t="s">
         <v>18</v>
       </c>
-      <c r="H3">
-        <v>1.21</v>
-      </c>
-      <c r="I3">
-        <v>48.57</v>
-      </c>
       <c r="J3">
-        <v>1.31</v>
+        <v>1.54</v>
       </c>
       <c r="K3">
-        <v>52.58</v>
+        <v>41.13</v>
       </c>
       <c r="L3" t="s">
-        <v>607</v>
+        <v>630</v>
       </c>
       <c r="M3">
-        <v>316540</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>104</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>202</v>
       </c>
       <c r="C4" t="s">
-        <v>608</v>
+        <v>625</v>
       </c>
       <c r="D4" t="s">
-        <v>609</v>
+        <v>626</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>240</v>
       </c>
       <c r="F4">
-        <v>49.811999999999898</v>
+        <v>24.859000000000002</v>
       </c>
       <c r="G4" t="s">
         <v>18</v>
       </c>
-      <c r="H4">
-        <v>1.23</v>
-      </c>
-      <c r="I4">
-        <v>61.27</v>
-      </c>
       <c r="J4">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="K4">
-        <v>66.25</v>
+        <v>38.78</v>
       </c>
       <c r="L4" t="s">
-        <v>610</v>
+        <v>631</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>15913</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B5" t="s">
-        <v>380</v>
+        <v>432</v>
       </c>
       <c r="C5" t="s">
-        <v>605</v>
+        <v>632</v>
       </c>
       <c r="D5" t="s">
-        <v>606</v>
+        <v>633</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F5">
-        <v>54.6099999999999</v>
+        <v>41.091000000000001</v>
       </c>
       <c r="G5" t="s">
         <v>18</v>
       </c>
-      <c r="H5">
-        <v>1.25</v>
-      </c>
-      <c r="I5">
-        <v>68.260000000000005</v>
-      </c>
       <c r="J5">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="K5">
-        <v>77</v>
+        <v>54.24</v>
       </c>
       <c r="L5" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="M5">
-        <v>316950</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>177</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>436</v>
       </c>
       <c r="C6" t="s">
-        <v>608</v>
+        <v>625</v>
       </c>
       <c r="D6" t="s">
-        <v>609</v>
+        <v>626</v>
       </c>
       <c r="E6" t="s">
-        <v>179</v>
+        <v>45</v>
       </c>
       <c r="F6">
-        <v>48.088999999999899</v>
+        <v>37.563000000000002</v>
       </c>
       <c r="G6" t="s">
         <v>18</v>
       </c>
       <c r="J6">
-        <v>1.68</v>
+        <v>1.35</v>
       </c>
       <c r="K6">
-        <v>80.790000000000006</v>
+        <v>50.71</v>
       </c>
       <c r="L6" t="s">
-        <v>128</v>
+        <v>448</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>16287</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>380</v>
       </c>
       <c r="C7" t="s">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="D7" t="s">
-        <v>613</v>
+        <v>629</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>240</v>
       </c>
       <c r="F7">
-        <v>33.817999999999898</v>
+        <v>26.739000000000001</v>
       </c>
       <c r="G7" t="s">
         <v>18</v>
       </c>
-      <c r="H7">
-        <v>1.25</v>
-      </c>
-      <c r="I7">
-        <v>42.27</v>
-      </c>
       <c r="J7">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="K7">
-        <v>48.36</v>
+        <v>43.05</v>
       </c>
       <c r="L7" t="s">
-        <v>614</v>
+        <v>634</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -13610,163 +13595,139 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>380</v>
+        <v>252</v>
       </c>
       <c r="C8" t="s">
-        <v>605</v>
+        <v>625</v>
       </c>
       <c r="D8" t="s">
-        <v>606</v>
+        <v>626</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>240</v>
       </c>
       <c r="F8">
-        <v>20.4149999999999</v>
+        <v>28.117999999999899</v>
       </c>
       <c r="G8" t="s">
         <v>18</v>
       </c>
-      <c r="H8">
-        <v>1.42</v>
-      </c>
-      <c r="I8">
-        <v>28.99</v>
-      </c>
       <c r="J8">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="K8">
-        <v>30.01</v>
+        <v>47.52</v>
       </c>
       <c r="L8" t="s">
-        <v>615</v>
+        <v>108</v>
       </c>
       <c r="M8">
-        <v>317270</v>
+        <v>16883</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>274</v>
+        <v>47</v>
       </c>
       <c r="B9" t="s">
         <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>602</v>
+        <v>632</v>
       </c>
       <c r="D9" t="s">
-        <v>603</v>
+        <v>633</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F9">
-        <v>36.362000000000002</v>
+        <v>43.542000000000002</v>
       </c>
       <c r="G9" t="s">
         <v>18</v>
       </c>
-      <c r="H9">
-        <v>1.46</v>
-      </c>
-      <c r="I9">
-        <v>53.09</v>
-      </c>
       <c r="J9">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="K9">
-        <v>55.27</v>
+        <v>61.83</v>
       </c>
       <c r="L9" t="s">
-        <v>616</v>
+        <v>267</v>
       </c>
       <c r="M9">
-        <v>430120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>274</v>
+        <v>47</v>
       </c>
       <c r="B10" t="s">
-        <v>380</v>
+        <v>208</v>
       </c>
       <c r="C10" t="s">
-        <v>605</v>
+        <v>625</v>
       </c>
       <c r="D10" t="s">
-        <v>606</v>
+        <v>626</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>240</v>
       </c>
       <c r="F10">
-        <v>30.867999999999899</v>
+        <v>31.337</v>
       </c>
       <c r="G10" t="s">
         <v>18</v>
       </c>
-      <c r="H10">
-        <v>1.46</v>
-      </c>
-      <c r="I10">
-        <v>45.07</v>
-      </c>
       <c r="J10">
-        <v>1.51</v>
+        <v>1.69</v>
       </c>
       <c r="K10">
-        <v>46.61</v>
+        <v>52.96</v>
       </c>
       <c r="L10" t="s">
-        <v>617</v>
+        <v>635</v>
       </c>
       <c r="M10">
-        <v>317370</v>
+        <v>16562</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>432</v>
       </c>
       <c r="C11" t="s">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="D11" t="s">
-        <v>613</v>
+        <v>629</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>240</v>
       </c>
       <c r="F11">
-        <v>24.591999999999899</v>
+        <v>28.210999999999899</v>
       </c>
       <c r="G11" t="s">
         <v>18</v>
       </c>
-      <c r="H11">
-        <v>1.46</v>
-      </c>
-      <c r="I11">
-        <v>35.9</v>
-      </c>
       <c r="J11">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="K11">
-        <v>37.380000000000003</v>
+        <v>48.24</v>
       </c>
       <c r="L11" t="s">
-        <v>618</v>
+        <v>547</v>
       </c>
       <c r="M11">
         <v>0</v>
@@ -13774,330 +13735,37 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>315</v>
       </c>
       <c r="B12" t="s">
-        <v>380</v>
+        <v>410</v>
       </c>
       <c r="C12" t="s">
-        <v>605</v>
+        <v>625</v>
       </c>
       <c r="D12" t="s">
-        <v>606</v>
+        <v>626</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>240</v>
       </c>
       <c r="F12">
-        <v>22.882000000000001</v>
+        <v>26.491</v>
       </c>
       <c r="G12" t="s">
         <v>18</v>
       </c>
-      <c r="H12">
-        <v>1.48</v>
-      </c>
-      <c r="I12">
-        <v>33.869999999999997</v>
-      </c>
       <c r="J12">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="K12">
-        <v>35.01</v>
+        <v>45.83</v>
       </c>
       <c r="L12" t="s">
-        <v>619</v>
+        <v>636</v>
       </c>
       <c r="M12">
-        <v>317685</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>299</v>
-      </c>
-      <c r="B13" t="s">
-        <v>93</v>
-      </c>
-      <c r="C13" t="s">
-        <v>605</v>
-      </c>
-      <c r="D13" t="s">
-        <v>606</v>
-      </c>
-      <c r="E13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13">
-        <v>44.963000000000001</v>
-      </c>
-      <c r="G13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13">
-        <v>1.54</v>
-      </c>
-      <c r="I13">
-        <v>69.239999999999995</v>
-      </c>
-      <c r="J13">
-        <v>1.6</v>
-      </c>
-      <c r="K13">
-        <v>71.94</v>
-      </c>
-      <c r="L13" t="s">
-        <v>505</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>299</v>
-      </c>
-      <c r="B14" t="s">
-        <v>224</v>
-      </c>
-      <c r="C14" t="s">
-        <v>605</v>
-      </c>
-      <c r="D14" t="s">
-        <v>606</v>
-      </c>
-      <c r="E14" t="s">
-        <v>17</v>
-      </c>
-      <c r="F14">
-        <v>30.207999999999899</v>
-      </c>
-      <c r="G14" t="s">
-        <v>18</v>
-      </c>
-      <c r="H14">
-        <v>1.54</v>
-      </c>
-      <c r="I14">
-        <v>46.52</v>
-      </c>
-      <c r="J14">
-        <v>1.59</v>
-      </c>
-      <c r="K14">
-        <v>48.03</v>
-      </c>
-      <c r="L14" t="s">
-        <v>620</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>69</v>
-      </c>
-      <c r="B15" t="s">
-        <v>93</v>
-      </c>
-      <c r="C15" t="s">
-        <v>608</v>
-      </c>
-      <c r="D15" t="s">
-        <v>609</v>
-      </c>
-      <c r="E15" t="s">
-        <v>17</v>
-      </c>
-      <c r="F15">
-        <v>48.701999999999899</v>
-      </c>
-      <c r="G15" t="s">
-        <v>18</v>
-      </c>
-      <c r="H15">
-        <v>1.6</v>
-      </c>
-      <c r="I15">
-        <v>77.92</v>
-      </c>
-      <c r="J15">
-        <v>1.61</v>
-      </c>
-      <c r="K15">
-        <v>78.41</v>
-      </c>
-      <c r="L15" t="s">
-        <v>130</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>69</v>
-      </c>
-      <c r="B16" t="s">
-        <v>93</v>
-      </c>
-      <c r="C16" t="s">
-        <v>612</v>
-      </c>
-      <c r="D16" t="s">
-        <v>613</v>
-      </c>
-      <c r="E16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F16">
-        <v>32.783000000000001</v>
-      </c>
-      <c r="G16" t="s">
-        <v>18</v>
-      </c>
-      <c r="H16">
-        <v>1.6</v>
-      </c>
-      <c r="I16">
-        <v>52.45</v>
-      </c>
-      <c r="J16">
-        <v>1.61</v>
-      </c>
-      <c r="K16">
-        <v>52.78</v>
-      </c>
-      <c r="L16" t="s">
-        <v>621</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>53</v>
-      </c>
-      <c r="B17" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" t="s">
-        <v>602</v>
-      </c>
-      <c r="D17" t="s">
-        <v>603</v>
-      </c>
-      <c r="E17" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17">
-        <v>40.512</v>
-      </c>
-      <c r="G17" t="s">
-        <v>18</v>
-      </c>
-      <c r="H17">
-        <v>1.6</v>
-      </c>
-      <c r="I17">
-        <v>64.819999999999993</v>
-      </c>
-      <c r="J17">
-        <v>1.62</v>
-      </c>
-      <c r="K17">
-        <v>65.63</v>
-      </c>
-      <c r="L17" t="s">
-        <v>622</v>
-      </c>
-      <c r="M17">
-        <v>430652</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>135</v>
-      </c>
-      <c r="B18" t="s">
-        <v>224</v>
-      </c>
-      <c r="C18" t="s">
-        <v>605</v>
-      </c>
-      <c r="D18" t="s">
-        <v>606</v>
-      </c>
-      <c r="E18" t="s">
-        <v>17</v>
-      </c>
-      <c r="F18">
-        <v>28.27</v>
-      </c>
-      <c r="G18" t="s">
-        <v>18</v>
-      </c>
-      <c r="H18">
-        <v>1.61</v>
-      </c>
-      <c r="I18">
-        <v>45.51</v>
-      </c>
-      <c r="J18">
-        <v>1.63</v>
-      </c>
-      <c r="K18">
-        <v>46.08</v>
-      </c>
-      <c r="L18" t="s">
-        <v>623</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>72</v>
-      </c>
-      <c r="B19" t="s">
-        <v>380</v>
-      </c>
-      <c r="C19" t="s">
-        <v>605</v>
-      </c>
-      <c r="D19" t="s">
-        <v>606</v>
-      </c>
-      <c r="E19" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19">
-        <v>50.142000000000003</v>
-      </c>
-      <c r="G19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H19">
-        <v>1.64</v>
-      </c>
-      <c r="I19">
-        <v>82.23</v>
-      </c>
-      <c r="J19">
-        <v>1.69</v>
-      </c>
-      <c r="K19">
-        <v>84.74</v>
-      </c>
-      <c r="L19" t="s">
-        <v>624</v>
-      </c>
-      <c r="M19">
-        <v>318930</v>
+        <v>17100</v>
       </c>
     </row>
   </sheetData>
@@ -14106,9 +13774,17 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
-  <dimension ref="A1:M12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -14156,66 +13832,78 @@
         <v>104</v>
       </c>
       <c r="B2" t="s">
-        <v>380</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>625</v>
+        <v>637</v>
       </c>
       <c r="D2" t="s">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="E2" t="s">
-        <v>240</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>37.261000000000003</v>
+        <v>62.2349999999999</v>
       </c>
       <c r="G2" t="s">
         <v>18</v>
       </c>
+      <c r="H2">
+        <v>1.21</v>
+      </c>
+      <c r="I2">
+        <v>75.3</v>
+      </c>
       <c r="J2">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="K2">
-        <v>57.01</v>
+        <v>82.15</v>
       </c>
       <c r="L2" t="s">
-        <v>627</v>
+        <v>639</v>
       </c>
       <c r="M2">
-        <v>15671</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>107</v>
       </c>
       <c r="B3" t="s">
-        <v>432</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="D3" t="s">
-        <v>629</v>
+        <v>641</v>
       </c>
       <c r="E3" t="s">
-        <v>240</v>
+        <v>45</v>
       </c>
       <c r="F3">
-        <v>26.707999999999899</v>
+        <v>27.9469999999999</v>
       </c>
       <c r="G3" t="s">
         <v>18</v>
       </c>
+      <c r="H3">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="I3">
+        <v>32.42</v>
+      </c>
       <c r="J3">
-        <v>1.54</v>
+        <v>1.31</v>
       </c>
       <c r="K3">
-        <v>41.13</v>
+        <v>36.61</v>
       </c>
       <c r="L3" t="s">
-        <v>630</v>
+        <v>642</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -14223,69 +13911,81 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>202</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>625</v>
+        <v>640</v>
       </c>
       <c r="D4" t="s">
-        <v>626</v>
+        <v>641</v>
       </c>
       <c r="E4" t="s">
-        <v>240</v>
+        <v>45</v>
       </c>
       <c r="F4">
-        <v>24.859000000000002</v>
+        <v>36.610999999999898</v>
       </c>
       <c r="G4" t="s">
         <v>18</v>
       </c>
+      <c r="H4">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="I4">
+        <v>42.47</v>
+      </c>
       <c r="J4">
-        <v>1.56</v>
+        <v>1.31</v>
       </c>
       <c r="K4">
-        <v>38.78</v>
+        <v>47.96</v>
       </c>
       <c r="L4" t="s">
-        <v>631</v>
+        <v>643</v>
       </c>
       <c r="M4">
-        <v>15913</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>107</v>
+        <v>343</v>
       </c>
       <c r="B5" t="s">
-        <v>432</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="D5" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="E5" t="s">
         <v>45</v>
       </c>
       <c r="F5">
-        <v>41.091000000000001</v>
+        <v>39.006999999999898</v>
       </c>
       <c r="G5" t="s">
         <v>18</v>
       </c>
+      <c r="H5">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="I5">
+        <v>45.25</v>
+      </c>
       <c r="J5">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="K5">
-        <v>54.24</v>
+        <v>53.05</v>
       </c>
       <c r="L5" t="s">
-        <v>616</v>
+        <v>644</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -14293,69 +13993,81 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>177</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
-        <v>436</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>625</v>
+        <v>640</v>
       </c>
       <c r="D6" t="s">
-        <v>626</v>
+        <v>641</v>
       </c>
       <c r="E6" t="s">
         <v>45</v>
       </c>
       <c r="F6">
-        <v>37.563000000000002</v>
+        <v>40.317</v>
       </c>
       <c r="G6" t="s">
         <v>18</v>
       </c>
+      <c r="H6">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="I6">
+        <v>46.77</v>
+      </c>
       <c r="J6">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="K6">
-        <v>50.71</v>
+        <v>56.04</v>
       </c>
       <c r="L6" t="s">
-        <v>448</v>
+        <v>645</v>
       </c>
       <c r="M6">
-        <v>16287</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s">
-        <v>380</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>628</v>
+        <v>646</v>
       </c>
       <c r="D7" t="s">
-        <v>629</v>
+        <v>647</v>
       </c>
       <c r="E7" t="s">
-        <v>240</v>
+        <v>45</v>
       </c>
       <c r="F7">
-        <v>26.739000000000001</v>
+        <v>30.34</v>
       </c>
       <c r="G7" t="s">
         <v>18</v>
       </c>
+      <c r="H7">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="I7">
+        <v>35.19</v>
+      </c>
       <c r="J7">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="K7">
-        <v>43.05</v>
+        <v>42.78</v>
       </c>
       <c r="L7" t="s">
-        <v>634</v>
+        <v>648</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -14366,66 +14078,78 @@
         <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>252</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>625</v>
+        <v>649</v>
       </c>
       <c r="D8" t="s">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="E8" t="s">
-        <v>240</v>
+        <v>17</v>
       </c>
       <c r="F8">
-        <v>28.117999999999899</v>
+        <v>68.076999999999899</v>
       </c>
       <c r="G8" t="s">
         <v>18</v>
       </c>
+      <c r="H8">
+        <v>1.21</v>
+      </c>
+      <c r="I8">
+        <v>82.37</v>
+      </c>
       <c r="J8">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="K8">
-        <v>47.52</v>
+        <v>106.2</v>
       </c>
       <c r="L8" t="s">
-        <v>108</v>
+        <v>599</v>
       </c>
       <c r="M8">
-        <v>16883</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="D9" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="E9" t="s">
         <v>45</v>
       </c>
       <c r="F9">
-        <v>43.542000000000002</v>
+        <v>33.427999999999898</v>
       </c>
       <c r="G9" t="s">
         <v>18</v>
       </c>
+      <c r="H9">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="I9">
+        <v>38.78</v>
+      </c>
       <c r="J9">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="K9">
-        <v>61.83</v>
+        <v>48.47</v>
       </c>
       <c r="L9" t="s">
-        <v>267</v>
+        <v>651</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -14433,107 +14157,43 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>135</v>
       </c>
       <c r="B10" t="s">
-        <v>208</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>625</v>
+        <v>640</v>
       </c>
       <c r="D10" t="s">
-        <v>626</v>
+        <v>641</v>
       </c>
       <c r="E10" t="s">
-        <v>240</v>
+        <v>45</v>
       </c>
       <c r="F10">
-        <v>31.337</v>
+        <v>38.040999999999897</v>
       </c>
       <c r="G10" t="s">
         <v>18</v>
       </c>
+      <c r="H10">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="I10">
+        <v>44.13</v>
+      </c>
       <c r="J10">
-        <v>1.69</v>
+        <v>1.46</v>
       </c>
       <c r="K10">
-        <v>52.96</v>
+        <v>55.54</v>
       </c>
       <c r="L10" t="s">
-        <v>635</v>
+        <v>532</v>
       </c>
       <c r="M10">
-        <v>16562</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>84</v>
-      </c>
-      <c r="B11" t="s">
-        <v>432</v>
-      </c>
-      <c r="C11" t="s">
-        <v>628</v>
-      </c>
-      <c r="D11" t="s">
-        <v>629</v>
-      </c>
-      <c r="E11" t="s">
-        <v>240</v>
-      </c>
-      <c r="F11">
-        <v>28.210999999999899</v>
-      </c>
-      <c r="G11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11">
-        <v>1.71</v>
-      </c>
-      <c r="K11">
-        <v>48.24</v>
-      </c>
-      <c r="L11" t="s">
-        <v>547</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>315</v>
-      </c>
-      <c r="B12" t="s">
-        <v>410</v>
-      </c>
-      <c r="C12" t="s">
-        <v>625</v>
-      </c>
-      <c r="D12" t="s">
-        <v>626</v>
-      </c>
-      <c r="E12" t="s">
-        <v>240</v>
-      </c>
-      <c r="F12">
-        <v>26.491</v>
-      </c>
-      <c r="G12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J12">
-        <v>1.73</v>
-      </c>
-      <c r="K12">
-        <v>45.83</v>
-      </c>
-      <c r="L12" t="s">
-        <v>636</v>
-      </c>
-      <c r="M12">
-        <v>17100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -14542,9 +14202,13 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
-  <dimension ref="A1:M10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -14589,22 +14253,22 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>432</v>
       </c>
       <c r="C2" t="s">
-        <v>637</v>
+        <v>602</v>
       </c>
       <c r="D2" t="s">
-        <v>638</v>
+        <v>603</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
       </c>
       <c r="F2">
-        <v>62.2349999999999</v>
+        <v>42.976999999999897</v>
       </c>
       <c r="G2" t="s">
         <v>18</v>
@@ -14613,16 +14277,16 @@
         <v>1.21</v>
       </c>
       <c r="I2">
-        <v>75.3</v>
+        <v>52</v>
       </c>
       <c r="J2">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="K2">
-        <v>82.15</v>
+        <v>56.3</v>
       </c>
       <c r="L2" t="s">
-        <v>639</v>
+        <v>604</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -14630,81 +14294,81 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>640</v>
+        <v>605</v>
       </c>
       <c r="D3" t="s">
-        <v>641</v>
+        <v>606</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="F3">
-        <v>27.9469999999999</v>
+        <v>40.137</v>
       </c>
       <c r="G3" t="s">
         <v>18</v>
       </c>
       <c r="H3">
-        <v>1.1599999999999999</v>
+        <v>1.21</v>
       </c>
       <c r="I3">
-        <v>32.42</v>
+        <v>48.57</v>
       </c>
       <c r="J3">
         <v>1.31</v>
       </c>
       <c r="K3">
-        <v>36.61</v>
+        <v>52.58</v>
       </c>
       <c r="L3" t="s">
-        <v>642</v>
+        <v>607</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>316540</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>640</v>
+        <v>608</v>
       </c>
       <c r="D4" t="s">
-        <v>641</v>
+        <v>609</v>
       </c>
       <c r="E4" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="F4">
-        <v>36.610999999999898</v>
+        <v>49.811999999999898</v>
       </c>
       <c r="G4" t="s">
         <v>18</v>
       </c>
       <c r="H4">
-        <v>1.1599999999999999</v>
+        <v>1.23</v>
       </c>
       <c r="I4">
-        <v>42.47</v>
+        <v>61.27</v>
       </c>
       <c r="J4">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="K4">
-        <v>47.96</v>
+        <v>66.25</v>
       </c>
       <c r="L4" t="s">
-        <v>643</v>
+        <v>610</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -14712,81 +14376,75 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>343</v>
+        <v>109</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>380</v>
       </c>
       <c r="C5" t="s">
-        <v>640</v>
+        <v>605</v>
       </c>
       <c r="D5" t="s">
-        <v>641</v>
+        <v>606</v>
       </c>
       <c r="E5" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="F5">
-        <v>39.006999999999898</v>
+        <v>54.6099999999999</v>
       </c>
       <c r="G5" t="s">
         <v>18</v>
       </c>
       <c r="H5">
-        <v>1.1599999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="I5">
-        <v>45.25</v>
+        <v>68.260000000000005</v>
       </c>
       <c r="J5">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="K5">
-        <v>53.05</v>
+        <v>77</v>
       </c>
       <c r="L5" t="s">
-        <v>644</v>
+        <v>611</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>316950</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>640</v>
+        <v>608</v>
       </c>
       <c r="D6" t="s">
-        <v>641</v>
+        <v>609</v>
       </c>
       <c r="E6" t="s">
-        <v>45</v>
+        <v>179</v>
       </c>
       <c r="F6">
-        <v>40.317</v>
+        <v>48.088999999999899</v>
       </c>
       <c r="G6" t="s">
         <v>18</v>
       </c>
-      <c r="H6">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="I6">
-        <v>46.77</v>
-      </c>
       <c r="J6">
-        <v>1.39</v>
+        <v>1.68</v>
       </c>
       <c r="K6">
-        <v>56.04</v>
+        <v>80.790000000000006</v>
       </c>
       <c r="L6" t="s">
-        <v>645</v>
+        <v>128</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -14794,40 +14452,40 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>646</v>
+        <v>612</v>
       </c>
       <c r="D7" t="s">
-        <v>647</v>
+        <v>613</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="F7">
-        <v>30.34</v>
+        <v>33.817999999999898</v>
       </c>
       <c r="G7" t="s">
         <v>18</v>
       </c>
       <c r="H7">
-        <v>1.1599999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="I7">
-        <v>35.19</v>
+        <v>42.27</v>
       </c>
       <c r="J7">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="K7">
-        <v>42.78</v>
+        <v>48.36</v>
       </c>
       <c r="L7" t="s">
-        <v>648</v>
+        <v>614</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -14835,125 +14493,494 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>380</v>
       </c>
       <c r="C8" t="s">
-        <v>649</v>
+        <v>605</v>
       </c>
       <c r="D8" t="s">
-        <v>650</v>
+        <v>606</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
       </c>
       <c r="F8">
-        <v>68.076999999999899</v>
+        <v>20.4149999999999</v>
       </c>
       <c r="G8" t="s">
         <v>18</v>
       </c>
       <c r="H8">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="I8">
-        <v>82.37</v>
+        <v>28.99</v>
       </c>
       <c r="J8">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="K8">
-        <v>106.2</v>
+        <v>30.01</v>
       </c>
       <c r="L8" t="s">
-        <v>599</v>
+        <v>615</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>317270</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>274</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>640</v>
+        <v>602</v>
       </c>
       <c r="D9" t="s">
-        <v>641</v>
+        <v>603</v>
       </c>
       <c r="E9" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="F9">
-        <v>33.427999999999898</v>
+        <v>36.362000000000002</v>
       </c>
       <c r="G9" t="s">
         <v>18</v>
       </c>
       <c r="H9">
-        <v>1.1599999999999999</v>
+        <v>1.46</v>
       </c>
       <c r="I9">
-        <v>38.78</v>
+        <v>53.09</v>
       </c>
       <c r="J9">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="K9">
-        <v>48.47</v>
+        <v>55.27</v>
       </c>
       <c r="L9" t="s">
-        <v>651</v>
+        <v>616</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>430120</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>274</v>
+      </c>
+      <c r="B10" t="s">
+        <v>380</v>
+      </c>
+      <c r="C10" t="s">
+        <v>605</v>
+      </c>
+      <c r="D10" t="s">
+        <v>606</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10">
+        <v>30.867999999999899</v>
+      </c>
+      <c r="G10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10">
+        <v>1.46</v>
+      </c>
+      <c r="I10">
+        <v>45.07</v>
+      </c>
+      <c r="J10">
+        <v>1.51</v>
+      </c>
+      <c r="K10">
+        <v>46.61</v>
+      </c>
+      <c r="L10" t="s">
+        <v>617</v>
+      </c>
+      <c r="M10">
+        <v>317370</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" t="s">
+        <v>612</v>
+      </c>
+      <c r="D11" t="s">
+        <v>613</v>
+      </c>
+      <c r="E11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11">
+        <v>24.591999999999899</v>
+      </c>
+      <c r="G11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11">
+        <v>1.46</v>
+      </c>
+      <c r="I11">
+        <v>35.9</v>
+      </c>
+      <c r="J11">
+        <v>1.52</v>
+      </c>
+      <c r="K11">
+        <v>37.380000000000003</v>
+      </c>
+      <c r="L11" t="s">
+        <v>618</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
+        <v>380</v>
+      </c>
+      <c r="C12" t="s">
+        <v>605</v>
+      </c>
+      <c r="D12" t="s">
+        <v>606</v>
+      </c>
+      <c r="E12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12">
+        <v>22.882000000000001</v>
+      </c>
+      <c r="G12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12">
+        <v>1.48</v>
+      </c>
+      <c r="I12">
+        <v>33.869999999999997</v>
+      </c>
+      <c r="J12">
+        <v>1.53</v>
+      </c>
+      <c r="K12">
+        <v>35.01</v>
+      </c>
+      <c r="L12" t="s">
+        <v>619</v>
+      </c>
+      <c r="M12">
+        <v>317685</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>299</v>
+      </c>
+      <c r="B13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" t="s">
+        <v>605</v>
+      </c>
+      <c r="D13" t="s">
+        <v>606</v>
+      </c>
+      <c r="E13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13">
+        <v>44.963000000000001</v>
+      </c>
+      <c r="G13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13">
+        <v>1.54</v>
+      </c>
+      <c r="I13">
+        <v>69.239999999999995</v>
+      </c>
+      <c r="J13">
+        <v>1.6</v>
+      </c>
+      <c r="K13">
+        <v>71.94</v>
+      </c>
+      <c r="L13" t="s">
+        <v>505</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>299</v>
+      </c>
+      <c r="B14" t="s">
+        <v>224</v>
+      </c>
+      <c r="C14" t="s">
+        <v>605</v>
+      </c>
+      <c r="D14" t="s">
+        <v>606</v>
+      </c>
+      <c r="E14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14">
+        <v>30.207999999999899</v>
+      </c>
+      <c r="G14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14">
+        <v>1.54</v>
+      </c>
+      <c r="I14">
+        <v>46.52</v>
+      </c>
+      <c r="J14">
+        <v>1.59</v>
+      </c>
+      <c r="K14">
+        <v>48.03</v>
+      </c>
+      <c r="L14" t="s">
+        <v>620</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" t="s">
+        <v>608</v>
+      </c>
+      <c r="D15" t="s">
+        <v>609</v>
+      </c>
+      <c r="E15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15">
+        <v>48.701999999999899</v>
+      </c>
+      <c r="G15" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15">
+        <v>1.6</v>
+      </c>
+      <c r="I15">
+        <v>77.92</v>
+      </c>
+      <c r="J15">
+        <v>1.61</v>
+      </c>
+      <c r="K15">
+        <v>78.41</v>
+      </c>
+      <c r="L15" t="s">
+        <v>130</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" t="s">
+        <v>612</v>
+      </c>
+      <c r="D16" t="s">
+        <v>613</v>
+      </c>
+      <c r="E16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16">
+        <v>32.783000000000001</v>
+      </c>
+      <c r="G16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16">
+        <v>1.6</v>
+      </c>
+      <c r="I16">
+        <v>52.45</v>
+      </c>
+      <c r="J16">
+        <v>1.61</v>
+      </c>
+      <c r="K16">
+        <v>52.78</v>
+      </c>
+      <c r="L16" t="s">
+        <v>621</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" t="s">
+        <v>602</v>
+      </c>
+      <c r="D17" t="s">
+        <v>603</v>
+      </c>
+      <c r="E17" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17">
+        <v>40.512</v>
+      </c>
+      <c r="G17" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17">
+        <v>1.6</v>
+      </c>
+      <c r="I17">
+        <v>64.819999999999993</v>
+      </c>
+      <c r="J17">
+        <v>1.62</v>
+      </c>
+      <c r="K17">
+        <v>65.63</v>
+      </c>
+      <c r="L17" t="s">
+        <v>622</v>
+      </c>
+      <c r="M17">
+        <v>430652</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>135</v>
       </c>
-      <c r="B10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" t="s">
-        <v>640</v>
-      </c>
-      <c r="D10" t="s">
-        <v>641</v>
-      </c>
-      <c r="E10" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10">
-        <v>38.040999999999897</v>
-      </c>
-      <c r="G10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="I10">
-        <v>44.13</v>
-      </c>
-      <c r="J10">
-        <v>1.46</v>
-      </c>
-      <c r="K10">
-        <v>55.54</v>
-      </c>
-      <c r="L10" t="s">
-        <v>532</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
+      <c r="B18" t="s">
+        <v>224</v>
+      </c>
+      <c r="C18" t="s">
+        <v>605</v>
+      </c>
+      <c r="D18" t="s">
+        <v>606</v>
+      </c>
+      <c r="E18" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18">
+        <v>28.27</v>
+      </c>
+      <c r="G18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18">
+        <v>1.61</v>
+      </c>
+      <c r="I18">
+        <v>45.51</v>
+      </c>
+      <c r="J18">
+        <v>1.63</v>
+      </c>
+      <c r="K18">
+        <v>46.08</v>
+      </c>
+      <c r="L18" t="s">
+        <v>623</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>72</v>
+      </c>
+      <c r="B19" t="s">
+        <v>380</v>
+      </c>
+      <c r="C19" t="s">
+        <v>605</v>
+      </c>
+      <c r="D19" t="s">
+        <v>606</v>
+      </c>
+      <c r="E19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19">
+        <v>50.142000000000003</v>
+      </c>
+      <c r="G19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19">
+        <v>1.64</v>
+      </c>
+      <c r="I19">
+        <v>82.23</v>
+      </c>
+      <c r="J19">
+        <v>1.69</v>
+      </c>
+      <c r="K19">
+        <v>84.74</v>
+      </c>
+      <c r="L19" t="s">
+        <v>624</v>
+      </c>
+      <c r="M19">
+        <v>318930</v>
       </c>
     </row>
   </sheetData>
@@ -14965,6 +14992,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -28863,6 +28895,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
   <dimension ref="A1:M103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="9" max="9" width="16.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">

--- a/A_FINAL_RESULT/eko_transactions.xlsx
+++ b/A_FINAL_RESULT/eko_transactions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\A_FINAL_RESULT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CAA947F-4CAE-4717-935B-F72CFC6E46AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD8DED28-2F9B-4B7C-B167-4A8258CEE03C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="35" activeTab="37" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ" sheetId="1" r:id="rId1"/>
@@ -32,9 +32,9 @@
     <sheet name="ДОК ТРАНС ЕООД" sheetId="17" r:id="rId17"/>
     <sheet name="ЕВРО ТРАНС ПРЕМИУМ ЕООД" sheetId="18" r:id="rId18"/>
     <sheet name="ЕВРОУЕЙ СЪРВИЗ ООД" sheetId="19" r:id="rId19"/>
-    <sheet name="ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ" sheetId="21" r:id="rId20"/>
-    <sheet name="ЗЕМЕДЕЛСКА ТЕХНИКА ООД" sheetId="22" r:id="rId21"/>
-    <sheet name="ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДС" sheetId="20" r:id="rId22"/>
+    <sheet name="ЖЕЛЯЗКОВ ИНЖЕНЕРИНГ - ПРОИЗВОДС" sheetId="20" r:id="rId20"/>
+    <sheet name="ЖИВКО НЕДЕЛЧЕВ ДИМИТРОВ" sheetId="21" r:id="rId21"/>
+    <sheet name="ЗЕМЕДЕЛСКА ТЕХНИКА ООД" sheetId="22" r:id="rId22"/>
     <sheet name="ЗП ВЕСЕЛИН СТЕФАНОВ ЖЕЛЯЗКОВ" sheetId="23" r:id="rId23"/>
     <sheet name="ИВО ИВАНОВ ЧЗС" sheetId="24" r:id="rId24"/>
     <sheet name="ИВОН СТРОЙ 2015 ЕООД" sheetId="25" r:id="rId25"/>
@@ -56,14 +56,13 @@
     <sheet name="ХРАНИНВЕСТ ЕООД % ДОСТАВКИ" sheetId="41" r:id="rId41"/>
     <sheet name="ХРАНИНВЕСТ ЕООД % ПРОДАЖБИ" sheetId="42" r:id="rId42"/>
     <sheet name="ХРАНИНВЕСТ ЕООД % ТЪРГОВЦИ" sheetId="43" r:id="rId43"/>
-    <sheet name="Unknown" sheetId="44" r:id="rId44"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8174" uniqueCount="1314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8161" uniqueCount="1314">
   <si>
     <t>Дата</t>
   </si>
@@ -3620,6 +3619,15 @@
     <t>07:37:00</t>
   </si>
   <si>
+    <t>СВ5723НB</t>
+  </si>
+  <si>
+    <t>78970152027720144</t>
+  </si>
+  <si>
+    <t>17:31:00</t>
+  </si>
+  <si>
     <t>06:45:00</t>
   </si>
   <si>
@@ -3635,12 +3643,21 @@
     <t>13:00:00</t>
   </si>
   <si>
+    <t>1125 Гоце Делчев</t>
+  </si>
+  <si>
     <t>В5038НТ</t>
   </si>
   <si>
     <t>78970155027720022</t>
   </si>
   <si>
+    <t>1110 Петрич вход</t>
+  </si>
+  <si>
+    <t>13:50:00</t>
+  </si>
+  <si>
     <t>08:22:00</t>
   </si>
   <si>
@@ -3987,24 +4004,6 @@
   </si>
   <si>
     <t>22:14:00</t>
-  </si>
-  <si>
-    <t>СВ5723НB</t>
-  </si>
-  <si>
-    <t>78970152027720144</t>
-  </si>
-  <si>
-    <t>17:31:00</t>
-  </si>
-  <si>
-    <t>1125 Гоце Делчев</t>
-  </si>
-  <si>
-    <t>1110 Петрич вход</t>
-  </si>
-  <si>
-    <t>13:50:00</t>
   </si>
 </sst>
 </file>
@@ -5025,16 +5024,8 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FF00B050"/>
-  </sheetPr>
   <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.85546875" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -5658,18 +5649,8 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FF00B050"/>
-  </sheetPr>
   <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.42578125" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -13338,6 +13319,789 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
+  <dimension ref="A1:M19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C2" t="s">
+        <v>602</v>
+      </c>
+      <c r="D2" t="s">
+        <v>603</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2">
+        <v>42.976999999999897</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2">
+        <v>1.21</v>
+      </c>
+      <c r="I2">
+        <v>52</v>
+      </c>
+      <c r="J2">
+        <v>1.31</v>
+      </c>
+      <c r="K2">
+        <v>56.3</v>
+      </c>
+      <c r="L2" t="s">
+        <v>604</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" t="s">
+        <v>605</v>
+      </c>
+      <c r="D3" t="s">
+        <v>606</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3">
+        <v>40.137</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3">
+        <v>1.21</v>
+      </c>
+      <c r="I3">
+        <v>48.57</v>
+      </c>
+      <c r="J3">
+        <v>1.31</v>
+      </c>
+      <c r="K3">
+        <v>52.58</v>
+      </c>
+      <c r="L3" t="s">
+        <v>607</v>
+      </c>
+      <c r="M3">
+        <v>316540</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" t="s">
+        <v>608</v>
+      </c>
+      <c r="D4" t="s">
+        <v>609</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4">
+        <v>49.811999999999898</v>
+      </c>
+      <c r="G4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4">
+        <v>1.23</v>
+      </c>
+      <c r="I4">
+        <v>61.27</v>
+      </c>
+      <c r="J4">
+        <v>1.33</v>
+      </c>
+      <c r="K4">
+        <v>66.25</v>
+      </c>
+      <c r="L4" t="s">
+        <v>610</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" t="s">
+        <v>380</v>
+      </c>
+      <c r="C5" t="s">
+        <v>605</v>
+      </c>
+      <c r="D5" t="s">
+        <v>606</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5">
+        <v>54.6099999999999</v>
+      </c>
+      <c r="G5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5">
+        <v>1.25</v>
+      </c>
+      <c r="I5">
+        <v>68.260000000000005</v>
+      </c>
+      <c r="J5">
+        <v>1.41</v>
+      </c>
+      <c r="K5">
+        <v>77</v>
+      </c>
+      <c r="L5" t="s">
+        <v>611</v>
+      </c>
+      <c r="M5">
+        <v>316950</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" t="s">
+        <v>608</v>
+      </c>
+      <c r="D6" t="s">
+        <v>609</v>
+      </c>
+      <c r="E6" t="s">
+        <v>179</v>
+      </c>
+      <c r="F6">
+        <v>48.088999999999899</v>
+      </c>
+      <c r="G6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6">
+        <v>1.68</v>
+      </c>
+      <c r="K6">
+        <v>80.790000000000006</v>
+      </c>
+      <c r="L6" t="s">
+        <v>128</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" t="s">
+        <v>612</v>
+      </c>
+      <c r="D7" t="s">
+        <v>613</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7">
+        <v>33.817999999999898</v>
+      </c>
+      <c r="G7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7">
+        <v>1.25</v>
+      </c>
+      <c r="I7">
+        <v>42.27</v>
+      </c>
+      <c r="J7">
+        <v>1.43</v>
+      </c>
+      <c r="K7">
+        <v>48.36</v>
+      </c>
+      <c r="L7" t="s">
+        <v>614</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
+        <v>380</v>
+      </c>
+      <c r="C8" t="s">
+        <v>605</v>
+      </c>
+      <c r="D8" t="s">
+        <v>606</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8">
+        <v>20.4149999999999</v>
+      </c>
+      <c r="G8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8">
+        <v>1.42</v>
+      </c>
+      <c r="I8">
+        <v>28.99</v>
+      </c>
+      <c r="J8">
+        <v>1.47</v>
+      </c>
+      <c r="K8">
+        <v>30.01</v>
+      </c>
+      <c r="L8" t="s">
+        <v>615</v>
+      </c>
+      <c r="M8">
+        <v>317270</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>274</v>
+      </c>
+      <c r="B9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" t="s">
+        <v>602</v>
+      </c>
+      <c r="D9" t="s">
+        <v>603</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9">
+        <v>36.362000000000002</v>
+      </c>
+      <c r="G9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9">
+        <v>1.46</v>
+      </c>
+      <c r="I9">
+        <v>53.09</v>
+      </c>
+      <c r="J9">
+        <v>1.52</v>
+      </c>
+      <c r="K9">
+        <v>55.27</v>
+      </c>
+      <c r="L9" t="s">
+        <v>616</v>
+      </c>
+      <c r="M9">
+        <v>430120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>274</v>
+      </c>
+      <c r="B10" t="s">
+        <v>380</v>
+      </c>
+      <c r="C10" t="s">
+        <v>605</v>
+      </c>
+      <c r="D10" t="s">
+        <v>606</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10">
+        <v>30.867999999999899</v>
+      </c>
+      <c r="G10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10">
+        <v>1.46</v>
+      </c>
+      <c r="I10">
+        <v>45.07</v>
+      </c>
+      <c r="J10">
+        <v>1.51</v>
+      </c>
+      <c r="K10">
+        <v>46.61</v>
+      </c>
+      <c r="L10" t="s">
+        <v>617</v>
+      </c>
+      <c r="M10">
+        <v>317370</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" t="s">
+        <v>612</v>
+      </c>
+      <c r="D11" t="s">
+        <v>613</v>
+      </c>
+      <c r="E11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11">
+        <v>24.591999999999899</v>
+      </c>
+      <c r="G11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11">
+        <v>1.46</v>
+      </c>
+      <c r="I11">
+        <v>35.9</v>
+      </c>
+      <c r="J11">
+        <v>1.52</v>
+      </c>
+      <c r="K11">
+        <v>37.380000000000003</v>
+      </c>
+      <c r="L11" t="s">
+        <v>618</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
+        <v>380</v>
+      </c>
+      <c r="C12" t="s">
+        <v>605</v>
+      </c>
+      <c r="D12" t="s">
+        <v>606</v>
+      </c>
+      <c r="E12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12">
+        <v>22.882000000000001</v>
+      </c>
+      <c r="G12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12">
+        <v>1.48</v>
+      </c>
+      <c r="I12">
+        <v>33.869999999999997</v>
+      </c>
+      <c r="J12">
+        <v>1.53</v>
+      </c>
+      <c r="K12">
+        <v>35.01</v>
+      </c>
+      <c r="L12" t="s">
+        <v>619</v>
+      </c>
+      <c r="M12">
+        <v>317685</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>299</v>
+      </c>
+      <c r="B13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" t="s">
+        <v>605</v>
+      </c>
+      <c r="D13" t="s">
+        <v>606</v>
+      </c>
+      <c r="E13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13">
+        <v>44.963000000000001</v>
+      </c>
+      <c r="G13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13">
+        <v>1.54</v>
+      </c>
+      <c r="I13">
+        <v>69.239999999999995</v>
+      </c>
+      <c r="J13">
+        <v>1.6</v>
+      </c>
+      <c r="K13">
+        <v>71.94</v>
+      </c>
+      <c r="L13" t="s">
+        <v>505</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>299</v>
+      </c>
+      <c r="B14" t="s">
+        <v>224</v>
+      </c>
+      <c r="C14" t="s">
+        <v>605</v>
+      </c>
+      <c r="D14" t="s">
+        <v>606</v>
+      </c>
+      <c r="E14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14">
+        <v>30.207999999999899</v>
+      </c>
+      <c r="G14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14">
+        <v>1.54</v>
+      </c>
+      <c r="I14">
+        <v>46.52</v>
+      </c>
+      <c r="J14">
+        <v>1.59</v>
+      </c>
+      <c r="K14">
+        <v>48.03</v>
+      </c>
+      <c r="L14" t="s">
+        <v>620</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" t="s">
+        <v>608</v>
+      </c>
+      <c r="D15" t="s">
+        <v>609</v>
+      </c>
+      <c r="E15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15">
+        <v>48.701999999999899</v>
+      </c>
+      <c r="G15" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15">
+        <v>1.6</v>
+      </c>
+      <c r="I15">
+        <v>77.92</v>
+      </c>
+      <c r="J15">
+        <v>1.61</v>
+      </c>
+      <c r="K15">
+        <v>78.41</v>
+      </c>
+      <c r="L15" t="s">
+        <v>130</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" t="s">
+        <v>612</v>
+      </c>
+      <c r="D16" t="s">
+        <v>613</v>
+      </c>
+      <c r="E16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16">
+        <v>32.783000000000001</v>
+      </c>
+      <c r="G16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16">
+        <v>1.6</v>
+      </c>
+      <c r="I16">
+        <v>52.45</v>
+      </c>
+      <c r="J16">
+        <v>1.61</v>
+      </c>
+      <c r="K16">
+        <v>52.78</v>
+      </c>
+      <c r="L16" t="s">
+        <v>621</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" t="s">
+        <v>602</v>
+      </c>
+      <c r="D17" t="s">
+        <v>603</v>
+      </c>
+      <c r="E17" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17">
+        <v>40.512</v>
+      </c>
+      <c r="G17" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17">
+        <v>1.6</v>
+      </c>
+      <c r="I17">
+        <v>64.819999999999993</v>
+      </c>
+      <c r="J17">
+        <v>1.62</v>
+      </c>
+      <c r="K17">
+        <v>65.63</v>
+      </c>
+      <c r="L17" t="s">
+        <v>622</v>
+      </c>
+      <c r="M17">
+        <v>430652</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>135</v>
+      </c>
+      <c r="B18" t="s">
+        <v>224</v>
+      </c>
+      <c r="C18" t="s">
+        <v>605</v>
+      </c>
+      <c r="D18" t="s">
+        <v>606</v>
+      </c>
+      <c r="E18" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18">
+        <v>28.27</v>
+      </c>
+      <c r="G18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18">
+        <v>1.61</v>
+      </c>
+      <c r="I18">
+        <v>45.51</v>
+      </c>
+      <c r="J18">
+        <v>1.63</v>
+      </c>
+      <c r="K18">
+        <v>46.08</v>
+      </c>
+      <c r="L18" t="s">
+        <v>623</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>72</v>
+      </c>
+      <c r="B19" t="s">
+        <v>380</v>
+      </c>
+      <c r="C19" t="s">
+        <v>605</v>
+      </c>
+      <c r="D19" t="s">
+        <v>606</v>
+      </c>
+      <c r="E19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19">
+        <v>50.142000000000003</v>
+      </c>
+      <c r="G19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19">
+        <v>1.64</v>
+      </c>
+      <c r="I19">
+        <v>82.23</v>
+      </c>
+      <c r="J19">
+        <v>1.69</v>
+      </c>
+      <c r="K19">
+        <v>84.74</v>
+      </c>
+      <c r="L19" t="s">
+        <v>624</v>
+      </c>
+      <c r="M19">
+        <v>318930</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13773,18 +14537,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -14194,793 +14950,6 @@
       </c>
       <c r="M10">
         <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
-  <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B2" t="s">
-        <v>432</v>
-      </c>
-      <c r="C2" t="s">
-        <v>602</v>
-      </c>
-      <c r="D2" t="s">
-        <v>603</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2">
-        <v>42.976999999999897</v>
-      </c>
-      <c r="G2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2">
-        <v>1.21</v>
-      </c>
-      <c r="I2">
-        <v>52</v>
-      </c>
-      <c r="J2">
-        <v>1.31</v>
-      </c>
-      <c r="K2">
-        <v>56.3</v>
-      </c>
-      <c r="L2" t="s">
-        <v>604</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C3" t="s">
-        <v>605</v>
-      </c>
-      <c r="D3" t="s">
-        <v>606</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3">
-        <v>40.137</v>
-      </c>
-      <c r="G3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3">
-        <v>1.21</v>
-      </c>
-      <c r="I3">
-        <v>48.57</v>
-      </c>
-      <c r="J3">
-        <v>1.31</v>
-      </c>
-      <c r="K3">
-        <v>52.58</v>
-      </c>
-      <c r="L3" t="s">
-        <v>607</v>
-      </c>
-      <c r="M3">
-        <v>316540</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C4" t="s">
-        <v>608</v>
-      </c>
-      <c r="D4" t="s">
-        <v>609</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4">
-        <v>49.811999999999898</v>
-      </c>
-      <c r="G4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4">
-        <v>1.23</v>
-      </c>
-      <c r="I4">
-        <v>61.27</v>
-      </c>
-      <c r="J4">
-        <v>1.33</v>
-      </c>
-      <c r="K4">
-        <v>66.25</v>
-      </c>
-      <c r="L4" t="s">
-        <v>610</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B5" t="s">
-        <v>380</v>
-      </c>
-      <c r="C5" t="s">
-        <v>605</v>
-      </c>
-      <c r="D5" t="s">
-        <v>606</v>
-      </c>
-      <c r="E5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5">
-        <v>54.6099999999999</v>
-      </c>
-      <c r="G5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5">
-        <v>1.25</v>
-      </c>
-      <c r="I5">
-        <v>68.260000000000005</v>
-      </c>
-      <c r="J5">
-        <v>1.41</v>
-      </c>
-      <c r="K5">
-        <v>77</v>
-      </c>
-      <c r="L5" t="s">
-        <v>611</v>
-      </c>
-      <c r="M5">
-        <v>316950</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" t="s">
-        <v>608</v>
-      </c>
-      <c r="D6" t="s">
-        <v>609</v>
-      </c>
-      <c r="E6" t="s">
-        <v>179</v>
-      </c>
-      <c r="F6">
-        <v>48.088999999999899</v>
-      </c>
-      <c r="G6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6">
-        <v>1.68</v>
-      </c>
-      <c r="K6">
-        <v>80.790000000000006</v>
-      </c>
-      <c r="L6" t="s">
-        <v>128</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C7" t="s">
-        <v>612</v>
-      </c>
-      <c r="D7" t="s">
-        <v>613</v>
-      </c>
-      <c r="E7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7">
-        <v>33.817999999999898</v>
-      </c>
-      <c r="G7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7">
-        <v>1.25</v>
-      </c>
-      <c r="I7">
-        <v>42.27</v>
-      </c>
-      <c r="J7">
-        <v>1.43</v>
-      </c>
-      <c r="K7">
-        <v>48.36</v>
-      </c>
-      <c r="L7" t="s">
-        <v>614</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" t="s">
-        <v>380</v>
-      </c>
-      <c r="C8" t="s">
-        <v>605</v>
-      </c>
-      <c r="D8" t="s">
-        <v>606</v>
-      </c>
-      <c r="E8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8">
-        <v>20.4149999999999</v>
-      </c>
-      <c r="G8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8">
-        <v>1.42</v>
-      </c>
-      <c r="I8">
-        <v>28.99</v>
-      </c>
-      <c r="J8">
-        <v>1.47</v>
-      </c>
-      <c r="K8">
-        <v>30.01</v>
-      </c>
-      <c r="L8" t="s">
-        <v>615</v>
-      </c>
-      <c r="M8">
-        <v>317270</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>274</v>
-      </c>
-      <c r="B9" t="s">
-        <v>93</v>
-      </c>
-      <c r="C9" t="s">
-        <v>602</v>
-      </c>
-      <c r="D9" t="s">
-        <v>603</v>
-      </c>
-      <c r="E9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9">
-        <v>36.362000000000002</v>
-      </c>
-      <c r="G9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9">
-        <v>1.46</v>
-      </c>
-      <c r="I9">
-        <v>53.09</v>
-      </c>
-      <c r="J9">
-        <v>1.52</v>
-      </c>
-      <c r="K9">
-        <v>55.27</v>
-      </c>
-      <c r="L9" t="s">
-        <v>616</v>
-      </c>
-      <c r="M9">
-        <v>430120</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>274</v>
-      </c>
-      <c r="B10" t="s">
-        <v>380</v>
-      </c>
-      <c r="C10" t="s">
-        <v>605</v>
-      </c>
-      <c r="D10" t="s">
-        <v>606</v>
-      </c>
-      <c r="E10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10">
-        <v>30.867999999999899</v>
-      </c>
-      <c r="G10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10">
-        <v>1.46</v>
-      </c>
-      <c r="I10">
-        <v>45.07</v>
-      </c>
-      <c r="J10">
-        <v>1.51</v>
-      </c>
-      <c r="K10">
-        <v>46.61</v>
-      </c>
-      <c r="L10" t="s">
-        <v>617</v>
-      </c>
-      <c r="M10">
-        <v>317370</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" t="s">
-        <v>93</v>
-      </c>
-      <c r="C11" t="s">
-        <v>612</v>
-      </c>
-      <c r="D11" t="s">
-        <v>613</v>
-      </c>
-      <c r="E11" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11">
-        <v>24.591999999999899</v>
-      </c>
-      <c r="G11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H11">
-        <v>1.46</v>
-      </c>
-      <c r="I11">
-        <v>35.9</v>
-      </c>
-      <c r="J11">
-        <v>1.52</v>
-      </c>
-      <c r="K11">
-        <v>37.380000000000003</v>
-      </c>
-      <c r="L11" t="s">
-        <v>618</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" t="s">
-        <v>380</v>
-      </c>
-      <c r="C12" t="s">
-        <v>605</v>
-      </c>
-      <c r="D12" t="s">
-        <v>606</v>
-      </c>
-      <c r="E12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12">
-        <v>22.882000000000001</v>
-      </c>
-      <c r="G12" t="s">
-        <v>18</v>
-      </c>
-      <c r="H12">
-        <v>1.48</v>
-      </c>
-      <c r="I12">
-        <v>33.869999999999997</v>
-      </c>
-      <c r="J12">
-        <v>1.53</v>
-      </c>
-      <c r="K12">
-        <v>35.01</v>
-      </c>
-      <c r="L12" t="s">
-        <v>619</v>
-      </c>
-      <c r="M12">
-        <v>317685</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>299</v>
-      </c>
-      <c r="B13" t="s">
-        <v>93</v>
-      </c>
-      <c r="C13" t="s">
-        <v>605</v>
-      </c>
-      <c r="D13" t="s">
-        <v>606</v>
-      </c>
-      <c r="E13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13">
-        <v>44.963000000000001</v>
-      </c>
-      <c r="G13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13">
-        <v>1.54</v>
-      </c>
-      <c r="I13">
-        <v>69.239999999999995</v>
-      </c>
-      <c r="J13">
-        <v>1.6</v>
-      </c>
-      <c r="K13">
-        <v>71.94</v>
-      </c>
-      <c r="L13" t="s">
-        <v>505</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>299</v>
-      </c>
-      <c r="B14" t="s">
-        <v>224</v>
-      </c>
-      <c r="C14" t="s">
-        <v>605</v>
-      </c>
-      <c r="D14" t="s">
-        <v>606</v>
-      </c>
-      <c r="E14" t="s">
-        <v>17</v>
-      </c>
-      <c r="F14">
-        <v>30.207999999999899</v>
-      </c>
-      <c r="G14" t="s">
-        <v>18</v>
-      </c>
-      <c r="H14">
-        <v>1.54</v>
-      </c>
-      <c r="I14">
-        <v>46.52</v>
-      </c>
-      <c r="J14">
-        <v>1.59</v>
-      </c>
-      <c r="K14">
-        <v>48.03</v>
-      </c>
-      <c r="L14" t="s">
-        <v>620</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>69</v>
-      </c>
-      <c r="B15" t="s">
-        <v>93</v>
-      </c>
-      <c r="C15" t="s">
-        <v>608</v>
-      </c>
-      <c r="D15" t="s">
-        <v>609</v>
-      </c>
-      <c r="E15" t="s">
-        <v>17</v>
-      </c>
-      <c r="F15">
-        <v>48.701999999999899</v>
-      </c>
-      <c r="G15" t="s">
-        <v>18</v>
-      </c>
-      <c r="H15">
-        <v>1.6</v>
-      </c>
-      <c r="I15">
-        <v>77.92</v>
-      </c>
-      <c r="J15">
-        <v>1.61</v>
-      </c>
-      <c r="K15">
-        <v>78.41</v>
-      </c>
-      <c r="L15" t="s">
-        <v>130</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>69</v>
-      </c>
-      <c r="B16" t="s">
-        <v>93</v>
-      </c>
-      <c r="C16" t="s">
-        <v>612</v>
-      </c>
-      <c r="D16" t="s">
-        <v>613</v>
-      </c>
-      <c r="E16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F16">
-        <v>32.783000000000001</v>
-      </c>
-      <c r="G16" t="s">
-        <v>18</v>
-      </c>
-      <c r="H16">
-        <v>1.6</v>
-      </c>
-      <c r="I16">
-        <v>52.45</v>
-      </c>
-      <c r="J16">
-        <v>1.61</v>
-      </c>
-      <c r="K16">
-        <v>52.78</v>
-      </c>
-      <c r="L16" t="s">
-        <v>621</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>53</v>
-      </c>
-      <c r="B17" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" t="s">
-        <v>602</v>
-      </c>
-      <c r="D17" t="s">
-        <v>603</v>
-      </c>
-      <c r="E17" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17">
-        <v>40.512</v>
-      </c>
-      <c r="G17" t="s">
-        <v>18</v>
-      </c>
-      <c r="H17">
-        <v>1.6</v>
-      </c>
-      <c r="I17">
-        <v>64.819999999999993</v>
-      </c>
-      <c r="J17">
-        <v>1.62</v>
-      </c>
-      <c r="K17">
-        <v>65.63</v>
-      </c>
-      <c r="L17" t="s">
-        <v>622</v>
-      </c>
-      <c r="M17">
-        <v>430652</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>135</v>
-      </c>
-      <c r="B18" t="s">
-        <v>224</v>
-      </c>
-      <c r="C18" t="s">
-        <v>605</v>
-      </c>
-      <c r="D18" t="s">
-        <v>606</v>
-      </c>
-      <c r="E18" t="s">
-        <v>17</v>
-      </c>
-      <c r="F18">
-        <v>28.27</v>
-      </c>
-      <c r="G18" t="s">
-        <v>18</v>
-      </c>
-      <c r="H18">
-        <v>1.61</v>
-      </c>
-      <c r="I18">
-        <v>45.51</v>
-      </c>
-      <c r="J18">
-        <v>1.63</v>
-      </c>
-      <c r="K18">
-        <v>46.08</v>
-      </c>
-      <c r="L18" t="s">
-        <v>623</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>72</v>
-      </c>
-      <c r="B19" t="s">
-        <v>380</v>
-      </c>
-      <c r="C19" t="s">
-        <v>605</v>
-      </c>
-      <c r="D19" t="s">
-        <v>606</v>
-      </c>
-      <c r="E19" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19">
-        <v>50.142000000000003</v>
-      </c>
-      <c r="G19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H19">
-        <v>1.64</v>
-      </c>
-      <c r="I19">
-        <v>82.23</v>
-      </c>
-      <c r="J19">
-        <v>1.69</v>
-      </c>
-      <c r="K19">
-        <v>84.74</v>
-      </c>
-      <c r="L19" t="s">
-        <v>624</v>
-      </c>
-      <c r="M19">
-        <v>318930</v>
       </c>
     </row>
   </sheetData>
@@ -14992,11 +14961,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.85546875" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -28895,9 +28859,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
   <dimension ref="A1:M103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="9" max="9" width="16.7109375" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -33928,8 +33889,11 @@
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2700-000000000000}">
-  <dimension ref="A1:M100"/>
+  <dimension ref="A1:M104"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -36214,34 +36178,40 @@
         <v>38</v>
       </c>
       <c r="B57" t="s">
-        <v>93</v>
+        <v>166</v>
       </c>
       <c r="C57" t="s">
-        <v>497</v>
+        <v>1185</v>
       </c>
       <c r="D57" t="s">
-        <v>1134</v>
+        <v>1186</v>
       </c>
       <c r="E57" t="s">
-        <v>179</v>
+        <v>17</v>
       </c>
       <c r="F57">
-        <v>18.190000000000001</v>
+        <v>76.269999999999897</v>
       </c>
       <c r="G57" t="s">
         <v>18</v>
       </c>
+      <c r="H57">
+        <v>1.48</v>
+      </c>
+      <c r="I57">
+        <v>112.88</v>
+      </c>
       <c r="J57">
-        <v>1.79</v>
+        <v>1.52</v>
       </c>
       <c r="K57">
-        <v>32.56</v>
+        <v>115.93</v>
       </c>
       <c r="L57" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="M57">
-        <v>0</v>
+        <v>230400</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
@@ -36252,37 +36222,31 @@
         <v>93</v>
       </c>
       <c r="C58" t="s">
-        <v>1127</v>
+        <v>497</v>
       </c>
       <c r="D58" t="s">
-        <v>1128</v>
+        <v>1134</v>
       </c>
       <c r="E58" t="s">
-        <v>17</v>
+        <v>179</v>
       </c>
       <c r="F58">
-        <v>65.337999999999894</v>
+        <v>18.190000000000001</v>
       </c>
       <c r="G58" t="s">
         <v>18</v>
       </c>
-      <c r="H58">
-        <v>1.48</v>
-      </c>
-      <c r="I58">
-        <v>96.7</v>
-      </c>
       <c r="J58">
-        <v>1.54</v>
+        <v>1.79</v>
       </c>
       <c r="K58">
-        <v>100.62</v>
+        <v>32.56</v>
       </c>
       <c r="L58" t="s">
-        <v>1106</v>
+        <v>1188</v>
       </c>
       <c r="M58">
-        <v>672482</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
@@ -36290,19 +36254,19 @@
         <v>38</v>
       </c>
       <c r="B59" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C59" t="s">
-        <v>1131</v>
+        <v>1127</v>
       </c>
       <c r="D59" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="E59" t="s">
         <v>17</v>
       </c>
       <c r="F59">
-        <v>67.352999999999895</v>
+        <v>65.337999999999894</v>
       </c>
       <c r="G59" t="s">
         <v>18</v>
@@ -36311,19 +36275,19 @@
         <v>1.48</v>
       </c>
       <c r="I59">
-        <v>99.68</v>
+        <v>96.7</v>
       </c>
       <c r="J59">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="K59">
-        <v>103.05</v>
+        <v>100.62</v>
       </c>
       <c r="L59" t="s">
-        <v>1186</v>
+        <v>1106</v>
       </c>
       <c r="M59">
-        <v>180920</v>
+        <v>672482</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
@@ -36331,19 +36295,19 @@
         <v>38</v>
       </c>
       <c r="B60" t="s">
-        <v>237</v>
+        <v>70</v>
       </c>
       <c r="C60" t="s">
-        <v>1172</v>
+        <v>1131</v>
       </c>
       <c r="D60" t="s">
-        <v>1173</v>
+        <v>1132</v>
       </c>
       <c r="E60" t="s">
         <v>17</v>
       </c>
       <c r="F60">
-        <v>72.441999999999894</v>
+        <v>67.352999999999895</v>
       </c>
       <c r="G60" t="s">
         <v>18</v>
@@ -36352,60 +36316,60 @@
         <v>1.48</v>
       </c>
       <c r="I60">
-        <v>107.21</v>
+        <v>99.68</v>
       </c>
       <c r="J60">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="K60">
-        <v>113.01</v>
+        <v>103.05</v>
       </c>
       <c r="L60" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="M60">
-        <v>192968</v>
+        <v>180920</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B61" t="s">
-        <v>93</v>
+        <v>237</v>
       </c>
       <c r="C61" t="s">
-        <v>1139</v>
+        <v>1172</v>
       </c>
       <c r="D61" t="s">
-        <v>1140</v>
+        <v>1173</v>
       </c>
       <c r="E61" t="s">
         <v>17</v>
       </c>
       <c r="F61">
-        <v>52</v>
+        <v>72.441999999999894</v>
       </c>
       <c r="G61" t="s">
         <v>18</v>
       </c>
       <c r="H61">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="I61">
-        <v>78.52</v>
+        <v>107.21</v>
       </c>
       <c r="J61">
         <v>1.56</v>
       </c>
       <c r="K61">
-        <v>81.12</v>
+        <v>113.01</v>
       </c>
       <c r="L61" t="s">
-        <v>1123</v>
+        <v>1190</v>
       </c>
       <c r="M61">
-        <v>232772</v>
+        <v>192968</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
@@ -36416,16 +36380,16 @@
         <v>93</v>
       </c>
       <c r="C62" t="s">
-        <v>497</v>
+        <v>1139</v>
       </c>
       <c r="D62" t="s">
-        <v>1134</v>
+        <v>1140</v>
       </c>
       <c r="E62" t="s">
         <v>17</v>
       </c>
       <c r="F62">
-        <v>60.628</v>
+        <v>52</v>
       </c>
       <c r="G62" t="s">
         <v>18</v>
@@ -36434,19 +36398,19 @@
         <v>1.51</v>
       </c>
       <c r="I62">
-        <v>91.55</v>
+        <v>78.52</v>
       </c>
       <c r="J62">
         <v>1.56</v>
       </c>
       <c r="K62">
-        <v>94.58</v>
+        <v>81.12</v>
       </c>
       <c r="L62" t="s">
-        <v>1188</v>
+        <v>1123</v>
       </c>
       <c r="M62">
-        <v>0</v>
+        <v>232772</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
@@ -36454,19 +36418,19 @@
         <v>42</v>
       </c>
       <c r="B63" t="s">
-        <v>224</v>
+        <v>93</v>
       </c>
       <c r="C63" t="s">
-        <v>1172</v>
+        <v>497</v>
       </c>
       <c r="D63" t="s">
-        <v>1173</v>
+        <v>1134</v>
       </c>
       <c r="E63" t="s">
         <v>17</v>
       </c>
       <c r="F63">
-        <v>70.619</v>
+        <v>60.628</v>
       </c>
       <c r="G63" t="s">
         <v>18</v>
@@ -36475,60 +36439,60 @@
         <v>1.51</v>
       </c>
       <c r="I63">
-        <v>106.63</v>
+        <v>91.55</v>
       </c>
       <c r="J63">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="K63">
-        <v>109.46</v>
+        <v>94.58</v>
       </c>
       <c r="L63" t="s">
-        <v>896</v>
+        <v>1191</v>
       </c>
       <c r="M63">
-        <v>193660</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B64" t="s">
-        <v>432</v>
+        <v>224</v>
       </c>
       <c r="C64" t="s">
-        <v>1139</v>
+        <v>1172</v>
       </c>
       <c r="D64" t="s">
-        <v>1140</v>
+        <v>1173</v>
       </c>
       <c r="E64" t="s">
         <v>17</v>
       </c>
       <c r="F64">
-        <v>56.628</v>
+        <v>70.619</v>
       </c>
       <c r="G64" t="s">
         <v>18</v>
       </c>
       <c r="H64">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="I64">
-        <v>86.64</v>
+        <v>106.63</v>
       </c>
       <c r="J64">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="K64">
-        <v>88.34</v>
+        <v>109.46</v>
       </c>
       <c r="L64" t="s">
-        <v>401</v>
+        <v>896</v>
       </c>
       <c r="M64">
-        <v>233302</v>
+        <v>193660</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
@@ -36536,19 +36500,19 @@
         <v>47</v>
       </c>
       <c r="B65" t="s">
-        <v>70</v>
+        <v>432</v>
       </c>
       <c r="C65" t="s">
-        <v>1131</v>
+        <v>1139</v>
       </c>
       <c r="D65" t="s">
-        <v>1132</v>
+        <v>1140</v>
       </c>
       <c r="E65" t="s">
         <v>17</v>
       </c>
       <c r="F65">
-        <v>70.923000000000002</v>
+        <v>56.628</v>
       </c>
       <c r="G65" t="s">
         <v>18</v>
@@ -36557,19 +36521,19 @@
         <v>1.53</v>
       </c>
       <c r="I65">
-        <v>108.51</v>
+        <v>86.64</v>
       </c>
       <c r="J65">
         <v>1.56</v>
       </c>
       <c r="K65">
-        <v>110.64</v>
+        <v>88.34</v>
       </c>
       <c r="L65" t="s">
-        <v>1177</v>
+        <v>401</v>
       </c>
       <c r="M65">
-        <v>181499</v>
+        <v>233302</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
@@ -36577,19 +36541,19 @@
         <v>47</v>
       </c>
       <c r="B66" t="s">
-        <v>385</v>
+        <v>70</v>
       </c>
       <c r="C66" t="s">
-        <v>1149</v>
+        <v>1131</v>
       </c>
       <c r="D66" t="s">
-        <v>1150</v>
+        <v>1132</v>
       </c>
       <c r="E66" t="s">
         <v>17</v>
       </c>
       <c r="F66">
-        <v>327.08999999999901</v>
+        <v>70.923000000000002</v>
       </c>
       <c r="G66" t="s">
         <v>18</v>
@@ -36598,19 +36562,19 @@
         <v>1.53</v>
       </c>
       <c r="I66">
-        <v>500.45</v>
+        <v>108.51</v>
       </c>
       <c r="J66">
         <v>1.56</v>
       </c>
       <c r="K66">
-        <v>510.26</v>
+        <v>110.64</v>
       </c>
       <c r="L66" t="s">
-        <v>1189</v>
+        <v>1177</v>
       </c>
       <c r="M66">
-        <v>995669</v>
+        <v>181499</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
@@ -36618,19 +36582,19 @@
         <v>47</v>
       </c>
       <c r="B67" t="s">
-        <v>75</v>
+        <v>385</v>
       </c>
       <c r="C67" t="s">
-        <v>1143</v>
+        <v>1149</v>
       </c>
       <c r="D67" t="s">
-        <v>1144</v>
+        <v>1150</v>
       </c>
       <c r="E67" t="s">
         <v>17</v>
       </c>
       <c r="F67">
-        <v>56.1679999999999</v>
+        <v>327.08999999999901</v>
       </c>
       <c r="G67" t="s">
         <v>18</v>
@@ -36639,19 +36603,19 @@
         <v>1.53</v>
       </c>
       <c r="I67">
-        <v>85.94</v>
+        <v>500.45</v>
       </c>
       <c r="J67">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="K67">
-        <v>87.06</v>
+        <v>510.26</v>
       </c>
       <c r="L67" t="s">
-        <v>1183</v>
+        <v>1192</v>
       </c>
       <c r="M67">
-        <v>226912</v>
+        <v>995669</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
@@ -36662,16 +36626,16 @@
         <v>75</v>
       </c>
       <c r="C68" t="s">
-        <v>1136</v>
+        <v>1143</v>
       </c>
       <c r="D68" t="s">
-        <v>1137</v>
+        <v>1144</v>
       </c>
       <c r="E68" t="s">
         <v>17</v>
       </c>
       <c r="F68">
-        <v>53.070999999999898</v>
+        <v>56.1679999999999</v>
       </c>
       <c r="G68" t="s">
         <v>18</v>
@@ -36680,60 +36644,60 @@
         <v>1.53</v>
       </c>
       <c r="I68">
-        <v>81.2</v>
+        <v>85.94</v>
       </c>
       <c r="J68">
         <v>1.55</v>
       </c>
       <c r="K68">
-        <v>82.26</v>
+        <v>87.06</v>
       </c>
       <c r="L68" t="s">
-        <v>773</v>
+        <v>1183</v>
       </c>
       <c r="M68">
-        <v>411754</v>
+        <v>226912</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="B69" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C69" t="s">
-        <v>1190</v>
+        <v>1136</v>
       </c>
       <c r="D69" t="s">
-        <v>1191</v>
+        <v>1137</v>
       </c>
       <c r="E69" t="s">
         <v>17</v>
       </c>
       <c r="F69">
-        <v>44.832000000000001</v>
+        <v>53.070999999999898</v>
       </c>
       <c r="G69" t="s">
         <v>18</v>
       </c>
       <c r="H69">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="I69">
-        <v>70.39</v>
+        <v>81.2</v>
       </c>
       <c r="J69">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="K69">
-        <v>72.180000000000007</v>
+        <v>82.26</v>
       </c>
       <c r="L69" t="s">
-        <v>1177</v>
+        <v>773</v>
       </c>
       <c r="M69">
-        <v>306214</v>
+        <v>411754</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
@@ -36741,60 +36705,60 @@
         <v>84</v>
       </c>
       <c r="B70" t="s">
-        <v>375</v>
+        <v>1193</v>
       </c>
       <c r="C70" t="s">
-        <v>1151</v>
+        <v>1185</v>
       </c>
       <c r="D70" t="s">
-        <v>1152</v>
+        <v>1186</v>
       </c>
       <c r="E70" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="F70">
-        <v>27.1709999999999</v>
+        <v>61.241999999999898</v>
       </c>
       <c r="G70" t="s">
         <v>18</v>
       </c>
       <c r="H70">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="I70">
-        <v>37.770000000000003</v>
+        <v>96.15</v>
       </c>
       <c r="J70">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="K70">
-        <v>39.67</v>
+        <v>98.6</v>
       </c>
       <c r="L70" t="s">
-        <v>654</v>
+        <v>510</v>
       </c>
       <c r="M70">
-        <v>126403</v>
+        <v>230990</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="B71" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="C71" t="s">
-        <v>1139</v>
+        <v>1194</v>
       </c>
       <c r="D71" t="s">
-        <v>1140</v>
+        <v>1195</v>
       </c>
       <c r="E71" t="s">
         <v>17</v>
       </c>
       <c r="F71">
-        <v>51.938000000000002</v>
+        <v>44.832000000000001</v>
       </c>
       <c r="G71" t="s">
         <v>18</v>
@@ -36803,101 +36767,101 @@
         <v>1.57</v>
       </c>
       <c r="I71">
-        <v>81.540000000000006</v>
+        <v>70.39</v>
       </c>
       <c r="J71">
         <v>1.61</v>
       </c>
       <c r="K71">
-        <v>83.62</v>
+        <v>72.180000000000007</v>
       </c>
       <c r="L71" t="s">
-        <v>788</v>
+        <v>1177</v>
       </c>
       <c r="M71">
-        <v>233859</v>
+        <v>306214</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="B72" t="s">
-        <v>1157</v>
+        <v>375</v>
       </c>
       <c r="C72" t="s">
-        <v>1172</v>
+        <v>1151</v>
       </c>
       <c r="D72" t="s">
-        <v>1173</v>
+        <v>1152</v>
       </c>
       <c r="E72" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F72">
-        <v>75.313000000000002</v>
+        <v>27.1709999999999</v>
       </c>
       <c r="G72" t="s">
         <v>18</v>
       </c>
       <c r="H72">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="I72">
-        <v>120.5</v>
+        <v>37.770000000000003</v>
       </c>
       <c r="J72">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="K72">
-        <v>120.5</v>
+        <v>39.67</v>
       </c>
       <c r="L72" t="s">
-        <v>1041</v>
+        <v>654</v>
       </c>
       <c r="M72">
-        <v>194507</v>
+        <v>126403</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="B73" t="s">
         <v>93</v>
       </c>
       <c r="C73" t="s">
-        <v>1127</v>
+        <v>1139</v>
       </c>
       <c r="D73" t="s">
-        <v>1128</v>
+        <v>1140</v>
       </c>
       <c r="E73" t="s">
         <v>17</v>
       </c>
       <c r="F73">
-        <v>60.719999999999899</v>
+        <v>51.938000000000002</v>
       </c>
       <c r="G73" t="s">
         <v>18</v>
       </c>
       <c r="H73">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="I73">
-        <v>97.15</v>
+        <v>81.540000000000006</v>
       </c>
       <c r="J73">
         <v>1.61</v>
       </c>
       <c r="K73">
-        <v>97.76</v>
+        <v>83.62</v>
       </c>
       <c r="L73" t="s">
-        <v>1192</v>
+        <v>788</v>
       </c>
       <c r="M73">
-        <v>672908</v>
+        <v>233859</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
@@ -36905,19 +36869,19 @@
         <v>69</v>
       </c>
       <c r="B74" t="s">
-        <v>93</v>
+        <v>1196</v>
       </c>
       <c r="C74" t="s">
-        <v>1149</v>
+        <v>1185</v>
       </c>
       <c r="D74" t="s">
-        <v>1150</v>
+        <v>1186</v>
       </c>
       <c r="E74" t="s">
         <v>17</v>
       </c>
       <c r="F74">
-        <v>338.11799999999897</v>
+        <v>56.378999999999898</v>
       </c>
       <c r="G74" t="s">
         <v>18</v>
@@ -36926,19 +36890,19 @@
         <v>1.6</v>
       </c>
       <c r="I74">
-        <v>540.99</v>
+        <v>90.21</v>
       </c>
       <c r="J74">
         <v>1.61</v>
       </c>
       <c r="K74">
-        <v>544.37</v>
+        <v>90.77</v>
       </c>
       <c r="L74" t="s">
-        <v>488</v>
+        <v>1197</v>
       </c>
       <c r="M74">
-        <v>996844</v>
+        <v>231530</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
@@ -36946,19 +36910,19 @@
         <v>69</v>
       </c>
       <c r="B75" t="s">
-        <v>93</v>
+        <v>1157</v>
       </c>
       <c r="C75" t="s">
-        <v>1139</v>
+        <v>1172</v>
       </c>
       <c r="D75" t="s">
-        <v>1140</v>
+        <v>1173</v>
       </c>
       <c r="E75" t="s">
         <v>17</v>
       </c>
       <c r="F75">
-        <v>45.658000000000001</v>
+        <v>75.313000000000002</v>
       </c>
       <c r="G75" t="s">
         <v>18</v>
@@ -36967,19 +36931,19 @@
         <v>1.6</v>
       </c>
       <c r="I75">
-        <v>73.05</v>
+        <v>120.5</v>
       </c>
       <c r="J75">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="K75">
-        <v>73.510000000000005</v>
+        <v>120.5</v>
       </c>
       <c r="L75" t="s">
-        <v>651</v>
+        <v>1041</v>
       </c>
       <c r="M75">
-        <v>234323</v>
+        <v>194507</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
@@ -36987,19 +36951,19 @@
         <v>69</v>
       </c>
       <c r="B76" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C76" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
       <c r="D76" t="s">
-        <v>1137</v>
+        <v>1128</v>
       </c>
       <c r="E76" t="s">
         <v>17</v>
       </c>
       <c r="F76">
-        <v>59.918999999999897</v>
+        <v>60.719999999999899</v>
       </c>
       <c r="G76" t="s">
         <v>18</v>
@@ -37008,115 +36972,121 @@
         <v>1.6</v>
       </c>
       <c r="I76">
-        <v>95.87</v>
+        <v>97.15</v>
       </c>
       <c r="J76">
         <v>1.61</v>
       </c>
       <c r="K76">
-        <v>96.47</v>
+        <v>97.76</v>
       </c>
       <c r="L76" t="s">
-        <v>346</v>
+        <v>1198</v>
       </c>
       <c r="M76">
-        <v>412101</v>
+        <v>672908</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="B77" t="s">
-        <v>1157</v>
+        <v>93</v>
       </c>
       <c r="C77" t="s">
-        <v>1167</v>
+        <v>1149</v>
       </c>
       <c r="D77" t="s">
-        <v>1168</v>
+        <v>1150</v>
       </c>
       <c r="E77" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="F77">
-        <v>40.701000000000001</v>
+        <v>338.11799999999897</v>
       </c>
       <c r="G77" t="s">
         <v>18</v>
       </c>
       <c r="H77">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="I77">
-        <v>56.98</v>
+        <v>540.99</v>
       </c>
       <c r="J77">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="K77">
-        <v>59.83</v>
+        <v>544.37</v>
       </c>
       <c r="L77" t="s">
-        <v>68</v>
+        <v>488</v>
       </c>
       <c r="M77">
-        <v>224611</v>
+        <v>996844</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="B78" t="s">
-        <v>1157</v>
+        <v>93</v>
       </c>
       <c r="C78" t="s">
-        <v>1167</v>
+        <v>1139</v>
       </c>
       <c r="D78" t="s">
-        <v>1168</v>
+        <v>1140</v>
       </c>
       <c r="E78" t="s">
-        <v>379</v>
+        <v>17</v>
       </c>
       <c r="F78">
-        <v>22.167000000000002</v>
+        <v>45.658000000000001</v>
       </c>
       <c r="G78" t="s">
         <v>18</v>
       </c>
+      <c r="H78">
+        <v>1.6</v>
+      </c>
+      <c r="I78">
+        <v>73.05</v>
+      </c>
       <c r="J78">
-        <v>0.66</v>
+        <v>1.61</v>
       </c>
       <c r="K78">
-        <v>14.63</v>
+        <v>73.510000000000005</v>
       </c>
       <c r="L78" t="s">
-        <v>68</v>
+        <v>651</v>
       </c>
       <c r="M78">
-        <v>224611</v>
+        <v>234323</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="B79" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="C79" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="D79" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
       <c r="E79" t="s">
         <v>17</v>
       </c>
       <c r="F79">
-        <v>68.727999999999895</v>
+        <v>59.918999999999897</v>
       </c>
       <c r="G79" t="s">
         <v>18</v>
@@ -37125,19 +37095,19 @@
         <v>1.6</v>
       </c>
       <c r="I79">
-        <v>109.96</v>
+        <v>95.87</v>
       </c>
       <c r="J79">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="K79">
-        <v>111.34</v>
+        <v>96.47</v>
       </c>
       <c r="L79" t="s">
-        <v>50</v>
+        <v>346</v>
       </c>
       <c r="M79">
-        <v>234909</v>
+        <v>412101</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
@@ -37145,40 +37115,40 @@
         <v>53</v>
       </c>
       <c r="B80" t="s">
-        <v>93</v>
+        <v>1157</v>
       </c>
       <c r="C80" t="s">
-        <v>1162</v>
+        <v>1167</v>
       </c>
       <c r="D80" t="s">
-        <v>1163</v>
+        <v>1168</v>
       </c>
       <c r="E80" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F80">
-        <v>68.772000000000006</v>
+        <v>40.701000000000001</v>
       </c>
       <c r="G80" t="s">
         <v>18</v>
       </c>
       <c r="H80">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="I80">
-        <v>110.04</v>
+        <v>56.98</v>
       </c>
       <c r="J80">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="K80">
-        <v>111.41</v>
+        <v>59.83</v>
       </c>
       <c r="L80" t="s">
-        <v>1193</v>
+        <v>68</v>
       </c>
       <c r="M80">
-        <v>57052</v>
+        <v>224611</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
@@ -37186,40 +37156,34 @@
         <v>53</v>
       </c>
       <c r="B81" t="s">
-        <v>70</v>
+        <v>1157</v>
       </c>
       <c r="C81" t="s">
-        <v>1190</v>
+        <v>1167</v>
       </c>
       <c r="D81" t="s">
-        <v>1191</v>
+        <v>1168</v>
       </c>
       <c r="E81" t="s">
-        <v>17</v>
+        <v>379</v>
       </c>
       <c r="F81">
-        <v>70.888999999999896</v>
+        <v>22.167000000000002</v>
       </c>
       <c r="G81" t="s">
         <v>18</v>
       </c>
-      <c r="H81">
-        <v>1.6</v>
-      </c>
-      <c r="I81">
-        <v>113.42</v>
-      </c>
       <c r="J81">
-        <v>1.62</v>
+        <v>0.66</v>
       </c>
       <c r="K81">
-        <v>114.84</v>
+        <v>14.63</v>
       </c>
       <c r="L81" t="s">
-        <v>1194</v>
+        <v>68</v>
       </c>
       <c r="M81">
-        <v>306887</v>
+        <v>224611</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
@@ -37227,19 +37191,19 @@
         <v>53</v>
       </c>
       <c r="B82" t="s">
-        <v>75</v>
+        <v>1193</v>
       </c>
       <c r="C82" t="s">
-        <v>1141</v>
+        <v>1185</v>
       </c>
       <c r="D82" t="s">
-        <v>1142</v>
+        <v>1186</v>
       </c>
       <c r="E82" t="s">
         <v>17</v>
       </c>
       <c r="F82">
-        <v>77.197999999999894</v>
+        <v>55.5489999999999</v>
       </c>
       <c r="G82" t="s">
         <v>18</v>
@@ -37248,24 +37212,24 @@
         <v>1.6</v>
       </c>
       <c r="I82">
-        <v>123.52</v>
+        <v>88.88</v>
       </c>
       <c r="J82">
         <v>1.62</v>
       </c>
       <c r="K82">
-        <v>125.06</v>
+        <v>89.99</v>
       </c>
       <c r="L82" t="s">
-        <v>561</v>
+        <v>1108</v>
       </c>
       <c r="M82">
-        <v>0</v>
+        <v>232010</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>135</v>
+        <v>53</v>
       </c>
       <c r="B83" t="s">
         <v>93</v>
@@ -37280,148 +37244,148 @@
         <v>17</v>
       </c>
       <c r="F83">
-        <v>60.238999999999898</v>
+        <v>68.727999999999895</v>
       </c>
       <c r="G83" t="s">
         <v>18</v>
       </c>
       <c r="H83">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="I83">
-        <v>96.98</v>
+        <v>109.96</v>
       </c>
       <c r="J83">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="K83">
-        <v>98.19</v>
+        <v>111.34</v>
       </c>
       <c r="L83" t="s">
         <v>50</v>
       </c>
       <c r="M83">
-        <v>235464</v>
+        <v>234909</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>135</v>
+        <v>53</v>
       </c>
       <c r="B84" t="s">
         <v>93</v>
       </c>
       <c r="C84" t="s">
-        <v>1136</v>
+        <v>1162</v>
       </c>
       <c r="D84" t="s">
-        <v>1137</v>
+        <v>1163</v>
       </c>
       <c r="E84" t="s">
         <v>17</v>
       </c>
       <c r="F84">
-        <v>52.411000000000001</v>
+        <v>68.772000000000006</v>
       </c>
       <c r="G84" t="s">
         <v>18</v>
       </c>
       <c r="H84">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="I84">
-        <v>84.38</v>
+        <v>110.04</v>
       </c>
       <c r="J84">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="K84">
-        <v>85.43</v>
+        <v>111.41</v>
       </c>
       <c r="L84" t="s">
-        <v>19</v>
+        <v>1199</v>
       </c>
       <c r="M84">
-        <v>412408</v>
+        <v>57052</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>135</v>
+        <v>53</v>
       </c>
       <c r="B85" t="s">
-        <v>736</v>
+        <v>70</v>
       </c>
       <c r="C85" t="s">
-        <v>1172</v>
+        <v>1194</v>
       </c>
       <c r="D85" t="s">
-        <v>1173</v>
+        <v>1195</v>
       </c>
       <c r="E85" t="s">
         <v>17</v>
       </c>
       <c r="F85">
-        <v>78.822000000000003</v>
+        <v>70.888999999999896</v>
       </c>
       <c r="G85" t="s">
         <v>18</v>
       </c>
       <c r="H85">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="I85">
-        <v>126.9</v>
+        <v>113.42</v>
       </c>
       <c r="J85">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="K85">
-        <v>128.47999999999999</v>
+        <v>114.84</v>
       </c>
       <c r="L85" t="s">
-        <v>910</v>
+        <v>1200</v>
       </c>
       <c r="M85">
-        <v>195484</v>
+        <v>306887</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>315</v>
+        <v>53</v>
       </c>
       <c r="B86" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="C86" t="s">
-        <v>497</v>
+        <v>1141</v>
       </c>
       <c r="D86" t="s">
-        <v>1134</v>
+        <v>1142</v>
       </c>
       <c r="E86" t="s">
         <v>17</v>
       </c>
       <c r="F86">
-        <v>49.509</v>
+        <v>77.197999999999894</v>
       </c>
       <c r="G86" t="s">
         <v>18</v>
       </c>
       <c r="H86">
+        <v>1.6</v>
+      </c>
+      <c r="I86">
+        <v>123.52</v>
+      </c>
+      <c r="J86">
         <v>1.62</v>
       </c>
-      <c r="I86">
-        <v>80.2</v>
-      </c>
-      <c r="J86">
-        <v>1.65</v>
-      </c>
       <c r="K86">
-        <v>81.69</v>
+        <v>125.06</v>
       </c>
       <c r="L86" t="s">
-        <v>1195</v>
+        <v>561</v>
       </c>
       <c r="M86">
         <v>0</v>
@@ -37429,262 +37393,262 @@
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>72</v>
+        <v>135</v>
       </c>
       <c r="B87" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="C87" t="s">
-        <v>1149</v>
+        <v>1139</v>
       </c>
       <c r="D87" t="s">
-        <v>1150</v>
+        <v>1140</v>
       </c>
       <c r="E87" t="s">
         <v>17</v>
       </c>
       <c r="F87">
-        <v>347.39100000000002</v>
+        <v>60.238999999999898</v>
       </c>
       <c r="G87" t="s">
         <v>18</v>
       </c>
       <c r="H87">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="I87">
-        <v>569.72</v>
+        <v>96.98</v>
       </c>
       <c r="J87">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="K87">
-        <v>587.09</v>
+        <v>98.19</v>
       </c>
       <c r="L87" t="s">
-        <v>1196</v>
+        <v>50</v>
       </c>
       <c r="M87">
-        <v>998017</v>
+        <v>235464</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>72</v>
+        <v>135</v>
       </c>
       <c r="B88" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="C88" t="s">
-        <v>1149</v>
+        <v>1136</v>
       </c>
       <c r="D88" t="s">
-        <v>1150</v>
+        <v>1137</v>
       </c>
       <c r="E88" t="s">
-        <v>194</v>
+        <v>17</v>
       </c>
       <c r="F88">
-        <v>43.472000000000001</v>
+        <v>52.411000000000001</v>
       </c>
       <c r="G88" t="s">
         <v>18</v>
       </c>
+      <c r="H88">
+        <v>1.61</v>
+      </c>
+      <c r="I88">
+        <v>84.38</v>
+      </c>
       <c r="J88">
-        <v>1.27</v>
+        <v>1.63</v>
       </c>
       <c r="K88">
-        <v>55.21</v>
+        <v>85.43</v>
       </c>
       <c r="L88" t="s">
-        <v>1196</v>
+        <v>19</v>
       </c>
       <c r="M88">
-        <v>998017</v>
+        <v>412408</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>72</v>
+        <v>135</v>
       </c>
       <c r="B89" t="s">
-        <v>75</v>
+        <v>736</v>
       </c>
       <c r="C89" t="s">
-        <v>1136</v>
+        <v>1172</v>
       </c>
       <c r="D89" t="s">
-        <v>1137</v>
+        <v>1173</v>
       </c>
       <c r="E89" t="s">
         <v>17</v>
       </c>
       <c r="F89">
-        <v>58.75</v>
+        <v>78.822000000000003</v>
       </c>
       <c r="G89" t="s">
         <v>18</v>
       </c>
       <c r="H89">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="I89">
-        <v>96.35</v>
+        <v>126.9</v>
       </c>
       <c r="J89">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="K89">
-        <v>98.7</v>
+        <v>128.47999999999999</v>
       </c>
       <c r="L89" t="s">
-        <v>113</v>
+        <v>910</v>
       </c>
       <c r="M89">
-        <v>412749</v>
+        <v>195484</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>72</v>
+        <v>315</v>
       </c>
       <c r="B90" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C90" t="s">
-        <v>1151</v>
+        <v>497</v>
       </c>
       <c r="D90" t="s">
-        <v>1152</v>
+        <v>1134</v>
       </c>
       <c r="E90" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="F90">
-        <v>28.277000000000001</v>
+        <v>49.509</v>
       </c>
       <c r="G90" t="s">
         <v>18</v>
       </c>
       <c r="H90">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="I90">
-        <v>40.15</v>
+        <v>80.2</v>
       </c>
       <c r="J90">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="K90">
-        <v>41.85</v>
+        <v>81.69</v>
       </c>
       <c r="L90" t="s">
-        <v>414</v>
+        <v>1201</v>
       </c>
       <c r="M90">
-        <v>126718</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="B91" t="s">
-        <v>432</v>
+        <v>204</v>
       </c>
       <c r="C91" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="D91" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="E91" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="F91">
-        <v>8.4730000000000008</v>
+        <v>347.39100000000002</v>
       </c>
       <c r="G91" t="s">
         <v>18</v>
       </c>
       <c r="H91">
-        <v>1.42</v>
+        <v>1.64</v>
       </c>
       <c r="I91">
-        <v>12.03</v>
+        <v>569.72</v>
       </c>
       <c r="J91">
-        <v>1.48</v>
+        <v>1.69</v>
       </c>
       <c r="K91">
-        <v>12.54</v>
+        <v>587.09</v>
       </c>
       <c r="L91" t="s">
-        <v>1197</v>
+        <v>1202</v>
       </c>
       <c r="M91">
-        <v>126841</v>
+        <v>998017</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="B92" t="s">
-        <v>93</v>
+        <v>204</v>
       </c>
       <c r="C92" t="s">
-        <v>1162</v>
+        <v>1149</v>
       </c>
       <c r="D92" t="s">
-        <v>1163</v>
+        <v>1150</v>
       </c>
       <c r="E92" t="s">
-        <v>17</v>
+        <v>194</v>
       </c>
       <c r="F92">
-        <v>27.379000000000001</v>
+        <v>43.472000000000001</v>
       </c>
       <c r="G92" t="s">
         <v>18</v>
       </c>
-      <c r="H92">
-        <v>1.64</v>
-      </c>
-      <c r="I92">
-        <v>44.9</v>
-      </c>
       <c r="J92">
-        <v>1.69</v>
+        <v>1.27</v>
       </c>
       <c r="K92">
-        <v>46.27</v>
+        <v>55.21</v>
       </c>
       <c r="L92" t="s">
-        <v>910</v>
+        <v>1202</v>
       </c>
       <c r="M92">
-        <v>57294</v>
+        <v>998017</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="C93" t="s">
-        <v>1170</v>
+        <v>1136</v>
       </c>
       <c r="D93" t="s">
-        <v>1171</v>
+        <v>1137</v>
       </c>
       <c r="E93" t="s">
         <v>17</v>
       </c>
       <c r="F93">
-        <v>58.722000000000001</v>
+        <v>58.75</v>
       </c>
       <c r="G93" t="s">
         <v>18</v>
@@ -37693,60 +37657,60 @@
         <v>1.64</v>
       </c>
       <c r="I93">
-        <v>96.3</v>
+        <v>96.35</v>
       </c>
       <c r="J93">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="K93">
-        <v>99.24</v>
+        <v>98.7</v>
       </c>
       <c r="L93" t="s">
-        <v>1198</v>
+        <v>113</v>
       </c>
       <c r="M93">
-        <v>84500</v>
+        <v>412749</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="B94" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C94" t="s">
-        <v>1136</v>
+        <v>1151</v>
       </c>
       <c r="D94" t="s">
-        <v>1137</v>
+        <v>1152</v>
       </c>
       <c r="E94" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F94">
-        <v>20.431999999999899</v>
+        <v>28.277000000000001</v>
       </c>
       <c r="G94" t="s">
         <v>18</v>
       </c>
       <c r="H94">
-        <v>1.64</v>
+        <v>1.42</v>
       </c>
       <c r="I94">
-        <v>33.51</v>
+        <v>40.15</v>
       </c>
       <c r="J94">
-        <v>1.69</v>
+        <v>1.48</v>
       </c>
       <c r="K94">
-        <v>34.53</v>
+        <v>41.85</v>
       </c>
       <c r="L94" t="s">
-        <v>1017</v>
+        <v>414</v>
       </c>
       <c r="M94">
-        <v>412884</v>
+        <v>126718</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
@@ -37754,40 +37718,40 @@
         <v>55</v>
       </c>
       <c r="B95" t="s">
-        <v>93</v>
+        <v>432</v>
       </c>
       <c r="C95" t="s">
-        <v>1139</v>
+        <v>1151</v>
       </c>
       <c r="D95" t="s">
-        <v>1140</v>
+        <v>1152</v>
       </c>
       <c r="E95" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F95">
-        <v>41.201000000000001</v>
+        <v>8.4730000000000008</v>
       </c>
       <c r="G95" t="s">
         <v>18</v>
       </c>
       <c r="H95">
-        <v>1.64</v>
+        <v>1.42</v>
       </c>
       <c r="I95">
-        <v>67.569999999999993</v>
+        <v>12.03</v>
       </c>
       <c r="J95">
-        <v>1.69</v>
+        <v>1.48</v>
       </c>
       <c r="K95">
-        <v>69.63</v>
+        <v>12.54</v>
       </c>
       <c r="L95" t="s">
-        <v>1199</v>
+        <v>1203</v>
       </c>
       <c r="M95">
-        <v>235875</v>
+        <v>126841</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
@@ -37798,16 +37762,16 @@
         <v>93</v>
       </c>
       <c r="C96" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
       <c r="D96" t="s">
-        <v>1160</v>
+        <v>1163</v>
       </c>
       <c r="E96" t="s">
         <v>17</v>
       </c>
       <c r="F96">
-        <v>65.1009999999999</v>
+        <v>27.379000000000001</v>
       </c>
       <c r="G96" t="s">
         <v>18</v>
@@ -37816,19 +37780,19 @@
         <v>1.64</v>
       </c>
       <c r="I96">
-        <v>106.77</v>
+        <v>44.9</v>
       </c>
       <c r="J96">
         <v>1.69</v>
       </c>
       <c r="K96">
-        <v>110.02</v>
+        <v>46.27</v>
       </c>
       <c r="L96" t="s">
-        <v>1200</v>
+        <v>910</v>
       </c>
       <c r="M96">
-        <v>362704</v>
+        <v>57294</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.25">
@@ -37836,19 +37800,19 @@
         <v>55</v>
       </c>
       <c r="B97" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C97" t="s">
-        <v>1131</v>
+        <v>1170</v>
       </c>
       <c r="D97" t="s">
-        <v>1132</v>
+        <v>1171</v>
       </c>
       <c r="E97" t="s">
         <v>17</v>
       </c>
       <c r="F97">
-        <v>72.9819999999999</v>
+        <v>58.722000000000001</v>
       </c>
       <c r="G97" t="s">
         <v>18</v>
@@ -37857,19 +37821,19 @@
         <v>1.64</v>
       </c>
       <c r="I97">
-        <v>119.69</v>
+        <v>96.3</v>
       </c>
       <c r="J97">
         <v>1.69</v>
       </c>
       <c r="K97">
-        <v>123.34</v>
+        <v>99.24</v>
       </c>
       <c r="L97" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="M97">
-        <v>182063</v>
+        <v>84500</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.25">
@@ -37877,19 +37841,19 @@
         <v>55</v>
       </c>
       <c r="B98" t="s">
-        <v>736</v>
+        <v>93</v>
       </c>
       <c r="C98" t="s">
-        <v>1129</v>
+        <v>1136</v>
       </c>
       <c r="D98" t="s">
-        <v>1130</v>
+        <v>1137</v>
       </c>
       <c r="E98" t="s">
         <v>17</v>
       </c>
       <c r="F98">
-        <v>67.45</v>
+        <v>20.431999999999899</v>
       </c>
       <c r="G98" t="s">
         <v>18</v>
@@ -37898,19 +37862,19 @@
         <v>1.64</v>
       </c>
       <c r="I98">
-        <v>110.62</v>
+        <v>33.51</v>
       </c>
       <c r="J98">
         <v>1.69</v>
       </c>
       <c r="K98">
-        <v>113.99</v>
+        <v>34.53</v>
       </c>
       <c r="L98" t="s">
-        <v>1202</v>
+        <v>1017</v>
       </c>
       <c r="M98">
-        <v>198010</v>
+        <v>412884</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
@@ -37918,19 +37882,19 @@
         <v>55</v>
       </c>
       <c r="B99" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C99" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="D99" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="E99" t="s">
         <v>17</v>
       </c>
       <c r="F99">
-        <v>32.130000000000003</v>
+        <v>41.201000000000001</v>
       </c>
       <c r="G99" t="s">
         <v>18</v>
@@ -37939,19 +37903,19 @@
         <v>1.64</v>
       </c>
       <c r="I99">
-        <v>52.69</v>
+        <v>67.569999999999993</v>
       </c>
       <c r="J99">
         <v>1.69</v>
       </c>
       <c r="K99">
-        <v>54.3</v>
+        <v>69.63</v>
       </c>
       <c r="L99" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="M99">
-        <v>0</v>
+        <v>235875</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
@@ -37959,19 +37923,19 @@
         <v>55</v>
       </c>
       <c r="B100" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C100" t="s">
-        <v>1175</v>
+        <v>1159</v>
       </c>
       <c r="D100" t="s">
-        <v>1176</v>
+        <v>1160</v>
       </c>
       <c r="E100" t="s">
         <v>17</v>
       </c>
       <c r="F100">
-        <v>65.088999999999899</v>
+        <v>65.1009999999999</v>
       </c>
       <c r="G100" t="s">
         <v>18</v>
@@ -37980,18 +37944,182 @@
         <v>1.64</v>
       </c>
       <c r="I100">
-        <v>106.75</v>
+        <v>106.77</v>
       </c>
       <c r="J100">
         <v>1.69</v>
       </c>
       <c r="K100">
+        <v>110.02</v>
+      </c>
+      <c r="L100" t="s">
+        <v>1206</v>
+      </c>
+      <c r="M100">
+        <v>362704</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>55</v>
+      </c>
+      <c r="B101" t="s">
+        <v>70</v>
+      </c>
+      <c r="C101" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D101" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E101" t="s">
+        <v>17</v>
+      </c>
+      <c r="F101">
+        <v>72.9819999999999</v>
+      </c>
+      <c r="G101" t="s">
+        <v>18</v>
+      </c>
+      <c r="H101">
+        <v>1.64</v>
+      </c>
+      <c r="I101">
+        <v>119.69</v>
+      </c>
+      <c r="J101">
+        <v>1.69</v>
+      </c>
+      <c r="K101">
+        <v>123.34</v>
+      </c>
+      <c r="L101" t="s">
+        <v>1207</v>
+      </c>
+      <c r="M101">
+        <v>182063</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>55</v>
+      </c>
+      <c r="B102" t="s">
+        <v>736</v>
+      </c>
+      <c r="C102" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D102" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E102" t="s">
+        <v>17</v>
+      </c>
+      <c r="F102">
+        <v>67.45</v>
+      </c>
+      <c r="G102" t="s">
+        <v>18</v>
+      </c>
+      <c r="H102">
+        <v>1.64</v>
+      </c>
+      <c r="I102">
+        <v>110.62</v>
+      </c>
+      <c r="J102">
+        <v>1.69</v>
+      </c>
+      <c r="K102">
+        <v>113.99</v>
+      </c>
+      <c r="L102" t="s">
+        <v>1208</v>
+      </c>
+      <c r="M102">
+        <v>198010</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>55</v>
+      </c>
+      <c r="B103" t="s">
+        <v>75</v>
+      </c>
+      <c r="C103" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D103" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E103" t="s">
+        <v>17</v>
+      </c>
+      <c r="F103">
+        <v>32.130000000000003</v>
+      </c>
+      <c r="G103" t="s">
+        <v>18</v>
+      </c>
+      <c r="H103">
+        <v>1.64</v>
+      </c>
+      <c r="I103">
+        <v>52.69</v>
+      </c>
+      <c r="J103">
+        <v>1.69</v>
+      </c>
+      <c r="K103">
+        <v>54.3</v>
+      </c>
+      <c r="L103" t="s">
+        <v>1209</v>
+      </c>
+      <c r="M103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>55</v>
+      </c>
+      <c r="B104" t="s">
+        <v>75</v>
+      </c>
+      <c r="C104" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D104" t="s">
+        <v>1176</v>
+      </c>
+      <c r="E104" t="s">
+        <v>17</v>
+      </c>
+      <c r="F104">
+        <v>65.088999999999899</v>
+      </c>
+      <c r="G104" t="s">
+        <v>18</v>
+      </c>
+      <c r="H104">
+        <v>1.64</v>
+      </c>
+      <c r="I104">
+        <v>106.75</v>
+      </c>
+      <c r="J104">
+        <v>1.69</v>
+      </c>
+      <c r="K104">
         <v>110</v>
       </c>
-      <c r="L100" t="s">
+      <c r="L104" t="s">
         <v>123</v>
       </c>
-      <c r="M100">
+      <c r="M104">
         <v>23204</v>
       </c>
     </row>
@@ -38054,10 +38182,10 @@
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1204</v>
+        <v>1210</v>
       </c>
       <c r="D2" t="s">
-        <v>1205</v>
+        <v>1211</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
@@ -38081,7 +38209,7 @@
         <v>61.07</v>
       </c>
       <c r="L2" t="s">
-        <v>1206</v>
+        <v>1212</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -38095,10 +38223,10 @@
         <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>1207</v>
+        <v>1213</v>
       </c>
       <c r="D3" t="s">
-        <v>1208</v>
+        <v>1214</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
@@ -38136,10 +38264,10 @@
         <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>1204</v>
+        <v>1210</v>
       </c>
       <c r="D4" t="s">
-        <v>1205</v>
+        <v>1211</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
@@ -38163,7 +38291,7 @@
         <v>69.22</v>
       </c>
       <c r="L4" t="s">
-        <v>1209</v>
+        <v>1215</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -38177,10 +38305,10 @@
         <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>1207</v>
+        <v>1213</v>
       </c>
       <c r="D5" t="s">
-        <v>1208</v>
+        <v>1214</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
@@ -38218,10 +38346,10 @@
         <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>1204</v>
+        <v>1210</v>
       </c>
       <c r="D6" t="s">
-        <v>1205</v>
+        <v>1211</v>
       </c>
       <c r="E6" t="s">
         <v>17</v>
@@ -38245,7 +38373,7 @@
         <v>65.08</v>
       </c>
       <c r="L6" t="s">
-        <v>1188</v>
+        <v>1191</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -38259,10 +38387,10 @@
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>1210</v>
+        <v>1216</v>
       </c>
       <c r="D7" t="s">
-        <v>1211</v>
+        <v>1217</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
@@ -38286,7 +38414,7 @@
         <v>78.930000000000007</v>
       </c>
       <c r="L7" t="s">
-        <v>1212</v>
+        <v>1218</v>
       </c>
       <c r="M7">
         <v>422600</v>
@@ -38300,10 +38428,10 @@
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>1210</v>
+        <v>1216</v>
       </c>
       <c r="D8" t="s">
-        <v>1211</v>
+        <v>1217</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
@@ -38341,10 +38469,10 @@
         <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>1204</v>
+        <v>1210</v>
       </c>
       <c r="D9" t="s">
-        <v>1205</v>
+        <v>1211</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
@@ -38382,10 +38510,10 @@
         <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>1207</v>
+        <v>1213</v>
       </c>
       <c r="D10" t="s">
-        <v>1208</v>
+        <v>1214</v>
       </c>
       <c r="E10" t="s">
         <v>17</v>
@@ -38423,10 +38551,10 @@
         <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>1204</v>
+        <v>1210</v>
       </c>
       <c r="D11" t="s">
-        <v>1205</v>
+        <v>1211</v>
       </c>
       <c r="E11" t="s">
         <v>17</v>
@@ -38515,10 +38643,10 @@
         <v>415</v>
       </c>
       <c r="C2" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="D2" t="s">
-        <v>1214</v>
+        <v>1220</v>
       </c>
       <c r="E2" t="s">
         <v>179</v>
@@ -38556,10 +38684,10 @@
         <v>432</v>
       </c>
       <c r="C3" t="s">
-        <v>1215</v>
+        <v>1221</v>
       </c>
       <c r="D3" t="s">
-        <v>1216</v>
+        <v>1222</v>
       </c>
       <c r="E3" t="s">
         <v>240</v>
@@ -38583,7 +38711,7 @@
         <v>110.64</v>
       </c>
       <c r="L3" t="s">
-        <v>1217</v>
+        <v>1223</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -38597,10 +38725,10 @@
         <v>151</v>
       </c>
       <c r="C4" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="D4" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
@@ -38624,7 +38752,7 @@
         <v>58.85</v>
       </c>
       <c r="L4" t="s">
-        <v>1220</v>
+        <v>1226</v>
       </c>
       <c r="M4">
         <v>349588</v>
@@ -38638,10 +38766,10 @@
         <v>97</v>
       </c>
       <c r="C5" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="D5" t="s">
-        <v>1214</v>
+        <v>1220</v>
       </c>
       <c r="E5" t="s">
         <v>179</v>
@@ -38679,10 +38807,10 @@
         <v>97</v>
       </c>
       <c r="C6" t="s">
-        <v>1221</v>
+        <v>1227</v>
       </c>
       <c r="D6" t="s">
-        <v>1222</v>
+        <v>1228</v>
       </c>
       <c r="E6" t="s">
         <v>17</v>
@@ -38720,10 +38848,10 @@
         <v>442</v>
       </c>
       <c r="C7" t="s">
-        <v>1223</v>
+        <v>1229</v>
       </c>
       <c r="D7" t="s">
-        <v>1224</v>
+        <v>1230</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
@@ -38747,7 +38875,7 @@
         <v>49.69</v>
       </c>
       <c r="L7" t="s">
-        <v>1225</v>
+        <v>1231</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -38761,10 +38889,10 @@
         <v>442</v>
       </c>
       <c r="C8" t="s">
-        <v>1223</v>
+        <v>1229</v>
       </c>
       <c r="D8" t="s">
-        <v>1224</v>
+        <v>1230</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
@@ -38802,10 +38930,10 @@
         <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>1226</v>
+        <v>1232</v>
       </c>
       <c r="D9" t="s">
-        <v>1227</v>
+        <v>1233</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
@@ -38843,10 +38971,10 @@
         <v>144</v>
       </c>
       <c r="C10" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="D10" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="E10" t="s">
         <v>17</v>
@@ -38870,7 +38998,7 @@
         <v>45.81</v>
       </c>
       <c r="L10" t="s">
-        <v>1228</v>
+        <v>1234</v>
       </c>
       <c r="M10">
         <v>350060</v>
@@ -38884,10 +39012,10 @@
         <v>375</v>
       </c>
       <c r="C11" t="s">
-        <v>1229</v>
+        <v>1235</v>
       </c>
       <c r="D11" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="E11" t="s">
         <v>179</v>
@@ -38925,10 +39053,10 @@
         <v>97</v>
       </c>
       <c r="C12" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="D12" t="s">
-        <v>1214</v>
+        <v>1220</v>
       </c>
       <c r="E12" t="s">
         <v>179</v>
@@ -38952,7 +39080,7 @@
         <v>147.28</v>
       </c>
       <c r="L12" t="s">
-        <v>1193</v>
+        <v>1199</v>
       </c>
       <c r="M12">
         <v>0</v>
@@ -38966,10 +39094,10 @@
         <v>202</v>
       </c>
       <c r="C13" t="s">
-        <v>1231</v>
+        <v>1237</v>
       </c>
       <c r="D13" t="s">
-        <v>1232</v>
+        <v>1238</v>
       </c>
       <c r="E13" t="s">
         <v>17</v>
@@ -39007,10 +39135,10 @@
         <v>202</v>
       </c>
       <c r="C14" t="s">
-        <v>1231</v>
+        <v>1237</v>
       </c>
       <c r="D14" t="s">
-        <v>1232</v>
+        <v>1238</v>
       </c>
       <c r="E14" t="s">
         <v>259</v>
@@ -39042,10 +39170,10 @@
         <v>392</v>
       </c>
       <c r="C15" t="s">
-        <v>1233</v>
+        <v>1239</v>
       </c>
       <c r="D15" t="s">
-        <v>1234</v>
+        <v>1240</v>
       </c>
       <c r="E15" t="s">
         <v>17</v>
@@ -39069,7 +39197,7 @@
         <v>63.52</v>
       </c>
       <c r="L15" t="s">
-        <v>1235</v>
+        <v>1241</v>
       </c>
       <c r="M15">
         <v>0</v>
@@ -39083,10 +39211,10 @@
         <v>495</v>
       </c>
       <c r="C16" t="s">
-        <v>1223</v>
+        <v>1229</v>
       </c>
       <c r="D16" t="s">
-        <v>1224</v>
+        <v>1230</v>
       </c>
       <c r="E16" t="s">
         <v>17</v>
@@ -39121,13 +39249,13 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>1236</v>
+        <v>1242</v>
       </c>
       <c r="C17" t="s">
-        <v>1237</v>
+        <v>1243</v>
       </c>
       <c r="D17" t="s">
-        <v>1238</v>
+        <v>1244</v>
       </c>
       <c r="E17" t="s">
         <v>17</v>
@@ -39165,10 +39293,10 @@
         <v>432</v>
       </c>
       <c r="C18" t="s">
-        <v>1221</v>
+        <v>1227</v>
       </c>
       <c r="D18" t="s">
-        <v>1222</v>
+        <v>1228</v>
       </c>
       <c r="E18" t="s">
         <v>17</v>
@@ -39206,10 +39334,10 @@
         <v>93</v>
       </c>
       <c r="C19" t="s">
-        <v>1239</v>
+        <v>1245</v>
       </c>
       <c r="D19" t="s">
-        <v>1240</v>
+        <v>1246</v>
       </c>
       <c r="E19" t="s">
         <v>45</v>
@@ -39247,10 +39375,10 @@
         <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>1241</v>
+        <v>1247</v>
       </c>
       <c r="D20" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="E20" t="s">
         <v>17</v>
@@ -39288,10 +39416,10 @@
         <v>442</v>
       </c>
       <c r="C21" t="s">
-        <v>1231</v>
+        <v>1237</v>
       </c>
       <c r="D21" t="s">
-        <v>1232</v>
+        <v>1238</v>
       </c>
       <c r="E21" t="s">
         <v>17</v>
@@ -39315,7 +39443,7 @@
         <v>120.35</v>
       </c>
       <c r="L21" t="s">
-        <v>1243</v>
+        <v>1249</v>
       </c>
       <c r="M21">
         <v>0</v>
@@ -39329,10 +39457,10 @@
         <v>202</v>
       </c>
       <c r="C22" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="D22" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="E22" t="s">
         <v>17</v>
@@ -39370,10 +39498,10 @@
         <v>754</v>
       </c>
       <c r="C23" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="D23" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="E23" t="s">
         <v>17</v>
@@ -39411,10 +39539,10 @@
         <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>1226</v>
+        <v>1232</v>
       </c>
       <c r="D24" t="s">
-        <v>1227</v>
+        <v>1233</v>
       </c>
       <c r="E24" t="s">
         <v>17</v>
@@ -39438,7 +39566,7 @@
         <v>49.05</v>
       </c>
       <c r="L24" t="s">
-        <v>1244</v>
+        <v>1250</v>
       </c>
       <c r="M24">
         <v>291662</v>
@@ -39452,10 +39580,10 @@
         <v>413</v>
       </c>
       <c r="C25" t="s">
-        <v>1233</v>
+        <v>1239</v>
       </c>
       <c r="D25" t="s">
-        <v>1234</v>
+        <v>1240</v>
       </c>
       <c r="E25" t="s">
         <v>17</v>
@@ -39493,10 +39621,10 @@
         <v>375</v>
       </c>
       <c r="C26" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="D26" t="s">
-        <v>1246</v>
+        <v>1252</v>
       </c>
       <c r="E26" t="s">
         <v>179</v>
@@ -39534,10 +39662,10 @@
         <v>97</v>
       </c>
       <c r="C27" t="s">
-        <v>1247</v>
+        <v>1253</v>
       </c>
       <c r="D27" t="s">
-        <v>1248</v>
+        <v>1254</v>
       </c>
       <c r="E27" t="s">
         <v>240</v>
@@ -39575,10 +39703,10 @@
         <v>97</v>
       </c>
       <c r="C28" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="D28" t="s">
-        <v>1214</v>
+        <v>1220</v>
       </c>
       <c r="E28" t="s">
         <v>179</v>
@@ -39616,10 +39744,10 @@
         <v>442</v>
       </c>
       <c r="C29" t="s">
-        <v>1223</v>
+        <v>1229</v>
       </c>
       <c r="D29" t="s">
-        <v>1224</v>
+        <v>1230</v>
       </c>
       <c r="E29" t="s">
         <v>17</v>
@@ -39643,7 +39771,7 @@
         <v>65.28</v>
       </c>
       <c r="L29" t="s">
-        <v>1249</v>
+        <v>1255</v>
       </c>
       <c r="M29">
         <v>0</v>
@@ -39657,10 +39785,10 @@
         <v>442</v>
       </c>
       <c r="C30" t="s">
-        <v>1223</v>
+        <v>1229</v>
       </c>
       <c r="D30" t="s">
-        <v>1224</v>
+        <v>1230</v>
       </c>
       <c r="E30" t="s">
         <v>17</v>
@@ -39698,10 +39826,10 @@
         <v>93</v>
       </c>
       <c r="C31" t="s">
-        <v>1250</v>
+        <v>1256</v>
       </c>
       <c r="D31" t="s">
-        <v>1251</v>
+        <v>1257</v>
       </c>
       <c r="E31" t="s">
         <v>17</v>
@@ -39725,7 +39853,7 @@
         <v>95.34</v>
       </c>
       <c r="L31" t="s">
-        <v>1252</v>
+        <v>1258</v>
       </c>
       <c r="M31">
         <v>0</v>
@@ -39739,10 +39867,10 @@
         <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>1253</v>
+        <v>1259</v>
       </c>
       <c r="D32" t="s">
-        <v>1254</v>
+        <v>1260</v>
       </c>
       <c r="E32" t="s">
         <v>179</v>
@@ -39766,7 +39894,7 @@
         <v>105.39</v>
       </c>
       <c r="L32" t="s">
-        <v>1212</v>
+        <v>1218</v>
       </c>
       <c r="M32">
         <v>0</v>
@@ -39780,10 +39908,10 @@
         <v>375</v>
       </c>
       <c r="C33" t="s">
-        <v>1221</v>
+        <v>1227</v>
       </c>
       <c r="D33" t="s">
-        <v>1222</v>
+        <v>1228</v>
       </c>
       <c r="E33" t="s">
         <v>17</v>
@@ -39821,10 +39949,10 @@
         <v>375</v>
       </c>
       <c r="C34" t="s">
-        <v>1229</v>
+        <v>1235</v>
       </c>
       <c r="D34" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="E34" t="s">
         <v>179</v>
@@ -39848,7 +39976,7 @@
         <v>112.34</v>
       </c>
       <c r="L34" t="s">
-        <v>1255</v>
+        <v>1261</v>
       </c>
       <c r="M34">
         <v>0</v>
@@ -39862,10 +39990,10 @@
         <v>415</v>
       </c>
       <c r="C35" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="D35" t="s">
-        <v>1214</v>
+        <v>1220</v>
       </c>
       <c r="E35" t="s">
         <v>179</v>
@@ -39889,7 +40017,7 @@
         <v>76.069999999999993</v>
       </c>
       <c r="L35" t="s">
-        <v>1256</v>
+        <v>1262</v>
       </c>
       <c r="M35">
         <v>0</v>
@@ -39903,10 +40031,10 @@
         <v>413</v>
       </c>
       <c r="C36" t="s">
-        <v>1233</v>
+        <v>1239</v>
       </c>
       <c r="D36" t="s">
-        <v>1234</v>
+        <v>1240</v>
       </c>
       <c r="E36" t="s">
         <v>17</v>
@@ -39930,7 +40058,7 @@
         <v>68.569999999999993</v>
       </c>
       <c r="L36" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
       <c r="M36">
         <v>0</v>
@@ -39944,10 +40072,10 @@
         <v>97</v>
       </c>
       <c r="C37" t="s">
-        <v>1215</v>
+        <v>1221</v>
       </c>
       <c r="D37" t="s">
-        <v>1216</v>
+        <v>1222</v>
       </c>
       <c r="E37" t="s">
         <v>240</v>
@@ -39985,10 +40113,10 @@
         <v>202</v>
       </c>
       <c r="C38" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="D38" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="E38" t="s">
         <v>17</v>
@@ -40012,7 +40140,7 @@
         <v>46.47</v>
       </c>
       <c r="L38" t="s">
-        <v>1258</v>
+        <v>1264</v>
       </c>
       <c r="M38">
         <v>371889</v>
@@ -40026,10 +40154,10 @@
         <v>408</v>
       </c>
       <c r="C39" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="D39" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="E39" t="s">
         <v>17</v>
@@ -40053,7 +40181,7 @@
         <v>66.89</v>
       </c>
       <c r="L39" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="M39">
         <v>352194</v>
@@ -40067,10 +40195,10 @@
         <v>294</v>
       </c>
       <c r="C40" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="D40" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="E40" t="s">
         <v>17</v>
@@ -40094,7 +40222,7 @@
         <v>35.93</v>
       </c>
       <c r="L40" t="s">
-        <v>1260</v>
+        <v>1266</v>
       </c>
       <c r="M40">
         <v>352353</v>
@@ -40108,10 +40236,10 @@
         <v>97</v>
       </c>
       <c r="C41" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="D41" t="s">
-        <v>1214</v>
+        <v>1220</v>
       </c>
       <c r="E41" t="s">
         <v>179</v>
@@ -40149,10 +40277,10 @@
         <v>380</v>
       </c>
       <c r="C42" t="s">
-        <v>1261</v>
+        <v>1267</v>
       </c>
       <c r="D42" t="s">
-        <v>1262</v>
+        <v>1268</v>
       </c>
       <c r="E42" t="s">
         <v>17</v>
@@ -40176,7 +40304,7 @@
         <v>92.75</v>
       </c>
       <c r="L42" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="M42">
         <v>300087</v>
@@ -40190,10 +40318,10 @@
         <v>410</v>
       </c>
       <c r="C43" t="s">
-        <v>1233</v>
+        <v>1239</v>
       </c>
       <c r="D43" t="s">
-        <v>1234</v>
+        <v>1240</v>
       </c>
       <c r="E43" t="s">
         <v>17</v>
@@ -40231,10 +40359,10 @@
         <v>294</v>
       </c>
       <c r="C44" t="s">
-        <v>1223</v>
+        <v>1229</v>
       </c>
       <c r="D44" t="s">
-        <v>1224</v>
+        <v>1230</v>
       </c>
       <c r="E44" t="s">
         <v>17</v>
@@ -40258,7 +40386,7 @@
         <v>47.66</v>
       </c>
       <c r="L44" t="s">
-        <v>1264</v>
+        <v>1270</v>
       </c>
       <c r="M44">
         <v>389572</v>
@@ -40272,10 +40400,10 @@
         <v>442</v>
       </c>
       <c r="C45" t="s">
-        <v>1265</v>
+        <v>1271</v>
       </c>
       <c r="D45" t="s">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="E45" t="s">
         <v>17</v>
@@ -40299,7 +40427,7 @@
         <v>87.53</v>
       </c>
       <c r="L45" t="s">
-        <v>1267</v>
+        <v>1273</v>
       </c>
       <c r="M45">
         <v>0</v>
@@ -40310,13 +40438,13 @@
         <v>26</v>
       </c>
       <c r="B46" t="s">
-        <v>1268</v>
+        <v>1274</v>
       </c>
       <c r="C46" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="D46" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="E46" t="s">
         <v>17</v>
@@ -40354,10 +40482,10 @@
         <v>202</v>
       </c>
       <c r="C47" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="D47" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="E47" t="s">
         <v>17</v>
@@ -40381,7 +40509,7 @@
         <v>66.44</v>
       </c>
       <c r="L47" t="s">
-        <v>1269</v>
+        <v>1275</v>
       </c>
       <c r="M47">
         <v>0</v>
@@ -40395,10 +40523,10 @@
         <v>432</v>
       </c>
       <c r="C48" t="s">
-        <v>1221</v>
+        <v>1227</v>
       </c>
       <c r="D48" t="s">
-        <v>1222</v>
+        <v>1228</v>
       </c>
       <c r="E48" t="s">
         <v>17</v>
@@ -40436,10 +40564,10 @@
         <v>93</v>
       </c>
       <c r="C49" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="D49" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="E49" t="s">
         <v>17</v>
@@ -40477,10 +40605,10 @@
         <v>93</v>
       </c>
       <c r="C50" t="s">
-        <v>1226</v>
+        <v>1232</v>
       </c>
       <c r="D50" t="s">
-        <v>1227</v>
+        <v>1233</v>
       </c>
       <c r="E50" t="s">
         <v>17</v>
@@ -40518,10 +40646,10 @@
         <v>410</v>
       </c>
       <c r="C51" t="s">
-        <v>1237</v>
+        <v>1243</v>
       </c>
       <c r="D51" t="s">
-        <v>1238</v>
+        <v>1244</v>
       </c>
       <c r="E51" t="s">
         <v>17</v>
@@ -40545,7 +40673,7 @@
         <v>131.66</v>
       </c>
       <c r="L51" t="s">
-        <v>1228</v>
+        <v>1234</v>
       </c>
       <c r="M51">
         <v>0</v>
@@ -40559,10 +40687,10 @@
         <v>294</v>
       </c>
       <c r="C52" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="D52" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="E52" t="s">
         <v>17</v>
@@ -40586,7 +40714,7 @@
         <v>43.55</v>
       </c>
       <c r="L52" t="s">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="M52">
         <v>0</v>
@@ -40600,10 +40728,10 @@
         <v>375</v>
       </c>
       <c r="C53" t="s">
-        <v>1271</v>
+        <v>1277</v>
       </c>
       <c r="D53" t="s">
-        <v>1272</v>
+        <v>1278</v>
       </c>
       <c r="E53" t="s">
         <v>179</v>
@@ -40627,7 +40755,7 @@
         <v>60.9</v>
       </c>
       <c r="L53" t="s">
-        <v>1273</v>
+        <v>1279</v>
       </c>
       <c r="M53">
         <v>292487</v>
@@ -40641,10 +40769,10 @@
         <v>375</v>
       </c>
       <c r="C54" t="s">
-        <v>1229</v>
+        <v>1235</v>
       </c>
       <c r="D54" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="E54" t="s">
         <v>179</v>
@@ -40682,10 +40810,10 @@
         <v>93</v>
       </c>
       <c r="C55" t="s">
-        <v>1215</v>
+        <v>1221</v>
       </c>
       <c r="D55" t="s">
-        <v>1216</v>
+        <v>1222</v>
       </c>
       <c r="E55" t="s">
         <v>240</v>
@@ -40723,10 +40851,10 @@
         <v>93</v>
       </c>
       <c r="C56" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="D56" t="s">
-        <v>1246</v>
+        <v>1252</v>
       </c>
       <c r="E56" t="s">
         <v>179</v>
@@ -40764,10 +40892,10 @@
         <v>151</v>
       </c>
       <c r="C57" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="D57" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="E57" t="s">
         <v>17</v>
@@ -40791,7 +40919,7 @@
         <v>53.4</v>
       </c>
       <c r="L57" t="s">
-        <v>1274</v>
+        <v>1280</v>
       </c>
       <c r="M57">
         <v>0</v>
@@ -40805,10 +40933,10 @@
         <v>97</v>
       </c>
       <c r="C58" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="D58" t="s">
-        <v>1214</v>
+        <v>1220</v>
       </c>
       <c r="E58" t="s">
         <v>179</v>
@@ -40832,7 +40960,7 @@
         <v>108.82</v>
       </c>
       <c r="L58" t="s">
-        <v>1275</v>
+        <v>1281</v>
       </c>
       <c r="M58">
         <v>0</v>
@@ -40846,10 +40974,10 @@
         <v>93</v>
       </c>
       <c r="C59" t="s">
-        <v>1265</v>
+        <v>1271</v>
       </c>
       <c r="D59" t="s">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="E59" t="s">
         <v>17</v>
@@ -40873,7 +41001,7 @@
         <v>142.71</v>
       </c>
       <c r="L59" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="M59">
         <v>0</v>
@@ -40887,10 +41015,10 @@
         <v>93</v>
       </c>
       <c r="C60" t="s">
-        <v>1241</v>
+        <v>1247</v>
       </c>
       <c r="D60" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="E60" t="s">
         <v>179</v>
@@ -40914,7 +41042,7 @@
         <v>86.48</v>
       </c>
       <c r="L60" t="s">
-        <v>1277</v>
+        <v>1283</v>
       </c>
       <c r="M60">
         <v>0</v>
@@ -40928,10 +41056,10 @@
         <v>75</v>
       </c>
       <c r="C61" t="s">
-        <v>1226</v>
+        <v>1232</v>
       </c>
       <c r="D61" t="s">
-        <v>1227</v>
+        <v>1233</v>
       </c>
       <c r="E61" t="s">
         <v>17</v>
@@ -40969,10 +41097,10 @@
         <v>202</v>
       </c>
       <c r="C62" t="s">
-        <v>1265</v>
+        <v>1271</v>
       </c>
       <c r="D62" t="s">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="E62" t="s">
         <v>17</v>
@@ -41010,10 +41138,10 @@
         <v>97</v>
       </c>
       <c r="C63" t="s">
-        <v>1247</v>
+        <v>1253</v>
       </c>
       <c r="D63" t="s">
-        <v>1248</v>
+        <v>1254</v>
       </c>
       <c r="E63" t="s">
         <v>240</v>
@@ -41037,7 +41165,7 @@
         <v>155</v>
       </c>
       <c r="L63" t="s">
-        <v>1278</v>
+        <v>1284</v>
       </c>
       <c r="M63">
         <v>0</v>
@@ -41051,10 +41179,10 @@
         <v>442</v>
       </c>
       <c r="C64" t="s">
-        <v>1247</v>
+        <v>1253</v>
       </c>
       <c r="D64" t="s">
-        <v>1248</v>
+        <v>1254</v>
       </c>
       <c r="E64" t="s">
         <v>45</v>
@@ -41089,13 +41217,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>1236</v>
+        <v>1242</v>
       </c>
       <c r="C65" t="s">
-        <v>1237</v>
+        <v>1243</v>
       </c>
       <c r="D65" t="s">
-        <v>1238</v>
+        <v>1244</v>
       </c>
       <c r="E65" t="s">
         <v>17</v>
@@ -41133,10 +41261,10 @@
         <v>432</v>
       </c>
       <c r="C66" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="D66" t="s">
-        <v>1214</v>
+        <v>1220</v>
       </c>
       <c r="E66" t="s">
         <v>179</v>
@@ -41160,7 +41288,7 @@
         <v>58.54</v>
       </c>
       <c r="L66" t="s">
-        <v>1228</v>
+        <v>1234</v>
       </c>
       <c r="M66">
         <v>0</v>
@@ -41174,10 +41302,10 @@
         <v>93</v>
       </c>
       <c r="C67" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="D67" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="E67" t="s">
         <v>17</v>
@@ -41201,7 +41329,7 @@
         <v>47.39</v>
       </c>
       <c r="L67" t="s">
-        <v>1279</v>
+        <v>1285</v>
       </c>
       <c r="M67">
         <v>0</v>
@@ -41215,10 +41343,10 @@
         <v>93</v>
       </c>
       <c r="C68" t="s">
-        <v>1239</v>
+        <v>1245</v>
       </c>
       <c r="D68" t="s">
-        <v>1240</v>
+        <v>1246</v>
       </c>
       <c r="E68" t="s">
         <v>45</v>
@@ -41256,10 +41384,10 @@
         <v>93</v>
       </c>
       <c r="C69" t="s">
-        <v>1226</v>
+        <v>1232</v>
       </c>
       <c r="D69" t="s">
-        <v>1227</v>
+        <v>1233</v>
       </c>
       <c r="E69" t="s">
         <v>17</v>
@@ -41297,10 +41425,10 @@
         <v>97</v>
       </c>
       <c r="C70" t="s">
-        <v>1221</v>
+        <v>1227</v>
       </c>
       <c r="D70" t="s">
-        <v>1222</v>
+        <v>1228</v>
       </c>
       <c r="E70" t="s">
         <v>17</v>
@@ -41338,10 +41466,10 @@
         <v>97</v>
       </c>
       <c r="C71" t="s">
-        <v>1247</v>
+        <v>1253</v>
       </c>
       <c r="D71" t="s">
-        <v>1248</v>
+        <v>1254</v>
       </c>
       <c r="E71" t="s">
         <v>240</v>
@@ -41365,7 +41493,7 @@
         <v>139.99</v>
       </c>
       <c r="L71" t="s">
-        <v>1280</v>
+        <v>1286</v>
       </c>
       <c r="M71">
         <v>0</v>
@@ -41379,10 +41507,10 @@
         <v>442</v>
       </c>
       <c r="C72" t="s">
-        <v>1265</v>
+        <v>1271</v>
       </c>
       <c r="D72" t="s">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="E72" t="s">
         <v>17</v>
@@ -41420,10 +41548,10 @@
         <v>442</v>
       </c>
       <c r="C73" t="s">
-        <v>1265</v>
+        <v>1271</v>
       </c>
       <c r="D73" t="s">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="E73" t="s">
         <v>194</v>
@@ -41452,13 +41580,13 @@
         <v>42</v>
       </c>
       <c r="B74" t="s">
-        <v>1268</v>
+        <v>1274</v>
       </c>
       <c r="C74" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="D74" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="E74" t="s">
         <v>17</v>
@@ -41496,10 +41624,10 @@
         <v>202</v>
       </c>
       <c r="C75" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="D75" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="E75" t="s">
         <v>17</v>
@@ -41523,7 +41651,7 @@
         <v>53.4</v>
       </c>
       <c r="L75" t="s">
-        <v>1281</v>
+        <v>1287</v>
       </c>
       <c r="M75">
         <v>0</v>
@@ -41537,10 +41665,10 @@
         <v>432</v>
       </c>
       <c r="C76" t="s">
-        <v>1282</v>
+        <v>1288</v>
       </c>
       <c r="D76" t="s">
-        <v>1283</v>
+        <v>1289</v>
       </c>
       <c r="E76" t="s">
         <v>17</v>
@@ -41578,10 +41706,10 @@
         <v>97</v>
       </c>
       <c r="C77" t="s">
-        <v>1215</v>
+        <v>1221</v>
       </c>
       <c r="D77" t="s">
-        <v>1216</v>
+        <v>1222</v>
       </c>
       <c r="E77" t="s">
         <v>240</v>
@@ -41605,7 +41733,7 @@
         <v>118.17</v>
       </c>
       <c r="L77" t="s">
-        <v>1264</v>
+        <v>1270</v>
       </c>
       <c r="M77">
         <v>0</v>
@@ -41619,10 +41747,10 @@
         <v>97</v>
       </c>
       <c r="C78" t="s">
-        <v>1284</v>
+        <v>1290</v>
       </c>
       <c r="D78" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="E78" t="s">
         <v>45</v>
@@ -41646,7 +41774,7 @@
         <v>53.62</v>
       </c>
       <c r="L78" t="s">
-        <v>1286</v>
+        <v>1292</v>
       </c>
       <c r="M78">
         <v>11945</v>
@@ -41660,10 +41788,10 @@
         <v>375</v>
       </c>
       <c r="C79" t="s">
-        <v>1271</v>
+        <v>1277</v>
       </c>
       <c r="D79" t="s">
-        <v>1272</v>
+        <v>1278</v>
       </c>
       <c r="E79" t="s">
         <v>179</v>
@@ -41701,10 +41829,10 @@
         <v>93</v>
       </c>
       <c r="C80" t="s">
-        <v>1226</v>
+        <v>1232</v>
       </c>
       <c r="D80" t="s">
-        <v>1227</v>
+        <v>1233</v>
       </c>
       <c r="E80" t="s">
         <v>17</v>
@@ -41728,7 +41856,7 @@
         <v>33.1</v>
       </c>
       <c r="L80" t="s">
-        <v>1287</v>
+        <v>1293</v>
       </c>
       <c r="M80">
         <v>293186</v>
@@ -41742,10 +41870,10 @@
         <v>375</v>
       </c>
       <c r="C81" t="s">
-        <v>1229</v>
+        <v>1235</v>
       </c>
       <c r="D81" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="E81" t="s">
         <v>179</v>
@@ -41769,7 +41897,7 @@
         <v>148.44999999999999</v>
       </c>
       <c r="L81" t="s">
-        <v>1288</v>
+        <v>1294</v>
       </c>
       <c r="M81">
         <v>0</v>
@@ -41783,10 +41911,10 @@
         <v>97</v>
       </c>
       <c r="C82" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="D82" t="s">
-        <v>1214</v>
+        <v>1220</v>
       </c>
       <c r="E82" t="s">
         <v>179</v>
@@ -41824,10 +41952,10 @@
         <v>442</v>
       </c>
       <c r="C83" t="s">
-        <v>1223</v>
+        <v>1229</v>
       </c>
       <c r="D83" t="s">
-        <v>1224</v>
+        <v>1230</v>
       </c>
       <c r="E83" t="s">
         <v>17</v>
@@ -41851,7 +41979,7 @@
         <v>51.21</v>
       </c>
       <c r="L83" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
       <c r="M83">
         <v>390823</v>
@@ -41865,10 +41993,10 @@
         <v>442</v>
       </c>
       <c r="C84" t="s">
-        <v>1223</v>
+        <v>1229</v>
       </c>
       <c r="D84" t="s">
-        <v>1224</v>
+        <v>1230</v>
       </c>
       <c r="E84" t="s">
         <v>17</v>
@@ -41906,10 +42034,10 @@
         <v>93</v>
       </c>
       <c r="C85" t="s">
-        <v>1226</v>
+        <v>1232</v>
       </c>
       <c r="D85" t="s">
-        <v>1227</v>
+        <v>1233</v>
       </c>
       <c r="E85" t="s">
         <v>17</v>
@@ -41933,7 +42061,7 @@
         <v>46.13</v>
       </c>
       <c r="L85" t="s">
-        <v>1290</v>
+        <v>1296</v>
       </c>
       <c r="M85">
         <v>293478</v>
@@ -41947,10 +42075,10 @@
         <v>736</v>
       </c>
       <c r="C86" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="D86" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="E86" t="s">
         <v>17</v>
@@ -41974,7 +42102,7 @@
         <v>62.32</v>
       </c>
       <c r="L86" t="s">
-        <v>1291</v>
+        <v>1297</v>
       </c>
       <c r="M86">
         <v>0</v>
@@ -41988,10 +42116,10 @@
         <v>75</v>
       </c>
       <c r="C87" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="D87" t="s">
-        <v>1246</v>
+        <v>1252</v>
       </c>
       <c r="E87" t="s">
         <v>179</v>
@@ -42015,7 +42143,7 @@
         <v>82.73</v>
       </c>
       <c r="L87" t="s">
-        <v>1292</v>
+        <v>1298</v>
       </c>
       <c r="M87">
         <v>360108</v>
@@ -42029,10 +42157,10 @@
         <v>413</v>
       </c>
       <c r="C88" t="s">
-        <v>1237</v>
+        <v>1243</v>
       </c>
       <c r="D88" t="s">
-        <v>1238</v>
+        <v>1244</v>
       </c>
       <c r="E88" t="s">
         <v>17</v>
@@ -42070,10 +42198,10 @@
         <v>202</v>
       </c>
       <c r="C89" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="D89" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="E89" t="s">
         <v>17</v>
@@ -42111,10 +42239,10 @@
         <v>432</v>
       </c>
       <c r="C90" t="s">
-        <v>1221</v>
+        <v>1227</v>
       </c>
       <c r="D90" t="s">
-        <v>1222</v>
+        <v>1228</v>
       </c>
       <c r="E90" t="s">
         <v>17</v>
@@ -42152,10 +42280,10 @@
         <v>97</v>
       </c>
       <c r="C91" t="s">
-        <v>1215</v>
+        <v>1221</v>
       </c>
       <c r="D91" t="s">
-        <v>1216</v>
+        <v>1222</v>
       </c>
       <c r="E91" t="s">
         <v>240</v>
@@ -42190,13 +42318,13 @@
         <v>69</v>
       </c>
       <c r="B92" t="s">
-        <v>1236</v>
+        <v>1242</v>
       </c>
       <c r="C92" t="s">
-        <v>1233</v>
+        <v>1239</v>
       </c>
       <c r="D92" t="s">
-        <v>1234</v>
+        <v>1240</v>
       </c>
       <c r="E92" t="s">
         <v>17</v>
@@ -42234,10 +42362,10 @@
         <v>93</v>
       </c>
       <c r="C93" t="s">
-        <v>1241</v>
+        <v>1247</v>
       </c>
       <c r="D93" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="E93" t="s">
         <v>17</v>
@@ -42275,10 +42403,10 @@
         <v>380</v>
       </c>
       <c r="C94" t="s">
-        <v>1261</v>
+        <v>1267</v>
       </c>
       <c r="D94" t="s">
-        <v>1262</v>
+        <v>1268</v>
       </c>
       <c r="E94" t="s">
         <v>17</v>
@@ -42302,7 +42430,7 @@
         <v>95.01</v>
       </c>
       <c r="L94" t="s">
-        <v>1293</v>
+        <v>1299</v>
       </c>
       <c r="M94">
         <v>300680</v>
@@ -42316,10 +42444,10 @@
         <v>380</v>
       </c>
       <c r="C95" t="s">
-        <v>1253</v>
+        <v>1259</v>
       </c>
       <c r="D95" t="s">
-        <v>1254</v>
+        <v>1260</v>
       </c>
       <c r="E95" t="s">
         <v>179</v>
@@ -42343,7 +42471,7 @@
         <v>93.89</v>
       </c>
       <c r="L95" t="s">
-        <v>1294</v>
+        <v>1300</v>
       </c>
       <c r="M95">
         <v>0</v>
@@ -42357,10 +42485,10 @@
         <v>290</v>
       </c>
       <c r="C96" t="s">
-        <v>1233</v>
+        <v>1239</v>
       </c>
       <c r="D96" t="s">
-        <v>1234</v>
+        <v>1240</v>
       </c>
       <c r="E96" t="s">
         <v>17</v>
@@ -42398,10 +42526,10 @@
         <v>442</v>
       </c>
       <c r="C97" t="s">
-        <v>1265</v>
+        <v>1271</v>
       </c>
       <c r="D97" t="s">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="E97" t="s">
         <v>17</v>
@@ -42439,10 +42567,10 @@
         <v>442</v>
       </c>
       <c r="C98" t="s">
-        <v>1265</v>
+        <v>1271</v>
       </c>
       <c r="D98" t="s">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="E98" t="s">
         <v>194</v>
@@ -42471,13 +42599,13 @@
         <v>53</v>
       </c>
       <c r="B99" t="s">
-        <v>1268</v>
+        <v>1274</v>
       </c>
       <c r="C99" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="D99" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="E99" t="s">
         <v>17</v>
@@ -42501,7 +42629,7 @@
         <v>68.88</v>
       </c>
       <c r="L99" t="s">
-        <v>1291</v>
+        <v>1297</v>
       </c>
       <c r="M99">
         <v>357137</v>
@@ -42515,10 +42643,10 @@
         <v>202</v>
       </c>
       <c r="C100" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="D100" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="E100" t="s">
         <v>17</v>
@@ -42556,10 +42684,10 @@
         <v>93</v>
       </c>
       <c r="C101" t="s">
-        <v>1226</v>
+        <v>1232</v>
       </c>
       <c r="D101" t="s">
-        <v>1227</v>
+        <v>1233</v>
       </c>
       <c r="E101" t="s">
         <v>17</v>
@@ -42597,10 +42725,10 @@
         <v>97</v>
       </c>
       <c r="C102" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="D102" t="s">
-        <v>1214</v>
+        <v>1220</v>
       </c>
       <c r="E102" t="s">
         <v>179</v>
@@ -42638,10 +42766,10 @@
         <v>432</v>
       </c>
       <c r="C103" t="s">
-        <v>1221</v>
+        <v>1227</v>
       </c>
       <c r="D103" t="s">
-        <v>1222</v>
+        <v>1228</v>
       </c>
       <c r="E103" t="s">
         <v>17</v>
@@ -42679,10 +42807,10 @@
         <v>93</v>
       </c>
       <c r="C104" t="s">
-        <v>1239</v>
+        <v>1245</v>
       </c>
       <c r="D104" t="s">
-        <v>1240</v>
+        <v>1246</v>
       </c>
       <c r="E104" t="s">
         <v>45</v>
@@ -42706,7 +42834,7 @@
         <v>36.840000000000003</v>
       </c>
       <c r="L104" t="s">
-        <v>1295</v>
+        <v>1301</v>
       </c>
       <c r="M104">
         <v>0</v>
@@ -42720,10 +42848,10 @@
         <v>442</v>
       </c>
       <c r="C105" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="D105" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="E105" t="s">
         <v>17</v>
@@ -42747,7 +42875,7 @@
         <v>56.82</v>
       </c>
       <c r="L105" t="s">
-        <v>1296</v>
+        <v>1302</v>
       </c>
       <c r="M105">
         <v>0</v>
@@ -42761,10 +42889,10 @@
         <v>93</v>
       </c>
       <c r="C106" t="s">
-        <v>1223</v>
+        <v>1229</v>
       </c>
       <c r="D106" t="s">
-        <v>1224</v>
+        <v>1230</v>
       </c>
       <c r="E106" t="s">
         <v>17</v>
@@ -42802,10 +42930,10 @@
         <v>144</v>
       </c>
       <c r="C107" t="s">
-        <v>1223</v>
+        <v>1229</v>
       </c>
       <c r="D107" t="s">
-        <v>1224</v>
+        <v>1230</v>
       </c>
       <c r="E107" t="s">
         <v>17</v>
@@ -42843,10 +42971,10 @@
         <v>375</v>
       </c>
       <c r="C108" t="s">
-        <v>1297</v>
+        <v>1303</v>
       </c>
       <c r="D108" t="s">
-        <v>1298</v>
+        <v>1304</v>
       </c>
       <c r="E108" t="s">
         <v>17</v>
@@ -42884,10 +43012,10 @@
         <v>375</v>
       </c>
       <c r="C109" t="s">
-        <v>1229</v>
+        <v>1235</v>
       </c>
       <c r="D109" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="E109" t="s">
         <v>179</v>
@@ -42911,7 +43039,7 @@
         <v>141.1</v>
       </c>
       <c r="L109" t="s">
-        <v>1299</v>
+        <v>1305</v>
       </c>
       <c r="M109">
         <v>0</v>
@@ -42925,10 +43053,10 @@
         <v>392</v>
       </c>
       <c r="C110" t="s">
-        <v>1237</v>
+        <v>1243</v>
       </c>
       <c r="D110" t="s">
-        <v>1238</v>
+        <v>1244</v>
       </c>
       <c r="E110" t="s">
         <v>17</v>
@@ -42966,10 +43094,10 @@
         <v>202</v>
       </c>
       <c r="C111" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="D111" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="E111" t="s">
         <v>17</v>
@@ -43058,10 +43186,10 @@
         <v>392</v>
       </c>
       <c r="C2" t="s">
-        <v>1300</v>
+        <v>1306</v>
       </c>
       <c r="D2" t="s">
-        <v>1301</v>
+        <v>1307</v>
       </c>
       <c r="E2" t="s">
         <v>45</v>
@@ -43085,7 +43213,7 @@
         <v>38.53</v>
       </c>
       <c r="L2" t="s">
-        <v>1302</v>
+        <v>1308</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -43099,10 +43227,10 @@
         <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>1303</v>
+        <v>1309</v>
       </c>
       <c r="D3" t="s">
-        <v>1304</v>
+        <v>1310</v>
       </c>
       <c r="E3" t="s">
         <v>45</v>
@@ -43126,7 +43254,7 @@
         <v>56.73</v>
       </c>
       <c r="L3" t="s">
-        <v>1228</v>
+        <v>1234</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -43140,10 +43268,10 @@
         <v>375</v>
       </c>
       <c r="C4" t="s">
-        <v>1305</v>
+        <v>1311</v>
       </c>
       <c r="D4" t="s">
-        <v>1306</v>
+        <v>1312</v>
       </c>
       <c r="E4" t="s">
         <v>45</v>
@@ -43167,201 +43295,10 @@
         <v>52.71</v>
       </c>
       <c r="L4" t="s">
-        <v>1307</v>
+        <v>1313</v>
       </c>
       <c r="M4">
         <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2B00-000000000000}">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1308</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1309</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2">
-        <v>76.269999999999897</v>
-      </c>
-      <c r="G2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2">
-        <v>1.52</v>
-      </c>
-      <c r="K2">
-        <v>115.93</v>
-      </c>
-      <c r="L2" t="s">
-        <v>1310</v>
-      </c>
-      <c r="M2">
-        <v>230400</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1311</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1308</v>
-      </c>
-      <c r="D3" t="s">
-        <v>1309</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3">
-        <v>61.241999999999898</v>
-      </c>
-      <c r="G3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3">
-        <v>1.61</v>
-      </c>
-      <c r="K3">
-        <v>98.6</v>
-      </c>
-      <c r="L3" t="s">
-        <v>510</v>
-      </c>
-      <c r="M3">
-        <v>230990</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1312</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1308</v>
-      </c>
-      <c r="D4" t="s">
-        <v>1309</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4">
-        <v>56.378999999999898</v>
-      </c>
-      <c r="G4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4">
-        <v>1.61</v>
-      </c>
-      <c r="K4">
-        <v>90.77</v>
-      </c>
-      <c r="L4" t="s">
-        <v>1313</v>
-      </c>
-      <c r="M4">
-        <v>231530</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1311</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1308</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1309</v>
-      </c>
-      <c r="E5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5">
-        <v>55.5489999999999</v>
-      </c>
-      <c r="G5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5">
-        <v>1.62</v>
-      </c>
-      <c r="K5">
-        <v>89.99</v>
-      </c>
-      <c r="L5" t="s">
-        <v>1108</v>
-      </c>
-      <c r="M5">
-        <v>232010</v>
       </c>
     </row>
   </sheetData>
@@ -43373,21 +43310,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.28515625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">

--- a/A_FINAL_RESULT/eko_transactions.xlsx
+++ b/A_FINAL_RESULT/eko_transactions.xlsx
@@ -568,10 +568,10 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -580,7 +580,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>138.58</v>
+        <v>135.3</v>
       </c>
       <c r="M2" t="n">
         <v>1.69</v>
@@ -628,10 +628,10 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -640,7 +640,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>28.04</v>
+        <v>27.38</v>
       </c>
       <c r="M3" t="n">
         <v>1.69</v>
@@ -688,19 +688,19 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="L4" t="n">
-        <v>43.44</v>
+        <v>42.42</v>
       </c>
       <c r="M4" t="n">
         <v>1.7</v>
@@ -748,19 +748,19 @@
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="L5" t="n">
-        <v>39.99</v>
+        <v>39.06</v>
       </c>
       <c r="M5" t="n">
         <v>1.72</v>
@@ -808,19 +808,19 @@
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>-0.26</v>
       </c>
       <c r="L6" t="n">
-        <v>46.46</v>
+        <v>45.4</v>
       </c>
       <c r="M6" t="n">
         <v>1.76</v>
@@ -876,9 +876,7 @@
       <c r="J7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
         <v>100.56</v>
       </c>
@@ -928,19 +926,19 @@
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="L8" t="n">
-        <v>119.72</v>
+        <v>121.12</v>
       </c>
       <c r="M8" t="n">
         <v>1.77</v>
@@ -1093,7 +1091,7 @@
         <v>0.03</v>
       </c>
       <c r="K2" t="n">
-        <v>2.32</v>
+        <v>0.87</v>
       </c>
       <c r="L2" t="n">
         <v>41.49</v>
@@ -1153,7 +1151,7 @@
         <v>0.03</v>
       </c>
       <c r="K3" t="n">
-        <v>1.27</v>
+        <v>0.48</v>
       </c>
       <c r="L3" t="n">
         <v>22.74</v>
@@ -1213,7 +1211,7 @@
         <v>0.03</v>
       </c>
       <c r="K4" t="n">
-        <v>1.54</v>
+        <v>0.66</v>
       </c>
       <c r="L4" t="n">
         <v>31.45</v>
@@ -1273,7 +1271,7 @@
         <v>0.03</v>
       </c>
       <c r="K5" t="n">
-        <v>0.88</v>
+        <v>0.38</v>
       </c>
       <c r="L5" t="n">
         <v>18.15</v>
@@ -1333,7 +1331,7 @@
         <v>0.03</v>
       </c>
       <c r="K6" t="n">
-        <v>1.82</v>
+        <v>0.68</v>
       </c>
       <c r="L6" t="n">
         <v>32.82</v>
@@ -1489,7 +1487,7 @@
         <v>0.09</v>
       </c>
       <c r="K2" t="n">
-        <v>13.86</v>
+        <v>5.94</v>
       </c>
       <c r="L2" t="n">
         <v>119.46</v>
@@ -1644,9 +1642,7 @@
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
         <v>42.23</v>
       </c>
@@ -1704,9 +1700,7 @@
       <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
         <v>57.8</v>
       </c>
@@ -1764,9 +1758,7 @@
       <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
         <v>22.39</v>
       </c>
@@ -1824,9 +1816,7 @@
       <c r="J5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
         <v>62.81</v>
       </c>
@@ -1884,9 +1874,7 @@
       <c r="J6" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
         <v>34.31</v>
       </c>
@@ -1944,9 +1932,7 @@
       <c r="J7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
         <v>28.62</v>
       </c>
@@ -2004,9 +1990,7 @@
       <c r="J8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
         <v>68.18000000000001</v>
       </c>
@@ -2064,9 +2048,7 @@
       <c r="J9" t="n">
         <v>0</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
         <v>29.6</v>
       </c>
@@ -2125,7 +2107,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>84.09</v>
@@ -2185,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>74.7</v>
@@ -2245,7 +2227,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.93</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>40.04</v>
@@ -2305,7 +2287,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>76.26000000000001</v>
@@ -2364,9 +2346,7 @@
       <c r="J14" t="n">
         <v>0</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
         <v>30.33</v>
       </c>
@@ -2425,7 +2405,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>39.64</v>
@@ -2484,9 +2464,7 @@
       <c r="J16" t="n">
         <v>0</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
         <v>4.34</v>
       </c>
@@ -2545,7 +2523,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>35.42</v>
@@ -2605,7 +2583,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>14.34</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>86.56</v>
@@ -2664,9 +2642,7 @@
       <c r="J19" t="n">
         <v>0</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
         <v>10.82</v>
       </c>
@@ -2725,7 +2701,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>90.7</v>
@@ -2785,7 +2761,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>82.83</v>
@@ -2941,7 +2917,7 @@
         <v>0.01</v>
       </c>
       <c r="K2" t="n">
-        <v>14.1</v>
+        <v>4.7</v>
       </c>
       <c r="L2" t="n">
         <v>780.2</v>
@@ -3001,7 +2977,7 @@
         <v>0.01</v>
       </c>
       <c r="K3" t="n">
-        <v>22.67</v>
+        <v>3.78</v>
       </c>
       <c r="L3" t="n">
         <v>627.2</v>
@@ -3181,7 +3157,7 @@
         <v>0.02</v>
       </c>
       <c r="K6" t="n">
-        <v>14.4</v>
+        <v>7.2</v>
       </c>
       <c r="L6" t="n">
         <v>622.84</v>
@@ -3241,7 +3217,7 @@
         <v>0.02</v>
       </c>
       <c r="K7" t="n">
-        <v>3.31</v>
+        <v>1.1</v>
       </c>
       <c r="L7" t="n">
         <v>95.52</v>
@@ -3301,7 +3277,7 @@
         <v>0.02</v>
       </c>
       <c r="K8" t="n">
-        <v>13.42</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="L8" t="n">
         <v>787.34</v>
@@ -3361,7 +3337,7 @@
         <v>0.02</v>
       </c>
       <c r="K9" t="n">
-        <v>11.51</v>
+        <v>7.68</v>
       </c>
       <c r="L9" t="n">
         <v>675.49</v>
@@ -3516,9 +3492,7 @@
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
         <v>55.7</v>
       </c>
@@ -3576,9 +3550,7 @@
       <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
         <v>13.28</v>
       </c>
@@ -3636,9 +3608,7 @@
       <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
         <v>128.74</v>
       </c>
@@ -3696,9 +3666,7 @@
       <c r="J5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
         <v>23.79</v>
       </c>
@@ -3756,9 +3724,7 @@
       <c r="J6" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
         <v>9.49</v>
       </c>
@@ -3816,9 +3782,7 @@
       <c r="J7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
         <v>138.34</v>
       </c>
@@ -3876,9 +3840,7 @@
       <c r="J8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
         <v>9.49</v>
       </c>
@@ -3936,9 +3898,7 @@
       <c r="J9" t="n">
         <v>0</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
         <v>118.94</v>
       </c>
@@ -3996,9 +3956,7 @@
       <c r="J10" t="n">
         <v>0</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
         <v>77.45999999999999</v>
       </c>
@@ -4056,9 +4014,7 @@
       <c r="J11" t="n">
         <v>0</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
         <v>118.61</v>
       </c>
@@ -4116,9 +4072,7 @@
       <c r="J12" t="n">
         <v>0</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
         <v>78.26000000000001</v>
       </c>
@@ -4273,7 +4227,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>37.03</v>
@@ -4333,7 +4287,7 @@
         <v>0.03</v>
       </c>
       <c r="K3" t="n">
-        <v>3.66</v>
+        <v>1.57</v>
       </c>
       <c r="L3" t="n">
         <v>74.67</v>
@@ -4393,7 +4347,7 @@
         <v>0.03</v>
       </c>
       <c r="K4" t="n">
-        <v>2.25</v>
+        <v>0.75</v>
       </c>
       <c r="L4" t="n">
         <v>35.78</v>
@@ -4453,7 +4407,7 @@
         <v>0.03</v>
       </c>
       <c r="K5" t="n">
-        <v>1.67</v>
+        <v>0.55</v>
       </c>
       <c r="L5" t="n">
         <v>26.46</v>
@@ -4513,7 +4467,7 @@
         <v>0.03</v>
       </c>
       <c r="K6" t="n">
-        <v>2.01</v>
+        <v>0.86</v>
       </c>
       <c r="L6" t="n">
         <v>41.33</v>
@@ -4669,7 +4623,7 @@
         <v>0.01</v>
       </c>
       <c r="K2" t="n">
-        <v>3.16</v>
+        <v>0.45</v>
       </c>
       <c r="L2" t="n">
         <v>76.37</v>
@@ -4729,7 +4683,7 @@
         <v>0.01</v>
       </c>
       <c r="K3" t="n">
-        <v>10.78</v>
+        <v>1.54</v>
       </c>
       <c r="L3" t="n">
         <v>260.37</v>
@@ -4789,7 +4743,7 @@
         <v>0.01</v>
       </c>
       <c r="K4" t="n">
-        <v>3.36</v>
+        <v>0.48</v>
       </c>
       <c r="L4" t="n">
         <v>81.12</v>
@@ -4849,7 +4803,7 @@
         <v>0.01</v>
       </c>
       <c r="K5" t="n">
-        <v>3.78</v>
+        <v>0.54</v>
       </c>
       <c r="L5" t="n">
         <v>91.26000000000001</v>
@@ -5005,7 +4959,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>20.51</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>676.75</v>
@@ -5065,7 +5019,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>36.05</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>849.8</v>
@@ -5125,7 +5079,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>27.24</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>641.98</v>
@@ -5185,7 +5139,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>47.6</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>1122.05</v>
@@ -5245,7 +5199,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>660.02</v>
@@ -5400,9 +5354,7 @@
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
         <v>341.72</v>
       </c>
@@ -5460,9 +5412,7 @@
       <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
         <v>340.02</v>
       </c>
@@ -5520,9 +5470,7 @@
       <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
         <v>173</v>
       </c>
@@ -5580,9 +5528,7 @@
       <c r="J5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
         <v>256.66</v>
       </c>
@@ -5641,7 +5587,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>215.07</v>
@@ -5701,7 +5647,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>8.43</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>362.58</v>
@@ -5761,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>7.21</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>248.09</v>
@@ -5821,7 +5767,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>12.36</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>352.26</v>
@@ -5881,7 +5827,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>13.2</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>376.2</v>
@@ -5941,7 +5887,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>295.8</v>
@@ -6001,7 +5947,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>200.1</v>
@@ -6156,9 +6102,7 @@
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
         <v>96.98</v>
       </c>
@@ -6373,7 +6317,7 @@
         <v>0.04</v>
       </c>
       <c r="K3" t="n">
-        <v>4.83</v>
+        <v>3.22</v>
       </c>
       <c r="L3" t="n">
         <v>116.02</v>
@@ -6529,7 +6473,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>37.26</v>
@@ -6589,7 +6533,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>33.99</v>
@@ -6649,7 +6593,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>67.92</v>
@@ -6709,7 +6653,7 @@
         <v>0.01</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3</v>
+        <v>0.43</v>
       </c>
       <c r="L5" t="n">
         <v>74.91</v>
@@ -6769,7 +6713,7 @@
         <v>0.02</v>
       </c>
       <c r="K6" t="n">
-        <v>0.92</v>
+        <v>0.46</v>
       </c>
       <c r="L6" t="n">
         <v>39.68</v>
@@ -6829,7 +6773,7 @@
         <v>0.02</v>
       </c>
       <c r="K7" t="n">
-        <v>1.36</v>
+        <v>0.91</v>
       </c>
       <c r="L7" t="n">
         <v>79.65000000000001</v>
@@ -6889,7 +6833,7 @@
         <v>0.02</v>
       </c>
       <c r="K8" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="L8" t="n">
         <v>96.93000000000001</v>
@@ -7044,9 +6988,7 @@
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
         <v>60.17</v>
       </c>
@@ -7104,9 +7046,7 @@
       <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
         <v>4.34</v>
       </c>
@@ -7164,9 +7104,7 @@
       <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
         <v>49.21</v>
       </c>
@@ -7224,9 +7162,7 @@
       <c r="J5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
         <v>63.15</v>
       </c>
@@ -7284,9 +7220,7 @@
       <c r="J6" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
         <v>69.91</v>
       </c>
@@ -7440,9 +7374,7 @@
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
         <v>51.83</v>
       </c>
@@ -7500,9 +7432,7 @@
       <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
         <v>18.4</v>
       </c>
@@ -7561,7 +7491,7 @@
         <v>0.03</v>
       </c>
       <c r="K4" t="n">
-        <v>2.09</v>
+        <v>0.89</v>
       </c>
       <c r="L4" t="n">
         <v>42.66</v>
@@ -7621,7 +7551,7 @@
         <v>0.03</v>
       </c>
       <c r="K5" t="n">
-        <v>1.39</v>
+        <v>0.52</v>
       </c>
       <c r="L5" t="n">
         <v>24.85</v>
@@ -7681,7 +7611,7 @@
         <v>0.03</v>
       </c>
       <c r="K6" t="n">
-        <v>2.48</v>
+        <v>1.06</v>
       </c>
       <c r="L6" t="n">
         <v>50.94</v>
@@ -7837,7 +7767,7 @@
         <v>0.03</v>
       </c>
       <c r="K2" t="n">
-        <v>1.98</v>
+        <v>1.19</v>
       </c>
       <c r="L2" t="n">
         <v>56.76</v>
@@ -7897,7 +7827,7 @@
         <v>0.01</v>
       </c>
       <c r="K3" t="n">
-        <v>1.93</v>
+        <v>0.48</v>
       </c>
       <c r="L3" t="n">
         <v>83.53</v>
@@ -8053,7 +7983,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>80.62</v>
@@ -8113,7 +8043,7 @@
         <v>0.01</v>
       </c>
       <c r="K3" t="n">
-        <v>2.11</v>
+        <v>0.7</v>
       </c>
       <c r="L3" t="n">
         <v>121.44</v>
@@ -8269,7 +8199,7 @@
         <v>0.01</v>
       </c>
       <c r="K2" t="n">
-        <v>1.03</v>
+        <v>0.34</v>
       </c>
       <c r="L2" t="n">
         <v>59.25</v>
@@ -8425,7 +8355,7 @@
         <v>0.03</v>
       </c>
       <c r="K2" t="n">
-        <v>3.17</v>
+        <v>1.36</v>
       </c>
       <c r="L2" t="n">
         <v>64.81</v>
@@ -8485,7 +8415,7 @@
         <v>0.03</v>
       </c>
       <c r="K3" t="n">
-        <v>2.22</v>
+        <v>0.95</v>
       </c>
       <c r="L3" t="n">
         <v>45.68</v>
@@ -8544,9 +8474,7 @@
       <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
         <v>4.34</v>
       </c>
@@ -8605,7 +8533,7 @@
         <v>0.03</v>
       </c>
       <c r="K5" t="n">
-        <v>3.84</v>
+        <v>1.65</v>
       </c>
       <c r="L5" t="n">
         <v>79.09</v>
@@ -8761,7 +8689,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>49.5</v>
@@ -8821,7 +8749,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>89.38</v>
@@ -8881,7 +8809,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>32.41</v>
@@ -8941,7 +8869,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>10.01</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>235.95</v>
@@ -9001,7 +8929,7 @@
         <v>0.03</v>
       </c>
       <c r="K6" t="n">
-        <v>0.58</v>
+        <v>0.25</v>
       </c>
       <c r="L6" t="n">
         <v>11.85</v>
@@ -9061,7 +8989,7 @@
         <v>0.01</v>
       </c>
       <c r="K7" t="n">
-        <v>1.31</v>
+        <v>0.44</v>
       </c>
       <c r="L7" t="n">
         <v>75.5</v>
@@ -9121,7 +9049,7 @@
         <v>0.03</v>
       </c>
       <c r="K8" t="n">
-        <v>0.68</v>
+        <v>0.29</v>
       </c>
       <c r="L8" t="n">
         <v>13.85</v>
@@ -9181,7 +9109,7 @@
         <v>0.01</v>
       </c>
       <c r="K9" t="n">
-        <v>1.48</v>
+        <v>0.49</v>
       </c>
       <c r="L9" t="n">
         <v>85.29000000000001</v>
@@ -9241,7 +9169,7 @@
         <v>0.01</v>
       </c>
       <c r="K10" t="n">
-        <v>1.88</v>
+        <v>0.63</v>
       </c>
       <c r="L10" t="n">
         <v>108.56</v>
@@ -9301,7 +9229,7 @@
         <v>0.01</v>
       </c>
       <c r="K11" t="n">
-        <v>1.37</v>
+        <v>0.46</v>
       </c>
       <c r="L11" t="n">
         <v>79.03</v>
@@ -9361,7 +9289,7 @@
         <v>0.01</v>
       </c>
       <c r="K12" t="n">
-        <v>1.49</v>
+        <v>0.5</v>
       </c>
       <c r="L12" t="n">
         <v>85.79000000000001</v>
@@ -9420,9 +9348,7 @@
       <c r="J13" t="n">
         <v>0</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
         <v>9.49</v>
       </c>
@@ -9481,7 +9407,7 @@
         <v>0.01</v>
       </c>
       <c r="K14" t="n">
-        <v>1.21</v>
+        <v>0.4</v>
       </c>
       <c r="L14" t="n">
         <v>69.79000000000001</v>
@@ -9541,7 +9467,7 @@
         <v>0.01</v>
       </c>
       <c r="K15" t="n">
-        <v>0.86</v>
+        <v>0.43</v>
       </c>
       <c r="L15" t="n">
         <v>74.39</v>
@@ -9601,7 +9527,7 @@
         <v>0.01</v>
       </c>
       <c r="K16" t="n">
-        <v>1.62</v>
+        <v>0.54</v>
       </c>
       <c r="L16" t="n">
         <v>93.68000000000001</v>
@@ -9661,7 +9587,7 @@
         <v>0.01</v>
       </c>
       <c r="K17" t="n">
-        <v>1.29</v>
+        <v>0.43</v>
       </c>
       <c r="L17" t="n">
         <v>74.39</v>
@@ -9721,7 +9647,7 @@
         <v>0.01</v>
       </c>
       <c r="K18" t="n">
-        <v>1.62</v>
+        <v>0.54</v>
       </c>
       <c r="L18" t="n">
         <v>93.42</v>
@@ -9781,7 +9707,7 @@
         <v>0.01</v>
       </c>
       <c r="K19" t="n">
-        <v>1.02</v>
+        <v>0.34</v>
       </c>
       <c r="L19" t="n">
         <v>58.78</v>
@@ -9841,7 +9767,7 @@
         <v>0.01</v>
       </c>
       <c r="K20" t="n">
-        <v>1.02</v>
+        <v>0.34</v>
       </c>
       <c r="L20" t="n">
         <v>58.82</v>
@@ -9901,7 +9827,7 @@
         <v>0.01</v>
       </c>
       <c r="K21" t="n">
-        <v>1.85</v>
+        <v>0.46</v>
       </c>
       <c r="L21" t="n">
         <v>79.87</v>
@@ -9961,7 +9887,7 @@
         <v>0.01</v>
       </c>
       <c r="K22" t="n">
-        <v>1.58</v>
+        <v>0.4</v>
       </c>
       <c r="L22" t="n">
         <v>68.34999999999999</v>
@@ -10021,7 +9947,7 @@
         <v>0.01</v>
       </c>
       <c r="K23" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="L23" t="n">
         <v>51.9</v>
@@ -10081,7 +10007,7 @@
         <v>0.01</v>
       </c>
       <c r="K24" t="n">
-        <v>1.8</v>
+        <v>0.45</v>
       </c>
       <c r="L24" t="n">
         <v>77.84999999999999</v>
@@ -10141,7 +10067,7 @@
         <v>0.03</v>
       </c>
       <c r="K25" t="n">
-        <v>0.43</v>
+        <v>0.18</v>
       </c>
       <c r="L25" t="n">
         <v>8.69</v>
@@ -10201,7 +10127,7 @@
         <v>0.01</v>
       </c>
       <c r="K26" t="n">
-        <v>2.21</v>
+        <v>0.55</v>
       </c>
       <c r="L26" t="n">
         <v>95.53</v>
@@ -10261,7 +10187,7 @@
         <v>0.02</v>
       </c>
       <c r="K27" t="n">
-        <v>1.47</v>
+        <v>0.74</v>
       </c>
       <c r="L27" t="n">
         <v>63.65</v>
@@ -10321,7 +10247,7 @@
         <v>0.02</v>
       </c>
       <c r="K28" t="n">
-        <v>2.01</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
         <v>86.84</v>
@@ -10381,7 +10307,7 @@
         <v>0.02</v>
       </c>
       <c r="K29" t="n">
-        <v>2.37</v>
+        <v>1.19</v>
       </c>
       <c r="L29" t="n">
         <v>102.59</v>
@@ -10441,7 +10367,7 @@
         <v>0.02</v>
       </c>
       <c r="K30" t="n">
-        <v>1.93</v>
+        <v>0.96</v>
       </c>
       <c r="L30" t="n">
         <v>83.26000000000001</v>
@@ -10501,7 +10427,7 @@
         <v>0.02</v>
       </c>
       <c r="K31" t="n">
-        <v>1.42</v>
+        <v>0.71</v>
       </c>
       <c r="L31" t="n">
         <v>61.57</v>
@@ -10561,7 +10487,7 @@
         <v>0.02</v>
       </c>
       <c r="K32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
         <v>86.38</v>
@@ -10621,7 +10547,7 @@
         <v>0.02</v>
       </c>
       <c r="K33" t="n">
-        <v>1.62</v>
+        <v>1.08</v>
       </c>
       <c r="L33" t="n">
         <v>95.04000000000001</v>
@@ -10681,7 +10607,7 @@
         <v>0.03</v>
       </c>
       <c r="K34" t="n">
-        <v>0.6</v>
+        <v>0.26</v>
       </c>
       <c r="L34" t="n">
         <v>12.4</v>
@@ -10740,9 +10666,7 @@
       <c r="J35" t="n">
         <v>0</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
         <v>49.08</v>
       </c>
@@ -10801,7 +10725,7 @@
         <v>0.02</v>
       </c>
       <c r="K36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
         <v>88</v>
@@ -10861,7 +10785,7 @@
         <v>0.02</v>
       </c>
       <c r="K37" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="L37" t="n">
         <v>70.23999999999999</v>
@@ -10921,7 +10845,7 @@
         <v>0.02</v>
       </c>
       <c r="K38" t="n">
-        <v>2.11</v>
+        <v>1.06</v>
       </c>
       <c r="L38" t="n">
         <v>93.02</v>
@@ -10980,9 +10904,7 @@
       <c r="J39" t="n">
         <v>0</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="n">
         <v>17.71</v>
       </c>
@@ -11137,7 +11059,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>58.53</v>
@@ -11197,7 +11119,7 @@
         <v>0.03</v>
       </c>
       <c r="K3" t="n">
-        <v>2.44</v>
+        <v>0.92</v>
       </c>
       <c r="L3" t="n">
         <v>43.62</v>
@@ -11257,7 +11179,7 @@
         <v>0.01</v>
       </c>
       <c r="K4" t="n">
-        <v>0.45</v>
+        <v>0.11</v>
       </c>
       <c r="L4" t="n">
         <v>19.55</v>
@@ -11317,7 +11239,7 @@
         <v>0.02</v>
       </c>
       <c r="K5" t="n">
-        <v>1.66</v>
+        <v>0.83</v>
       </c>
       <c r="L5" t="n">
         <v>71.73999999999999</v>
@@ -11377,7 +11299,7 @@
         <v>0.02</v>
       </c>
       <c r="K6" t="n">
-        <v>1.53</v>
+        <v>0.44</v>
       </c>
       <c r="L6" t="n">
         <v>37.94</v>
@@ -11437,7 +11359,7 @@
         <v>0.02</v>
       </c>
       <c r="K7" t="n">
-        <v>2.22</v>
+        <v>1.11</v>
       </c>
       <c r="L7" t="n">
         <v>97.79000000000001</v>
@@ -11497,7 +11419,7 @@
         <v>0.02</v>
       </c>
       <c r="K8" t="n">
-        <v>2.88</v>
+        <v>1.44</v>
       </c>
       <c r="L8" t="n">
         <v>126.72</v>
@@ -11557,7 +11479,7 @@
         <v>0.02</v>
       </c>
       <c r="K9" t="n">
-        <v>0.77</v>
+        <v>0.31</v>
       </c>
       <c r="L9" t="n">
         <v>27.25</v>
@@ -11712,9 +11634,7 @@
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
         <v>57.46</v>
       </c>
@@ -11772,9 +11692,7 @@
       <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
         <v>64.7</v>
       </c>
@@ -11832,9 +11750,7 @@
       <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
         <v>96.34999999999999</v>
       </c>
@@ -11892,9 +11808,7 @@
       <c r="J5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
         <v>83.67</v>
       </c>
@@ -11952,9 +11866,7 @@
       <c r="J6" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
         <v>91.53</v>
       </c>
@@ -12012,9 +11924,7 @@
       <c r="J7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
         <v>37.4</v>
       </c>
@@ -12072,9 +11982,7 @@
       <c r="J8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
         <v>41.54</v>
       </c>
@@ -12132,9 +12040,7 @@
       <c r="J9" t="n">
         <v>0</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
         <v>43</v>
       </c>
@@ -12192,9 +12098,7 @@
       <c r="J10" t="n">
         <v>0</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
         <v>80.65000000000001</v>
       </c>
@@ -12252,9 +12156,7 @@
       <c r="J11" t="n">
         <v>0</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
         <v>29.92</v>
       </c>
@@ -12312,9 +12214,7 @@
       <c r="J12" t="n">
         <v>0</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
         <v>57</v>
       </c>
@@ -12372,9 +12272,7 @@
       <c r="J13" t="n">
         <v>0</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
         <v>42.01</v>
       </c>
@@ -12432,9 +12330,7 @@
       <c r="J14" t="n">
         <v>0</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
         <v>109.12</v>
       </c>
@@ -12492,9 +12388,7 @@
       <c r="J15" t="n">
         <v>0</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
         <v>45</v>
       </c>
@@ -12553,7 +12447,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>30.78</v>
@@ -12613,7 +12507,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>85.31999999999999</v>
@@ -12673,7 +12567,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>90.98999999999999</v>
@@ -12733,7 +12627,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>43.71</v>
@@ -12793,7 +12687,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>61.56</v>
@@ -12853,7 +12747,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>42.33</v>
@@ -12913,7 +12807,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>87</v>
@@ -12973,7 +12867,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>87</v>
@@ -13033,7 +12927,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>69.59999999999999</v>
@@ -13189,7 +13083,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>80.37</v>
@@ -13249,7 +13143,7 @@
         <v>0.02</v>
       </c>
       <c r="K3" t="n">
-        <v>0.85</v>
+        <v>0.21</v>
       </c>
       <c r="L3" t="n">
         <v>15.14</v>
@@ -13309,7 +13203,7 @@
         <v>0.01</v>
       </c>
       <c r="K4" t="n">
-        <v>2.84</v>
+        <v>0.57</v>
       </c>
       <c r="L4" t="n">
         <v>97.15000000000001</v>
@@ -13369,7 +13263,7 @@
         <v>0.01</v>
       </c>
       <c r="K5" t="n">
-        <v>1.37</v>
+        <v>0.46</v>
       </c>
       <c r="L5" t="n">
         <v>78.81999999999999</v>
@@ -13429,7 +13323,7 @@
         <v>0.01</v>
       </c>
       <c r="K6" t="n">
-        <v>1.96</v>
+        <v>0.49</v>
       </c>
       <c r="L6" t="n">
         <v>84.65000000000001</v>
@@ -13489,7 +13383,7 @@
         <v>0.02</v>
       </c>
       <c r="K7" t="n">
-        <v>2.28</v>
+        <v>1.14</v>
       </c>
       <c r="L7" t="n">
         <v>98.72</v>
@@ -13549,7 +13443,7 @@
         <v>0.02</v>
       </c>
       <c r="K8" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="L8" t="n">
         <v>29.32</v>
@@ -13765,7 +13659,7 @@
         <v>0.04</v>
       </c>
       <c r="K3" t="n">
-        <v>2.21</v>
+        <v>1.47</v>
       </c>
       <c r="L3" t="n">
         <v>53.01</v>
@@ -13825,7 +13719,7 @@
         <v>0.04</v>
       </c>
       <c r="K4" t="n">
-        <v>2.16</v>
+        <v>1.44</v>
       </c>
       <c r="L4" t="n">
         <v>51.87</v>
@@ -13885,7 +13779,7 @@
         <v>0.04</v>
       </c>
       <c r="K5" t="n">
-        <v>4.09</v>
+        <v>2.73</v>
       </c>
       <c r="L5" t="n">
         <v>98.91</v>
@@ -14041,7 +13935,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>66</v>
@@ -14101,7 +13995,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>97.28</v>
@@ -14161,7 +14055,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>160.14</v>
@@ -14221,7 +14115,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>51.28</v>
@@ -14281,7 +14175,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>93.08</v>
@@ -14341,7 +14235,7 @@
         <v>0.01</v>
       </c>
       <c r="K7" t="n">
-        <v>2.37</v>
+        <v>0.47</v>
       </c>
       <c r="L7" t="n">
         <v>80.04000000000001</v>
@@ -14401,7 +14295,7 @@
         <v>0.03</v>
       </c>
       <c r="K8" t="n">
-        <v>2.11</v>
+        <v>0.91</v>
       </c>
       <c r="L8" t="n">
         <v>43.18</v>
@@ -14521,7 +14415,7 @@
         <v>0.03</v>
       </c>
       <c r="K10" t="n">
-        <v>2.04</v>
+        <v>0.87</v>
       </c>
       <c r="L10" t="n">
         <v>41.58</v>
@@ -14581,7 +14475,7 @@
         <v>0.01</v>
       </c>
       <c r="K11" t="n">
-        <v>1.7</v>
+        <v>0.57</v>
       </c>
       <c r="L11" t="n">
         <v>98.09</v>
@@ -14641,7 +14535,7 @@
         <v>0.01</v>
       </c>
       <c r="K12" t="n">
-        <v>3.85</v>
+        <v>1.28</v>
       </c>
       <c r="L12" t="n">
         <v>221.94</v>
@@ -14701,7 +14595,7 @@
         <v>0.01</v>
       </c>
       <c r="K13" t="n">
-        <v>1.41</v>
+        <v>0.47</v>
       </c>
       <c r="L13" t="n">
         <v>81.48999999999999</v>
@@ -14761,7 +14655,7 @@
         <v>0.01</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>173</v>
@@ -14821,7 +14715,7 @@
         <v>0.01</v>
       </c>
       <c r="K15" t="n">
-        <v>1.02</v>
+        <v>0.34</v>
       </c>
       <c r="L15" t="n">
         <v>58.98</v>
@@ -14881,7 +14775,7 @@
         <v>0.01</v>
       </c>
       <c r="K16" t="n">
-        <v>2.36</v>
+        <v>0.79</v>
       </c>
       <c r="L16" t="n">
         <v>136.08</v>
@@ -14941,7 +14835,7 @@
         <v>0.01</v>
       </c>
       <c r="K17" t="n">
-        <v>2.56</v>
+        <v>0.64</v>
       </c>
       <c r="L17" t="n">
         <v>110.72</v>
@@ -15001,7 +14895,7 @@
         <v>0.03</v>
       </c>
       <c r="K18" t="n">
-        <v>1.46</v>
+        <v>0.63</v>
       </c>
       <c r="L18" t="n">
         <v>29.85</v>
@@ -15061,7 +14955,7 @@
         <v>0.01</v>
       </c>
       <c r="K19" t="n">
-        <v>2.41</v>
+        <v>0.6</v>
       </c>
       <c r="L19" t="n">
         <v>104.07</v>
@@ -15121,7 +15015,7 @@
         <v>0.01</v>
       </c>
       <c r="K20" t="n">
-        <v>2.04</v>
+        <v>0.51</v>
       </c>
       <c r="L20" t="n">
         <v>88.12</v>
@@ -15181,7 +15075,7 @@
         <v>0.02</v>
       </c>
       <c r="K21" t="n">
-        <v>4.7</v>
+        <v>2.35</v>
       </c>
       <c r="L21" t="n">
         <v>203.17</v>
@@ -15241,7 +15135,7 @@
         <v>0.02</v>
       </c>
       <c r="K22" t="n">
-        <v>3.17</v>
+        <v>1.59</v>
       </c>
       <c r="L22" t="n">
         <v>137.17</v>
@@ -15301,7 +15195,7 @@
         <v>0.03</v>
       </c>
       <c r="K23" t="n">
-        <v>0.71</v>
+        <v>0.3</v>
       </c>
       <c r="L23" t="n">
         <v>14.47</v>
@@ -15361,7 +15255,7 @@
         <v>0.02</v>
       </c>
       <c r="K24" t="n">
-        <v>2.44</v>
+        <v>1.22</v>
       </c>
       <c r="L24" t="n">
         <v>105.37</v>
@@ -15421,7 +15315,7 @@
         <v>0.02</v>
       </c>
       <c r="K25" t="n">
-        <v>1.01</v>
+        <v>0.67</v>
       </c>
       <c r="L25" t="n">
         <v>59.06</v>
@@ -15481,7 +15375,7 @@
         <v>0.03</v>
       </c>
       <c r="K26" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="L26" t="n">
         <v>57.6</v>
@@ -15541,7 +15435,7 @@
         <v>0.02</v>
       </c>
       <c r="K27" t="n">
-        <v>1.86</v>
+        <v>1.24</v>
       </c>
       <c r="L27" t="n">
         <v>109.27</v>
@@ -15601,7 +15495,7 @@
         <v>0.03</v>
       </c>
       <c r="K28" t="n">
-        <v>3.46</v>
+        <v>1.48</v>
       </c>
       <c r="L28" t="n">
         <v>71.12</v>
@@ -15661,7 +15555,7 @@
         <v>0.02</v>
       </c>
       <c r="K29" t="n">
-        <v>2.2</v>
+        <v>1.46</v>
       </c>
       <c r="L29" t="n">
         <v>128.83</v>
@@ -15721,7 +15615,7 @@
         <v>0.02</v>
       </c>
       <c r="K30" t="n">
-        <v>3.07</v>
+        <v>2.04</v>
       </c>
       <c r="L30" t="n">
         <v>179.82</v>
@@ -15781,7 +15675,7 @@
         <v>0.02</v>
       </c>
       <c r="K31" t="n">
-        <v>2.94</v>
+        <v>1.96</v>
       </c>
       <c r="L31" t="n">
         <v>172.19</v>
@@ -15841,7 +15735,7 @@
         <v>0.02</v>
       </c>
       <c r="K32" t="n">
-        <v>1.21</v>
+        <v>0.8</v>
       </c>
       <c r="L32" t="n">
         <v>70.8</v>
@@ -15997,7 +15891,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>106.54</v>
@@ -16153,7 +16047,7 @@
         <v>0.03</v>
       </c>
       <c r="K2" t="n">
-        <v>1.65</v>
+        <v>0.83</v>
       </c>
       <c r="L2" t="n">
         <v>39.44</v>
@@ -16212,9 +16106,7 @@
       <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
         <v>11.94</v>
       </c>
@@ -16273,7 +16165,7 @@
         <v>0.03</v>
       </c>
       <c r="K4" t="n">
-        <v>1.05</v>
+        <v>0.63</v>
       </c>
       <c r="L4" t="n">
         <v>30.03</v>
@@ -16333,7 +16225,7 @@
         <v>0.03</v>
       </c>
       <c r="K5" t="n">
-        <v>1.78</v>
+        <v>1.07</v>
       </c>
       <c r="L5" t="n">
         <v>50.83</v>
@@ -16393,7 +16285,7 @@
         <v>0.03</v>
       </c>
       <c r="K6" t="n">
-        <v>1.91</v>
+        <v>0.72</v>
       </c>
       <c r="L6" t="n">
         <v>34.13</v>
@@ -16453,7 +16345,7 @@
         <v>0.03</v>
       </c>
       <c r="K7" t="n">
-        <v>2.23</v>
+        <v>0.84</v>
       </c>
       <c r="L7" t="n">
         <v>39.9</v>
@@ -16513,7 +16405,7 @@
         <v>0.03</v>
       </c>
       <c r="K8" t="n">
-        <v>2.33</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>47.67</v>
@@ -16573,7 +16465,7 @@
         <v>0.03</v>
       </c>
       <c r="K9" t="n">
-        <v>2.01</v>
+        <v>0.86</v>
       </c>
       <c r="L9" t="n">
         <v>41.09</v>
@@ -16633,7 +16525,7 @@
         <v>0.03</v>
       </c>
       <c r="K10" t="n">
-        <v>1.06</v>
+        <v>0.4</v>
       </c>
       <c r="L10" t="n">
         <v>18.93</v>
@@ -16693,7 +16585,7 @@
         <v>0.09</v>
       </c>
       <c r="K11" t="n">
-        <v>11.66</v>
+        <v>5.25</v>
       </c>
       <c r="L11" t="n">
         <v>107.83</v>
@@ -16848,9 +16740,7 @@
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
         <v>38</v>
       </c>
@@ -16908,9 +16798,7 @@
       <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
         <v>29.92</v>
       </c>
@@ -16968,9 +16856,7 @@
       <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
         <v>40.83</v>
       </c>
@@ -17029,7 +16915,7 @@
         <v>0.01</v>
       </c>
       <c r="K5" t="n">
-        <v>1.25</v>
+        <v>0.42</v>
       </c>
       <c r="L5" t="n">
         <v>72.3</v>
@@ -17088,9 +16974,7 @@
       <c r="J6" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
         <v>28.63</v>
       </c>
@@ -17148,9 +17032,7 @@
       <c r="J7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
         <v>32.85</v>
       </c>
@@ -17208,9 +17090,7 @@
       <c r="J8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
         <v>32.64</v>
       </c>
@@ -17269,7 +17149,7 @@
         <v>0.01</v>
       </c>
       <c r="K9" t="n">
-        <v>1.67</v>
+        <v>0.42</v>
       </c>
       <c r="L9" t="n">
         <v>72.31999999999999</v>
@@ -17328,9 +17208,7 @@
       <c r="J10" t="n">
         <v>0</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
         <v>34.09</v>
       </c>
@@ -17389,7 +17267,7 @@
         <v>0.02</v>
       </c>
       <c r="K11" t="n">
-        <v>1.03</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L11" t="n">
         <v>60.33</v>
@@ -17449,7 +17327,7 @@
         <v>0.02</v>
       </c>
       <c r="K12" t="n">
-        <v>1.93</v>
+        <v>0.77</v>
       </c>
       <c r="L12" t="n">
         <v>68.03</v>
@@ -17508,9 +17386,7 @@
       <c r="J13" t="n">
         <v>0</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
         <v>39.23</v>
       </c>
@@ -17665,7 +17541,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>65.55</v>
@@ -17725,7 +17601,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>91.45999999999999</v>
@@ -17785,7 +17661,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>135.14</v>
@@ -17845,7 +17721,7 @@
         <v>0.03</v>
       </c>
       <c r="K5" t="n">
-        <v>1.56</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L5" t="n">
         <v>44.75</v>
@@ -17905,7 +17781,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>89.81</v>
@@ -17965,7 +17841,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>115.5</v>
@@ -18025,7 +17901,7 @@
         <v>0.01</v>
       </c>
       <c r="K8" t="n">
-        <v>6.9</v>
+        <v>2.3</v>
       </c>
       <c r="L8" t="n">
         <v>397.9</v>
@@ -18085,7 +17961,7 @@
         <v>0.01</v>
       </c>
       <c r="K9" t="n">
-        <v>6.6</v>
+        <v>2.2</v>
       </c>
       <c r="L9" t="n">
         <v>380.6</v>
@@ -18145,7 +18021,7 @@
         <v>0.01</v>
       </c>
       <c r="K10" t="n">
-        <v>7.2</v>
+        <v>2.4</v>
       </c>
       <c r="L10" t="n">
         <v>415.2</v>
@@ -18205,7 +18081,7 @@
         <v>0.01</v>
       </c>
       <c r="K11" t="n">
-        <v>6.5</v>
+        <v>2.17</v>
       </c>
       <c r="L11" t="n">
         <v>374.96</v>
@@ -18265,7 +18141,7 @@
         <v>0.03</v>
       </c>
       <c r="K12" t="n">
-        <v>2.47</v>
+        <v>1.06</v>
       </c>
       <c r="L12" t="n">
         <v>50.49</v>
@@ -18325,7 +18201,7 @@
         <v>0.01</v>
       </c>
       <c r="K13" t="n">
-        <v>2.87</v>
+        <v>0.96</v>
       </c>
       <c r="L13" t="n">
         <v>165.67</v>
@@ -18385,7 +18261,7 @@
         <v>0.01</v>
       </c>
       <c r="K14" t="n">
-        <v>1.89</v>
+        <v>0.63</v>
       </c>
       <c r="L14" t="n">
         <v>108.87</v>
@@ -18445,7 +18321,7 @@
         <v>0.01</v>
       </c>
       <c r="K15" t="n">
-        <v>6.84</v>
+        <v>2.28</v>
       </c>
       <c r="L15" t="n">
         <v>394.44</v>
@@ -18505,7 +18381,7 @@
         <v>0.01</v>
       </c>
       <c r="K16" t="n">
-        <v>11.31</v>
+        <v>3.77</v>
       </c>
       <c r="L16" t="n">
         <v>652.21</v>
@@ -18565,7 +18441,7 @@
         <v>0.01</v>
       </c>
       <c r="K17" t="n">
-        <v>1.65</v>
+        <v>0.55</v>
       </c>
       <c r="L17" t="n">
         <v>95.15000000000001</v>
@@ -18625,7 +18501,7 @@
         <v>0.03</v>
       </c>
       <c r="K18" t="n">
-        <v>2.88</v>
+        <v>1.23</v>
       </c>
       <c r="L18" t="n">
         <v>58.76</v>
@@ -18685,7 +18561,7 @@
         <v>0.01</v>
       </c>
       <c r="K19" t="n">
-        <v>11.6</v>
+        <v>2.9</v>
       </c>
       <c r="L19" t="n">
         <v>501.7</v>
@@ -18745,7 +18621,7 @@
         <v>0.01</v>
       </c>
       <c r="K20" t="n">
-        <v>9.4</v>
+        <v>2.35</v>
       </c>
       <c r="L20" t="n">
         <v>406.55</v>
@@ -18805,7 +18681,7 @@
         <v>0.01</v>
       </c>
       <c r="K21" t="n">
-        <v>10.12</v>
+        <v>2.53</v>
       </c>
       <c r="L21" t="n">
         <v>437.69</v>
@@ -18865,7 +18741,7 @@
         <v>0.02</v>
       </c>
       <c r="K22" t="n">
-        <v>1.71</v>
+        <v>0.86</v>
       </c>
       <c r="L22" t="n">
         <v>73.98</v>
@@ -18925,7 +18801,7 @@
         <v>0.02</v>
       </c>
       <c r="K23" t="n">
-        <v>8.9</v>
+        <v>4.45</v>
       </c>
       <c r="L23" t="n">
         <v>384.85</v>
@@ -18985,7 +18861,7 @@
         <v>0.02</v>
       </c>
       <c r="K24" t="n">
-        <v>6.4</v>
+        <v>3.2</v>
       </c>
       <c r="L24" t="n">
         <v>276.87</v>
@@ -19045,7 +18921,7 @@
         <v>0.03</v>
       </c>
       <c r="K25" t="n">
-        <v>2.31</v>
+        <v>0.99</v>
       </c>
       <c r="L25" t="n">
         <v>47.1</v>
@@ -19105,7 +18981,7 @@
         <v>0.09</v>
       </c>
       <c r="K26" t="n">
-        <v>10.34</v>
+        <v>5.17</v>
       </c>
       <c r="L26" t="n">
         <v>105.69</v>
@@ -19165,7 +19041,7 @@
         <v>0.02</v>
       </c>
       <c r="K27" t="n">
-        <v>3.25</v>
+        <v>1.08</v>
       </c>
       <c r="L27" t="n">
         <v>93.68000000000001</v>
@@ -19225,7 +19101,7 @@
         <v>0.03</v>
       </c>
       <c r="K28" t="n">
-        <v>5.41</v>
+        <v>1.8</v>
       </c>
       <c r="L28" t="n">
         <v>85.98999999999999</v>
@@ -19285,7 +19161,7 @@
         <v>0.02</v>
       </c>
       <c r="K29" t="n">
-        <v>6.78</v>
+        <v>4.52</v>
       </c>
       <c r="L29" t="n">
         <v>397.76</v>
@@ -19345,7 +19221,7 @@
         <v>0.02</v>
       </c>
       <c r="K30" t="n">
-        <v>6.15</v>
+        <v>4.1</v>
       </c>
       <c r="L30" t="n">
         <v>360.8</v>
@@ -19405,7 +19281,7 @@
         <v>0.02</v>
       </c>
       <c r="K31" t="n">
-        <v>9.42</v>
+        <v>6.28</v>
       </c>
       <c r="L31" t="n">
         <v>552.66</v>
@@ -19465,7 +19341,7 @@
         <v>0.03</v>
       </c>
       <c r="K32" t="n">
-        <v>2.98</v>
+        <v>1.28</v>
       </c>
       <c r="L32" t="n">
         <v>61.3</v>
@@ -19525,7 +19401,7 @@
         <v>0.02</v>
       </c>
       <c r="K33" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L33" t="n">
         <v>352.04</v>
@@ -19585,7 +19461,7 @@
         <v>0.02</v>
       </c>
       <c r="K34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L34" t="n">
         <v>176</v>
@@ -19645,7 +19521,7 @@
         <v>0.02</v>
       </c>
       <c r="K35" t="n">
-        <v>8.57</v>
+        <v>4.29</v>
       </c>
       <c r="L35" t="n">
         <v>377.26</v>
@@ -19705,7 +19581,7 @@
         <v>0.02</v>
       </c>
       <c r="K36" t="n">
-        <v>7.68</v>
+        <v>3.84</v>
       </c>
       <c r="L36" t="n">
         <v>337.92</v>
@@ -19765,7 +19641,7 @@
         <v>0.02</v>
       </c>
       <c r="K37" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L37" t="n">
         <v>352</v>
@@ -19825,7 +19701,7 @@
         <v>0.02</v>
       </c>
       <c r="K38" t="n">
-        <v>8.16</v>
+        <v>4.08</v>
       </c>
       <c r="L38" t="n">
         <v>359.15</v>
@@ -19981,7 +19857,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>101.36</v>
@@ -20137,7 +20013,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>76.53</v>
@@ -20197,7 +20073,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>97.53</v>
@@ -20257,7 +20133,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>94.34</v>
@@ -20317,7 +20193,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>89.05</v>
@@ -20377,7 +20253,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>116.64</v>
@@ -20437,7 +20313,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>96.31</v>
@@ -20497,7 +20373,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>75.52</v>
@@ -20557,7 +20433,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>119.4</v>
@@ -20617,7 +20493,7 @@
         <v>0.03</v>
       </c>
       <c r="K10" t="n">
-        <v>1.89</v>
+        <v>0.95</v>
       </c>
       <c r="L10" t="n">
         <v>45.12</v>
@@ -20677,7 +20553,7 @@
         <v>0.01</v>
       </c>
       <c r="K11" t="n">
-        <v>1.84</v>
+        <v>0.61</v>
       </c>
       <c r="L11" t="n">
         <v>105.82</v>
@@ -20737,7 +20613,7 @@
         <v>0.01</v>
       </c>
       <c r="K12" t="n">
-        <v>1.4</v>
+        <v>0.46</v>
       </c>
       <c r="L12" t="n">
         <v>80.44</v>
@@ -20797,7 +20673,7 @@
         <v>0.01</v>
       </c>
       <c r="K13" t="n">
-        <v>7.69</v>
+        <v>2.56</v>
       </c>
       <c r="L13" t="n">
         <v>443.27</v>
@@ -20857,7 +20733,7 @@
         <v>0.01</v>
       </c>
       <c r="K14" t="n">
-        <v>1.88</v>
+        <v>0.63</v>
       </c>
       <c r="L14" t="n">
         <v>108.46</v>
@@ -20917,7 +20793,7 @@
         <v>0.01</v>
       </c>
       <c r="K15" t="n">
-        <v>1.89</v>
+        <v>0.63</v>
       </c>
       <c r="L15" t="n">
         <v>109.08</v>
@@ -20977,7 +20853,7 @@
         <v>0.01</v>
       </c>
       <c r="K16" t="n">
-        <v>2.12</v>
+        <v>0.71</v>
       </c>
       <c r="L16" t="n">
         <v>122.53</v>
@@ -21037,7 +20913,7 @@
         <v>0.03</v>
       </c>
       <c r="K17" t="n">
-        <v>2.59</v>
+        <v>1.11</v>
       </c>
       <c r="L17" t="n">
         <v>52.94</v>
@@ -21096,9 +20972,7 @@
       <c r="J18" t="n">
         <v>0</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
         <v>17.84</v>
       </c>
@@ -21157,7 +21031,7 @@
         <v>0.01</v>
       </c>
       <c r="K19" t="n">
-        <v>0.57</v>
+        <v>0.19</v>
       </c>
       <c r="L19" t="n">
         <v>32.76</v>
@@ -21217,7 +21091,7 @@
         <v>0.01</v>
       </c>
       <c r="K20" t="n">
-        <v>2.13</v>
+        <v>0.71</v>
       </c>
       <c r="L20" t="n">
         <v>122.67</v>
@@ -21277,7 +21151,7 @@
         <v>0.01</v>
       </c>
       <c r="K21" t="n">
-        <v>1.7</v>
+        <v>0.42</v>
       </c>
       <c r="L21" t="n">
         <v>73.33</v>
@@ -21337,7 +21211,7 @@
         <v>0.01</v>
       </c>
       <c r="K22" t="n">
-        <v>2.1</v>
+        <v>0.53</v>
       </c>
       <c r="L22" t="n">
         <v>90.98</v>
@@ -21397,7 +21271,7 @@
         <v>0.01</v>
       </c>
       <c r="K23" t="n">
-        <v>3.18</v>
+        <v>0.8</v>
       </c>
       <c r="L23" t="n">
         <v>137.59</v>
@@ -21457,7 +21331,7 @@
         <v>0.03</v>
       </c>
       <c r="K24" t="n">
-        <v>2.03</v>
+        <v>0.87</v>
       </c>
       <c r="L24" t="n">
         <v>41.37</v>
@@ -21517,7 +21391,7 @@
         <v>0.01</v>
       </c>
       <c r="K25" t="n">
-        <v>2.41</v>
+        <v>0.6</v>
       </c>
       <c r="L25" t="n">
         <v>104.06</v>
@@ -21577,7 +21451,7 @@
         <v>0.01</v>
       </c>
       <c r="K26" t="n">
-        <v>2.39</v>
+        <v>0.6</v>
       </c>
       <c r="L26" t="n">
         <v>103.42</v>
@@ -21637,7 +21511,7 @@
         <v>0.01</v>
       </c>
       <c r="K27" t="n">
-        <v>2.58</v>
+        <v>0.64</v>
       </c>
       <c r="L27" t="n">
         <v>111.43</v>
@@ -21697,7 +21571,7 @@
         <v>0.02</v>
       </c>
       <c r="K28" t="n">
-        <v>0.61</v>
+        <v>0.31</v>
       </c>
       <c r="L28" t="n">
         <v>26.52</v>
@@ -21757,7 +21631,7 @@
         <v>0.02</v>
       </c>
       <c r="K29" t="n">
-        <v>1.81</v>
+        <v>0.9</v>
       </c>
       <c r="L29" t="n">
         <v>78.14</v>
@@ -21817,7 +21691,7 @@
         <v>0.02</v>
       </c>
       <c r="K30" t="n">
-        <v>2.1</v>
+        <v>1.05</v>
       </c>
       <c r="L30" t="n">
         <v>90.95</v>
@@ -21877,7 +21751,7 @@
         <v>0.02</v>
       </c>
       <c r="K31" t="n">
-        <v>3.07</v>
+        <v>1.54</v>
       </c>
       <c r="L31" t="n">
         <v>132.87</v>
@@ -21937,7 +21811,7 @@
         <v>0.02</v>
       </c>
       <c r="K32" t="n">
-        <v>2.34</v>
+        <v>1.17</v>
       </c>
       <c r="L32" t="n">
         <v>101.31</v>
@@ -21997,7 +21871,7 @@
         <v>0.02</v>
       </c>
       <c r="K33" t="n">
-        <v>3.03</v>
+        <v>1.51</v>
       </c>
       <c r="L33" t="n">
         <v>131.01</v>
@@ -22057,7 +21931,7 @@
         <v>0.02</v>
       </c>
       <c r="K34" t="n">
-        <v>2.63</v>
+        <v>1.31</v>
       </c>
       <c r="L34" t="n">
         <v>113.55</v>
@@ -22117,7 +21991,7 @@
         <v>0.02</v>
       </c>
       <c r="K35" t="n">
-        <v>2.2</v>
+        <v>1.47</v>
       </c>
       <c r="L35" t="n">
         <v>126.76</v>
@@ -22177,7 +22051,7 @@
         <v>0.02</v>
       </c>
       <c r="K36" t="n">
-        <v>2.29</v>
+        <v>1.15</v>
       </c>
       <c r="L36" t="n">
         <v>99.22</v>
@@ -22237,7 +22111,7 @@
         <v>0.02</v>
       </c>
       <c r="K37" t="n">
-        <v>2.58</v>
+        <v>1.29</v>
       </c>
       <c r="L37" t="n">
         <v>111.66</v>
@@ -22297,7 +22171,7 @@
         <v>0.02</v>
       </c>
       <c r="K38" t="n">
-        <v>3.05</v>
+        <v>1.02</v>
       </c>
       <c r="L38" t="n">
         <v>87.84999999999999</v>
@@ -22357,7 +22231,7 @@
         <v>0.02</v>
       </c>
       <c r="K39" t="n">
-        <v>1.53</v>
+        <v>1.02</v>
       </c>
       <c r="L39" t="n">
         <v>89.83</v>
@@ -22417,7 +22291,7 @@
         <v>0.02</v>
       </c>
       <c r="K40" t="n">
-        <v>1.53</v>
+        <v>1.02</v>
       </c>
       <c r="L40" t="n">
         <v>89.70999999999999</v>
@@ -22477,7 +22351,7 @@
         <v>0.02</v>
       </c>
       <c r="K41" t="n">
-        <v>2.01</v>
+        <v>1.34</v>
       </c>
       <c r="L41" t="n">
         <v>118.03</v>
@@ -22537,7 +22411,7 @@
         <v>0.02</v>
       </c>
       <c r="K42" t="n">
-        <v>1.05</v>
+        <v>0.53</v>
       </c>
       <c r="L42" t="n">
         <v>46.41</v>
@@ -22597,7 +22471,7 @@
         <v>0.02</v>
       </c>
       <c r="K43" t="n">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="L43" t="n">
         <v>91.52</v>
@@ -22657,7 +22531,7 @@
         <v>0.02</v>
       </c>
       <c r="K44" t="n">
-        <v>1.95</v>
+        <v>0.97</v>
       </c>
       <c r="L44" t="n">
         <v>85.59999999999999</v>
@@ -22717,7 +22591,7 @@
         <v>0.02</v>
       </c>
       <c r="K45" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="L45" t="n">
         <v>79.25</v>
@@ -22777,7 +22651,7 @@
         <v>0.02</v>
       </c>
       <c r="K46" t="n">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="L46" t="n">
         <v>110.04</v>
@@ -22837,7 +22711,7 @@
         <v>0.02</v>
       </c>
       <c r="K47" t="n">
-        <v>2.39</v>
+        <v>1.19</v>
       </c>
       <c r="L47" t="n">
         <v>104.96</v>
@@ -22897,7 +22771,7 @@
         <v>0.02</v>
       </c>
       <c r="K48" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="L48" t="n">
         <v>88.83</v>
@@ -22957,7 +22831,7 @@
         <v>0.02</v>
       </c>
       <c r="K49" t="n">
-        <v>1.37</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L49" t="n">
         <v>60.3</v>
@@ -23017,7 +22891,7 @@
         <v>0.02</v>
       </c>
       <c r="K50" t="n">
-        <v>2.05</v>
+        <v>1.03</v>
       </c>
       <c r="L50" t="n">
         <v>90.31</v>
@@ -23077,7 +22951,7 @@
         <v>0.03</v>
       </c>
       <c r="K51" t="n">
-        <v>0.55</v>
+        <v>0.24</v>
       </c>
       <c r="L51" t="n">
         <v>11.32</v>
@@ -23136,9 +23010,7 @@
       <c r="J52" t="n">
         <v>0</v>
       </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="n">
         <v>19.49</v>
       </c>
@@ -23197,7 +23069,7 @@
         <v>0.03</v>
       </c>
       <c r="K53" t="n">
-        <v>2.03</v>
+        <v>0.87</v>
       </c>
       <c r="L53" t="n">
         <v>41.78</v>
@@ -23257,7 +23129,7 @@
         <v>0.02</v>
       </c>
       <c r="K54" t="n">
-        <v>1.71</v>
+        <v>0.86</v>
       </c>
       <c r="L54" t="n">
         <v>75.31</v>
@@ -23317,7 +23189,7 @@
         <v>0.03</v>
       </c>
       <c r="K55" t="n">
-        <v>2.21</v>
+        <v>0.83</v>
       </c>
       <c r="L55" t="n">
         <v>39.79</v>
@@ -23473,7 +23345,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>92.59</v>
@@ -23533,7 +23405,7 @@
         <v>0.01</v>
       </c>
       <c r="K3" t="n">
-        <v>3.44</v>
+        <v>0.49</v>
       </c>
       <c r="L3" t="n">
         <v>82.94</v>
@@ -23593,7 +23465,7 @@
         <v>0.02</v>
       </c>
       <c r="K4" t="n">
-        <v>1.78</v>
+        <v>0.89</v>
       </c>
       <c r="L4" t="n">
         <v>77.13</v>
@@ -23653,7 +23525,7 @@
         <v>0.02</v>
       </c>
       <c r="K5" t="n">
-        <v>2.49</v>
+        <v>1.25</v>
       </c>
       <c r="L5" t="n">
         <v>107.83</v>
@@ -23713,7 +23585,7 @@
         <v>0.02</v>
       </c>
       <c r="K6" t="n">
-        <v>1.76</v>
+        <v>0.88</v>
       </c>
       <c r="L6" t="n">
         <v>77.56999999999999</v>
@@ -23869,7 +23741,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>85.37</v>
@@ -23929,7 +23801,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>71.61</v>
@@ -23989,7 +23861,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>63.32</v>
@@ -24049,7 +23921,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>45.05</v>
@@ -24109,7 +23981,7 @@
         <v>0.09</v>
       </c>
       <c r="K6" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="L6" t="n">
         <v>87</v>
@@ -24169,7 +24041,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>104</v>
@@ -24229,7 +24101,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>63.69</v>
@@ -24289,7 +24161,7 @@
         <v>0.09</v>
       </c>
       <c r="K9" t="n">
-        <v>2.34</v>
+        <v>7.01</v>
       </c>
       <c r="L9" t="n">
         <v>132.39</v>
@@ -24349,7 +24221,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>68.73</v>
@@ -24409,7 +24281,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>101.62</v>
@@ -24469,7 +24341,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>106.86</v>
@@ -24529,7 +24401,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>73.56999999999999</v>
@@ -24589,7 +24461,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>72.06999999999999</v>
@@ -24649,7 +24521,7 @@
         <v>0.09</v>
       </c>
       <c r="K15" t="n">
-        <v>2.75</v>
+        <v>8.25</v>
       </c>
       <c r="L15" t="n">
         <v>155.86</v>
@@ -24709,7 +24581,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>49.3</v>
@@ -24769,7 +24641,7 @@
         <v>0.09</v>
       </c>
       <c r="K17" t="n">
-        <v>12.45</v>
+        <v>5.6</v>
       </c>
       <c r="L17" t="n">
         <v>112.7</v>
@@ -24829,7 +24701,7 @@
         <v>0.09</v>
       </c>
       <c r="K18" t="n">
-        <v>11.04</v>
+        <v>4.97</v>
       </c>
       <c r="L18" t="n">
         <v>99.93000000000001</v>
@@ -24889,7 +24761,7 @@
         <v>0.01</v>
       </c>
       <c r="K19" t="n">
-        <v>1.92</v>
+        <v>0.64</v>
       </c>
       <c r="L19" t="n">
         <v>110.95</v>
@@ -24949,7 +24821,7 @@
         <v>0.01</v>
       </c>
       <c r="K20" t="n">
-        <v>0.72</v>
+        <v>0.24</v>
       </c>
       <c r="L20" t="n">
         <v>41.66</v>
@@ -25009,7 +24881,7 @@
         <v>0.09</v>
       </c>
       <c r="K21" t="n">
-        <v>14.44</v>
+        <v>6.5</v>
       </c>
       <c r="L21" t="n">
         <v>130.72</v>
@@ -25069,7 +24941,7 @@
         <v>0.03</v>
       </c>
       <c r="K22" t="n">
-        <v>2.81</v>
+        <v>1.2</v>
       </c>
       <c r="L22" t="n">
         <v>57.42</v>
@@ -25129,7 +25001,7 @@
         <v>0.09</v>
       </c>
       <c r="K23" t="n">
-        <v>8.49</v>
+        <v>3.82</v>
       </c>
       <c r="L23" t="n">
         <v>76.87</v>
@@ -25189,7 +25061,7 @@
         <v>0.01</v>
       </c>
       <c r="K24" t="n">
-        <v>1.35</v>
+        <v>0.45</v>
       </c>
       <c r="L24" t="n">
         <v>77.62</v>
@@ -25249,7 +25121,7 @@
         <v>0.01</v>
       </c>
       <c r="K25" t="n">
-        <v>1.52</v>
+        <v>0.38</v>
       </c>
       <c r="L25" t="n">
         <v>65.65000000000001</v>
@@ -25309,7 +25181,7 @@
         <v>0.01</v>
       </c>
       <c r="K26" t="n">
-        <v>1.42</v>
+        <v>0.36</v>
       </c>
       <c r="L26" t="n">
         <v>61.52</v>
@@ -25369,7 +25241,7 @@
         <v>0.09</v>
       </c>
       <c r="K27" t="n">
-        <v>5.2</v>
+        <v>2.23</v>
       </c>
       <c r="L27" t="n">
         <v>44.8</v>
@@ -25429,7 +25301,7 @@
         <v>0.09</v>
       </c>
       <c r="K28" t="n">
-        <v>5.2</v>
+        <v>2.23</v>
       </c>
       <c r="L28" t="n">
         <v>44.84</v>
@@ -25489,7 +25361,7 @@
         <v>0.09</v>
       </c>
       <c r="K29" t="n">
-        <v>7.35</v>
+        <v>3.15</v>
       </c>
       <c r="L29" t="n">
         <v>63.35</v>
@@ -25549,7 +25421,7 @@
         <v>0.02</v>
       </c>
       <c r="K30" t="n">
-        <v>2.09</v>
+        <v>1.05</v>
       </c>
       <c r="L30" t="n">
         <v>90.56999999999999</v>
@@ -25609,7 +25481,7 @@
         <v>0.02</v>
       </c>
       <c r="K31" t="n">
-        <v>1.74</v>
+        <v>0.87</v>
       </c>
       <c r="L31" t="n">
         <v>75.43000000000001</v>
@@ -25669,7 +25541,7 @@
         <v>0.02</v>
       </c>
       <c r="K32" t="n">
-        <v>1.23</v>
+        <v>0.61</v>
       </c>
       <c r="L32" t="n">
         <v>53.18</v>
@@ -25729,7 +25601,7 @@
         <v>0.09</v>
       </c>
       <c r="K33" t="n">
-        <v>8.76</v>
+        <v>4.38</v>
       </c>
       <c r="L33" t="n">
         <v>89.53</v>
@@ -25789,7 +25661,7 @@
         <v>0.02</v>
       </c>
       <c r="K34" t="n">
-        <v>2.32</v>
+        <v>1.16</v>
       </c>
       <c r="L34" t="n">
         <v>100.53</v>
@@ -25849,7 +25721,7 @@
         <v>0.02</v>
       </c>
       <c r="K35" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="L35" t="n">
         <v>155.77</v>
@@ -25909,7 +25781,7 @@
         <v>0.02</v>
       </c>
       <c r="K36" t="n">
-        <v>1.13</v>
+        <v>0.57</v>
       </c>
       <c r="L36" t="n">
         <v>49.07</v>
@@ -25969,7 +25841,7 @@
         <v>0.02</v>
       </c>
       <c r="K37" t="n">
-        <v>3.75</v>
+        <v>1.25</v>
       </c>
       <c r="L37" t="n">
         <v>108.05</v>
@@ -26029,7 +25901,7 @@
         <v>0.09</v>
       </c>
       <c r="K38" t="n">
-        <v>13.02</v>
+        <v>5.86</v>
       </c>
       <c r="L38" t="n">
         <v>119.76</v>
@@ -26089,7 +25961,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>4.69</v>
+        <v>6.57</v>
       </c>
       <c r="L39" t="n">
         <v>160.56</v>
@@ -26149,7 +26021,7 @@
         <v>0.02</v>
       </c>
       <c r="K40" t="n">
-        <v>1.05</v>
+        <v>0.7</v>
       </c>
       <c r="L40" t="n">
         <v>61.64</v>
@@ -26209,7 +26081,7 @@
         <v>0.02</v>
       </c>
       <c r="K41" t="n">
-        <v>1.06</v>
+        <v>0.71</v>
       </c>
       <c r="L41" t="n">
         <v>62.31</v>
@@ -26268,9 +26140,7 @@
       <c r="J42" t="n">
         <v>0</v>
       </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="n">
         <v>25.96</v>
       </c>
@@ -26329,7 +26199,7 @@
         <v>0.02</v>
       </c>
       <c r="K43" t="n">
-        <v>1.74</v>
+        <v>1.16</v>
       </c>
       <c r="L43" t="n">
         <v>102.35</v>
@@ -26389,7 +26259,7 @@
         <v>0.02</v>
       </c>
       <c r="K44" t="n">
-        <v>1.42</v>
+        <v>0.95</v>
       </c>
       <c r="L44" t="n">
         <v>83.39</v>
@@ -26449,7 +26319,7 @@
         <v>0.09</v>
       </c>
       <c r="K45" t="n">
-        <v>12.85</v>
+        <v>6.09</v>
       </c>
       <c r="L45" t="n">
         <v>125.09</v>
@@ -26509,7 +26379,7 @@
         <v>0.02</v>
       </c>
       <c r="K46" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="L46" t="n">
         <v>47.47</v>
@@ -26569,7 +26439,7 @@
         <v>0.02</v>
       </c>
       <c r="K47" t="n">
-        <v>0.97</v>
+        <v>0.65</v>
       </c>
       <c r="L47" t="n">
         <v>57.12</v>
@@ -26629,7 +26499,7 @@
         <v>0.02</v>
       </c>
       <c r="K48" t="n">
-        <v>2.49</v>
+        <v>1.24</v>
       </c>
       <c r="L48" t="n">
         <v>109.42</v>
@@ -26689,7 +26559,7 @@
         <v>0.02</v>
       </c>
       <c r="K49" t="n">
-        <v>1.43</v>
+        <v>0.57</v>
       </c>
       <c r="L49" t="n">
         <v>50.44</v>
@@ -26749,7 +26619,7 @@
         <v>0.02</v>
       </c>
       <c r="K50" t="n">
-        <v>2.3</v>
+        <v>1.15</v>
       </c>
       <c r="L50" t="n">
         <v>100.99</v>
@@ -26905,7 +26775,7 @@
         <v>0.03</v>
       </c>
       <c r="K2" t="n">
-        <v>1.87</v>
+        <v>0.8</v>
       </c>
       <c r="L2" t="n">
         <v>38.12</v>
@@ -27061,7 +26931,7 @@
         <v>0.03</v>
       </c>
       <c r="K2" t="n">
-        <v>2.08</v>
+        <v>1.25</v>
       </c>
       <c r="L2" t="n">
         <v>59.59</v>
@@ -27121,7 +26991,7 @@
         <v>0.03</v>
       </c>
       <c r="K3" t="n">
-        <v>2.85</v>
+        <v>1.22</v>
       </c>
       <c r="L3" t="n">
         <v>58.2</v>
@@ -27277,7 +27147,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>21.75</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>897.36</v>
@@ -27337,7 +27207,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>14.26</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>588.15</v>
@@ -27397,7 +27267,7 @@
         <v>0.01</v>
       </c>
       <c r="K4" t="n">
-        <v>1.55</v>
+        <v>0.31</v>
       </c>
       <c r="L4" t="n">
         <v>52.94</v>
@@ -27457,7 +27327,7 @@
         <v>0.01</v>
       </c>
       <c r="K5" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="L5" t="n">
         <v>1557</v>
@@ -27517,7 +27387,7 @@
         <v>0.01</v>
       </c>
       <c r="K6" t="n">
-        <v>29.7</v>
+        <v>9.9</v>
       </c>
       <c r="L6" t="n">
         <v>1712.7</v>
@@ -27577,7 +27447,7 @@
         <v>0.03</v>
       </c>
       <c r="K7" t="n">
-        <v>3.63</v>
+        <v>1.56</v>
       </c>
       <c r="L7" t="n">
         <v>74.22</v>
@@ -27637,7 +27507,7 @@
         <v>0.02</v>
       </c>
       <c r="K8" t="n">
-        <v>2.22</v>
+        <v>0.74</v>
       </c>
       <c r="L8" t="n">
         <v>64.01000000000001</v>
@@ -27697,7 +27567,7 @@
         <v>0.02</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.67</v>
+        <v>1.34</v>
       </c>
       <c r="L9" t="n">
         <v>117.94</v>
@@ -27757,7 +27627,7 @@
         <v>0.02</v>
       </c>
       <c r="K10" t="n">
-        <v>26.28</v>
+        <v>13.14</v>
       </c>
       <c r="L10" t="n">
         <v>1156.3</v>
@@ -27817,7 +27687,7 @@
         <v>0.02</v>
       </c>
       <c r="K11" t="n">
-        <v>1.65</v>
+        <v>0.66</v>
       </c>
       <c r="L11" t="n">
         <v>58.08</v>
@@ -27973,7 +27843,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>19.52</v>
@@ -28033,7 +27903,7 @@
         <v>0.01</v>
       </c>
       <c r="K3" t="n">
-        <v>0.85</v>
+        <v>0.17</v>
       </c>
       <c r="L3" t="n">
         <v>29.21</v>
@@ -28093,7 +27963,7 @@
         <v>0.02</v>
       </c>
       <c r="K4" t="n">
-        <v>0.34</v>
+        <v>0.22</v>
       </c>
       <c r="L4" t="n">
         <v>19.68</v>
@@ -28153,7 +28023,7 @@
         <v>0.02</v>
       </c>
       <c r="K5" t="n">
-        <v>0.36</v>
+        <v>0.18</v>
       </c>
       <c r="L5" t="n">
         <v>15.63</v>
@@ -28213,7 +28083,7 @@
         <v>0.02</v>
       </c>
       <c r="K6" t="n">
-        <v>0.74</v>
+        <v>0.19</v>
       </c>
       <c r="L6" t="n">
         <v>13.29</v>
@@ -28369,7 +28239,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>19.86</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>468.12</v>
@@ -28429,7 +28299,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>106.24</v>
@@ -28489,7 +28359,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>55.49</v>
@@ -28549,7 +28419,7 @@
         <v>0.01</v>
       </c>
       <c r="K5" t="n">
-        <v>1.76</v>
+        <v>0.59</v>
       </c>
       <c r="L5" t="n">
         <v>101.25</v>
@@ -28609,7 +28479,7 @@
         <v>0.01</v>
       </c>
       <c r="K6" t="n">
-        <v>0.93</v>
+        <v>0.31</v>
       </c>
       <c r="L6" t="n">
         <v>53.89</v>
@@ -28669,7 +28539,7 @@
         <v>0.01</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3</v>
+        <v>0.43</v>
       </c>
       <c r="L7" t="n">
         <v>75.03</v>
@@ -28729,7 +28599,7 @@
         <v>0.01</v>
       </c>
       <c r="K8" t="n">
-        <v>1.99</v>
+        <v>0.5</v>
       </c>
       <c r="L8" t="n">
         <v>86.14</v>
@@ -28789,7 +28659,7 @@
         <v>0.01</v>
       </c>
       <c r="K9" t="n">
-        <v>5.66</v>
+        <v>1.42</v>
       </c>
       <c r="L9" t="n">
         <v>244.95</v>
@@ -28849,7 +28719,7 @@
         <v>0.01</v>
       </c>
       <c r="K10" t="n">
-        <v>2.59</v>
+        <v>0.65</v>
       </c>
       <c r="L10" t="n">
         <v>112.07</v>
@@ -28909,7 +28779,7 @@
         <v>0.01</v>
       </c>
       <c r="K11" t="n">
-        <v>1.9</v>
+        <v>0.48</v>
       </c>
       <c r="L11" t="n">
         <v>82.18000000000001</v>
@@ -28969,7 +28839,7 @@
         <v>0.09</v>
       </c>
       <c r="K12" t="n">
-        <v>6.38</v>
+        <v>3.19</v>
       </c>
       <c r="L12" t="n">
         <v>65.19</v>
@@ -29029,7 +28899,7 @@
         <v>0.02</v>
       </c>
       <c r="K13" t="n">
-        <v>1.97</v>
+        <v>0.98</v>
       </c>
       <c r="L13" t="n">
         <v>85.11</v>
@@ -29088,9 +28958,7 @@
       <c r="J14" t="n">
         <v>0</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
         <v>9.49</v>
       </c>
@@ -29149,7 +29017,7 @@
         <v>0.02</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="L15" t="n">
         <v>60.62</v>
@@ -29209,7 +29077,7 @@
         <v>0.02</v>
       </c>
       <c r="K16" t="n">
-        <v>1.85</v>
+        <v>0.93</v>
       </c>
       <c r="L16" t="n">
         <v>80.19</v>
@@ -29269,7 +29137,7 @@
         <v>0.02</v>
       </c>
       <c r="K17" t="n">
-        <v>3.97</v>
+        <v>1.98</v>
       </c>
       <c r="L17" t="n">
         <v>171.51</v>
@@ -29329,7 +29197,7 @@
         <v>0.02</v>
       </c>
       <c r="K18" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="L18" t="n">
         <v>132.27</v>
@@ -29389,7 +29257,7 @@
         <v>0.02</v>
       </c>
       <c r="K19" t="n">
-        <v>10.25</v>
+        <v>6.83</v>
       </c>
       <c r="L19" t="n">
         <v>601.11</v>
@@ -29449,7 +29317,7 @@
         <v>0.02</v>
       </c>
       <c r="K20" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="L20" t="n">
         <v>105.6</v>
@@ -29509,7 +29377,7 @@
         <v>0.02</v>
       </c>
       <c r="K21" t="n">
-        <v>3.33</v>
+        <v>1.67</v>
       </c>
       <c r="L21" t="n">
         <v>146.54</v>
@@ -29569,7 +29437,7 @@
         <v>0.02</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L22" t="n">
         <v>44.07</v>
@@ -29725,7 +29593,7 @@
         <v>0.09</v>
       </c>
       <c r="K2" t="n">
-        <v>5.92</v>
+        <v>2.67</v>
       </c>
       <c r="L2" t="n">
         <v>51.54</v>
@@ -29785,7 +29653,7 @@
         <v>0.09</v>
       </c>
       <c r="K3" t="n">
-        <v>2.06</v>
+        <v>4.63</v>
       </c>
       <c r="L3" t="n">
         <v>87.38</v>
@@ -29845,7 +29713,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>90.75</v>
@@ -29905,7 +29773,7 @@
         <v>0.09</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.11</v>
       </c>
       <c r="L5" t="n">
         <v>39.83</v>
@@ -29965,7 +29833,7 @@
         <v>0.09</v>
       </c>
       <c r="K6" t="n">
-        <v>1.54</v>
+        <v>4.62</v>
       </c>
       <c r="L6" t="n">
         <v>87.20999999999999</v>
@@ -30024,9 +29892,7 @@
       <c r="J7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
         <v>6.64</v>
       </c>
@@ -30084,9 +29950,7 @@
       <c r="J8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
         <v>2.14</v>
       </c>
@@ -30145,7 +30009,7 @@
         <v>0.03</v>
       </c>
       <c r="K9" t="n">
-        <v>0.71</v>
+        <v>0.35</v>
       </c>
       <c r="L9" t="n">
         <v>16.84</v>
@@ -30205,7 +30069,7 @@
         <v>0.03</v>
       </c>
       <c r="K10" t="n">
-        <v>0.88</v>
+        <v>0.53</v>
       </c>
       <c r="L10" t="n">
         <v>25.23</v>
@@ -30265,7 +30129,7 @@
         <v>0.03</v>
       </c>
       <c r="K11" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="L11" t="n">
         <v>42.83</v>
@@ -30325,7 +30189,7 @@
         <v>0.09</v>
       </c>
       <c r="K12" t="n">
-        <v>0.72</v>
+        <v>1.63</v>
       </c>
       <c r="L12" t="n">
         <v>30.76</v>
@@ -30385,7 +30249,7 @@
         <v>0.09</v>
       </c>
       <c r="K13" t="n">
-        <v>0.93</v>
+        <v>2.79</v>
       </c>
       <c r="L13" t="n">
         <v>52.77</v>
@@ -30445,7 +30309,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>2.35</v>
+        <v>2.74</v>
       </c>
       <c r="L14" t="n">
         <v>66.47</v>
@@ -30505,7 +30369,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="L15" t="n">
         <v>16.39</v>
@@ -30565,7 +30429,7 @@
         <v>0.09</v>
       </c>
       <c r="K16" t="n">
-        <v>8.949999999999999</v>
+        <v>4.03</v>
       </c>
       <c r="L16" t="n">
         <v>81.04000000000001</v>
@@ -30625,7 +30489,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>1.47</v>
+        <v>1.71</v>
       </c>
       <c r="L17" t="n">
         <v>41.52</v>
@@ -30685,7 +30549,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>2.59</v>
+        <v>3.63</v>
       </c>
       <c r="L18" t="n">
         <v>88.17</v>
@@ -30745,7 +30609,7 @@
         <v>0.03</v>
       </c>
       <c r="K19" t="n">
-        <v>2.71</v>
+        <v>1.02</v>
       </c>
       <c r="L19" t="n">
         <v>48.48</v>
@@ -30805,7 +30669,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>1.81</v>
+        <v>2.11</v>
       </c>
       <c r="L20" t="n">
         <v>51.32</v>
@@ -30865,7 +30729,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="L21" t="n">
         <v>37.64</v>
@@ -30925,7 +30789,7 @@
         <v>0.03</v>
       </c>
       <c r="K22" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="L22" t="n">
         <v>42.9</v>
@@ -30985,7 +30849,7 @@
         <v>0.03</v>
       </c>
       <c r="K23" t="n">
-        <v>2.47</v>
+        <v>0.93</v>
       </c>
       <c r="L23" t="n">
         <v>44.19</v>
@@ -31045,7 +30909,7 @@
         <v>0.03</v>
       </c>
       <c r="K24" t="n">
-        <v>1.37</v>
+        <v>0.51</v>
       </c>
       <c r="L24" t="n">
         <v>24.53</v>
@@ -31104,9 +30968,7 @@
       <c r="J25" t="n">
         <v>0</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
         <v>9.49</v>
       </c>
@@ -31165,7 +31027,7 @@
         <v>0.09</v>
       </c>
       <c r="K26" t="n">
-        <v>4.9</v>
+        <v>2.45</v>
       </c>
       <c r="L26" t="n">
         <v>50.1</v>
@@ -31225,7 +31087,7 @@
         <v>0.09</v>
       </c>
       <c r="K27" t="n">
-        <v>8.73</v>
+        <v>4.37</v>
       </c>
       <c r="L27" t="n">
         <v>89.26000000000001</v>
@@ -31285,7 +31147,7 @@
         <v>0.09</v>
       </c>
       <c r="K28" t="n">
-        <v>3.32</v>
+        <v>1.66</v>
       </c>
       <c r="L28" t="n">
         <v>33.95</v>
@@ -31345,7 +31207,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="L29" t="n">
         <v>46.19</v>
@@ -31405,7 +31267,7 @@
         <v>0.09</v>
       </c>
       <c r="K30" t="n">
-        <v>6</v>
+        <v>2.57</v>
       </c>
       <c r="L30" t="n">
         <v>52.59</v>
@@ -31525,7 +31387,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>2.43</v>
+        <v>2.84</v>
       </c>
       <c r="L32" t="n">
         <v>68.95999999999999</v>
@@ -31585,7 +31447,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>1.08</v>
+        <v>1.51</v>
       </c>
       <c r="L33" t="n">
         <v>36.81</v>
@@ -31645,7 +31507,7 @@
         <v>0.03</v>
       </c>
       <c r="K34" t="n">
-        <v>2.44</v>
+        <v>0.91</v>
       </c>
       <c r="L34" t="n">
         <v>43.87</v>
@@ -31705,7 +31567,7 @@
         <v>0.09</v>
       </c>
       <c r="K35" t="n">
-        <v>5.94</v>
+        <v>2.81</v>
       </c>
       <c r="L35" t="n">
         <v>57.85</v>
@@ -31765,7 +31627,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>2.03</v>
+        <v>2.37</v>
       </c>
       <c r="L36" t="n">
         <v>57.97</v>
@@ -31825,7 +31687,7 @@
         <v>0.09</v>
       </c>
       <c r="K37" t="n">
-        <v>16.05</v>
+        <v>7.22</v>
       </c>
       <c r="L37" t="n">
         <v>148.48</v>
@@ -31981,7 +31843,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>79.3</v>
@@ -32041,7 +31903,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>78.73</v>
@@ -32101,7 +31963,7 @@
         <v>0.01</v>
       </c>
       <c r="K4" t="n">
-        <v>1.17</v>
+        <v>0.39</v>
       </c>
       <c r="L4" t="n">
         <v>67.51000000000001</v>
@@ -32161,7 +32023,7 @@
         <v>0.01</v>
       </c>
       <c r="K5" t="n">
-        <v>0.61</v>
+        <v>0.2</v>
       </c>
       <c r="L5" t="n">
         <v>35.4</v>
@@ -32221,7 +32083,7 @@
         <v>0.01</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4</v>
+        <v>0.47</v>
       </c>
       <c r="L6" t="n">
         <v>80.76000000000001</v>

--- a/A_FINAL_RESULT/eko_transactions.xlsx
+++ b/A_FINAL_RESULT/eko_transactions.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -829,17 +829,19 @@
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>-2.96</v>
+      </c>
       <c r="L6" t="n">
-        <v>13.65</v>
+        <v>13.49</v>
       </c>
       <c r="M6" t="n">
         <v>0.83</v>
@@ -2547,7 +2549,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4 Л. ЛЯТНА ТЕЧНОСТ ЗА ЧИСТАЧКИ ГОТОВА</t>
+          <t>4 Л. ЛЯTHA TEЧHOCT ЗA ЧИCTAЧKИ ГOTOBA</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -2817,7 +2819,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5ЛSONAX ЗИМНА ТЕЧНОСТ ЧИСТАЧКИ-ГОТОВ</t>
+          <t>5ЛSONAX ЗИMHA TEЧHOCT ЧИCTAЧKИ-ГOTOB</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -3107,7 +3109,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -3405,7 +3407,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -3523,7 +3525,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2Л ЕКО ЛЯТНА ТЕЧНОСТ ЗА ЧИСТАЧКИ-ГОТОВА</t>
+          <t>2Л EKO ЛЯTHA TEЧHOCT ЗA ЧИCTAЧKИ-ГOTOBA</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -3701,7 +3703,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -3879,7 +3881,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -3997,7 +3999,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -4175,7 +4177,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -4293,7 +4295,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -4411,7 +4413,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -4469,7 +4471,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -4527,7 +4529,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -4585,7 +4587,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -5183,7 +5185,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -6511,7 +6513,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>5Л. ДОБАВКА ADBLUE ДИЗЕЛОВИ ДВИГАТЕЛИ</t>
+          <t>5Л. ДOБABKA ADBLUE ДИЗEЛOBИ ДBИГATEЛИ</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -6627,7 +6629,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10 Л. ДОБАВКА ADBLUE ДИЗЕЛОВИ ДВИГАТЕЛИ</t>
+          <t>10 Л. ДOБABKA ADBLUE ДИЗEЛOBИ ДBИГATEЛИ</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -6685,7 +6687,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4 Л. ЛЯТНА ТЕЧНОСТ ЗА ЧИСТАЧКИ ГОТОВА</t>
+          <t>4 Л. ЛЯTHA TEЧHOCT ЗA ЧИCTAЧKИ ГOTOBA</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -6801,7 +6803,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4 Л. ЛЯТНА ТЕЧНОСТ ЗА ЧИСТАЧКИ ГОТОВА</t>
+          <t>4 Л. ЛЯTHA TEЧHOCT ЗA ЧИCTAЧKИ ГOTOBA</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -7091,7 +7093,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4 Л. ЛЯТНА ТЕЧНОСТ ЗА ЧИСТАЧКИ ГОТОВА</t>
+          <t>4 Л. ЛЯTHA TEЧHOCT ЗA ЧИCTAЧKИ ГOTOBA</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -7323,7 +7325,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4 Л. ЛЯТНА ТЕЧНОСТ ЗА ЧИСТАЧКИ ГОТОВА</t>
+          <t>4 Л. ЛЯTHA TEЧHOCT ЗA ЧИCTAЧKИ ГOTOBA</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -14461,7 +14463,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2Л ЕКО ЛЯТНА ТЕЧНОСТ ЗА ЧИСТАЧКИ-ГОТОВА</t>
+          <t>2Л EKO ЛЯTHA TEЧHOCT ЗA ЧИCTAЧKИ-ГOTOBA</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -16955,7 +16957,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -16963,17 +16965,19 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>-5.25</v>
+      </c>
       <c r="L3" t="n">
-        <v>24.2</v>
+        <v>23.91</v>
       </c>
       <c r="M3" t="n">
         <v>0.83</v>
@@ -17167,7 +17171,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -17175,17 +17179,19 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>-6.36</v>
+      </c>
       <c r="L3" t="n">
-        <v>29.32</v>
+        <v>28.97</v>
       </c>
       <c r="M3" t="n">
         <v>0.83</v>
@@ -17777,7 +17783,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -17835,7 +17841,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -17843,17 +17849,19 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>-4.12</v>
+      </c>
       <c r="L3" t="n">
-        <v>19</v>
+        <v>18.77</v>
       </c>
       <c r="M3" t="n">
         <v>0.83</v>
@@ -18109,7 +18117,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2Л ЕКО ЛЯТНА ТЕЧНОСТ ЗА ЧИСТАЧКИ-ГОТОВА</t>
+          <t>2Л EKO ЛЯTHA TEЧHOCT ЗA ЧИCTAЧKИ-ГOTOBA</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -18563,7 +18571,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -18571,17 +18579,19 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>-5.05</v>
+      </c>
       <c r="L2" t="n">
-        <v>23.3</v>
+        <v>23.02</v>
       </c>
       <c r="M2" t="n">
         <v>0.83</v>
@@ -19653,7 +19663,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4 Л. ЛЯТНА ТЕЧНОСТ ЗА ЧИСТАЧКИ ГОТОВА</t>
+          <t>4 Л. ЛЯTHA TEЧHOCT ЗA ЧИCTAЧKИ ГOTOBA</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -20971,7 +20981,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>4Л MEGATRON SYNTHETIC 5W-40 МАСЛО</t>
+          <t>4Л MEGATRON SYNTHETIC 5W-40 MACЛO</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -21327,7 +21337,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>4 Л. ЛЯТНА ТЕЧНОСТ ЗА ЧИСТАЧКИ ГОТОВА</t>
+          <t>4 Л. ЛЯTHA TEЧHOCT ЗA ЧИCTAЧKИ ГOTOBA</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -21745,7 +21755,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2Л ЕКО ЛЯТНА ТЕЧНОСТ ЗА ЧИСТАЧКИ-ГОТОВА</t>
+          <t>2Л EKO ЛЯTHA TEЧHOCT ЗA ЧИCTAЧKИ-ГOTOBA</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -22043,7 +22053,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>4 Л. ЛЯТНА ТЕЧНОСТ ЗА ЧИСТАЧКИ ГОТОВА</t>
+          <t>4 Л. ЛЯTHA TEЧHOCT ЗA ЧИCTAЧKИ ГOTOBA</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -24139,7 +24149,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>АРОМАТИЗАТОР АРЕОН МОН XXL</t>
+          <t>APOMATИЗATOP APEOH MOH XXL</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -25781,7 +25791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P66"/>
+  <dimension ref="A1:P111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26365,7 +26375,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -26373,17 +26383,19 @@
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>-5.47</v>
+      </c>
       <c r="L10" t="n">
-        <v>25.24</v>
+        <v>24.94</v>
       </c>
       <c r="M10" t="n">
         <v>0.83</v>
@@ -26413,47 +26425,47 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>В 6049 НХ</t>
+          <t>В 8978 ВР</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>78970155027721509</t>
+          <t>78970155027721699</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>53.947</v>
+        <v>30.41</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>1.48</v>
+        <v>0.82</v>
       </c>
       <c r="I11" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>4.86</v>
+        <v>-5.47</v>
       </c>
       <c r="L11" t="n">
-        <v>79.84</v>
+        <v>24.94</v>
       </c>
       <c r="M11" t="n">
-        <v>1.51</v>
+        <v>0.83</v>
       </c>
       <c r="N11" t="n">
-        <v>81.45999999999999</v>
+        <v>25.24</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>11:41:40.000000</t>
+          <t>10:12:38.000000</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -26473,47 +26485,47 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>В 6049 НХ</t>
+          <t>В 8978 ВР</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>78970155027721509</t>
+          <t>78970155027721699</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>53.947</v>
+        <v>30.41</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>1.48</v>
+        <v>0.82</v>
       </c>
       <c r="I12" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>4.86</v>
+        <v>-5.47</v>
       </c>
       <c r="L12" t="n">
-        <v>79.84</v>
+        <v>24.94</v>
       </c>
       <c r="M12" t="n">
-        <v>1.51</v>
+        <v>0.83</v>
       </c>
       <c r="N12" t="n">
-        <v>81.45999999999999</v>
+        <v>25.24</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>11:41:40.000000</t>
+          <t>10:12:38.000000</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -26533,47 +26545,47 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>В 6049 НХ</t>
+          <t>В 8978 ВР</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>78970155027721509</t>
+          <t>78970155027721699</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>53.947</v>
+        <v>30.41</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>1.48</v>
+        <v>0.82</v>
       </c>
       <c r="I13" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>4.86</v>
+        <v>-5.47</v>
       </c>
       <c r="L13" t="n">
-        <v>79.84</v>
+        <v>24.94</v>
       </c>
       <c r="M13" t="n">
-        <v>1.51</v>
+        <v>0.83</v>
       </c>
       <c r="N13" t="n">
-        <v>81.45999999999999</v>
+        <v>25.24</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>11:41:40.000000</t>
+          <t>10:12:38.000000</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -26593,47 +26605,47 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>В 6049 НХ</t>
+          <t>В 8978 ВР</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>78970155027721509</t>
+          <t>78970155027721699</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>53.947</v>
+        <v>30.41</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>1.48</v>
+        <v>0.82</v>
       </c>
       <c r="I14" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>4.86</v>
+        <v>-5.47</v>
       </c>
       <c r="L14" t="n">
-        <v>79.84</v>
+        <v>24.94</v>
       </c>
       <c r="M14" t="n">
-        <v>1.51</v>
+        <v>0.83</v>
       </c>
       <c r="N14" t="n">
-        <v>81.45999999999999</v>
+        <v>25.24</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>11:41:40.000000</t>
+          <t>10:12:38.000000</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -26653,47 +26665,47 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>В 6049 НХ</t>
+          <t>В 8978 ВР</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>78970155027721509</t>
+          <t>78970155027721699</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>53.947</v>
+        <v>30.41</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>1.48</v>
+        <v>0.82</v>
       </c>
       <c r="I15" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>4.86</v>
+        <v>-5.47</v>
       </c>
       <c r="L15" t="n">
-        <v>79.84</v>
+        <v>24.94</v>
       </c>
       <c r="M15" t="n">
-        <v>1.51</v>
+        <v>0.83</v>
       </c>
       <c r="N15" t="n">
-        <v>81.45999999999999</v>
+        <v>25.24</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>11:41:40.000000</t>
+          <t>10:12:38.000000</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -26768,50 +26780,52 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Варна Порт</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>В 7230 ВР</t>
+          <t>В 6049 НХ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>78970155027721574</t>
+          <t>78970155027721509</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>19.361</v>
+        <v>53.947</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.83</v>
+        <v>1.48</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="n">
+        <v>4.86</v>
+      </c>
       <c r="L17" t="n">
-        <v>16.07</v>
+        <v>79.84</v>
       </c>
       <c r="M17" t="n">
-        <v>0.83</v>
+        <v>1.51</v>
       </c>
       <c r="N17" t="n">
-        <v>16.07</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>16:04:24.000000</t>
+          <t>11:41:40.000000</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -26821,55 +26835,57 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Търговище</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>В 7230 ВР</t>
+          <t>В 6049 НХ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>78970155027721574</t>
+          <t>78970155027721509</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>16.59</v>
+        <v>53.947</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>0.83</v>
+        <v>1.48</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>4.86</v>
+      </c>
       <c r="L18" t="n">
-        <v>13.77</v>
+        <v>79.84</v>
       </c>
       <c r="M18" t="n">
-        <v>0.83</v>
+        <v>1.51</v>
       </c>
       <c r="N18" t="n">
-        <v>13.77</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>07:04:39.000000</t>
+          <t>11:41:40.000000</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -26879,55 +26895,57 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Севлиево</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>В 7230 ВР</t>
+          <t>В 6049 НХ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>78970155027721574</t>
+          <t>78970155027721509</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>10.795</v>
+        <v>53.947</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.83</v>
+        <v>1.48</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>4.86</v>
+      </c>
       <c r="L19" t="n">
-        <v>8.960000000000001</v>
+        <v>79.84</v>
       </c>
       <c r="M19" t="n">
-        <v>0.83</v>
+        <v>1.51</v>
       </c>
       <c r="N19" t="n">
-        <v>8.960000000000001</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>09:25:30.000000</t>
+          <t>11:41:40.000000</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -26937,22 +26955,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Варна Сливница</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> В 5782 КН</t>
+          <t>В 6049 НХ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>78970155027721376</t>
+          <t>78970155027721509</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -26961,7 +26979,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>38</v>
+        <v>53.947</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
@@ -26974,20 +26992,20 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>3.42</v>
+        <v>4.86</v>
       </c>
       <c r="L20" t="n">
-        <v>56.24</v>
+        <v>79.84</v>
       </c>
       <c r="M20" t="n">
         <v>1.51</v>
       </c>
       <c r="N20" t="n">
-        <v>57.38</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>12:13:25.000000</t>
+          <t>11:41:40.000000</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -26997,22 +27015,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Варна Сливница</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> В 5782 КН</t>
+          <t>В 6049 НХ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>78970155027721376</t>
+          <t>78970155027721509</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -27021,7 +27039,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>38</v>
+        <v>53.947</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
@@ -27034,20 +27052,20 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>3.42</v>
+        <v>4.86</v>
       </c>
       <c r="L21" t="n">
-        <v>56.24</v>
+        <v>79.84</v>
       </c>
       <c r="M21" t="n">
         <v>1.51</v>
       </c>
       <c r="N21" t="n">
-        <v>57.38</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>12:13:25.000000</t>
+          <t>11:41:40.000000</t>
         </is>
       </c>
       <c r="P21" t="n">
@@ -27057,57 +27075,57 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Варна Сливница</t>
+          <t>Варна Порт</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> В 5782 КН</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>78970155027721376</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>38</v>
+        <v>19.361</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>1.48</v>
+        <v>0.82</v>
       </c>
       <c r="I22" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>3.42</v>
+        <v>-3.48</v>
       </c>
       <c r="L22" t="n">
-        <v>56.24</v>
+        <v>15.88</v>
       </c>
       <c r="M22" t="n">
-        <v>1.51</v>
+        <v>0.83</v>
       </c>
       <c r="N22" t="n">
-        <v>57.38</v>
+        <v>16.07</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>12:13:25.000000</t>
+          <t>16:04:24.000000</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -27117,57 +27135,57 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Варна Сливница</t>
+          <t>Варна Порт</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve"> В 5782 КН</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>78970155027721376</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>38</v>
+        <v>19.361</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>1.48</v>
+        <v>0.82</v>
       </c>
       <c r="I23" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>3.42</v>
+        <v>-3.48</v>
       </c>
       <c r="L23" t="n">
-        <v>56.24</v>
+        <v>15.88</v>
       </c>
       <c r="M23" t="n">
-        <v>1.51</v>
+        <v>0.83</v>
       </c>
       <c r="N23" t="n">
-        <v>57.38</v>
+        <v>16.07</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>12:13:25.000000</t>
+          <t>16:04:24.000000</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -27177,57 +27195,57 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Варна Сливница</t>
+          <t>Варна Порт</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve"> В 5782 КН</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>78970155027721376</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>38</v>
+        <v>19.361</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>1.48</v>
+        <v>0.82</v>
       </c>
       <c r="I24" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>3.42</v>
+        <v>-3.48</v>
       </c>
       <c r="L24" t="n">
-        <v>56.24</v>
+        <v>15.88</v>
       </c>
       <c r="M24" t="n">
-        <v>1.51</v>
+        <v>0.83</v>
       </c>
       <c r="N24" t="n">
-        <v>57.38</v>
+        <v>16.07</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>12:13:25.000000</t>
+          <t>16:04:24.000000</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -27237,57 +27255,57 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Варна Сливница</t>
+          <t>Варна Порт</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve"> В 5782 КН</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>78970155027721376</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>38</v>
+        <v>19.361</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>1.48</v>
+        <v>0.82</v>
       </c>
       <c r="I25" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>3.42</v>
+        <v>-3.48</v>
       </c>
       <c r="L25" t="n">
-        <v>56.24</v>
+        <v>15.88</v>
       </c>
       <c r="M25" t="n">
-        <v>1.51</v>
+        <v>0.83</v>
       </c>
       <c r="N25" t="n">
-        <v>57.38</v>
+        <v>16.07</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>12:13:25.000000</t>
+          <t>16:04:24.000000</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -27297,57 +27315,57 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Варна Варненчик</t>
+          <t>Варна Порт</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B 8917 BP</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>78970155027721269</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>32.149</v>
+        <v>19.361</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>1.78</v>
+        <v>0.82</v>
       </c>
       <c r="I26" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>3.54</v>
+        <v>-3.48</v>
       </c>
       <c r="L26" t="n">
-        <v>57.23</v>
+        <v>15.88</v>
       </c>
       <c r="M26" t="n">
-        <v>1.81</v>
+        <v>0.83</v>
       </c>
       <c r="N26" t="n">
-        <v>58.19</v>
+        <v>16.07</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>12:39:08.000000</t>
+          <t>16:04:24.000000</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -27357,57 +27375,57 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Варна Варненчик</t>
+          <t>Варна Порт</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B 8917 BP</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>78970155027721269</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>32.149</v>
+        <v>19.361</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>1.78</v>
+        <v>0.82</v>
       </c>
       <c r="I27" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>3.54</v>
+        <v>-3.48</v>
       </c>
       <c r="L27" t="n">
-        <v>57.23</v>
+        <v>15.88</v>
       </c>
       <c r="M27" t="n">
-        <v>1.81</v>
+        <v>0.83</v>
       </c>
       <c r="N27" t="n">
-        <v>58.19</v>
+        <v>16.07</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>12:39:08.000000</t>
+          <t>16:04:24.000000</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -27422,52 +27440,52 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Варна Варненчик</t>
+          <t>Търговище</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B 8917 BP</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>78970155027721269</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>32.149</v>
+        <v>16.59</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>1.78</v>
+        <v>0.82</v>
       </c>
       <c r="I28" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>3.54</v>
+        <v>-2.99</v>
       </c>
       <c r="L28" t="n">
-        <v>57.23</v>
+        <v>13.6</v>
       </c>
       <c r="M28" t="n">
-        <v>1.81</v>
+        <v>0.83</v>
       </c>
       <c r="N28" t="n">
-        <v>58.19</v>
+        <v>13.77</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>12:39:08.000000</t>
+          <t>07:04:39.000000</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -27482,52 +27500,52 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Варна Варненчик</t>
+          <t>Търговище</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B 8917 BP</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>78970155027721269</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>32.149</v>
+        <v>16.59</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>1.78</v>
+        <v>0.82</v>
       </c>
       <c r="I29" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>3.54</v>
+        <v>-2.99</v>
       </c>
       <c r="L29" t="n">
-        <v>57.23</v>
+        <v>13.6</v>
       </c>
       <c r="M29" t="n">
-        <v>1.81</v>
+        <v>0.83</v>
       </c>
       <c r="N29" t="n">
-        <v>58.19</v>
+        <v>13.77</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>12:39:08.000000</t>
+          <t>07:04:39.000000</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -27542,52 +27560,52 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Варна Варненчик</t>
+          <t>Търговище</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B 8917 BP</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>78970155027721269</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>32.149</v>
+        <v>16.59</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>1.78</v>
+        <v>0.82</v>
       </c>
       <c r="I30" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>3.54</v>
+        <v>-2.99</v>
       </c>
       <c r="L30" t="n">
-        <v>57.23</v>
+        <v>13.6</v>
       </c>
       <c r="M30" t="n">
-        <v>1.81</v>
+        <v>0.83</v>
       </c>
       <c r="N30" t="n">
-        <v>58.19</v>
+        <v>13.77</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>12:39:08.000000</t>
+          <t>07:04:39.000000</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -27602,52 +27620,52 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Варна Варненчик</t>
+          <t>Търговище</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B 8917 BP</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>78970155027721269</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>32.149</v>
+        <v>16.59</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>1.78</v>
+        <v>0.82</v>
       </c>
       <c r="I31" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>3.54</v>
+        <v>-2.99</v>
       </c>
       <c r="L31" t="n">
-        <v>57.23</v>
+        <v>13.6</v>
       </c>
       <c r="M31" t="n">
-        <v>1.81</v>
+        <v>0.83</v>
       </c>
       <c r="N31" t="n">
-        <v>58.19</v>
+        <v>13.77</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>12:39:08.000000</t>
+          <t>07:04:39.000000</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -27662,52 +27680,52 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Варна Чайка</t>
+          <t>Търговище</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B 4160 TK</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>78970155027721293</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>42.801</v>
+        <v>16.59</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>1.78</v>
+        <v>0.82</v>
       </c>
       <c r="I32" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>4.71</v>
+        <v>-2.99</v>
       </c>
       <c r="L32" t="n">
-        <v>76.19</v>
+        <v>13.6</v>
       </c>
       <c r="M32" t="n">
-        <v>1.81</v>
+        <v>0.83</v>
       </c>
       <c r="N32" t="n">
-        <v>77.47</v>
+        <v>13.77</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>13:21:42.000000</t>
+          <t>07:04:39.000000</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -27722,52 +27740,52 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Варна Чайка</t>
+          <t>Търговище</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B 4160 TK</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>78970155027721293</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>42.801</v>
+        <v>16.59</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>1.78</v>
+        <v>0.82</v>
       </c>
       <c r="I33" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>4.71</v>
+        <v>-2.99</v>
       </c>
       <c r="L33" t="n">
-        <v>76.19</v>
+        <v>13.6</v>
       </c>
       <c r="M33" t="n">
-        <v>1.81</v>
+        <v>0.83</v>
       </c>
       <c r="N33" t="n">
-        <v>77.47</v>
+        <v>13.77</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>13:21:42.000000</t>
+          <t>07:04:39.000000</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -27782,52 +27800,52 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Варна Чайка</t>
+          <t>Севлиево</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B 4160 TK</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>78970155027721293</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>42.801</v>
+        <v>10.795</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>1.78</v>
+        <v>0.82</v>
       </c>
       <c r="I34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>4.71</v>
+        <v>-1.94</v>
       </c>
       <c r="L34" t="n">
-        <v>76.19</v>
+        <v>8.85</v>
       </c>
       <c r="M34" t="n">
-        <v>1.81</v>
+        <v>0.83</v>
       </c>
       <c r="N34" t="n">
-        <v>77.47</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>13:21:42.000000</t>
+          <t>09:25:30.000000</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -27842,52 +27860,52 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Варна Чайка</t>
+          <t>Севлиево</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B 4160 TK</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>78970155027721293</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>42.801</v>
+        <v>10.795</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>1.78</v>
+        <v>0.82</v>
       </c>
       <c r="I35" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>4.71</v>
+        <v>-1.94</v>
       </c>
       <c r="L35" t="n">
-        <v>76.19</v>
+        <v>8.85</v>
       </c>
       <c r="M35" t="n">
-        <v>1.81</v>
+        <v>0.83</v>
       </c>
       <c r="N35" t="n">
-        <v>77.47</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>13:21:42.000000</t>
+          <t>09:25:30.000000</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -27902,52 +27920,52 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Варна Чайка</t>
+          <t>Севлиево</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B 4160 TK</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>78970155027721293</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>42.801</v>
+        <v>10.795</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>1.78</v>
+        <v>0.82</v>
       </c>
       <c r="I36" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>4.71</v>
+        <v>-1.94</v>
       </c>
       <c r="L36" t="n">
-        <v>76.19</v>
+        <v>8.85</v>
       </c>
       <c r="M36" t="n">
-        <v>1.81</v>
+        <v>0.83</v>
       </c>
       <c r="N36" t="n">
-        <v>77.47</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>13:21:42.000000</t>
+          <t>09:25:30.000000</t>
         </is>
       </c>
       <c r="P36" t="n">
@@ -27962,52 +27980,52 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Варна Чайка</t>
+          <t>Севлиево</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B 4160 TK</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>78970155027721293</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>42.801</v>
+        <v>10.795</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>1.78</v>
+        <v>0.82</v>
       </c>
       <c r="I37" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>4.71</v>
+        <v>-1.94</v>
       </c>
       <c r="L37" t="n">
-        <v>76.19</v>
+        <v>8.85</v>
       </c>
       <c r="M37" t="n">
-        <v>1.81</v>
+        <v>0.83</v>
       </c>
       <c r="N37" t="n">
-        <v>77.47</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>13:21:42.000000</t>
+          <t>09:25:30.000000</t>
         </is>
       </c>
       <c r="P37" t="n">
@@ -28022,52 +28040,52 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Варна Варненчик</t>
+          <t>Севлиево</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B 6386 HH</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>78970155027721301</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>58.149</v>
+        <v>10.795</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>1.78</v>
+        <v>0.82</v>
       </c>
       <c r="I38" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>6.4</v>
+        <v>-1.94</v>
       </c>
       <c r="L38" t="n">
-        <v>103.51</v>
+        <v>8.85</v>
       </c>
       <c r="M38" t="n">
-        <v>1.81</v>
+        <v>0.83</v>
       </c>
       <c r="N38" t="n">
-        <v>105.25</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>13:48:32.000000</t>
+          <t>09:25:30.000000</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -28082,52 +28100,52 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Варна Варненчик</t>
+          <t>Севлиево</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B 6386 HH</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>78970155027721301</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>58.149</v>
+        <v>10.795</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>1.78</v>
+        <v>0.82</v>
       </c>
       <c r="I39" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>6.4</v>
+        <v>-1.94</v>
       </c>
       <c r="L39" t="n">
-        <v>103.51</v>
+        <v>8.85</v>
       </c>
       <c r="M39" t="n">
-        <v>1.81</v>
+        <v>0.83</v>
       </c>
       <c r="N39" t="n">
-        <v>105.25</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>13:48:32.000000</t>
+          <t>09:25:30.000000</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -28142,30 +28160,30 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Варна Варненчик</t>
+          <t>Варна Сливница</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B 6386 HH</t>
+          <t xml:space="preserve"> В 5782 КН</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>78970155027721301</t>
+          <t>78970155027721376</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>58.149</v>
+        <v>38</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="I40" t="n">
         <v>0.03</v>
@@ -28174,20 +28192,20 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>6.4</v>
+        <v>3.42</v>
       </c>
       <c r="L40" t="n">
-        <v>103.51</v>
+        <v>56.24</v>
       </c>
       <c r="M40" t="n">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="N40" t="n">
-        <v>105.25</v>
+        <v>57.38</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>13:48:32.000000</t>
+          <t>12:13:25.000000</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -28202,30 +28220,30 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Варна Варненчик</t>
+          <t>Варна Сливница</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B 6386 HH</t>
+          <t xml:space="preserve"> В 5782 КН</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>78970155027721301</t>
+          <t>78970155027721376</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>58.149</v>
+        <v>38</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="I41" t="n">
         <v>0.03</v>
@@ -28234,20 +28252,20 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>6.4</v>
+        <v>3.42</v>
       </c>
       <c r="L41" t="n">
-        <v>103.51</v>
+        <v>56.24</v>
       </c>
       <c r="M41" t="n">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="N41" t="n">
-        <v>105.25</v>
+        <v>57.38</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>13:48:32.000000</t>
+          <t>12:13:25.000000</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -28262,30 +28280,30 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Варна Варненчик</t>
+          <t>Варна Сливница</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B 6386 HH</t>
+          <t xml:space="preserve"> В 5782 КН</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>78970155027721301</t>
+          <t>78970155027721376</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>58.149</v>
+        <v>38</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="I42" t="n">
         <v>0.03</v>
@@ -28294,20 +28312,20 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>6.4</v>
+        <v>3.42</v>
       </c>
       <c r="L42" t="n">
-        <v>103.51</v>
+        <v>56.24</v>
       </c>
       <c r="M42" t="n">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="N42" t="n">
-        <v>105.25</v>
+        <v>57.38</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>13:48:32.000000</t>
+          <t>12:13:25.000000</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -28322,30 +28340,30 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Варна Варненчик</t>
+          <t>Варна Сливница</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B 6386 HH</t>
+          <t xml:space="preserve"> В 5782 КН</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>78970155027721301</t>
+          <t>78970155027721376</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>58.149</v>
+        <v>38</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="I43" t="n">
         <v>0.03</v>
@@ -28354,20 +28372,20 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>6.4</v>
+        <v>3.42</v>
       </c>
       <c r="L43" t="n">
-        <v>103.51</v>
+        <v>56.24</v>
       </c>
       <c r="M43" t="n">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="N43" t="n">
-        <v>105.25</v>
+        <v>57.38</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>13:48:32.000000</t>
+          <t>12:13:25.000000</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -28382,17 +28400,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Варна Сливница</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Служебна ОВ 1</t>
+          <t xml:space="preserve"> В 5782 КН</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>78970155027721764</t>
+          <t>78970155027721376</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -28401,7 +28419,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>19.98</v>
+        <v>38</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
@@ -28414,20 +28432,20 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>1.8</v>
+        <v>3.42</v>
       </c>
       <c r="L44" t="n">
-        <v>29.57</v>
+        <v>56.24</v>
       </c>
       <c r="M44" t="n">
         <v>1.51</v>
       </c>
       <c r="N44" t="n">
-        <v>30.17</v>
+        <v>57.38</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>14:30:23.000000</t>
+          <t>12:13:25.000000</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -28442,17 +28460,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Варна Сливница</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Служебна ОВ 1</t>
+          <t xml:space="preserve"> В 5782 КН</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>78970155027721764</t>
+          <t>78970155027721376</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -28461,7 +28479,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>19.98</v>
+        <v>38</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
@@ -28474,20 +28492,20 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>1.8</v>
+        <v>3.42</v>
       </c>
       <c r="L45" t="n">
-        <v>29.57</v>
+        <v>56.24</v>
       </c>
       <c r="M45" t="n">
         <v>1.51</v>
       </c>
       <c r="N45" t="n">
-        <v>30.17</v>
+        <v>57.38</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>14:30:23.000000</t>
+          <t>12:13:25.000000</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -28502,30 +28520,30 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Варна Варненчик</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Служебна ОВ 1</t>
+          <t>B 8917 BP</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>78970155027721764</t>
+          <t>78970155027721269</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>DIESEL EKONOMY</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>19.98</v>
+        <v>32.149</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="I46" t="n">
         <v>0.03</v>
@@ -28534,20 +28552,20 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>1.8</v>
+        <v>3.54</v>
       </c>
       <c r="L46" t="n">
-        <v>29.57</v>
+        <v>57.23</v>
       </c>
       <c r="M46" t="n">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="N46" t="n">
-        <v>30.17</v>
+        <v>58.19</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>14:30:23.000000</t>
+          <t>12:39:08.000000</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -28562,30 +28580,30 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Варна Варненчик</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Служебна ОВ 1</t>
+          <t>B 8917 BP</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>78970155027721764</t>
+          <t>78970155027721269</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>DIESEL EKONOMY</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>19.98</v>
+        <v>32.149</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="I47" t="n">
         <v>0.03</v>
@@ -28594,20 +28612,20 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>1.8</v>
+        <v>3.54</v>
       </c>
       <c r="L47" t="n">
-        <v>29.57</v>
+        <v>57.23</v>
       </c>
       <c r="M47" t="n">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="N47" t="n">
-        <v>30.17</v>
+        <v>58.19</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>14:30:23.000000</t>
+          <t>12:39:08.000000</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -28622,30 +28640,30 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Варна Варненчик</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Служебна ОВ 1</t>
+          <t>B 8917 BP</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>78970155027721764</t>
+          <t>78970155027721269</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>DIESEL EKONOMY</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>19.98</v>
+        <v>32.149</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="I48" t="n">
         <v>0.03</v>
@@ -28654,20 +28672,20 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>1.8</v>
+        <v>3.54</v>
       </c>
       <c r="L48" t="n">
-        <v>29.57</v>
+        <v>57.23</v>
       </c>
       <c r="M48" t="n">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="N48" t="n">
-        <v>30.17</v>
+        <v>58.19</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>14:30:23.000000</t>
+          <t>12:39:08.000000</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -28682,30 +28700,30 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Варна Варненчик</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Служебна ОВ 1</t>
+          <t>B 8917 BP</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>78970155027721764</t>
+          <t>78970155027721269</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>DIESEL EKONOMY</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>19.98</v>
+        <v>32.149</v>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="I49" t="n">
         <v>0.03</v>
@@ -28714,20 +28732,20 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>1.8</v>
+        <v>3.54</v>
       </c>
       <c r="L49" t="n">
-        <v>29.57</v>
+        <v>57.23</v>
       </c>
       <c r="M49" t="n">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="N49" t="n">
-        <v>30.17</v>
+        <v>58.19</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>14:30:23.000000</t>
+          <t>12:39:08.000000</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -28742,50 +28760,52 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Варна Чайка</t>
+          <t>Варна Варненчик</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>В 7242 ВР</t>
+          <t>B 8917 BP</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>78970155027721616</t>
+          <t>78970155027721269</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>DIESEL EKONOMY</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>37.482</v>
+        <v>32.149</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>0.83</v>
+        <v>1.78</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="n">
+        <v>3.54</v>
+      </c>
       <c r="L50" t="n">
-        <v>31.11</v>
+        <v>57.23</v>
       </c>
       <c r="M50" t="n">
-        <v>0.83</v>
+        <v>1.81</v>
       </c>
       <c r="N50" t="n">
-        <v>31.11</v>
+        <v>58.19</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>16:36:03.000000</t>
+          <t>12:39:08.000000</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -28795,35 +28815,35 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Варна Порт</t>
+          <t>Варна Варненчик</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>В 6512 КС</t>
+          <t>B 8917 BP</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>78970155027721525</t>
+          <t>78970155027721269</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>DIESEL EKONOMY</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>38.702</v>
+        <v>32.149</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="I51" t="n">
         <v>0.03</v>
@@ -28832,58 +28852,58 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>3.48</v>
+        <v>3.54</v>
       </c>
       <c r="L51" t="n">
-        <v>57.28</v>
+        <v>57.23</v>
       </c>
       <c r="M51" t="n">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="N51" t="n">
-        <v>58.44</v>
+        <v>58.19</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>09:08:29.000000</t>
+          <t>12:39:08.000000</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>331738</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Варна Порт</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>В 6512 КС</t>
+          <t>B 4160 TK</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>78970155027721525</t>
+          <t>78970155027721293</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>DIESEL EKONOMY</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>38.702</v>
+        <v>42.801</v>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="I52" t="n">
         <v>0.03</v>
@@ -28892,58 +28912,58 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>3.48</v>
+        <v>4.71</v>
       </c>
       <c r="L52" t="n">
-        <v>57.28</v>
+        <v>76.19</v>
       </c>
       <c r="M52" t="n">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="N52" t="n">
-        <v>58.44</v>
+        <v>77.47</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>09:08:29.000000</t>
+          <t>13:21:42.000000</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>331738</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Варна Порт</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>В 6512 КС</t>
+          <t>B 4160 TK</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>78970155027721525</t>
+          <t>78970155027721293</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>DIESEL EKONOMY</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>38.702</v>
+        <v>42.801</v>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="I53" t="n">
         <v>0.03</v>
@@ -28952,58 +28972,58 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>3.48</v>
+        <v>4.71</v>
       </c>
       <c r="L53" t="n">
-        <v>57.28</v>
+        <v>76.19</v>
       </c>
       <c r="M53" t="n">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="N53" t="n">
-        <v>58.44</v>
+        <v>77.47</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>09:08:29.000000</t>
+          <t>13:21:42.000000</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>331738</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Варна Порт</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>В 6512 КС</t>
+          <t>B 4160 TK</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>78970155027721525</t>
+          <t>78970155027721293</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>DIESEL EKONOMY</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>38.702</v>
+        <v>42.801</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="I54" t="n">
         <v>0.03</v>
@@ -29012,58 +29032,58 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>3.48</v>
+        <v>4.71</v>
       </c>
       <c r="L54" t="n">
-        <v>57.28</v>
+        <v>76.19</v>
       </c>
       <c r="M54" t="n">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="N54" t="n">
-        <v>58.44</v>
+        <v>77.47</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>09:08:29.000000</t>
+          <t>13:21:42.000000</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>331738</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Варна Порт</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>В 6512 КС</t>
+          <t>B 4160 TK</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>78970155027721525</t>
+          <t>78970155027721293</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>DIESEL EKONOMY</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>38.702</v>
+        <v>42.801</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="I55" t="n">
         <v>0.03</v>
@@ -29072,58 +29092,58 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>3.48</v>
+        <v>4.71</v>
       </c>
       <c r="L55" t="n">
-        <v>57.28</v>
+        <v>76.19</v>
       </c>
       <c r="M55" t="n">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="N55" t="n">
-        <v>58.44</v>
+        <v>77.47</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>09:08:29.000000</t>
+          <t>13:21:42.000000</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>331738</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Варна Порт</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>В 6512 КС</t>
+          <t>B 4160 TK</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>78970155027721525</t>
+          <t>78970155027721293</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>DIESEL EKONOMY</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>38.702</v>
+        <v>42.801</v>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="I56" t="n">
         <v>0.03</v>
@@ -29132,78 +29152,80 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>3.48</v>
+        <v>4.71</v>
       </c>
       <c r="L56" t="n">
-        <v>57.28</v>
+        <v>76.19</v>
       </c>
       <c r="M56" t="n">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="N56" t="n">
-        <v>58.44</v>
+        <v>77.47</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>09:08:29.000000</t>
+          <t>13:21:42.000000</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>331738</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Благоевград Център</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>В 7230 ВР</t>
+          <t>B 4160 TK</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>78970155027721574</t>
+          <t>78970155027721293</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>DIESEL EKONOMY</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>25.916</v>
+        <v>42.801</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>0.83</v>
+        <v>1.78</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="n">
+        <v>4.71</v>
+      </c>
       <c r="L57" t="n">
-        <v>21.51</v>
+        <v>76.19</v>
       </c>
       <c r="M57" t="n">
-        <v>0.83</v>
+        <v>1.81</v>
       </c>
       <c r="N57" t="n">
-        <v>21.51</v>
+        <v>77.47</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>09:24:58.000000</t>
+          <t>13:21:42.000000</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -29213,22 +29235,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Варна Варненчик</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B 4161 TK</t>
+          <t>B 6386 HH</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>78970155027721285</t>
+          <t>78970155027721301</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -29237,11 +29259,11 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>40</v>
+        <v>58.149</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="I58" t="n">
         <v>0.03</v>
@@ -29250,20 +29272,20 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="L58" t="n">
-        <v>70.8</v>
+        <v>103.51</v>
       </c>
       <c r="M58" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="N58" t="n">
-        <v>72</v>
+        <v>105.25</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>13:08:08.000000</t>
+          <t>13:48:32.000000</t>
         </is>
       </c>
       <c r="P58" t="n">
@@ -29273,22 +29295,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Варна Варненчик</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>B 4161 TK</t>
+          <t>B 6386 HH</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>78970155027721285</t>
+          <t>78970155027721301</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -29297,11 +29319,11 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>40</v>
+        <v>58.149</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="I59" t="n">
         <v>0.03</v>
@@ -29310,20 +29332,20 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="L59" t="n">
-        <v>70.8</v>
+        <v>103.51</v>
       </c>
       <c r="M59" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="N59" t="n">
-        <v>72</v>
+        <v>105.25</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>13:08:08.000000</t>
+          <t>13:48:32.000000</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -29333,22 +29355,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Варна Варненчик</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B 4161 TK</t>
+          <t>B 6386 HH</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>78970155027721285</t>
+          <t>78970155027721301</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -29357,11 +29379,11 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>40</v>
+        <v>58.149</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="I60" t="n">
         <v>0.03</v>
@@ -29370,20 +29392,20 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="L60" t="n">
-        <v>70.8</v>
+        <v>103.51</v>
       </c>
       <c r="M60" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="N60" t="n">
-        <v>72</v>
+        <v>105.25</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>13:08:08.000000</t>
+          <t>13:48:32.000000</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -29393,22 +29415,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Варна Варненчик</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>B 4161 TK</t>
+          <t>B 6386 HH</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>78970155027721285</t>
+          <t>78970155027721301</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -29417,11 +29439,11 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>40</v>
+        <v>58.149</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="I61" t="n">
         <v>0.03</v>
@@ -29430,20 +29452,20 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="L61" t="n">
-        <v>70.8</v>
+        <v>103.51</v>
       </c>
       <c r="M61" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="N61" t="n">
-        <v>72</v>
+        <v>105.25</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>13:08:08.000000</t>
+          <t>13:48:32.000000</t>
         </is>
       </c>
       <c r="P61" t="n">
@@ -29453,22 +29475,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Варна Варненчик</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>B 4161 TK</t>
+          <t>B 6386 HH</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>78970155027721285</t>
+          <t>78970155027721301</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -29477,11 +29499,11 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>40</v>
+        <v>58.149</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="I62" t="n">
         <v>0.03</v>
@@ -29490,20 +29512,20 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="L62" t="n">
-        <v>70.8</v>
+        <v>103.51</v>
       </c>
       <c r="M62" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="N62" t="n">
-        <v>72</v>
+        <v>105.25</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>13:08:08.000000</t>
+          <t>13:48:32.000000</t>
         </is>
       </c>
       <c r="P62" t="n">
@@ -29513,22 +29535,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Варна Варненчик</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>B 4161 TK</t>
+          <t>B 6386 HH</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>78970155027721285</t>
+          <t>78970155027721301</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -29537,11 +29559,11 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>40</v>
+        <v>58.149</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="I63" t="n">
         <v>0.03</v>
@@ -29550,20 +29572,20 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="L63" t="n">
-        <v>70.8</v>
+        <v>103.51</v>
       </c>
       <c r="M63" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="N63" t="n">
-        <v>72</v>
+        <v>105.25</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>13:08:08.000000</t>
+          <t>13:48:32.000000</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -29573,55 +29595,57 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Севлиево</t>
+          <t>Варна</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>В 7230 ВР</t>
+          <t>Служебна ОВ 1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>78970155027721574</t>
+          <t>78970155027721764</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>27.663</v>
+        <v>19.98</v>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>0.83</v>
+        <v>1.48</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="n">
+        <v>1.8</v>
+      </c>
       <c r="L64" t="n">
-        <v>22.96</v>
+        <v>29.57</v>
       </c>
       <c r="M64" t="n">
-        <v>0.83</v>
+        <v>1.51</v>
       </c>
       <c r="N64" t="n">
-        <v>22.96</v>
+        <v>30.17</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>14:05:46.000000</t>
+          <t>14:30:23.000000</t>
         </is>
       </c>
       <c r="P64" t="n">
@@ -29631,55 +29655,57 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Търговище</t>
+          <t>Варна</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>В 7230 ВР</t>
+          <t>Служебна ОВ 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>78970155027721574</t>
+          <t>78970155027721764</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>10.157</v>
+        <v>19.98</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>0.83</v>
+        <v>1.48</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="n">
+        <v>1.8</v>
+      </c>
       <c r="L65" t="n">
-        <v>8.43</v>
+        <v>29.57</v>
       </c>
       <c r="M65" t="n">
-        <v>0.83</v>
+        <v>1.51</v>
       </c>
       <c r="N65" t="n">
-        <v>8.43</v>
+        <v>30.17</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>16:03:15.000000</t>
+          <t>14:30:23.000000</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -29689,7 +29715,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -29699,48 +29725,2750 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>В8972ВР</t>
+          <t>Служебна ОВ 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>78970155027721343</t>
+          <t>78970155027721764</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>28.072</v>
+        <v>19.98</v>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L66" t="n">
+        <v>29.57</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="N66" t="n">
+        <v>30.17</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>14:30:23.000000</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Варна</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Служебна ОВ 1</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>78970155027721764</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>95 EKONOMY UNLEADED</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L67" t="n">
+        <v>29.57</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="N67" t="n">
+        <v>30.17</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>14:30:23.000000</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Варна</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Служебна ОВ 1</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>78970155027721764</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>95 EKONOMY UNLEADED</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L68" t="n">
+        <v>29.57</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="N68" t="n">
+        <v>30.17</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>14:30:23.000000</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Варна</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Служебна ОВ 1</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>78970155027721764</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>95 EKONOMY UNLEADED</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L69" t="n">
+        <v>29.57</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="N69" t="n">
+        <v>30.17</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>14:30:23.000000</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Варна Чайка</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>В 7242 ВР</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>78970155027721616</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>37.482</v>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-6.75</v>
+      </c>
+      <c r="L70" t="n">
+        <v>30.74</v>
+      </c>
+      <c r="M70" t="n">
         <v>0.83</v>
       </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="n">
+      <c r="N70" t="n">
+        <v>31.11</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>16:36:03.000000</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Варна Чайка</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>В 7242 ВР</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>78970155027721616</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>37.482</v>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>-6.75</v>
+      </c>
+      <c r="L71" t="n">
+        <v>30.74</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N71" t="n">
+        <v>31.11</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>16:36:03.000000</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Варна Чайка</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>В 7242 ВР</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>78970155027721616</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>37.482</v>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-6.75</v>
+      </c>
+      <c r="L72" t="n">
+        <v>30.74</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N72" t="n">
+        <v>31.11</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>16:36:03.000000</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Варна Чайка</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>В 7242 ВР</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>78970155027721616</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>37.482</v>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>-6.75</v>
+      </c>
+      <c r="L73" t="n">
+        <v>30.74</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N73" t="n">
+        <v>31.11</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>16:36:03.000000</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Варна Чайка</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>В 7242 ВР</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>78970155027721616</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>37.482</v>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-6.75</v>
+      </c>
+      <c r="L74" t="n">
+        <v>30.74</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N74" t="n">
+        <v>31.11</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>16:36:03.000000</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Варна Чайка</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>В 7242 ВР</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>78970155027721616</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>37.482</v>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-6.75</v>
+      </c>
+      <c r="L75" t="n">
+        <v>30.74</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N75" t="n">
+        <v>31.11</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>16:36:03.000000</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Варна Порт</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>В 6512 КС</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>78970155027721525</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>95 EKONOMY UNLEADED</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>38.702</v>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="L76" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="N76" t="n">
+        <v>58.44</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>09:08:29.000000</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>331738</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Варна Порт</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>В 6512 КС</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>78970155027721525</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>95 EKONOMY UNLEADED</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>38.702</v>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="L77" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="M77" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="N77" t="n">
+        <v>58.44</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>09:08:29.000000</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>331738</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Варна Порт</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>В 6512 КС</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>78970155027721525</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>95 EKONOMY UNLEADED</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>38.702</v>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="L78" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="N78" t="n">
+        <v>58.44</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>09:08:29.000000</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>331738</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Варна Порт</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>В 6512 КС</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>78970155027721525</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>95 EKONOMY UNLEADED</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>38.702</v>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="L79" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="N79" t="n">
+        <v>58.44</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>09:08:29.000000</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>331738</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Варна Порт</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>В 6512 КС</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>78970155027721525</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>95 EKONOMY UNLEADED</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>38.702</v>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="L80" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="N80" t="n">
+        <v>58.44</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>09:08:29.000000</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>331738</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Варна Порт</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>В 6512 КС</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>78970155027721525</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>95 EKONOMY UNLEADED</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>38.702</v>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="L81" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="M81" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="N81" t="n">
+        <v>58.44</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>09:08:29.000000</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>331738</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Благоевград Център</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>В 7230 ВР</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>78970155027721574</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>25.916</v>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>-4.66</v>
+      </c>
+      <c r="L82" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N82" t="n">
+        <v>21.51</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>09:24:58.000000</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Благоевград Център</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>В 7230 ВР</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>78970155027721574</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>25.916</v>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>-4.66</v>
+      </c>
+      <c r="L83" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N83" t="n">
+        <v>21.51</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>09:24:58.000000</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Благоевград Център</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>В 7230 ВР</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>78970155027721574</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>25.916</v>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>-4.66</v>
+      </c>
+      <c r="L84" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N84" t="n">
+        <v>21.51</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>09:24:58.000000</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Благоевград Център</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>В 7230 ВР</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>78970155027721574</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>25.916</v>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>-4.66</v>
+      </c>
+      <c r="L85" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N85" t="n">
+        <v>21.51</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>09:24:58.000000</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Благоевград Център</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>В 7230 ВР</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>78970155027721574</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>25.916</v>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>-4.66</v>
+      </c>
+      <c r="L86" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N86" t="n">
+        <v>21.51</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>09:24:58.000000</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Благоевград Център</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>В 7230 ВР</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>78970155027721574</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>25.916</v>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>-4.66</v>
+      </c>
+      <c r="L87" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N87" t="n">
+        <v>21.51</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>09:24:58.000000</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Варна</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>B 4161 TK</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>78970155027721285</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>DIESEL EKONOMY</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>40</v>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L88" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N88" t="n">
+        <v>72</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>13:08:08.000000</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Варна</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>B 4161 TK</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>78970155027721285</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>DIESEL EKONOMY</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>40</v>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L89" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N89" t="n">
+        <v>72</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>13:08:08.000000</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Варна</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>B 4161 TK</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>78970155027721285</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>DIESEL EKONOMY</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>40</v>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L90" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N90" t="n">
+        <v>72</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>13:08:08.000000</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Варна</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>B 4161 TK</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>78970155027721285</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>DIESEL EKONOMY</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>40</v>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L91" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N91" t="n">
+        <v>72</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>13:08:08.000000</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Варна</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>B 4161 TK</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>78970155027721285</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>DIESEL EKONOMY</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>40</v>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L92" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="M92" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N92" t="n">
+        <v>72</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>13:08:08.000000</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Варна</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>B 4161 TK</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>78970155027721285</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>DIESEL EKONOMY</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>40</v>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L93" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="M93" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N93" t="n">
+        <v>72</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>13:08:08.000000</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Севлиево</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>В 7230 ВР</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>78970155027721574</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>27.663</v>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="L94" t="n">
+        <v>22.68</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N94" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>14:05:46.000000</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Севлиево</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>В 7230 ВР</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>78970155027721574</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>27.663</v>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="L95" t="n">
+        <v>22.68</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N95" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>14:05:46.000000</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Севлиево</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>В 7230 ВР</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>78970155027721574</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>27.663</v>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="L96" t="n">
+        <v>22.68</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N96" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>14:05:46.000000</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Севлиево</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>В 7230 ВР</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>78970155027721574</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>27.663</v>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="L97" t="n">
+        <v>22.68</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N97" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>14:05:46.000000</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Севлиево</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>В 7230 ВР</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>78970155027721574</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>27.663</v>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="L98" t="n">
+        <v>22.68</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N98" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>14:05:46.000000</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Севлиево</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>В 7230 ВР</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>78970155027721574</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>27.663</v>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="L99" t="n">
+        <v>22.68</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N99" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>14:05:46.000000</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Търговище</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>В 7230 ВР</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>78970155027721574</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>10.157</v>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="L100" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N100" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>16:03:15.000000</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Търговище</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>В 7230 ВР</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>78970155027721574</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>10.157</v>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="L101" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N101" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>16:03:15.000000</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Търговище</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>В 7230 ВР</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>78970155027721574</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>10.157</v>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="L102" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N102" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>16:03:15.000000</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Търговище</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>В 7230 ВР</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>78970155027721574</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>10.157</v>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="L103" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N103" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>16:03:15.000000</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Търговище</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>В 7230 ВР</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>78970155027721574</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>10.157</v>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="L104" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N104" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>16:03:15.000000</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Търговище</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>В 7230 ВР</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>78970155027721574</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>10.157</v>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="L105" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N105" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>16:03:15.000000</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Варна</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>В8972ВР</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>78970155027721343</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>28.072</v>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="L106" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N106" t="n">
         <v>23.3</v>
       </c>
-      <c r="M66" t="n">
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>09:12:30.000000</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Варна</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>В8972ВР</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>78970155027721343</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>28.072</v>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="L107" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="M107" t="n">
         <v>0.83</v>
       </c>
-      <c r="N66" t="n">
+      <c r="N107" t="n">
         <v>23.3</v>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="O107" t="inlineStr">
         <is>
           <t>09:12:30.000000</t>
         </is>
       </c>
-      <c r="P66" t="n">
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Варна</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>В8972ВР</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>78970155027721343</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>28.072</v>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="L108" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N108" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>09:12:30.000000</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Варна</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>В8972ВР</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>78970155027721343</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>28.072</v>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="L109" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N109" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>09:12:30.000000</t>
+        </is>
+      </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Варна</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>В8972ВР</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>78970155027721343</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>28.072</v>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="L110" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N110" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>09:12:30.000000</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Варна</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>В8972ВР</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>78970155027721343</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>28.072</v>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="L111" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N111" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>09:12:30.000000</t>
+        </is>
+      </c>
+      <c r="P111" t="n">
         <v>0</v>
       </c>
     </row>
@@ -31027,7 +33755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31135,7 +33863,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -31193,7 +33921,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -31201,17 +33929,19 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>-5.16</v>
+      </c>
       <c r="L3" t="n">
-        <v>23.78</v>
+        <v>23.49</v>
       </c>
       <c r="M3" t="n">
         <v>0.83</v>
@@ -31231,7 +33961,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -31241,48 +33971,650 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>В 2763 ТА</t>
+          <t>В 2764 ТА</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>78970155027721996</t>
+          <t>78970155027722002</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>28.277</v>
+        <v>28.651</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>-5.16</v>
+      </c>
       <c r="L4" t="n">
-        <v>23.47</v>
+        <v>23.49</v>
       </c>
       <c r="M4" t="n">
         <v>0.83</v>
       </c>
       <c r="N4" t="n">
+        <v>23.78</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>11:56:06.000000</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>56450</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Варна Порт</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>В 2764 ТА</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>78970155027722002</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>28.651</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-5.16</v>
+      </c>
+      <c r="L5" t="n">
+        <v>23.49</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N5" t="n">
+        <v>23.78</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>11:56:06.000000</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>56450</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Варна Порт</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>В 2764 ТА</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>78970155027722002</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>28.651</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-5.16</v>
+      </c>
+      <c r="L6" t="n">
+        <v>23.49</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N6" t="n">
+        <v>23.78</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>11:56:06.000000</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>56450</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Варна Порт</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>В 2764 ТА</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>78970155027722002</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>28.651</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-5.16</v>
+      </c>
+      <c r="L7" t="n">
+        <v>23.49</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N7" t="n">
+        <v>23.78</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>11:56:06.000000</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>56450</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Варна Порт</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>В 2764 ТА</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>78970155027722002</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>28.651</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-5.16</v>
+      </c>
+      <c r="L8" t="n">
+        <v>23.49</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N8" t="n">
+        <v>23.78</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>11:56:06.000000</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>56450</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Варна Порт</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>В 2763 ТА</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>78970155027721996</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>28.277</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-5.09</v>
+      </c>
+      <c r="L9" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N9" t="n">
         <v>23.47</v>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>15:21:46.000000</t>
         </is>
       </c>
-      <c r="P4" t="n">
+      <c r="P9" t="n">
+        <v>57260</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Варна Порт</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>В 2763 ТА</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>78970155027721996</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>28.277</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-5.09</v>
+      </c>
+      <c r="L10" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N10" t="n">
+        <v>23.47</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>15:21:46.000000</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>57260</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Варна Порт</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>В 2763 ТА</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>78970155027721996</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>28.277</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-5.09</v>
+      </c>
+      <c r="L11" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N11" t="n">
+        <v>23.47</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>15:21:46.000000</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>57260</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Варна Порт</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>В 2763 ТА</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>78970155027721996</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>28.277</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-5.09</v>
+      </c>
+      <c r="L12" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N12" t="n">
+        <v>23.47</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>15:21:46.000000</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>57260</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Варна Порт</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>В 2763 ТА</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>78970155027721996</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>28.277</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-5.09</v>
+      </c>
+      <c r="L13" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N13" t="n">
+        <v>23.47</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>15:21:46.000000</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>57260</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Варна Порт</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>В 2763 ТА</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>78970155027721996</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>28.277</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-5.09</v>
+      </c>
+      <c r="L14" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N14" t="n">
+        <v>23.47</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>15:21:46.000000</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
         <v>57260</v>
       </c>
     </row>
@@ -38371,7 +41703,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -39747,7 +43079,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -39755,17 +43087,19 @@
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="n">
+        <v>-4.79</v>
+      </c>
       <c r="L38" t="n">
-        <v>22.09</v>
+        <v>21.82</v>
       </c>
       <c r="M38" t="n">
         <v>0.83</v>
@@ -44437,7 +47771,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -44555,7 +47889,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -45129,7 +48463,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -45137,17 +48471,19 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>-4.88</v>
+      </c>
       <c r="L2" t="n">
-        <v>22.52</v>
+        <v>22.25</v>
       </c>
       <c r="M2" t="n">
         <v>0.83</v>
@@ -45403,7 +48739,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -45411,17 +48747,19 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>24.85</v>
+      </c>
       <c r="L2" t="n">
-        <v>25.15</v>
+        <v>24.85</v>
       </c>
       <c r="M2" t="n">
         <v>0.83</v>
@@ -45461,7 +48799,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -45469,17 +48807,19 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>27.64</v>
+      </c>
       <c r="L3" t="n">
-        <v>27.98</v>
+        <v>27.64</v>
       </c>
       <c r="M3" t="n">
         <v>0.83</v>
@@ -45519,7 +48859,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -45527,17 +48867,19 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>-4.78</v>
+      </c>
       <c r="L4" t="n">
-        <v>22.02</v>
+        <v>21.75</v>
       </c>
       <c r="M4" t="n">
         <v>0.83</v>
@@ -45577,7 +48919,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -45585,17 +48927,19 @@
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>-3.66</v>
+      </c>
       <c r="L5" t="n">
-        <v>16.9</v>
+        <v>16.7</v>
       </c>
       <c r="M5" t="n">
         <v>0.83</v>
@@ -45731,7 +49075,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -45739,17 +49083,19 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>-5.55</v>
+      </c>
       <c r="L2" t="n">
-        <v>25.61</v>
+        <v>25.3</v>
       </c>
       <c r="M2" t="n">
         <v>0.83</v>
@@ -46101,7 +49447,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -46109,17 +49455,19 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>-1.5</v>
+      </c>
       <c r="L2" t="n">
-        <v>6.9</v>
+        <v>6.82</v>
       </c>
       <c r="M2" t="n">
         <v>0.83</v>
@@ -46687,7 +50035,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -47801,7 +51149,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -47859,7 +51207,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -47917,7 +51265,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -48035,7 +51383,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -48093,7 +51441,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -48151,7 +51499,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -48269,7 +51617,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -48447,7 +51795,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -48565,7 +51913,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -48683,7 +52031,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -48801,7 +52149,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -49039,7 +52387,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -49097,7 +52445,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -49155,7 +52503,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -49273,7 +52621,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -55979,7 +59327,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -58017,7 +61365,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -60895,7 +64243,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -70781,7 +74129,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -70839,7 +74187,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -71013,7 +74361,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -71071,7 +74419,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -71129,7 +74477,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -71187,7 +74535,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -71361,7 +74709,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -71419,7 +74767,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -71535,7 +74883,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -71709,7 +75057,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -71767,7 +75115,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -71825,7 +75173,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -71941,7 +75289,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -71999,7 +75347,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -72115,7 +75463,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Е GAS LPG</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -73925,7 +77273,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4 Л. ЛЯТНА ТЕЧНОСТ ЗА ЧИСТАЧКИ ГОТОВА</t>
+          <t>4 Л. ЛЯTHA TEЧHOCT ЗA ЧИCTAЧKИ ГOTOBA</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -75123,7 +78471,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>10 Л. ДОБАВКА ADPLUS ДИЗЕЛОВИ ДВИГАТЕЛИ</t>
+          <t>10 Л. ДOБABKA ADPLUS ДИЗEЛOBИ ДBИГATEЛИ</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -75301,7 +78649,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>10 Л. ДОБАВКА ADPLUS ДИЗЕЛОВИ ДВИГАТЕЛИ</t>
+          <t>10 Л. ДOБABKA ADPLUS ДИЗEЛOBИ ДBИГATEЛИ</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -75419,7 +78767,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ОСРАМ Н7 64210 55W 12V PH26D</t>
+          <t>OCPAM H7 64210 55W 12V PH26D</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -75597,7 +78945,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>5Л. ДОБАВКА ADBLUE ДИЗЕЛОВИ ДВИГАТЕЛИ</t>
+          <t>5Л. ДOБABKA ADBLUE ДИЗEЛOBИ ДBИГATEЛИ</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -76587,7 +79935,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>50МЛ. АРОМАТИЗАТОР "АРЕОН ПАРФЮМ"</t>
+          <t>50MЛ. APOMATИЗATOP "APEOH ПAPФЮM"</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -76645,7 +79993,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ХАРТИЕН АРОМАТИЗАТОР АРЕОН VIP</t>
+          <t>XAPTИEH APOMATИЗATOP APEOH VIP</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -77663,7 +81011,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>4 Л. ЛЯТНА ТЕЧНОСТ ЗА ЧИСТАЧКИ ГОТОВА</t>
+          <t>4 Л. ЛЯTHA TEЧHOCT ЗA ЧИCTAЧKИ ГOTOBA</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -78981,7 +82329,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2Л ЕКО ЛЯТНА ТЕЧНОСТ ЗА ЧИСТАЧКИ-ГОТОВА</t>
+          <t>2Л EKO ЛЯTHA TEЧHOCT ЗA ЧИCTAЧKИ-ГOTOBA</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -79279,7 +82627,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2Л ЕКО ЛЯТНА ТЕЧНОСТ ЗА ЧИСТАЧКИ-ГОТОВА</t>
+          <t>2Л EKO ЛЯTHA TEЧHOCT ЗA ЧИCTAЧKИ-ГOTOBA</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -80117,7 +83465,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2Л ЕКО ЛЯТНА ТЕЧНОСТ ЗА ЧИСТАЧКИ-ГОТОВА</t>
+          <t>2Л EKO ЛЯTHA TEЧHOCT ЗA ЧИCTAЧKИ-ГOTOBA</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -80355,7 +83703,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2Л ЕКО ЛЯТНА ТЕЧНОСТ ЗА ЧИСТАЧКИ-ГОТОВА</t>
+          <t>2Л EKO ЛЯTHA TEЧHOCT ЗA ЧИCTAЧKИ-ГOTOBA</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -80533,7 +83881,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>10 Л. ДОБАВКА ADPLUS ДИЗЕЛОВИ ДВИГАТЕЛИ</t>
+          <t>10 Л. ДOБABKA ADPLUS ДИЗEЛOBИ ДBИГATEЛИ</t>
         </is>
       </c>
       <c r="F73" t="n">

--- a/A_FINAL_RESULT/eko_transactions.xlsx
+++ b/A_FINAL_RESULT/eko_transactions.xlsx
@@ -1585,7 +1585,7 @@
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
         <v>0.6</v>
       </c>
       <c r="L10" t="n">
-        <v>51.55</v>
+        <v>50.95</v>
       </c>
       <c r="M10" t="n">
         <v>1.82</v>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -2053,7 +2053,7 @@
         <v>0.28</v>
       </c>
       <c r="L7" t="n">
-        <v>23.68</v>
+        <v>23.41</v>
       </c>
       <c r="M7" t="n">
         <v>1.82</v>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -4665,7 +4665,7 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>34.41</v>
+        <v>34.01</v>
       </c>
       <c r="M35" t="n">
         <v>1.82</v>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -4725,7 +4725,7 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>71.11</v>
+        <v>70.27</v>
       </c>
       <c r="M36" t="n">
         <v>1.82</v>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -4785,7 +4785,7 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>94.62</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="M37" t="n">
         <v>1.82</v>
@@ -6253,10 +6253,10 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="K17" t="n">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="L17" t="n">
         <v>89.3</v>
@@ -6313,10 +6313,10 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="K18" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="L18" t="n">
         <v>602</v>
@@ -6373,10 +6373,10 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="K19" t="n">
-        <v>9.94</v>
+        <v>19.88</v>
       </c>
       <c r="L19" t="n">
         <v>854.84</v>
@@ -8503,7 +8503,7 @@
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -8515,7 +8515,7 @@
         <v>1.55</v>
       </c>
       <c r="L12" t="n">
-        <v>74.02</v>
+        <v>73.5</v>
       </c>
       <c r="M12" t="n">
         <v>1.51</v>
@@ -10932,7 +10932,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>6.48</v>
+        <v>8.1</v>
       </c>
       <c r="L14" t="n">
         <v>144.2</v>
@@ -12927,7 +12927,7 @@
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -12939,7 +12939,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>272.06</v>
+        <v>268.86</v>
       </c>
       <c r="M27" t="n">
         <v>1.82</v>
@@ -12987,7 +12987,7 @@
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>234.83</v>
+        <v>232.07</v>
       </c>
       <c r="M28" t="n">
         <v>1.82</v>
@@ -14377,19 +14377,19 @@
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K14" t="n">
-        <v>0.77</v>
+        <v>1.15</v>
       </c>
       <c r="L14" t="n">
-        <v>66.17</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="M14" t="n">
         <v>1.82</v>
@@ -17361,17 +17361,19 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>0.9</v>
+      </c>
       <c r="L2" t="n">
-        <v>15.1</v>
+        <v>14.8</v>
       </c>
       <c r="M2" t="n">
         <v>1.51</v>
@@ -18031,17 +18033,19 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>-4.48</v>
+      </c>
       <c r="L2" t="n">
-        <v>20.66</v>
+        <v>20.41</v>
       </c>
       <c r="M2" t="n">
         <v>0.83</v>
@@ -19044,7 +19048,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>7.03</v>
+        <v>8.59</v>
       </c>
       <c r="L3" t="n">
         <v>139.86</v>
@@ -23319,7 +23323,7 @@
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
@@ -23331,7 +23335,7 @@
         <v>0.88</v>
       </c>
       <c r="L70" t="n">
-        <v>75.93000000000001</v>
+        <v>75.05</v>
       </c>
       <c r="M70" t="n">
         <v>1.82</v>
@@ -23379,7 +23383,7 @@
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
@@ -23391,7 +23395,7 @@
         <v>1.04</v>
       </c>
       <c r="L71" t="n">
-        <v>89.44</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="M71" t="n">
         <v>1.82</v>
@@ -23439,7 +23443,7 @@
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
@@ -23451,7 +23455,7 @@
         <v>0.7</v>
       </c>
       <c r="L72" t="n">
-        <v>60.21</v>
+        <v>59.51</v>
       </c>
       <c r="M72" t="n">
         <v>1.82</v>
@@ -23557,7 +23561,7 @@
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="I74" t="n">
         <v>0</v>
@@ -23569,7 +23573,7 @@
         <v>0.97</v>
       </c>
       <c r="L74" t="n">
-        <v>83.59</v>
+        <v>82.62</v>
       </c>
       <c r="M74" t="n">
         <v>1.82</v>
@@ -26091,7 +26095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P117"/>
+  <dimension ref="A1:P127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26207,17 +26211,19 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>2.07</v>
+      </c>
       <c r="L2" t="n">
-        <v>34.73</v>
+        <v>34.04</v>
       </c>
       <c r="M2" t="n">
         <v>1.51</v>
@@ -26247,12 +26253,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>В 2852 РК</t>
+          <t>В 4582 РР</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>78970155027721442</t>
+          <t>78970155027721475</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -26261,31 +26267,33 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>41.543</v>
+        <v>23</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>2.07</v>
+      </c>
       <c r="L3" t="n">
-        <v>62.73</v>
+        <v>34.04</v>
       </c>
       <c r="M3" t="n">
         <v>1.51</v>
       </c>
       <c r="N3" t="n">
-        <v>62.73</v>
+        <v>34.73</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>16:59:27.000000</t>
+          <t>16:11:23.000000</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -26295,57 +26303,57 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Варна Порт</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>В 9347 РН</t>
+          <t>В 4582 РР</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>78970155027721731</t>
+          <t>78970155027721475</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>DIESEL DOUBLE FILTERED</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>29.587</v>
+        <v>23</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="L4" t="n">
-        <v>52.66</v>
+        <v>34.04</v>
       </c>
       <c r="M4" t="n">
-        <v>2.06</v>
+        <v>1.51</v>
       </c>
       <c r="N4" t="n">
-        <v>60.95</v>
+        <v>34.73</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>10:10:20.000000</t>
+          <t>16:11:23.000000</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -26355,57 +26363,57 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Варна Порт</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>В 9347 РН</t>
+          <t>В 4582 РР</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>78970155027721731</t>
+          <t>78970155027721475</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>DIESEL DOUBLE FILTERED</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>29.587</v>
+        <v>23</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="L5" t="n">
-        <v>52.66</v>
+        <v>34.04</v>
       </c>
       <c r="M5" t="n">
-        <v>2.06</v>
+        <v>1.51</v>
       </c>
       <c r="N5" t="n">
-        <v>60.95</v>
+        <v>34.73</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>10:10:20.000000</t>
+          <t>16:11:23.000000</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -26415,57 +26423,57 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Варна Порт</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>В 9347 РН</t>
+          <t>В 4582 РР</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>78970155027721731</t>
+          <t>78970155027721475</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DIESEL DOUBLE FILTERED</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>29.587</v>
+        <v>23</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="L6" t="n">
-        <v>52.66</v>
+        <v>34.04</v>
       </c>
       <c r="M6" t="n">
-        <v>2.06</v>
+        <v>1.51</v>
       </c>
       <c r="N6" t="n">
-        <v>60.95</v>
+        <v>34.73</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>10:10:20.000000</t>
+          <t>16:11:23.000000</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -26475,57 +26483,57 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Варна Порт</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>В 9347 РН</t>
+          <t>В 4582 РР</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>78970155027721731</t>
+          <t>78970155027721475</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>DIESEL DOUBLE FILTERED</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>29.587</v>
+        <v>23</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="L7" t="n">
-        <v>52.66</v>
+        <v>34.04</v>
       </c>
       <c r="M7" t="n">
-        <v>2.06</v>
+        <v>1.51</v>
       </c>
       <c r="N7" t="n">
-        <v>60.95</v>
+        <v>34.73</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>10:10:20.000000</t>
+          <t>16:11:23.000000</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -26535,57 +26543,57 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Варна Порт</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>В 9347 РН</t>
+          <t>В 2852 РК</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>78970155027721731</t>
+          <t>78970155027721442</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DIESEL DOUBLE FILTERED</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>29.587</v>
+        <v>41.543</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="L8" t="n">
-        <v>52.66</v>
+        <v>61.48</v>
       </c>
       <c r="M8" t="n">
-        <v>2.06</v>
+        <v>1.51</v>
       </c>
       <c r="N8" t="n">
-        <v>60.95</v>
+        <v>62.73</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>10:10:20.000000</t>
+          <t>16:59:27.000000</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -26595,57 +26603,57 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Варна Порт</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>В 9347 РН</t>
+          <t>В 2852 РК</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>78970155027721731</t>
+          <t>78970155027721442</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>DIESEL DOUBLE FILTERED</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>29.587</v>
+        <v>41.543</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="L9" t="n">
-        <v>52.66</v>
+        <v>61.48</v>
       </c>
       <c r="M9" t="n">
-        <v>2.06</v>
+        <v>1.51</v>
       </c>
       <c r="N9" t="n">
-        <v>60.95</v>
+        <v>62.73</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>10:10:20.000000</t>
+          <t>16:59:27.000000</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -26655,7 +26663,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -26665,47 +26673,47 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>В 8978 ВР</t>
+          <t>В 2852 РК</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>78970155027721699</t>
+          <t>78970155027721442</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>E GAS LPG</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>30.41</v>
+        <v>41.543</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>0.82</v>
+        <v>1.48</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.47</v>
+        <v>3.74</v>
       </c>
       <c r="L10" t="n">
-        <v>24.94</v>
+        <v>61.48</v>
       </c>
       <c r="M10" t="n">
-        <v>0.83</v>
+        <v>1.51</v>
       </c>
       <c r="N10" t="n">
-        <v>25.24</v>
+        <v>62.73</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>10:12:38.000000</t>
+          <t>16:59:27.000000</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -26715,7 +26723,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -26725,47 +26733,47 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>В 8978 ВР</t>
+          <t>В 2852 РК</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>78970155027721699</t>
+          <t>78970155027721442</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>E GAS LPG</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>30.41</v>
+        <v>41.543</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.82</v>
+        <v>1.48</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.47</v>
+        <v>3.74</v>
       </c>
       <c r="L11" t="n">
-        <v>24.94</v>
+        <v>61.48</v>
       </c>
       <c r="M11" t="n">
-        <v>0.83</v>
+        <v>1.51</v>
       </c>
       <c r="N11" t="n">
-        <v>25.24</v>
+        <v>62.73</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>10:12:38.000000</t>
+          <t>16:59:27.000000</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -26775,7 +26783,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -26785,47 +26793,47 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>В 8978 ВР</t>
+          <t>В 2852 РК</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>78970155027721699</t>
+          <t>78970155027721442</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>E GAS LPG</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>30.41</v>
+        <v>41.543</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.82</v>
+        <v>1.48</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>-5.47</v>
+        <v>3.74</v>
       </c>
       <c r="L12" t="n">
-        <v>24.94</v>
+        <v>61.48</v>
       </c>
       <c r="M12" t="n">
-        <v>0.83</v>
+        <v>1.51</v>
       </c>
       <c r="N12" t="n">
-        <v>25.24</v>
+        <v>62.73</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>10:12:38.000000</t>
+          <t>16:59:27.000000</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -26835,7 +26843,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -26845,47 +26853,47 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>В 8978 ВР</t>
+          <t>В 2852 РК</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>78970155027721699</t>
+          <t>78970155027721442</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>E GAS LPG</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>30.41</v>
+        <v>41.543</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.82</v>
+        <v>1.48</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.47</v>
+        <v>3.74</v>
       </c>
       <c r="L13" t="n">
-        <v>24.94</v>
+        <v>61.48</v>
       </c>
       <c r="M13" t="n">
-        <v>0.83</v>
+        <v>1.51</v>
       </c>
       <c r="N13" t="n">
-        <v>25.24</v>
+        <v>62.73</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>10:12:38.000000</t>
+          <t>16:59:27.000000</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -26900,52 +26908,52 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Варна Чайка</t>
+          <t>Варна Порт</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>В 8978 ВР</t>
+          <t>В 9347 РН</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>78970155027721699</t>
+          <t>78970155027721731</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>E GAS LPG</t>
+          <t>DIESEL DOUBLE FILTERED</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>30.41</v>
+        <v>29.587</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.82</v>
+        <v>1.78</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.47</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>24.94</v>
+        <v>52.66</v>
       </c>
       <c r="M14" t="n">
-        <v>0.83</v>
+        <v>2.06</v>
       </c>
       <c r="N14" t="n">
-        <v>25.24</v>
+        <v>60.95</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>10:12:38.000000</t>
+          <t>10:10:20.000000</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -26960,52 +26968,52 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Варна Чайка</t>
+          <t>Варна Порт</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>В 8978 ВР</t>
+          <t>В 9347 РН</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>78970155027721699</t>
+          <t>78970155027721731</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>E GAS LPG</t>
+          <t>DIESEL DOUBLE FILTERED</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>30.41</v>
+        <v>29.587</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.82</v>
+        <v>1.78</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.47</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>24.94</v>
+        <v>52.66</v>
       </c>
       <c r="M15" t="n">
-        <v>0.83</v>
+        <v>2.06</v>
       </c>
       <c r="N15" t="n">
-        <v>25.24</v>
+        <v>60.95</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>10:12:38.000000</t>
+          <t>10:10:20.000000</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -27020,52 +27028,52 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Варна Чайка</t>
+          <t>Варна Порт</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>В 6049 НХ</t>
+          <t>В 9347 РН</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>78970155027721509</t>
+          <t>78970155027721731</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>DIESEL DOUBLE FILTERED</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>53.947</v>
+        <v>29.587</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="I16" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>79.84</v>
+        <v>52.66</v>
       </c>
       <c r="M16" t="n">
-        <v>1.51</v>
+        <v>2.06</v>
       </c>
       <c r="N16" t="n">
-        <v>81.45999999999999</v>
+        <v>60.95</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>11:41:40.000000</t>
+          <t>10:10:20.000000</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -27080,52 +27088,52 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Варна Чайка</t>
+          <t>Варна Порт</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>В 6049 НХ</t>
+          <t>В 9347 РН</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>78970155027721509</t>
+          <t>78970155027721731</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>DIESEL DOUBLE FILTERED</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>53.947</v>
+        <v>29.587</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="I17" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>79.84</v>
+        <v>52.66</v>
       </c>
       <c r="M17" t="n">
-        <v>1.51</v>
+        <v>2.06</v>
       </c>
       <c r="N17" t="n">
-        <v>81.45999999999999</v>
+        <v>60.95</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>11:41:40.000000</t>
+          <t>10:10:20.000000</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -27140,52 +27148,52 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Варна Чайка</t>
+          <t>Варна Порт</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>В 6049 НХ</t>
+          <t>В 9347 РН</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>78970155027721509</t>
+          <t>78970155027721731</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>DIESEL DOUBLE FILTERED</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>53.947</v>
+        <v>29.587</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="I18" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>79.84</v>
+        <v>52.66</v>
       </c>
       <c r="M18" t="n">
-        <v>1.51</v>
+        <v>2.06</v>
       </c>
       <c r="N18" t="n">
-        <v>81.45999999999999</v>
+        <v>60.95</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>11:41:40.000000</t>
+          <t>10:10:20.000000</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -27200,52 +27208,52 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Варна Чайка</t>
+          <t>Варна Порт</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>В 6049 НХ</t>
+          <t>В 9347 РН</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>78970155027721509</t>
+          <t>78970155027721731</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>DIESEL DOUBLE FILTERED</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>53.947</v>
+        <v>29.587</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="I19" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>79.84</v>
+        <v>52.66</v>
       </c>
       <c r="M19" t="n">
-        <v>1.51</v>
+        <v>2.06</v>
       </c>
       <c r="N19" t="n">
-        <v>81.45999999999999</v>
+        <v>60.95</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>11:41:40.000000</t>
+          <t>10:10:20.000000</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -27265,47 +27273,47 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>В 6049 НХ</t>
+          <t>В 8978 ВР</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>78970155027721509</t>
+          <t>78970155027721699</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>53.947</v>
+        <v>30.41</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>1.48</v>
+        <v>0.82</v>
       </c>
       <c r="I20" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>4.86</v>
+        <v>-5.47</v>
       </c>
       <c r="L20" t="n">
-        <v>79.84</v>
+        <v>24.94</v>
       </c>
       <c r="M20" t="n">
-        <v>1.51</v>
+        <v>0.83</v>
       </c>
       <c r="N20" t="n">
-        <v>81.45999999999999</v>
+        <v>25.24</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>11:41:40.000000</t>
+          <t>10:12:38.000000</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -27325,47 +27333,47 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>В 6049 НХ</t>
+          <t>В 8978 ВР</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>78970155027721509</t>
+          <t>78970155027721699</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>53.947</v>
+        <v>30.41</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>1.48</v>
+        <v>0.82</v>
       </c>
       <c r="I21" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>4.86</v>
+        <v>-5.47</v>
       </c>
       <c r="L21" t="n">
-        <v>79.84</v>
+        <v>24.94</v>
       </c>
       <c r="M21" t="n">
-        <v>1.51</v>
+        <v>0.83</v>
       </c>
       <c r="N21" t="n">
-        <v>81.45999999999999</v>
+        <v>25.24</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>11:41:40.000000</t>
+          <t>10:12:38.000000</t>
         </is>
       </c>
       <c r="P21" t="n">
@@ -27385,51 +27393,51 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>В 0804 ТР</t>
+          <t>В 8978 ВР</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>78970155027722655</t>
+          <t>78970155027721699</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>34</v>
+        <v>30.41</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>1.48</v>
+        <v>0.82</v>
       </c>
       <c r="I22" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>3.06</v>
+        <v>-5.47</v>
       </c>
       <c r="L22" t="n">
-        <v>50.32</v>
+        <v>24.94</v>
       </c>
       <c r="M22" t="n">
-        <v>1.51</v>
+        <v>0.83</v>
       </c>
       <c r="N22" t="n">
-        <v>51.34</v>
+        <v>25.24</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>12:53:01.000000</t>
+          <t>10:12:38.000000</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>49643</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -27445,51 +27453,51 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>В 0804 ТР</t>
+          <t>В 8978 ВР</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>78970155027722655</t>
+          <t>78970155027721699</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>34</v>
+        <v>30.41</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>1.48</v>
+        <v>0.82</v>
       </c>
       <c r="I23" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>3.06</v>
+        <v>-5.47</v>
       </c>
       <c r="L23" t="n">
-        <v>50.32</v>
+        <v>24.94</v>
       </c>
       <c r="M23" t="n">
-        <v>1.51</v>
+        <v>0.83</v>
       </c>
       <c r="N23" t="n">
-        <v>51.34</v>
+        <v>25.24</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>12:53:01.000000</t>
+          <t>10:12:38.000000</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>49643</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -27505,51 +27513,51 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>В 0804 ТР</t>
+          <t>В 8978 ВР</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>78970155027722655</t>
+          <t>78970155027721699</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>34</v>
+        <v>30.41</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>1.48</v>
+        <v>0.82</v>
       </c>
       <c r="I24" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>3.06</v>
+        <v>-5.47</v>
       </c>
       <c r="L24" t="n">
-        <v>50.32</v>
+        <v>24.94</v>
       </c>
       <c r="M24" t="n">
-        <v>1.51</v>
+        <v>0.83</v>
       </c>
       <c r="N24" t="n">
-        <v>51.34</v>
+        <v>25.24</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>12:53:01.000000</t>
+          <t>10:12:38.000000</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>49643</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -27565,51 +27573,51 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>В 0804 ТР</t>
+          <t>В 8978 ВР</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>78970155027722655</t>
+          <t>78970155027721699</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>34</v>
+        <v>30.41</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>1.48</v>
+        <v>0.82</v>
       </c>
       <c r="I25" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>3.06</v>
+        <v>-5.47</v>
       </c>
       <c r="L25" t="n">
-        <v>50.32</v>
+        <v>24.94</v>
       </c>
       <c r="M25" t="n">
-        <v>1.51</v>
+        <v>0.83</v>
       </c>
       <c r="N25" t="n">
-        <v>51.34</v>
+        <v>25.24</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>12:53:01.000000</t>
+          <t>10:12:38.000000</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>49643</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -27625,12 +27633,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>В 0804 ТР</t>
+          <t>В 6049 НХ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>78970155027722655</t>
+          <t>78970155027721509</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -27639,7 +27647,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>34</v>
+        <v>53.947</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
@@ -27652,24 +27660,24 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>3.06</v>
+        <v>4.86</v>
       </c>
       <c r="L26" t="n">
-        <v>50.32</v>
+        <v>79.84</v>
       </c>
       <c r="M26" t="n">
         <v>1.51</v>
       </c>
       <c r="N26" t="n">
-        <v>51.34</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>12:53:01.000000</t>
+          <t>11:41:40.000000</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>49643</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -27685,12 +27693,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>В 0804 ТР</t>
+          <t>В 6049 НХ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>78970155027722655</t>
+          <t>78970155027721509</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -27699,7 +27707,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>34</v>
+        <v>53.947</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
@@ -27712,24 +27720,24 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>3.06</v>
+        <v>4.86</v>
       </c>
       <c r="L27" t="n">
-        <v>50.32</v>
+        <v>79.84</v>
       </c>
       <c r="M27" t="n">
         <v>1.51</v>
       </c>
       <c r="N27" t="n">
-        <v>51.34</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>12:53:01.000000</t>
+          <t>11:41:40.000000</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>49643</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -27740,52 +27748,52 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Варна Порт</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>В 7230 ВР</t>
+          <t>В 6049 НХ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>78970155027721574</t>
+          <t>78970155027721509</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>E GAS LPG</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>19.361</v>
+        <v>53.947</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>0.82</v>
+        <v>1.48</v>
       </c>
       <c r="I28" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>-3.48</v>
+        <v>4.86</v>
       </c>
       <c r="L28" t="n">
-        <v>15.88</v>
+        <v>79.84</v>
       </c>
       <c r="M28" t="n">
-        <v>0.83</v>
+        <v>1.51</v>
       </c>
       <c r="N28" t="n">
-        <v>16.07</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>16:04:24.000000</t>
+          <t>11:41:40.000000</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -27800,52 +27808,52 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Варна Порт</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>В 7230 ВР</t>
+          <t>В 6049 НХ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>78970155027721574</t>
+          <t>78970155027721509</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>E GAS LPG</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>19.361</v>
+        <v>53.947</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>0.82</v>
+        <v>1.48</v>
       </c>
       <c r="I29" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.48</v>
+        <v>4.86</v>
       </c>
       <c r="L29" t="n">
-        <v>15.88</v>
+        <v>79.84</v>
       </c>
       <c r="M29" t="n">
-        <v>0.83</v>
+        <v>1.51</v>
       </c>
       <c r="N29" t="n">
-        <v>16.07</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>16:04:24.000000</t>
+          <t>11:41:40.000000</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -27860,52 +27868,52 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Варна Порт</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>В 7230 ВР</t>
+          <t>В 6049 НХ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>78970155027721574</t>
+          <t>78970155027721509</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>E GAS LPG</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>19.361</v>
+        <v>53.947</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>0.82</v>
+        <v>1.48</v>
       </c>
       <c r="I30" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.48</v>
+        <v>4.86</v>
       </c>
       <c r="L30" t="n">
-        <v>15.88</v>
+        <v>79.84</v>
       </c>
       <c r="M30" t="n">
-        <v>0.83</v>
+        <v>1.51</v>
       </c>
       <c r="N30" t="n">
-        <v>16.07</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>16:04:24.000000</t>
+          <t>11:41:40.000000</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -27920,52 +27928,52 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Варна Порт</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>В 7230 ВР</t>
+          <t>В 6049 НХ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>78970155027721574</t>
+          <t>78970155027721509</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>E GAS LPG</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>19.361</v>
+        <v>53.947</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>0.82</v>
+        <v>1.48</v>
       </c>
       <c r="I31" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.48</v>
+        <v>4.86</v>
       </c>
       <c r="L31" t="n">
-        <v>15.88</v>
+        <v>79.84</v>
       </c>
       <c r="M31" t="n">
-        <v>0.83</v>
+        <v>1.51</v>
       </c>
       <c r="N31" t="n">
-        <v>16.07</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>16:04:24.000000</t>
+          <t>11:41:40.000000</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -27980,56 +27988,56 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Варна Порт</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>В 7230 ВР</t>
+          <t>В 0804 ТР</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>78970155027721574</t>
+          <t>78970155027722655</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>E GAS LPG</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>19.361</v>
+        <v>34</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>0.82</v>
+        <v>1.48</v>
       </c>
       <c r="I32" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>-3.48</v>
+        <v>3.06</v>
       </c>
       <c r="L32" t="n">
-        <v>15.88</v>
+        <v>50.32</v>
       </c>
       <c r="M32" t="n">
-        <v>0.83</v>
+        <v>1.51</v>
       </c>
       <c r="N32" t="n">
-        <v>16.07</v>
+        <v>51.34</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>16:04:24.000000</t>
+          <t>12:53:01.000000</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>49643</v>
       </c>
     </row>
     <row r="33">
@@ -28040,307 +28048,307 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Варна Порт</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>В 7230 ВР</t>
+          <t>В 0804 ТР</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>78970155027721574</t>
+          <t>78970155027722655</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>E GAS LPG</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>19.361</v>
+        <v>34</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>0.82</v>
+        <v>1.48</v>
       </c>
       <c r="I33" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>-3.48</v>
+        <v>3.06</v>
       </c>
       <c r="L33" t="n">
-        <v>15.88</v>
+        <v>50.32</v>
       </c>
       <c r="M33" t="n">
-        <v>0.83</v>
+        <v>1.51</v>
       </c>
       <c r="N33" t="n">
-        <v>16.07</v>
+        <v>51.34</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>16:04:24.000000</t>
+          <t>12:53:01.000000</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>49643</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Търговище</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>В 7230 ВР</t>
+          <t>В 0804 ТР</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>78970155027721574</t>
+          <t>78970155027722655</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>E GAS LPG</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>16.59</v>
+        <v>34</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>0.82</v>
+        <v>1.48</v>
       </c>
       <c r="I34" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>-2.99</v>
+        <v>3.06</v>
       </c>
       <c r="L34" t="n">
-        <v>13.6</v>
+        <v>50.32</v>
       </c>
       <c r="M34" t="n">
-        <v>0.83</v>
+        <v>1.51</v>
       </c>
       <c r="N34" t="n">
-        <v>13.77</v>
+        <v>51.34</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>07:04:39.000000</t>
+          <t>12:53:01.000000</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>49643</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Търговище</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>В 7230 ВР</t>
+          <t>В 0804 ТР</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>78970155027721574</t>
+          <t>78970155027722655</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>E GAS LPG</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>16.59</v>
+        <v>34</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>0.82</v>
+        <v>1.48</v>
       </c>
       <c r="I35" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.99</v>
+        <v>3.06</v>
       </c>
       <c r="L35" t="n">
-        <v>13.6</v>
+        <v>50.32</v>
       </c>
       <c r="M35" t="n">
-        <v>0.83</v>
+        <v>1.51</v>
       </c>
       <c r="N35" t="n">
-        <v>13.77</v>
+        <v>51.34</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>07:04:39.000000</t>
+          <t>12:53:01.000000</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>49643</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Търговище</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>В 7230 ВР</t>
+          <t>В 0804 ТР</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>78970155027721574</t>
+          <t>78970155027722655</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>E GAS LPG</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>16.59</v>
+        <v>34</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>0.82</v>
+        <v>1.48</v>
       </c>
       <c r="I36" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>-2.99</v>
+        <v>3.06</v>
       </c>
       <c r="L36" t="n">
-        <v>13.6</v>
+        <v>50.32</v>
       </c>
       <c r="M36" t="n">
-        <v>0.83</v>
+        <v>1.51</v>
       </c>
       <c r="N36" t="n">
-        <v>13.77</v>
+        <v>51.34</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>07:04:39.000000</t>
+          <t>12:53:01.000000</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>49643</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Търговище</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>В 7230 ВР</t>
+          <t>В 0804 ТР</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>78970155027721574</t>
+          <t>78970155027722655</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>E GAS LPG</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>16.59</v>
+        <v>34</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>0.82</v>
+        <v>1.48</v>
       </c>
       <c r="I37" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>-2.99</v>
+        <v>3.06</v>
       </c>
       <c r="L37" t="n">
-        <v>13.6</v>
+        <v>50.32</v>
       </c>
       <c r="M37" t="n">
-        <v>0.83</v>
+        <v>1.51</v>
       </c>
       <c r="N37" t="n">
-        <v>13.77</v>
+        <v>51.34</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>07:04:39.000000</t>
+          <t>12:53:01.000000</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>49643</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Търговище</t>
+          <t>Варна Порт</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -28359,7 +28367,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>16.59</v>
+        <v>19.361</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
@@ -28372,20 +28380,20 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>-2.99</v>
+        <v>-3.48</v>
       </c>
       <c r="L38" t="n">
-        <v>13.6</v>
+        <v>15.88</v>
       </c>
       <c r="M38" t="n">
         <v>0.83</v>
       </c>
       <c r="N38" t="n">
-        <v>13.77</v>
+        <v>16.07</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>07:04:39.000000</t>
+          <t>16:04:24.000000</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -28395,12 +28403,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Търговище</t>
+          <t>Варна Порт</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -28419,7 +28427,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>16.59</v>
+        <v>19.361</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
@@ -28432,20 +28440,20 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>-2.99</v>
+        <v>-3.48</v>
       </c>
       <c r="L39" t="n">
-        <v>13.6</v>
+        <v>15.88</v>
       </c>
       <c r="M39" t="n">
         <v>0.83</v>
       </c>
       <c r="N39" t="n">
-        <v>13.77</v>
+        <v>16.07</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>07:04:39.000000</t>
+          <t>16:04:24.000000</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -28455,22 +28463,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Варна Сливница</t>
+          <t>Варна Порт</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>В 0592 ВТ</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>78970155027722622</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -28479,7 +28487,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>33.904</v>
+        <v>19.361</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
@@ -28492,20 +28500,20 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>-6.1</v>
+        <v>-3.48</v>
       </c>
       <c r="L40" t="n">
-        <v>27.8</v>
+        <v>15.88</v>
       </c>
       <c r="M40" t="n">
         <v>0.83</v>
       </c>
       <c r="N40" t="n">
-        <v>28.14</v>
+        <v>16.07</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>09:24:37.000000</t>
+          <t>16:04:24.000000</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -28515,22 +28523,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Варна Сливница</t>
+          <t>Варна Порт</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>В 0592 ВТ</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>78970155027722622</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -28539,7 +28547,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>33.904</v>
+        <v>19.361</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
@@ -28552,20 +28560,20 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>-6.1</v>
+        <v>-3.48</v>
       </c>
       <c r="L41" t="n">
-        <v>27.8</v>
+        <v>15.88</v>
       </c>
       <c r="M41" t="n">
         <v>0.83</v>
       </c>
       <c r="N41" t="n">
-        <v>28.14</v>
+        <v>16.07</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>09:24:37.000000</t>
+          <t>16:04:24.000000</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -28575,22 +28583,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Варна Сливница</t>
+          <t>Варна Порт</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>В 0592 ВТ</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>78970155027722622</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -28599,7 +28607,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>33.904</v>
+        <v>19.361</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
@@ -28612,20 +28620,20 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>-6.1</v>
+        <v>-3.48</v>
       </c>
       <c r="L42" t="n">
-        <v>27.8</v>
+        <v>15.88</v>
       </c>
       <c r="M42" t="n">
         <v>0.83</v>
       </c>
       <c r="N42" t="n">
-        <v>28.14</v>
+        <v>16.07</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>09:24:37.000000</t>
+          <t>16:04:24.000000</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -28635,22 +28643,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Варна Сливница</t>
+          <t>Варна Порт</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>В 0592 ВТ</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>78970155027722622</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -28659,7 +28667,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>33.904</v>
+        <v>19.361</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
@@ -28672,20 +28680,20 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>-6.1</v>
+        <v>-3.48</v>
       </c>
       <c r="L43" t="n">
-        <v>27.8</v>
+        <v>15.88</v>
       </c>
       <c r="M43" t="n">
         <v>0.83</v>
       </c>
       <c r="N43" t="n">
-        <v>28.14</v>
+        <v>16.07</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>09:24:37.000000</t>
+          <t>16:04:24.000000</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -28700,17 +28708,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Варна Сливница</t>
+          <t>Търговище</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>В 0592 ВТ</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>78970155027722622</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -28719,7 +28727,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>33.904</v>
+        <v>16.59</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
@@ -28732,20 +28740,20 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>-6.1</v>
+        <v>-2.99</v>
       </c>
       <c r="L44" t="n">
-        <v>27.8</v>
+        <v>13.6</v>
       </c>
       <c r="M44" t="n">
         <v>0.83</v>
       </c>
       <c r="N44" t="n">
-        <v>28.14</v>
+        <v>13.77</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>09:24:37.000000</t>
+          <t>07:04:39.000000</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -28760,17 +28768,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Варна Сливница</t>
+          <t>Търговище</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>В 0592 ВТ</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>78970155027722622</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -28779,7 +28787,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>33.904</v>
+        <v>16.59</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
@@ -28792,20 +28800,20 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>-6.1</v>
+        <v>-2.99</v>
       </c>
       <c r="L45" t="n">
-        <v>27.8</v>
+        <v>13.6</v>
       </c>
       <c r="M45" t="n">
         <v>0.83</v>
       </c>
       <c r="N45" t="n">
-        <v>28.14</v>
+        <v>13.77</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>09:24:37.000000</t>
+          <t>07:04:39.000000</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -28820,7 +28828,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Севлиево</t>
+          <t>Търговище</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -28839,7 +28847,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>10.795</v>
+        <v>16.59</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
@@ -28852,20 +28860,20 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.94</v>
+        <v>-2.99</v>
       </c>
       <c r="L46" t="n">
-        <v>8.85</v>
+        <v>13.6</v>
       </c>
       <c r="M46" t="n">
         <v>0.83</v>
       </c>
       <c r="N46" t="n">
-        <v>8.960000000000001</v>
+        <v>13.77</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>09:25:30.000000</t>
+          <t>07:04:39.000000</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -28880,7 +28888,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Севлиево</t>
+          <t>Търговище</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -28899,7 +28907,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>10.795</v>
+        <v>16.59</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
@@ -28912,20 +28920,20 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.94</v>
+        <v>-2.99</v>
       </c>
       <c r="L47" t="n">
-        <v>8.85</v>
+        <v>13.6</v>
       </c>
       <c r="M47" t="n">
         <v>0.83</v>
       </c>
       <c r="N47" t="n">
-        <v>8.960000000000001</v>
+        <v>13.77</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>09:25:30.000000</t>
+          <t>07:04:39.000000</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -28940,7 +28948,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Севлиево</t>
+          <t>Търговище</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -28959,7 +28967,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>10.795</v>
+        <v>16.59</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
@@ -28972,20 +28980,20 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>-1.94</v>
+        <v>-2.99</v>
       </c>
       <c r="L48" t="n">
-        <v>8.85</v>
+        <v>13.6</v>
       </c>
       <c r="M48" t="n">
         <v>0.83</v>
       </c>
       <c r="N48" t="n">
-        <v>8.960000000000001</v>
+        <v>13.77</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>09:25:30.000000</t>
+          <t>07:04:39.000000</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -29000,7 +29008,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Севлиево</t>
+          <t>Търговище</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -29019,7 +29027,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>10.795</v>
+        <v>16.59</v>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
@@ -29032,20 +29040,20 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.94</v>
+        <v>-2.99</v>
       </c>
       <c r="L49" t="n">
-        <v>8.85</v>
+        <v>13.6</v>
       </c>
       <c r="M49" t="n">
         <v>0.83</v>
       </c>
       <c r="N49" t="n">
-        <v>8.960000000000001</v>
+        <v>13.77</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>09:25:30.000000</t>
+          <t>07:04:39.000000</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -29060,17 +29068,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Севлиево</t>
+          <t>Варна Сливница</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>В 7230 ВР</t>
+          <t>В 0592 ВТ</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>78970155027721574</t>
+          <t>78970155027722622</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -29079,7 +29087,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>10.795</v>
+        <v>33.904</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
@@ -29092,20 +29100,20 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>-1.94</v>
+        <v>-6.1</v>
       </c>
       <c r="L50" t="n">
-        <v>8.85</v>
+        <v>27.8</v>
       </c>
       <c r="M50" t="n">
         <v>0.83</v>
       </c>
       <c r="N50" t="n">
-        <v>8.960000000000001</v>
+        <v>28.14</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>09:25:30.000000</t>
+          <t>09:24:37.000000</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -29120,17 +29128,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Севлиево</t>
+          <t>Варна Сливница</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>В 7230 ВР</t>
+          <t>В 0592 ВТ</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>78970155027721574</t>
+          <t>78970155027722622</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -29139,7 +29147,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>10.795</v>
+        <v>33.904</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
@@ -29152,20 +29160,20 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>-1.94</v>
+        <v>-6.1</v>
       </c>
       <c r="L51" t="n">
-        <v>8.85</v>
+        <v>27.8</v>
       </c>
       <c r="M51" t="n">
         <v>0.83</v>
       </c>
       <c r="N51" t="n">
-        <v>8.960000000000001</v>
+        <v>28.14</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>09:25:30.000000</t>
+          <t>09:24:37.000000</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -29185,47 +29193,47 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve"> В 5782 КН</t>
+          <t>В 0592 ВТ</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>78970155027721376</t>
+          <t>78970155027722622</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>38</v>
+        <v>33.904</v>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>1.48</v>
+        <v>0.82</v>
       </c>
       <c r="I52" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>3.42</v>
+        <v>-6.1</v>
       </c>
       <c r="L52" t="n">
-        <v>56.24</v>
+        <v>27.8</v>
       </c>
       <c r="M52" t="n">
-        <v>1.51</v>
+        <v>0.83</v>
       </c>
       <c r="N52" t="n">
-        <v>57.38</v>
+        <v>28.14</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>12:13:25.000000</t>
+          <t>09:24:37.000000</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -29245,47 +29253,47 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve"> В 5782 КН</t>
+          <t>В 0592 ВТ</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>78970155027721376</t>
+          <t>78970155027722622</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>38</v>
+        <v>33.904</v>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>1.48</v>
+        <v>0.82</v>
       </c>
       <c r="I53" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>3.42</v>
+        <v>-6.1</v>
       </c>
       <c r="L53" t="n">
-        <v>56.24</v>
+        <v>27.8</v>
       </c>
       <c r="M53" t="n">
-        <v>1.51</v>
+        <v>0.83</v>
       </c>
       <c r="N53" t="n">
-        <v>57.38</v>
+        <v>28.14</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>12:13:25.000000</t>
+          <t>09:24:37.000000</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -29305,47 +29313,47 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve"> В 5782 КН</t>
+          <t>В 0592 ВТ</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>78970155027721376</t>
+          <t>78970155027722622</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>38</v>
+        <v>33.904</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>1.48</v>
+        <v>0.82</v>
       </c>
       <c r="I54" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>3.42</v>
+        <v>-6.1</v>
       </c>
       <c r="L54" t="n">
-        <v>56.24</v>
+        <v>27.8</v>
       </c>
       <c r="M54" t="n">
-        <v>1.51</v>
+        <v>0.83</v>
       </c>
       <c r="N54" t="n">
-        <v>57.38</v>
+        <v>28.14</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>12:13:25.000000</t>
+          <t>09:24:37.000000</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -29365,47 +29373,47 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve"> В 5782 КН</t>
+          <t>В 0592 ВТ</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>78970155027721376</t>
+          <t>78970155027722622</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>38</v>
+        <v>33.904</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>1.48</v>
+        <v>0.82</v>
       </c>
       <c r="I55" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>3.42</v>
+        <v>-6.1</v>
       </c>
       <c r="L55" t="n">
-        <v>56.24</v>
+        <v>27.8</v>
       </c>
       <c r="M55" t="n">
-        <v>1.51</v>
+        <v>0.83</v>
       </c>
       <c r="N55" t="n">
-        <v>57.38</v>
+        <v>28.14</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>12:13:25.000000</t>
+          <t>09:24:37.000000</t>
         </is>
       </c>
       <c r="P55" t="n">
@@ -29420,52 +29428,52 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Варна Сливница</t>
+          <t>Севлиево</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve"> В 5782 КН</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>78970155027721376</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>38</v>
+        <v>10.795</v>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>1.48</v>
+        <v>0.82</v>
       </c>
       <c r="I56" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>3.42</v>
+        <v>-1.94</v>
       </c>
       <c r="L56" t="n">
-        <v>56.24</v>
+        <v>8.85</v>
       </c>
       <c r="M56" t="n">
-        <v>1.51</v>
+        <v>0.83</v>
       </c>
       <c r="N56" t="n">
-        <v>57.38</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>12:13:25.000000</t>
+          <t>09:25:30.000000</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -29480,52 +29488,52 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Варна Сливница</t>
+          <t>Севлиево</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve"> В 5782 КН</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>78970155027721376</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>38</v>
+        <v>10.795</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>1.48</v>
+        <v>0.82</v>
       </c>
       <c r="I57" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>3.42</v>
+        <v>-1.94</v>
       </c>
       <c r="L57" t="n">
-        <v>56.24</v>
+        <v>8.85</v>
       </c>
       <c r="M57" t="n">
-        <v>1.51</v>
+        <v>0.83</v>
       </c>
       <c r="N57" t="n">
-        <v>57.38</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>12:13:25.000000</t>
+          <t>09:25:30.000000</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -29540,52 +29548,52 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Варна Варненчик</t>
+          <t>Севлиево</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B 8917 BP</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>78970155027721269</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>32.149</v>
+        <v>10.795</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>1.78</v>
+        <v>0.82</v>
       </c>
       <c r="I58" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>3.54</v>
+        <v>-1.94</v>
       </c>
       <c r="L58" t="n">
-        <v>57.23</v>
+        <v>8.85</v>
       </c>
       <c r="M58" t="n">
-        <v>1.81</v>
+        <v>0.83</v>
       </c>
       <c r="N58" t="n">
-        <v>58.19</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>12:39:08.000000</t>
+          <t>09:25:30.000000</t>
         </is>
       </c>
       <c r="P58" t="n">
@@ -29600,52 +29608,52 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Варна Варненчик</t>
+          <t>Севлиево</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>B 8917 BP</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>78970155027721269</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>32.149</v>
+        <v>10.795</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>1.78</v>
+        <v>0.82</v>
       </c>
       <c r="I59" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>3.54</v>
+        <v>-1.94</v>
       </c>
       <c r="L59" t="n">
-        <v>57.23</v>
+        <v>8.85</v>
       </c>
       <c r="M59" t="n">
-        <v>1.81</v>
+        <v>0.83</v>
       </c>
       <c r="N59" t="n">
-        <v>58.19</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>12:39:08.000000</t>
+          <t>09:25:30.000000</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -29660,52 +29668,52 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Варна Варненчик</t>
+          <t>Севлиево</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B 8917 BP</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>78970155027721269</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>32.149</v>
+        <v>10.795</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>1.78</v>
+        <v>0.82</v>
       </c>
       <c r="I60" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>3.54</v>
+        <v>-1.94</v>
       </c>
       <c r="L60" t="n">
-        <v>57.23</v>
+        <v>8.85</v>
       </c>
       <c r="M60" t="n">
-        <v>1.81</v>
+        <v>0.83</v>
       </c>
       <c r="N60" t="n">
-        <v>58.19</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>12:39:08.000000</t>
+          <t>09:25:30.000000</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -29720,52 +29728,52 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Варна Варненчик</t>
+          <t>Севлиево</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>B 8917 BP</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>78970155027721269</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>32.149</v>
+        <v>10.795</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>1.78</v>
+        <v>0.82</v>
       </c>
       <c r="I61" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>3.54</v>
+        <v>-1.94</v>
       </c>
       <c r="L61" t="n">
-        <v>57.23</v>
+        <v>8.85</v>
       </c>
       <c r="M61" t="n">
-        <v>1.81</v>
+        <v>0.83</v>
       </c>
       <c r="N61" t="n">
-        <v>58.19</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>12:39:08.000000</t>
+          <t>09:25:30.000000</t>
         </is>
       </c>
       <c r="P61" t="n">
@@ -29780,30 +29788,30 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Варна Варненчик</t>
+          <t>Варна Сливница</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>B 8917 BP</t>
+          <t xml:space="preserve"> В 5782 КН</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>78970155027721269</t>
+          <t>78970155027721376</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>32.149</v>
+        <v>38</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="I62" t="n">
         <v>0.03</v>
@@ -29812,20 +29820,20 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>3.54</v>
+        <v>3.42</v>
       </c>
       <c r="L62" t="n">
-        <v>57.23</v>
+        <v>56.24</v>
       </c>
       <c r="M62" t="n">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="N62" t="n">
-        <v>58.19</v>
+        <v>57.38</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>12:39:08.000000</t>
+          <t>12:13:25.000000</t>
         </is>
       </c>
       <c r="P62" t="n">
@@ -29840,30 +29848,30 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Варна Варненчик</t>
+          <t>Варна Сливница</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>B 8917 BP</t>
+          <t xml:space="preserve"> В 5782 КН</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>78970155027721269</t>
+          <t>78970155027721376</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>32.149</v>
+        <v>38</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="I63" t="n">
         <v>0.03</v>
@@ -29872,20 +29880,20 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>3.54</v>
+        <v>3.42</v>
       </c>
       <c r="L63" t="n">
-        <v>57.23</v>
+        <v>56.24</v>
       </c>
       <c r="M63" t="n">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="N63" t="n">
-        <v>58.19</v>
+        <v>57.38</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>12:39:08.000000</t>
+          <t>12:13:25.000000</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -29900,30 +29908,30 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Варна Чайка</t>
+          <t>Варна Сливница</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>B 4160 TK</t>
+          <t xml:space="preserve"> В 5782 КН</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>78970155027721293</t>
+          <t>78970155027721376</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>42.801</v>
+        <v>38</v>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="I64" t="n">
         <v>0.03</v>
@@ -29932,20 +29940,20 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>4.71</v>
+        <v>3.42</v>
       </c>
       <c r="L64" t="n">
-        <v>76.19</v>
+        <v>56.24</v>
       </c>
       <c r="M64" t="n">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="N64" t="n">
-        <v>77.47</v>
+        <v>57.38</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>13:21:42.000000</t>
+          <t>12:13:25.000000</t>
         </is>
       </c>
       <c r="P64" t="n">
@@ -29960,30 +29968,30 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Варна Чайка</t>
+          <t>Варна Сливница</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>B 4160 TK</t>
+          <t xml:space="preserve"> В 5782 КН</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>78970155027721293</t>
+          <t>78970155027721376</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>42.801</v>
+        <v>38</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="I65" t="n">
         <v>0.03</v>
@@ -29992,20 +30000,20 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>4.71</v>
+        <v>3.42</v>
       </c>
       <c r="L65" t="n">
-        <v>76.19</v>
+        <v>56.24</v>
       </c>
       <c r="M65" t="n">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="N65" t="n">
-        <v>77.47</v>
+        <v>57.38</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>13:21:42.000000</t>
+          <t>12:13:25.000000</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -30020,30 +30028,30 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Варна Чайка</t>
+          <t>Варна Сливница</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>B 4160 TK</t>
+          <t xml:space="preserve"> В 5782 КН</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>78970155027721293</t>
+          <t>78970155027721376</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>42.801</v>
+        <v>38</v>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="I66" t="n">
         <v>0.03</v>
@@ -30052,20 +30060,20 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>4.71</v>
+        <v>3.42</v>
       </c>
       <c r="L66" t="n">
-        <v>76.19</v>
+        <v>56.24</v>
       </c>
       <c r="M66" t="n">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="N66" t="n">
-        <v>77.47</v>
+        <v>57.38</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>13:21:42.000000</t>
+          <t>12:13:25.000000</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -30080,30 +30088,30 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Варна Чайка</t>
+          <t>Варна Сливница</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>B 4160 TK</t>
+          <t xml:space="preserve"> В 5782 КН</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>78970155027721293</t>
+          <t>78970155027721376</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>42.801</v>
+        <v>38</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="I67" t="n">
         <v>0.03</v>
@@ -30112,20 +30120,20 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>4.71</v>
+        <v>3.42</v>
       </c>
       <c r="L67" t="n">
-        <v>76.19</v>
+        <v>56.24</v>
       </c>
       <c r="M67" t="n">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="N67" t="n">
-        <v>77.47</v>
+        <v>57.38</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>13:21:42.000000</t>
+          <t>12:13:25.000000</t>
         </is>
       </c>
       <c r="P67" t="n">
@@ -30140,17 +30148,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Варна Чайка</t>
+          <t>Варна Варненчик</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>B 4160 TK</t>
+          <t>B 8917 BP</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>78970155027721293</t>
+          <t>78970155027721269</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -30159,7 +30167,7 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>42.801</v>
+        <v>32.149</v>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
@@ -30172,20 +30180,20 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>4.71</v>
+        <v>3.54</v>
       </c>
       <c r="L68" t="n">
-        <v>76.19</v>
+        <v>57.23</v>
       </c>
       <c r="M68" t="n">
         <v>1.81</v>
       </c>
       <c r="N68" t="n">
-        <v>77.47</v>
+        <v>58.19</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>13:21:42.000000</t>
+          <t>12:39:08.000000</t>
         </is>
       </c>
       <c r="P68" t="n">
@@ -30200,17 +30208,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Варна Чайка</t>
+          <t>Варна Варненчик</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>B 4160 TK</t>
+          <t>B 8917 BP</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>78970155027721293</t>
+          <t>78970155027721269</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -30219,7 +30227,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>42.801</v>
+        <v>32.149</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
@@ -30232,20 +30240,20 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>4.71</v>
+        <v>3.54</v>
       </c>
       <c r="L69" t="n">
-        <v>76.19</v>
+        <v>57.23</v>
       </c>
       <c r="M69" t="n">
         <v>1.81</v>
       </c>
       <c r="N69" t="n">
-        <v>77.47</v>
+        <v>58.19</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>13:21:42.000000</t>
+          <t>12:39:08.000000</t>
         </is>
       </c>
       <c r="P69" t="n">
@@ -30260,30 +30268,30 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Варна Варненчик</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Служебна ОВ 1</t>
+          <t>B 8917 BP</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>78970155027721764</t>
+          <t>78970155027721269</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>DIESEL EKONOMY</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>19.98</v>
+        <v>32.149</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="I70" t="n">
         <v>0.03</v>
@@ -30292,20 +30300,20 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>1.8</v>
+        <v>3.54</v>
       </c>
       <c r="L70" t="n">
-        <v>29.57</v>
+        <v>57.23</v>
       </c>
       <c r="M70" t="n">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="N70" t="n">
-        <v>30.17</v>
+        <v>58.19</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>14:30:23.000000</t>
+          <t>12:39:08.000000</t>
         </is>
       </c>
       <c r="P70" t="n">
@@ -30320,30 +30328,30 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Варна Варненчик</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Служебна ОВ 1</t>
+          <t>B 8917 BP</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>78970155027721764</t>
+          <t>78970155027721269</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>DIESEL EKONOMY</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>19.98</v>
+        <v>32.149</v>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="I71" t="n">
         <v>0.03</v>
@@ -30352,20 +30360,20 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>1.8</v>
+        <v>3.54</v>
       </c>
       <c r="L71" t="n">
-        <v>29.57</v>
+        <v>57.23</v>
       </c>
       <c r="M71" t="n">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="N71" t="n">
-        <v>30.17</v>
+        <v>58.19</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>14:30:23.000000</t>
+          <t>12:39:08.000000</t>
         </is>
       </c>
       <c r="P71" t="n">
@@ -30380,30 +30388,30 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Варна Варненчик</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Служебна ОВ 1</t>
+          <t>B 8917 BP</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>78970155027721764</t>
+          <t>78970155027721269</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>DIESEL EKONOMY</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>19.98</v>
+        <v>32.149</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="I72" t="n">
         <v>0.03</v>
@@ -30412,20 +30420,20 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>1.8</v>
+        <v>3.54</v>
       </c>
       <c r="L72" t="n">
-        <v>29.57</v>
+        <v>57.23</v>
       </c>
       <c r="M72" t="n">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="N72" t="n">
-        <v>30.17</v>
+        <v>58.19</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>14:30:23.000000</t>
+          <t>12:39:08.000000</t>
         </is>
       </c>
       <c r="P72" t="n">
@@ -30440,30 +30448,30 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Варна Варненчик</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Служебна ОВ 1</t>
+          <t>B 8917 BP</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>78970155027721764</t>
+          <t>78970155027721269</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>DIESEL EKONOMY</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>19.98</v>
+        <v>32.149</v>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="I73" t="n">
         <v>0.03</v>
@@ -30472,20 +30480,20 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>1.8</v>
+        <v>3.54</v>
       </c>
       <c r="L73" t="n">
-        <v>29.57</v>
+        <v>57.23</v>
       </c>
       <c r="M73" t="n">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="N73" t="n">
-        <v>30.17</v>
+        <v>58.19</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>14:30:23.000000</t>
+          <t>12:39:08.000000</t>
         </is>
       </c>
       <c r="P73" t="n">
@@ -30500,30 +30508,30 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Служебна ОВ 1</t>
+          <t>B 4160 TK</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>78970155027721764</t>
+          <t>78970155027721293</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>DIESEL EKONOMY</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>19.98</v>
+        <v>42.801</v>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="I74" t="n">
         <v>0.03</v>
@@ -30532,20 +30540,20 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>1.8</v>
+        <v>4.71</v>
       </c>
       <c r="L74" t="n">
-        <v>29.57</v>
+        <v>76.19</v>
       </c>
       <c r="M74" t="n">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="N74" t="n">
-        <v>30.17</v>
+        <v>77.47</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>14:30:23.000000</t>
+          <t>13:21:42.000000</t>
         </is>
       </c>
       <c r="P74" t="n">
@@ -30560,30 +30568,30 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Служебна ОВ 1</t>
+          <t>B 4160 TK</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>78970155027721764</t>
+          <t>78970155027721293</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>DIESEL EKONOMY</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>19.98</v>
+        <v>42.801</v>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="I75" t="n">
         <v>0.03</v>
@@ -30592,20 +30600,20 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>1.8</v>
+        <v>4.71</v>
       </c>
       <c r="L75" t="n">
-        <v>29.57</v>
+        <v>76.19</v>
       </c>
       <c r="M75" t="n">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="N75" t="n">
-        <v>30.17</v>
+        <v>77.47</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>14:30:23.000000</t>
+          <t>13:21:42.000000</t>
         </is>
       </c>
       <c r="P75" t="n">
@@ -30625,47 +30633,47 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>В 7242 ВР</t>
+          <t>B 4160 TK</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>78970155027721616</t>
+          <t>78970155027721293</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>E GAS LPG</t>
+          <t>DIESEL EKONOMY</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>37.482</v>
+        <v>42.801</v>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>0.82</v>
+        <v>1.78</v>
       </c>
       <c r="I76" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>-6.75</v>
+        <v>4.71</v>
       </c>
       <c r="L76" t="n">
-        <v>30.74</v>
+        <v>76.19</v>
       </c>
       <c r="M76" t="n">
-        <v>0.83</v>
+        <v>1.81</v>
       </c>
       <c r="N76" t="n">
-        <v>31.11</v>
+        <v>77.47</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>16:36:03.000000</t>
+          <t>13:21:42.000000</t>
         </is>
       </c>
       <c r="P76" t="n">
@@ -30685,47 +30693,47 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>В 7242 ВР</t>
+          <t>B 4160 TK</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>78970155027721616</t>
+          <t>78970155027721293</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>E GAS LPG</t>
+          <t>DIESEL EKONOMY</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>37.482</v>
+        <v>42.801</v>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>0.82</v>
+        <v>1.78</v>
       </c>
       <c r="I77" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>-6.75</v>
+        <v>4.71</v>
       </c>
       <c r="L77" t="n">
-        <v>30.74</v>
+        <v>76.19</v>
       </c>
       <c r="M77" t="n">
-        <v>0.83</v>
+        <v>1.81</v>
       </c>
       <c r="N77" t="n">
-        <v>31.11</v>
+        <v>77.47</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>16:36:03.000000</t>
+          <t>13:21:42.000000</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -30745,47 +30753,47 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>В 7242 ВР</t>
+          <t>B 4160 TK</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>78970155027721616</t>
+          <t>78970155027721293</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>E GAS LPG</t>
+          <t>DIESEL EKONOMY</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>37.482</v>
+        <v>42.801</v>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>0.82</v>
+        <v>1.78</v>
       </c>
       <c r="I78" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>-6.75</v>
+        <v>4.71</v>
       </c>
       <c r="L78" t="n">
-        <v>30.74</v>
+        <v>76.19</v>
       </c>
       <c r="M78" t="n">
-        <v>0.83</v>
+        <v>1.81</v>
       </c>
       <c r="N78" t="n">
-        <v>31.11</v>
+        <v>77.47</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>16:36:03.000000</t>
+          <t>13:21:42.000000</t>
         </is>
       </c>
       <c r="P78" t="n">
@@ -30805,47 +30813,47 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>В 7242 ВР</t>
+          <t>B 4160 TK</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>78970155027721616</t>
+          <t>78970155027721293</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>E GAS LPG</t>
+          <t>DIESEL EKONOMY</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>37.482</v>
+        <v>42.801</v>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>0.82</v>
+        <v>1.78</v>
       </c>
       <c r="I79" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>-6.75</v>
+        <v>4.71</v>
       </c>
       <c r="L79" t="n">
-        <v>30.74</v>
+        <v>76.19</v>
       </c>
       <c r="M79" t="n">
-        <v>0.83</v>
+        <v>1.81</v>
       </c>
       <c r="N79" t="n">
-        <v>31.11</v>
+        <v>77.47</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>16:36:03.000000</t>
+          <t>13:21:42.000000</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -30860,52 +30868,52 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Варна Чайка</t>
+          <t>Варна</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>В 7242 ВР</t>
+          <t>Служебна ОВ 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>78970155027721616</t>
+          <t>78970155027721764</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>E GAS LPG</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>37.482</v>
+        <v>19.98</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>0.82</v>
+        <v>1.48</v>
       </c>
       <c r="I80" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>-6.75</v>
+        <v>1.8</v>
       </c>
       <c r="L80" t="n">
-        <v>30.74</v>
+        <v>29.57</v>
       </c>
       <c r="M80" t="n">
-        <v>0.83</v>
+        <v>1.51</v>
       </c>
       <c r="N80" t="n">
-        <v>31.11</v>
+        <v>30.17</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>16:36:03.000000</t>
+          <t>14:30:23.000000</t>
         </is>
       </c>
       <c r="P80" t="n">
@@ -30920,52 +30928,52 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Варна Чайка</t>
+          <t>Варна</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>В 7242 ВР</t>
+          <t>Служебна ОВ 1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>78970155027721616</t>
+          <t>78970155027721764</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>E GAS LPG</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>37.482</v>
+        <v>19.98</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>0.82</v>
+        <v>1.48</v>
       </c>
       <c r="I81" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>-6.75</v>
+        <v>1.8</v>
       </c>
       <c r="L81" t="n">
-        <v>30.74</v>
+        <v>29.57</v>
       </c>
       <c r="M81" t="n">
-        <v>0.83</v>
+        <v>1.51</v>
       </c>
       <c r="N81" t="n">
-        <v>31.11</v>
+        <v>30.17</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>16:36:03.000000</t>
+          <t>14:30:23.000000</t>
         </is>
       </c>
       <c r="P81" t="n">
@@ -30975,22 +30983,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Варна Порт</t>
+          <t>Варна</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>В 6512 КС</t>
+          <t>Служебна ОВ 1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>78970155027721525</t>
+          <t>78970155027721764</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -30999,7 +31007,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>38.702</v>
+        <v>19.98</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
@@ -31012,45 +31020,45 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>3.48</v>
+        <v>1.8</v>
       </c>
       <c r="L82" t="n">
-        <v>57.28</v>
+        <v>29.57</v>
       </c>
       <c r="M82" t="n">
         <v>1.51</v>
       </c>
       <c r="N82" t="n">
-        <v>58.44</v>
+        <v>30.17</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>09:08:29.000000</t>
+          <t>14:30:23.000000</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>331738</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Варна Порт</t>
+          <t>Варна</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>В 6512 КС</t>
+          <t>Служебна ОВ 1</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>78970155027721525</t>
+          <t>78970155027721764</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -31059,7 +31067,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>38.702</v>
+        <v>19.98</v>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
@@ -31072,45 +31080,45 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>3.48</v>
+        <v>1.8</v>
       </c>
       <c r="L83" t="n">
-        <v>57.28</v>
+        <v>29.57</v>
       </c>
       <c r="M83" t="n">
         <v>1.51</v>
       </c>
       <c r="N83" t="n">
-        <v>58.44</v>
+        <v>30.17</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>09:08:29.000000</t>
+          <t>14:30:23.000000</t>
         </is>
       </c>
       <c r="P83" t="n">
-        <v>331738</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Варна Порт</t>
+          <t>Варна</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>В 6512 КС</t>
+          <t>Служебна ОВ 1</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>78970155027721525</t>
+          <t>78970155027721764</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -31119,7 +31127,7 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>38.702</v>
+        <v>19.98</v>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
@@ -31132,45 +31140,45 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>3.48</v>
+        <v>1.8</v>
       </c>
       <c r="L84" t="n">
-        <v>57.28</v>
+        <v>29.57</v>
       </c>
       <c r="M84" t="n">
         <v>1.51</v>
       </c>
       <c r="N84" t="n">
-        <v>58.44</v>
+        <v>30.17</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>09:08:29.000000</t>
+          <t>14:30:23.000000</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>331738</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Варна Порт</t>
+          <t>Варна</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>В 6512 КС</t>
+          <t>Служебна ОВ 1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>78970155027721525</t>
+          <t>78970155027721764</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -31179,7 +31187,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>38.702</v>
+        <v>19.98</v>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
@@ -31192,165 +31200,165 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>3.48</v>
+        <v>1.8</v>
       </c>
       <c r="L85" t="n">
-        <v>57.28</v>
+        <v>29.57</v>
       </c>
       <c r="M85" t="n">
         <v>1.51</v>
       </c>
       <c r="N85" t="n">
-        <v>58.44</v>
+        <v>30.17</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>09:08:29.000000</t>
+          <t>14:30:23.000000</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>331738</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Варна Порт</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>В 6512 КС</t>
+          <t>В 7242 ВР</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>78970155027721525</t>
+          <t>78970155027721616</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>38.702</v>
+        <v>37.482</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>1.48</v>
+        <v>0.82</v>
       </c>
       <c r="I86" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>3.48</v>
+        <v>-6.75</v>
       </c>
       <c r="L86" t="n">
-        <v>57.28</v>
+        <v>30.74</v>
       </c>
       <c r="M86" t="n">
-        <v>1.51</v>
+        <v>0.83</v>
       </c>
       <c r="N86" t="n">
-        <v>58.44</v>
+        <v>31.11</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>09:08:29.000000</t>
+          <t>16:36:03.000000</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>331738</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Варна Порт</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>В 6512 КС</t>
+          <t>В 7242 ВР</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>78970155027721525</t>
+          <t>78970155027721616</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>95 EKONOMY UNLEADED</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>38.702</v>
+        <v>37.482</v>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>1.48</v>
+        <v>0.82</v>
       </c>
       <c r="I87" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>3.48</v>
+        <v>-6.75</v>
       </c>
       <c r="L87" t="n">
-        <v>57.28</v>
+        <v>30.74</v>
       </c>
       <c r="M87" t="n">
-        <v>1.51</v>
+        <v>0.83</v>
       </c>
       <c r="N87" t="n">
-        <v>58.44</v>
+        <v>31.11</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>09:08:29.000000</t>
+          <t>16:36:03.000000</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>331738</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Благоевград Център</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>В 7230 ВР</t>
+          <t>В 7242 ВР</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>78970155027721574</t>
+          <t>78970155027721616</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -31359,7 +31367,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>25.916</v>
+        <v>37.482</v>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
@@ -31372,20 +31380,20 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>-4.66</v>
+        <v>-6.75</v>
       </c>
       <c r="L88" t="n">
-        <v>21.25</v>
+        <v>30.74</v>
       </c>
       <c r="M88" t="n">
         <v>0.83</v>
       </c>
       <c r="N88" t="n">
-        <v>21.51</v>
+        <v>31.11</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>09:24:58.000000</t>
+          <t>16:36:03.000000</t>
         </is>
       </c>
       <c r="P88" t="n">
@@ -31395,22 +31403,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Благоевград Център</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>В 7230 ВР</t>
+          <t>В 7242 ВР</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>78970155027721574</t>
+          <t>78970155027721616</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -31419,7 +31427,7 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>25.916</v>
+        <v>37.482</v>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
@@ -31432,20 +31440,20 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>-4.66</v>
+        <v>-6.75</v>
       </c>
       <c r="L89" t="n">
-        <v>21.25</v>
+        <v>30.74</v>
       </c>
       <c r="M89" t="n">
         <v>0.83</v>
       </c>
       <c r="N89" t="n">
-        <v>21.51</v>
+        <v>31.11</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>09:24:58.000000</t>
+          <t>16:36:03.000000</t>
         </is>
       </c>
       <c r="P89" t="n">
@@ -31455,22 +31463,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Благоевград Център</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>В 7230 ВР</t>
+          <t>В 7242 ВР</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>78970155027721574</t>
+          <t>78970155027721616</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -31479,7 +31487,7 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>25.916</v>
+        <v>37.482</v>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
@@ -31492,20 +31500,20 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>-4.66</v>
+        <v>-6.75</v>
       </c>
       <c r="L90" t="n">
-        <v>21.25</v>
+        <v>30.74</v>
       </c>
       <c r="M90" t="n">
         <v>0.83</v>
       </c>
       <c r="N90" t="n">
-        <v>21.51</v>
+        <v>31.11</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>09:24:58.000000</t>
+          <t>16:36:03.000000</t>
         </is>
       </c>
       <c r="P90" t="n">
@@ -31515,22 +31523,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Благоевград Център</t>
+          <t>Варна Чайка</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>В 7230 ВР</t>
+          <t>В 7242 ВР</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>78970155027721574</t>
+          <t>78970155027721616</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -31539,7 +31547,7 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>25.916</v>
+        <v>37.482</v>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
@@ -31552,20 +31560,20 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>-4.66</v>
+        <v>-6.75</v>
       </c>
       <c r="L91" t="n">
-        <v>21.25</v>
+        <v>30.74</v>
       </c>
       <c r="M91" t="n">
         <v>0.83</v>
       </c>
       <c r="N91" t="n">
-        <v>21.51</v>
+        <v>31.11</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>09:24:58.000000</t>
+          <t>16:36:03.000000</t>
         </is>
       </c>
       <c r="P91" t="n">
@@ -31580,56 +31588,56 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Благоевград Център</t>
+          <t>Варна Порт</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>В 7230 ВР</t>
+          <t>В 6512 КС</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>78970155027721574</t>
+          <t>78970155027721525</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>E GAS LPG</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>25.916</v>
+        <v>38.702</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>0.82</v>
+        <v>1.48</v>
       </c>
       <c r="I92" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>-4.66</v>
+        <v>3.48</v>
       </c>
       <c r="L92" t="n">
-        <v>21.25</v>
+        <v>57.28</v>
       </c>
       <c r="M92" t="n">
-        <v>0.83</v>
+        <v>1.51</v>
       </c>
       <c r="N92" t="n">
-        <v>21.51</v>
+        <v>58.44</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>09:24:58.000000</t>
+          <t>09:08:29.000000</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>331738</v>
       </c>
     </row>
     <row r="93">
@@ -31640,56 +31648,56 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Благоевград Център</t>
+          <t>Варна Порт</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>В 7230 ВР</t>
+          <t>В 6512 КС</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>78970155027721574</t>
+          <t>78970155027721525</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>E GAS LPG</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>25.916</v>
+        <v>38.702</v>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>0.82</v>
+        <v>1.48</v>
       </c>
       <c r="I93" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>-4.66</v>
+        <v>3.48</v>
       </c>
       <c r="L93" t="n">
-        <v>21.25</v>
+        <v>57.28</v>
       </c>
       <c r="M93" t="n">
-        <v>0.83</v>
+        <v>1.51</v>
       </c>
       <c r="N93" t="n">
-        <v>21.51</v>
+        <v>58.44</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>09:24:58.000000</t>
+          <t>09:08:29.000000</t>
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>331738</v>
       </c>
     </row>
     <row r="94">
@@ -31700,30 +31708,30 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Варна Порт</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>B 4161 TK</t>
+          <t>В 6512 КС</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>78970155027721285</t>
+          <t>78970155027721525</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>40</v>
+        <v>38.702</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>1.77</v>
+        <v>1.48</v>
       </c>
       <c r="I94" t="n">
         <v>0.03</v>
@@ -31732,24 +31740,24 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>4.8</v>
+        <v>3.48</v>
       </c>
       <c r="L94" t="n">
-        <v>70.8</v>
+        <v>57.28</v>
       </c>
       <c r="M94" t="n">
-        <v>1.8</v>
+        <v>1.51</v>
       </c>
       <c r="N94" t="n">
-        <v>72</v>
+        <v>58.44</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>13:08:08.000000</t>
+          <t>09:08:29.000000</t>
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>331738</v>
       </c>
     </row>
     <row r="95">
@@ -31760,30 +31768,30 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Варна Порт</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>B 4161 TK</t>
+          <t>В 6512 КС</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>78970155027721285</t>
+          <t>78970155027721525</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>40</v>
+        <v>38.702</v>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>1.77</v>
+        <v>1.48</v>
       </c>
       <c r="I95" t="n">
         <v>0.03</v>
@@ -31792,24 +31800,24 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>4.8</v>
+        <v>3.48</v>
       </c>
       <c r="L95" t="n">
-        <v>70.8</v>
+        <v>57.28</v>
       </c>
       <c r="M95" t="n">
-        <v>1.8</v>
+        <v>1.51</v>
       </c>
       <c r="N95" t="n">
-        <v>72</v>
+        <v>58.44</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>13:08:08.000000</t>
+          <t>09:08:29.000000</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>331738</v>
       </c>
     </row>
     <row r="96">
@@ -31820,30 +31828,30 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Варна Порт</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>B 4161 TK</t>
+          <t>В 6512 КС</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>78970155027721285</t>
+          <t>78970155027721525</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>40</v>
+        <v>38.702</v>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>1.77</v>
+        <v>1.48</v>
       </c>
       <c r="I96" t="n">
         <v>0.03</v>
@@ -31852,24 +31860,24 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>4.8</v>
+        <v>3.48</v>
       </c>
       <c r="L96" t="n">
-        <v>70.8</v>
+        <v>57.28</v>
       </c>
       <c r="M96" t="n">
-        <v>1.8</v>
+        <v>1.51</v>
       </c>
       <c r="N96" t="n">
-        <v>72</v>
+        <v>58.44</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>13:08:08.000000</t>
+          <t>09:08:29.000000</t>
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>331738</v>
       </c>
     </row>
     <row r="97">
@@ -31880,30 +31888,30 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Варна Порт</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>B 4161 TK</t>
+          <t>В 6512 КС</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>78970155027721285</t>
+          <t>78970155027721525</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>95 EKONOMY UNLEADED</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>40</v>
+        <v>38.702</v>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>1.77</v>
+        <v>1.48</v>
       </c>
       <c r="I97" t="n">
         <v>0.03</v>
@@ -31912,24 +31920,24 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>4.8</v>
+        <v>3.48</v>
       </c>
       <c r="L97" t="n">
-        <v>70.8</v>
+        <v>57.28</v>
       </c>
       <c r="M97" t="n">
-        <v>1.8</v>
+        <v>1.51</v>
       </c>
       <c r="N97" t="n">
-        <v>72</v>
+        <v>58.44</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>13:08:08.000000</t>
+          <t>09:08:29.000000</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>331738</v>
       </c>
     </row>
     <row r="98">
@@ -31940,52 +31948,52 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Благоевград Център</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>B 4161 TK</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>78970155027721285</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>40</v>
+        <v>25.916</v>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>1.77</v>
+        <v>0.82</v>
       </c>
       <c r="I98" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>4.8</v>
+        <v>-4.66</v>
       </c>
       <c r="L98" t="n">
-        <v>70.8</v>
+        <v>21.25</v>
       </c>
       <c r="M98" t="n">
-        <v>1.8</v>
+        <v>0.83</v>
       </c>
       <c r="N98" t="n">
-        <v>72</v>
+        <v>21.51</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>13:08:08.000000</t>
+          <t>09:24:58.000000</t>
         </is>
       </c>
       <c r="P98" t="n">
@@ -32000,52 +32008,52 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Благоевград Център</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>B 4161 TK</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>78970155027721285</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>DIESEL EKONOMY</t>
+          <t>E GAS LPG</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>40</v>
+        <v>25.916</v>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>1.77</v>
+        <v>0.82</v>
       </c>
       <c r="I99" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>4.8</v>
+        <v>-4.66</v>
       </c>
       <c r="L99" t="n">
-        <v>70.8</v>
+        <v>21.25</v>
       </c>
       <c r="M99" t="n">
-        <v>1.8</v>
+        <v>0.83</v>
       </c>
       <c r="N99" t="n">
-        <v>72</v>
+        <v>21.51</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>13:08:08.000000</t>
+          <t>09:24:58.000000</t>
         </is>
       </c>
       <c r="P99" t="n">
@@ -32060,7 +32068,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Севлиево</t>
+          <t>Благоевград Център</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -32079,7 +32087,7 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>27.663</v>
+        <v>25.916</v>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
@@ -32092,20 +32100,20 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>-4.98</v>
+        <v>-4.66</v>
       </c>
       <c r="L100" t="n">
-        <v>22.68</v>
+        <v>21.25</v>
       </c>
       <c r="M100" t="n">
         <v>0.83</v>
       </c>
       <c r="N100" t="n">
-        <v>22.96</v>
+        <v>21.51</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>14:05:46.000000</t>
+          <t>09:24:58.000000</t>
         </is>
       </c>
       <c r="P100" t="n">
@@ -32120,7 +32128,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Севлиево</t>
+          <t>Благоевград Център</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -32139,7 +32147,7 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>27.663</v>
+        <v>25.916</v>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
@@ -32152,20 +32160,20 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>-4.98</v>
+        <v>-4.66</v>
       </c>
       <c r="L101" t="n">
-        <v>22.68</v>
+        <v>21.25</v>
       </c>
       <c r="M101" t="n">
         <v>0.83</v>
       </c>
       <c r="N101" t="n">
-        <v>22.96</v>
+        <v>21.51</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>14:05:46.000000</t>
+          <t>09:24:58.000000</t>
         </is>
       </c>
       <c r="P101" t="n">
@@ -32180,7 +32188,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Севлиево</t>
+          <t>Благоевград Център</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -32199,7 +32207,7 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>27.663</v>
+        <v>25.916</v>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
@@ -32212,20 +32220,20 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>-4.98</v>
+        <v>-4.66</v>
       </c>
       <c r="L102" t="n">
-        <v>22.68</v>
+        <v>21.25</v>
       </c>
       <c r="M102" t="n">
         <v>0.83</v>
       </c>
       <c r="N102" t="n">
-        <v>22.96</v>
+        <v>21.51</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>14:05:46.000000</t>
+          <t>09:24:58.000000</t>
         </is>
       </c>
       <c r="P102" t="n">
@@ -32240,7 +32248,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Севлиево</t>
+          <t>Благоевград Център</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -32259,7 +32267,7 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>27.663</v>
+        <v>25.916</v>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
@@ -32272,20 +32280,20 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>-4.98</v>
+        <v>-4.66</v>
       </c>
       <c r="L103" t="n">
-        <v>22.68</v>
+        <v>21.25</v>
       </c>
       <c r="M103" t="n">
         <v>0.83</v>
       </c>
       <c r="N103" t="n">
-        <v>22.96</v>
+        <v>21.51</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>14:05:46.000000</t>
+          <t>09:24:58.000000</t>
         </is>
       </c>
       <c r="P103" t="n">
@@ -32300,52 +32308,52 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Севлиево</t>
+          <t>Варна</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>В 7230 ВР</t>
+          <t>B 4161 TK</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>78970155027721574</t>
+          <t>78970155027721285</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>E GAS LPG</t>
+          <t>DIESEL EKONOMY</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>27.663</v>
+        <v>40</v>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
-        <v>0.82</v>
+        <v>1.77</v>
       </c>
       <c r="I104" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>-4.98</v>
+        <v>4.8</v>
       </c>
       <c r="L104" t="n">
-        <v>22.68</v>
+        <v>70.8</v>
       </c>
       <c r="M104" t="n">
-        <v>0.83</v>
+        <v>1.8</v>
       </c>
       <c r="N104" t="n">
-        <v>22.96</v>
+        <v>72</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>14:05:46.000000</t>
+          <t>13:08:08.000000</t>
         </is>
       </c>
       <c r="P104" t="n">
@@ -32360,52 +32368,52 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Севлиево</t>
+          <t>Варна</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>В 7230 ВР</t>
+          <t>B 4161 TK</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>78970155027721574</t>
+          <t>78970155027721285</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>E GAS LPG</t>
+          <t>DIESEL EKONOMY</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>27.663</v>
+        <v>40</v>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>0.82</v>
+        <v>1.77</v>
       </c>
       <c r="I105" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>-4.98</v>
+        <v>4.8</v>
       </c>
       <c r="L105" t="n">
-        <v>22.68</v>
+        <v>70.8</v>
       </c>
       <c r="M105" t="n">
-        <v>0.83</v>
+        <v>1.8</v>
       </c>
       <c r="N105" t="n">
-        <v>22.96</v>
+        <v>72</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>14:05:46.000000</t>
+          <t>13:08:08.000000</t>
         </is>
       </c>
       <c r="P105" t="n">
@@ -32420,52 +32428,52 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Търговище</t>
+          <t>Варна</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>В 7230 ВР</t>
+          <t>B 4161 TK</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>78970155027721574</t>
+          <t>78970155027721285</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>E GAS LPG</t>
+          <t>DIESEL EKONOMY</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>10.157</v>
+        <v>40</v>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
-        <v>0.82</v>
+        <v>1.77</v>
       </c>
       <c r="I106" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>-1.83</v>
+        <v>4.8</v>
       </c>
       <c r="L106" t="n">
-        <v>8.33</v>
+        <v>70.8</v>
       </c>
       <c r="M106" t="n">
-        <v>0.83</v>
+        <v>1.8</v>
       </c>
       <c r="N106" t="n">
-        <v>8.43</v>
+        <v>72</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>16:03:15.000000</t>
+          <t>13:08:08.000000</t>
         </is>
       </c>
       <c r="P106" t="n">
@@ -32480,52 +32488,52 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Търговище</t>
+          <t>Варна</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>В 7230 ВР</t>
+          <t>B 4161 TK</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>78970155027721574</t>
+          <t>78970155027721285</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>E GAS LPG</t>
+          <t>DIESEL EKONOMY</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>10.157</v>
+        <v>40</v>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>0.82</v>
+        <v>1.77</v>
       </c>
       <c r="I107" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>-1.83</v>
+        <v>4.8</v>
       </c>
       <c r="L107" t="n">
-        <v>8.33</v>
+        <v>70.8</v>
       </c>
       <c r="M107" t="n">
-        <v>0.83</v>
+        <v>1.8</v>
       </c>
       <c r="N107" t="n">
-        <v>8.43</v>
+        <v>72</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>16:03:15.000000</t>
+          <t>13:08:08.000000</t>
         </is>
       </c>
       <c r="P107" t="n">
@@ -32540,52 +32548,52 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Търговище</t>
+          <t>Варна</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>В 7230 ВР</t>
+          <t>B 4161 TK</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>78970155027721574</t>
+          <t>78970155027721285</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>E GAS LPG</t>
+          <t>DIESEL EKONOMY</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>10.157</v>
+        <v>40</v>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>0.82</v>
+        <v>1.77</v>
       </c>
       <c r="I108" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>-1.83</v>
+        <v>4.8</v>
       </c>
       <c r="L108" t="n">
-        <v>8.33</v>
+        <v>70.8</v>
       </c>
       <c r="M108" t="n">
-        <v>0.83</v>
+        <v>1.8</v>
       </c>
       <c r="N108" t="n">
-        <v>8.43</v>
+        <v>72</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>16:03:15.000000</t>
+          <t>13:08:08.000000</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -32600,52 +32608,52 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Търговище</t>
+          <t>Варна</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>В 7230 ВР</t>
+          <t>B 4161 TK</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>78970155027721574</t>
+          <t>78970155027721285</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>E GAS LPG</t>
+          <t>DIESEL EKONOMY</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>10.157</v>
+        <v>40</v>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>0.82</v>
+        <v>1.77</v>
       </c>
       <c r="I109" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>-1.83</v>
+        <v>4.8</v>
       </c>
       <c r="L109" t="n">
-        <v>8.33</v>
+        <v>70.8</v>
       </c>
       <c r="M109" t="n">
-        <v>0.83</v>
+        <v>1.8</v>
       </c>
       <c r="N109" t="n">
-        <v>8.43</v>
+        <v>72</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>16:03:15.000000</t>
+          <t>13:08:08.000000</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -32660,7 +32668,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Търговище</t>
+          <t>Севлиево</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -32679,7 +32687,7 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>10.157</v>
+        <v>27.663</v>
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
@@ -32692,20 +32700,20 @@
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>-1.83</v>
+        <v>-4.98</v>
       </c>
       <c r="L110" t="n">
-        <v>8.33</v>
+        <v>22.68</v>
       </c>
       <c r="M110" t="n">
         <v>0.83</v>
       </c>
       <c r="N110" t="n">
-        <v>8.43</v>
+        <v>22.96</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>16:03:15.000000</t>
+          <t>14:05:46.000000</t>
         </is>
       </c>
       <c r="P110" t="n">
@@ -32720,7 +32728,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Търговище</t>
+          <t>Севлиево</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -32739,7 +32747,7 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>10.157</v>
+        <v>27.663</v>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
@@ -32752,20 +32760,20 @@
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>-1.83</v>
+        <v>-4.98</v>
       </c>
       <c r="L111" t="n">
-        <v>8.33</v>
+        <v>22.68</v>
       </c>
       <c r="M111" t="n">
         <v>0.83</v>
       </c>
       <c r="N111" t="n">
-        <v>8.43</v>
+        <v>22.96</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>16:03:15.000000</t>
+          <t>14:05:46.000000</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -32775,22 +32783,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Севлиево</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>В8972ВР</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>78970155027721343</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -32799,7 +32807,7 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>28.072</v>
+        <v>27.663</v>
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
@@ -32812,20 +32820,20 @@
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>-5.05</v>
+        <v>-4.98</v>
       </c>
       <c r="L112" t="n">
-        <v>23.02</v>
+        <v>22.68</v>
       </c>
       <c r="M112" t="n">
         <v>0.83</v>
       </c>
       <c r="N112" t="n">
-        <v>23.3</v>
+        <v>22.96</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>09:12:30.000000</t>
+          <t>14:05:46.000000</t>
         </is>
       </c>
       <c r="P112" t="n">
@@ -32835,22 +32843,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Севлиево</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>В8972ВР</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>78970155027721343</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -32859,7 +32867,7 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>28.072</v>
+        <v>27.663</v>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
@@ -32872,20 +32880,20 @@
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>-5.05</v>
+        <v>-4.98</v>
       </c>
       <c r="L113" t="n">
-        <v>23.02</v>
+        <v>22.68</v>
       </c>
       <c r="M113" t="n">
         <v>0.83</v>
       </c>
       <c r="N113" t="n">
-        <v>23.3</v>
+        <v>22.96</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>09:12:30.000000</t>
+          <t>14:05:46.000000</t>
         </is>
       </c>
       <c r="P113" t="n">
@@ -32895,22 +32903,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Севлиево</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>В8972ВР</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>78970155027721343</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -32919,7 +32927,7 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>28.072</v>
+        <v>27.663</v>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
@@ -32932,20 +32940,20 @@
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>-5.05</v>
+        <v>-4.98</v>
       </c>
       <c r="L114" t="n">
-        <v>23.02</v>
+        <v>22.68</v>
       </c>
       <c r="M114" t="n">
         <v>0.83</v>
       </c>
       <c r="N114" t="n">
-        <v>23.3</v>
+        <v>22.96</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>09:12:30.000000</t>
+          <t>14:05:46.000000</t>
         </is>
       </c>
       <c r="P114" t="n">
@@ -32955,22 +32963,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Севлиево</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>В8972ВР</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>78970155027721343</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -32979,7 +32987,7 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>28.072</v>
+        <v>27.663</v>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
@@ -32992,20 +33000,20 @@
         <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>-5.05</v>
+        <v>-4.98</v>
       </c>
       <c r="L115" t="n">
-        <v>23.02</v>
+        <v>22.68</v>
       </c>
       <c r="M115" t="n">
         <v>0.83</v>
       </c>
       <c r="N115" t="n">
-        <v>23.3</v>
+        <v>22.96</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>09:12:30.000000</t>
+          <t>14:05:46.000000</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -33015,22 +33023,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Търговище</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>В8972ВР</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>78970155027721343</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -33039,7 +33047,7 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>28.072</v>
+        <v>10.157</v>
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
@@ -33052,20 +33060,20 @@
         <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>-5.05</v>
+        <v>-1.83</v>
       </c>
       <c r="L116" t="n">
-        <v>23.02</v>
+        <v>8.33</v>
       </c>
       <c r="M116" t="n">
         <v>0.83</v>
       </c>
       <c r="N116" t="n">
-        <v>23.3</v>
+        <v>8.43</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>09:12:30.000000</t>
+          <t>16:03:15.000000</t>
         </is>
       </c>
       <c r="P116" t="n">
@@ -33075,22 +33083,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Варна</t>
+          <t>Търговище</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>В8972ВР</t>
+          <t>В 7230 ВР</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>78970155027721343</t>
+          <t>78970155027721574</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -33099,7 +33107,7 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>28.072</v>
+        <v>10.157</v>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
@@ -33112,23 +33120,623 @@
         <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>-5.05</v>
+        <v>-1.83</v>
       </c>
       <c r="L117" t="n">
-        <v>23.02</v>
+        <v>8.33</v>
       </c>
       <c r="M117" t="n">
         <v>0.83</v>
       </c>
       <c r="N117" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>16:03:15.000000</t>
+        </is>
+      </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Търговище</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>В 7230 ВР</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>78970155027721574</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>10.157</v>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="L118" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N118" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>16:03:15.000000</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Търговище</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>В 7230 ВР</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>78970155027721574</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>10.157</v>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="L119" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N119" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>16:03:15.000000</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Търговище</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>В 7230 ВР</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>78970155027721574</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>10.157</v>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="L120" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N120" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>16:03:15.000000</t>
+        </is>
+      </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Търговище</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>В 7230 ВР</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>78970155027721574</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>10.157</v>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="L121" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N121" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>16:03:15.000000</t>
+        </is>
+      </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Варна</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>В8972ВР</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>78970155027721343</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>28.072</v>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="L122" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N122" t="n">
         <v>23.3</v>
       </c>
-      <c r="O117" t="inlineStr">
+      <c r="O122" t="inlineStr">
         <is>
           <t>09:12:30.000000</t>
         </is>
       </c>
-      <c r="P117" t="n">
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Варна</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>В8972ВР</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>78970155027721343</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>28.072</v>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="L123" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N123" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>09:12:30.000000</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Варна</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>В8972ВР</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>78970155027721343</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>28.072</v>
+      </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="L124" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N124" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>09:12:30.000000</t>
+        </is>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Варна</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>В8972ВР</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>78970155027721343</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>28.072</v>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="L125" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N125" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>09:12:30.000000</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Варна</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>В8972ВР</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>78970155027721343</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>28.072</v>
+      </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="L126" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N126" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>09:12:30.000000</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Варна</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>В8972ВР</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>78970155027721343</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>28.072</v>
+      </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="L127" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N127" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>09:12:30.000000</t>
+        </is>
+      </c>
+      <c r="P127" t="n">
         <v>0</v>
       </c>
     </row>
@@ -41205,7 +41813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41321,17 +41929,19 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>-5.4</v>
+      </c>
       <c r="L2" t="n">
-        <v>24.9</v>
+        <v>24.6</v>
       </c>
       <c r="M2" t="n">
         <v>0.83</v>
@@ -41351,7 +41961,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -41361,12 +41971,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>В 2764 ТА</t>
+          <t>В 2763 ТА</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>78970155027722002</t>
+          <t>78970155027721996</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -41375,7 +41985,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>28.651</v>
+        <v>30</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
@@ -41388,30 +41998,30 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-5.16</v>
+        <v>-5.4</v>
       </c>
       <c r="L3" t="n">
-        <v>23.49</v>
+        <v>24.6</v>
       </c>
       <c r="M3" t="n">
         <v>0.83</v>
       </c>
       <c r="N3" t="n">
-        <v>23.78</v>
+        <v>24.9</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>11:56:06.000000</t>
+          <t>16:08:47.000000</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>56450</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -41421,12 +42031,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>В 2764 ТА</t>
+          <t>В 2763 ТА</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>78970155027722002</t>
+          <t>78970155027721996</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -41435,7 +42045,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>28.651</v>
+        <v>30</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
@@ -41448,30 +42058,30 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.16</v>
+        <v>-5.4</v>
       </c>
       <c r="L4" t="n">
-        <v>23.49</v>
+        <v>24.6</v>
       </c>
       <c r="M4" t="n">
         <v>0.83</v>
       </c>
       <c r="N4" t="n">
-        <v>23.78</v>
+        <v>24.9</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>11:56:06.000000</t>
+          <t>16:08:47.000000</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>56450</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -41481,12 +42091,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>В 2764 ТА</t>
+          <t>В 2763 ТА</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>78970155027722002</t>
+          <t>78970155027721996</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -41495,7 +42105,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>28.651</v>
+        <v>30</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
@@ -41508,30 +42118,30 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-5.16</v>
+        <v>-5.4</v>
       </c>
       <c r="L5" t="n">
-        <v>23.49</v>
+        <v>24.6</v>
       </c>
       <c r="M5" t="n">
         <v>0.83</v>
       </c>
       <c r="N5" t="n">
-        <v>23.78</v>
+        <v>24.9</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>11:56:06.000000</t>
+          <t>16:08:47.000000</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>56450</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -41541,12 +42151,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>В 2764 ТА</t>
+          <t>В 2763 ТА</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>78970155027722002</t>
+          <t>78970155027721996</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -41555,7 +42165,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>28.651</v>
+        <v>30</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
@@ -41568,30 +42178,30 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.16</v>
+        <v>-5.4</v>
       </c>
       <c r="L6" t="n">
-        <v>23.49</v>
+        <v>24.6</v>
       </c>
       <c r="M6" t="n">
         <v>0.83</v>
       </c>
       <c r="N6" t="n">
-        <v>23.78</v>
+        <v>24.9</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>11:56:06.000000</t>
+          <t>16:08:47.000000</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>56450</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -41601,12 +42211,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>В 2764 ТА</t>
+          <t>В 2763 ТА</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>78970155027722002</t>
+          <t>78970155027721996</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -41615,7 +42225,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>28.651</v>
+        <v>30</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
@@ -41628,24 +42238,24 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.16</v>
+        <v>-5.4</v>
       </c>
       <c r="L7" t="n">
-        <v>23.49</v>
+        <v>24.6</v>
       </c>
       <c r="M7" t="n">
         <v>0.83</v>
       </c>
       <c r="N7" t="n">
-        <v>23.78</v>
+        <v>24.9</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>11:56:06.000000</t>
+          <t>16:08:47.000000</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>56450</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -41711,7 +42321,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -41721,12 +42331,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>В 2763 ТА</t>
+          <t>В 2764 ТА</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>78970155027721996</t>
+          <t>78970155027722002</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -41735,7 +42345,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>28.277</v>
+        <v>28.651</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
@@ -41748,30 +42358,30 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.09</v>
+        <v>-5.16</v>
       </c>
       <c r="L9" t="n">
-        <v>23.19</v>
+        <v>23.49</v>
       </c>
       <c r="M9" t="n">
         <v>0.83</v>
       </c>
       <c r="N9" t="n">
-        <v>23.47</v>
+        <v>23.78</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>15:21:46.000000</t>
+          <t>11:56:06.000000</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>57260</v>
+        <v>56450</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -41781,12 +42391,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>В 2763 ТА</t>
+          <t>В 2764 ТА</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>78970155027721996</t>
+          <t>78970155027722002</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -41795,7 +42405,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>28.277</v>
+        <v>28.651</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
@@ -41808,30 +42418,30 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.09</v>
+        <v>-5.16</v>
       </c>
       <c r="L10" t="n">
-        <v>23.19</v>
+        <v>23.49</v>
       </c>
       <c r="M10" t="n">
         <v>0.83</v>
       </c>
       <c r="N10" t="n">
-        <v>23.47</v>
+        <v>23.78</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>15:21:46.000000</t>
+          <t>11:56:06.000000</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>57260</v>
+        <v>56450</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -41841,12 +42451,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>В 2763 ТА</t>
+          <t>В 2764 ТА</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>78970155027721996</t>
+          <t>78970155027722002</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -41855,7 +42465,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>28.277</v>
+        <v>28.651</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
@@ -41868,30 +42478,30 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.09</v>
+        <v>-5.16</v>
       </c>
       <c r="L11" t="n">
-        <v>23.19</v>
+        <v>23.49</v>
       </c>
       <c r="M11" t="n">
         <v>0.83</v>
       </c>
       <c r="N11" t="n">
-        <v>23.47</v>
+        <v>23.78</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>15:21:46.000000</t>
+          <t>11:56:06.000000</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>57260</v>
+        <v>56450</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -41901,12 +42511,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>В 2763 ТА</t>
+          <t>В 2764 ТА</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>78970155027721996</t>
+          <t>78970155027722002</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -41915,7 +42525,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>28.277</v>
+        <v>28.651</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
@@ -41928,30 +42538,30 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>-5.09</v>
+        <v>-5.16</v>
       </c>
       <c r="L12" t="n">
-        <v>23.19</v>
+        <v>23.49</v>
       </c>
       <c r="M12" t="n">
         <v>0.83</v>
       </c>
       <c r="N12" t="n">
-        <v>23.47</v>
+        <v>23.78</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>15:21:46.000000</t>
+          <t>11:56:06.000000</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>57260</v>
+        <v>56450</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -41961,12 +42571,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>В 2763 ТА</t>
+          <t>В 2764 ТА</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>78970155027721996</t>
+          <t>78970155027722002</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -41975,7 +42585,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>28.277</v>
+        <v>28.651</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
@@ -41988,24 +42598,24 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.09</v>
+        <v>-5.16</v>
       </c>
       <c r="L13" t="n">
-        <v>23.19</v>
+        <v>23.49</v>
       </c>
       <c r="M13" t="n">
         <v>0.83</v>
       </c>
       <c r="N13" t="n">
-        <v>23.47</v>
+        <v>23.78</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>15:21:46.000000</t>
+          <t>11:56:06.000000</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>57260</v>
+        <v>56450</v>
       </c>
     </row>
     <row r="14">
@@ -42065,6 +42675,306 @@
         </is>
       </c>
       <c r="P14" t="n">
+        <v>57260</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Варна Порт</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>В 2763 ТА</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>78970155027721996</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>28.277</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-5.09</v>
+      </c>
+      <c r="L15" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N15" t="n">
+        <v>23.47</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>15:21:46.000000</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>57260</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Варна Порт</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>В 2763 ТА</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>78970155027721996</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>28.277</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-5.09</v>
+      </c>
+      <c r="L16" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N16" t="n">
+        <v>23.47</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>15:21:46.000000</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>57260</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Варна Порт</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>В 2763 ТА</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>78970155027721996</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>28.277</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-5.09</v>
+      </c>
+      <c r="L17" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N17" t="n">
+        <v>23.47</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>15:21:46.000000</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>57260</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Варна Порт</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>В 2763 ТА</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>78970155027721996</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>28.277</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-5.09</v>
+      </c>
+      <c r="L18" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N18" t="n">
+        <v>23.47</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>15:21:46.000000</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>57260</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Варна Порт</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>В 2763 ТА</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>78970155027721996</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>E GAS LPG</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>28.277</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-5.09</v>
+      </c>
+      <c r="L19" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N19" t="n">
+        <v>23.47</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>15:21:46.000000</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
         <v>57260</v>
       </c>
     </row>
@@ -44876,7 +45786,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="L47" t="n">
         <v>29.4</v>
@@ -44936,7 +45846,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="L48" t="n">
         <v>22.05</v>
@@ -47891,17 +48801,19 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>1.54</v>
+      </c>
       <c r="L2" t="n">
-        <v>25.48</v>
+        <v>25.06</v>
       </c>
       <c r="M2" t="n">
         <v>1.82</v>
@@ -47949,17 +48861,19 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>1.97</v>
+      </c>
       <c r="L3" t="n">
-        <v>32.63</v>
+        <v>32.09</v>
       </c>
       <c r="M3" t="n">
         <v>1.82</v>
@@ -48007,17 +48921,19 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="L4" t="n">
-        <v>24.75</v>
+        <v>24.34</v>
       </c>
       <c r="M4" t="n">
         <v>1.82</v>
@@ -48065,7 +48981,7 @@
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>2.07</v>
+        <v>1.78</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -48073,9 +48989,11 @@
       <c r="J5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
       <c r="L5" t="n">
-        <v>35.77</v>
+        <v>30.76</v>
       </c>
       <c r="M5" t="n">
         <v>2.07</v>
@@ -48123,17 +49041,19 @@
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>5.56</v>
+      </c>
       <c r="L6" t="n">
-        <v>92</v>
+        <v>90.48</v>
       </c>
       <c r="M6" t="n">
         <v>1.82</v>
@@ -48181,17 +49101,19 @@
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="n">
+        <v>1.63</v>
+      </c>
       <c r="L7" t="n">
-        <v>26.99</v>
+        <v>26.55</v>
       </c>
       <c r="M7" t="n">
         <v>1.82</v>
@@ -48239,17 +49161,19 @@
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="n">
+        <v>3.4</v>
+      </c>
       <c r="L8" t="n">
-        <v>56.33</v>
+        <v>55.4</v>
       </c>
       <c r="M8" t="n">
         <v>1.82</v>
@@ -48297,17 +49221,19 @@
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>0.77</v>
+      </c>
       <c r="L9" t="n">
-        <v>12.68</v>
+        <v>12.47</v>
       </c>
       <c r="M9" t="n">
         <v>1.82</v>
@@ -48355,17 +49281,19 @@
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>14.3</v>
+      </c>
       <c r="L10" t="n">
-        <v>236.62</v>
+        <v>232.72</v>
       </c>
       <c r="M10" t="n">
         <v>1.82</v>
@@ -48413,17 +49341,19 @@
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>4.4</v>
+      </c>
       <c r="L11" t="n">
-        <v>72.83</v>
+        <v>71.63</v>
       </c>
       <c r="M11" t="n">
         <v>1.82</v>
@@ -48471,17 +49401,19 @@
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>1.97</v>
+      </c>
       <c r="L12" t="n">
-        <v>32.56</v>
+        <v>32.02</v>
       </c>
       <c r="M12" t="n">
         <v>1.82</v>
@@ -48529,17 +49461,19 @@
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>2.31</v>
+      </c>
       <c r="L13" t="n">
-        <v>38.22</v>
+        <v>37.59</v>
       </c>
       <c r="M13" t="n">
         <v>1.82</v>
@@ -48587,17 +49521,19 @@
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>2.19</v>
+      </c>
       <c r="L14" t="n">
-        <v>36.22</v>
+        <v>35.62</v>
       </c>
       <c r="M14" t="n">
         <v>1.82</v>
@@ -48645,17 +49581,19 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>-5.85</v>
+      </c>
       <c r="L15" t="n">
-        <v>26.98</v>
+        <v>26.65</v>
       </c>
       <c r="M15" t="n">
         <v>0.83</v>
@@ -48703,17 +49641,19 @@
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>5.5</v>
+      </c>
       <c r="L16" t="n">
-        <v>91</v>
+        <v>89.5</v>
       </c>
       <c r="M16" t="n">
         <v>1.82</v>
@@ -51317,7 +52257,7 @@
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -51329,7 +52269,7 @@
         <v>1.47</v>
       </c>
       <c r="L8" t="n">
-        <v>52.88</v>
+        <v>52.51</v>
       </c>
       <c r="M8" t="n">
         <v>1.51</v>
@@ -54653,7 +55593,7 @@
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
@@ -54665,7 +55605,7 @@
         <v>1.09</v>
       </c>
       <c r="L53" t="n">
-        <v>93.47</v>
+        <v>92.38</v>
       </c>
       <c r="M53" t="n">
         <v>1.82</v>
@@ -55750,7 +56690,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>27.64</v>
+        <v>-6.07</v>
       </c>
       <c r="L3" t="n">
         <v>27.64</v>
@@ -56077,7 +57017,7 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -56089,7 +57029,7 @@
         <v>0.79</v>
       </c>
       <c r="L3" t="n">
-        <v>37.88</v>
+        <v>37.62</v>
       </c>
       <c r="M3" t="n">
         <v>1.51</v>
@@ -63377,7 +64317,7 @@
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
@@ -63389,7 +64329,7 @@
         <v>3.72</v>
       </c>
       <c r="L63" t="n">
-        <v>319.77</v>
+        <v>316.05</v>
       </c>
       <c r="M63" t="n">
         <v>1.82</v>
@@ -63437,7 +64377,7 @@
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
@@ -63449,7 +64389,7 @@
         <v>6</v>
       </c>
       <c r="L64" t="n">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="M64" t="n">
         <v>1.82</v>
@@ -63497,7 +64437,7 @@
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
@@ -63509,7 +64449,7 @@
         <v>5</v>
       </c>
       <c r="L65" t="n">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="M65" t="n">
         <v>1.82</v>
@@ -63557,7 +64497,7 @@
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
@@ -63569,7 +64509,7 @@
         <v>3.8</v>
       </c>
       <c r="L66" t="n">
-        <v>326.8</v>
+        <v>323</v>
       </c>
       <c r="M66" t="n">
         <v>1.82</v>
@@ -70165,7 +71105,7 @@
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
@@ -70177,7 +71117,7 @@
         <v>1.2</v>
       </c>
       <c r="L83" t="n">
-        <v>102.96</v>
+        <v>101.77</v>
       </c>
       <c r="M83" t="n">
         <v>1.82</v>
@@ -70225,7 +71165,7 @@
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
@@ -70237,7 +71177,7 @@
         <v>0.86</v>
       </c>
       <c r="L84" t="n">
-        <v>73.72</v>
+        <v>72.87</v>
       </c>
       <c r="M84" t="n">
         <v>1.82</v>
@@ -70285,7 +71225,7 @@
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
@@ -70297,7 +71237,7 @@
         <v>1.11</v>
       </c>
       <c r="L85" t="n">
-        <v>95.41</v>
+        <v>94.3</v>
       </c>
       <c r="M85" t="n">
         <v>1.82</v>
@@ -73895,7 +74835,7 @@
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -73907,7 +74847,7 @@
         <v>15</v>
       </c>
       <c r="L17" t="n">
-        <v>1290</v>
+        <v>1275</v>
       </c>
       <c r="M17" t="n">
         <v>1.82</v>
@@ -73955,7 +74895,7 @@
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -73967,7 +74907,7 @@
         <v>2</v>
       </c>
       <c r="L18" t="n">
-        <v>171.98</v>
+        <v>169.98</v>
       </c>
       <c r="M18" t="n">
         <v>1.82</v>
@@ -84047,7 +84987,7 @@
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -84059,7 +84999,7 @@
         <v>1.63</v>
       </c>
       <c r="L38" t="n">
-        <v>140.03</v>
+        <v>138.4</v>
       </c>
       <c r="M38" t="n">
         <v>1.82</v>
@@ -88025,7 +88965,7 @@
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
@@ -88037,7 +88977,7 @@
         <v>0.59</v>
       </c>
       <c r="L53" t="n">
-        <v>27.96</v>
+        <v>27.77</v>
       </c>
       <c r="M53" t="n">
         <v>1.52</v>
@@ -88085,7 +89025,7 @@
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
@@ -88097,7 +89037,7 @@
         <v>0.85</v>
       </c>
       <c r="L54" t="n">
-        <v>73.5</v>
+        <v>72.64</v>
       </c>
       <c r="M54" t="n">
         <v>1.82</v>
@@ -88145,7 +89085,7 @@
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
@@ -88157,7 +89097,7 @@
         <v>0.64</v>
       </c>
       <c r="L55" t="n">
-        <v>30.42</v>
+        <v>30.21</v>
       </c>
       <c r="M55" t="n">
         <v>1.51</v>
@@ -88265,7 +89205,7 @@
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
@@ -88277,7 +89217,7 @@
         <v>0.59</v>
       </c>
       <c r="L57" t="n">
-        <v>28.15</v>
+        <v>27.95</v>
       </c>
       <c r="M57" t="n">
         <v>1.51</v>
@@ -88325,7 +89265,7 @@
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
@@ -88337,7 +89277,7 @@
         <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>47.89</v>
+        <v>47.55</v>
       </c>
       <c r="M58" t="n">
         <v>1.52</v>
@@ -88385,7 +89325,7 @@
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
@@ -88397,7 +89337,7 @@
         <v>1.06</v>
       </c>
       <c r="L59" t="n">
-        <v>50.57</v>
+        <v>50.21</v>
       </c>
       <c r="M59" t="n">
         <v>1.52</v>

--- a/A_FINAL_RESULT/eko_transactions.xlsx
+++ b/A_FINAL_RESULT/eko_transactions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\A_FINAL_RESULT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9990C39D-0FC3-4CA7-B2BC-E901D92DE8F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F671E940-DA1B-4D6D-A805-666F2EDA5B78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="57" activeTab="40" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="33" activeTab="35" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OП ТАСРУД" sheetId="1" r:id="rId1"/>
@@ -25547,6 +25547,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
   <dimension ref="A1:P17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">

--- a/A_FINAL_RESULT/eko_transactions.xlsx
+++ b/A_FINAL_RESULT/eko_transactions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\A_FINAL_RESULT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F671E940-DA1B-4D6D-A805-666F2EDA5B78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FF54C21-91EA-42EB-AC86-EE8A37DA5B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="33" activeTab="35" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="12" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OП ТАСРУД" sheetId="1" r:id="rId1"/>
@@ -5354,7 +5354,7 @@
         <v>21</v>
       </c>
       <c r="H2">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5362,11 +5362,8 @@
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
-        <v>0.14000000000000001</v>
-      </c>
       <c r="L2">
-        <v>79.3</v>
+        <v>81.22</v>
       </c>
       <c r="M2">
         <v>1.69</v>
@@ -5404,7 +5401,7 @@
         <v>21</v>
       </c>
       <c r="H3">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5412,11 +5409,8 @@
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
-        <v>0.14000000000000001</v>
-      </c>
       <c r="L3">
-        <v>78.73</v>
+        <v>81.12</v>
       </c>
       <c r="M3">
         <v>1.7</v>
@@ -8707,6 +8701,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:P22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -8781,19 +8778,16 @@
         <v>21</v>
       </c>
       <c r="H2">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0.01</v>
-      </c>
-      <c r="K2">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>780.2</v>
+        <v>794.3</v>
       </c>
       <c r="M2">
         <v>1.69</v>
@@ -8831,19 +8825,16 @@
         <v>21</v>
       </c>
       <c r="H3">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0.01</v>
-      </c>
-      <c r="K3">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>627.20000000000005</v>
+        <v>649.87</v>
       </c>
       <c r="M3">
         <v>1.72</v>
@@ -8981,19 +8972,19 @@
         <v>21</v>
       </c>
       <c r="H6">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K6">
-        <v>7.2</v>
+        <v>10.8</v>
       </c>
       <c r="L6">
-        <v>622.84</v>
+        <v>626.44000000000005</v>
       </c>
       <c r="M6">
         <v>1.77</v>
@@ -9031,19 +9022,19 @@
         <v>21</v>
       </c>
       <c r="H7">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K7">
-        <v>1.1000000000000001</v>
+        <v>1.66</v>
       </c>
       <c r="L7">
-        <v>95.52</v>
+        <v>96.07</v>
       </c>
       <c r="M7">
         <v>1.79</v>
@@ -9081,19 +9072,19 @@
         <v>21</v>
       </c>
       <c r="H8">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K8">
-        <v>8.9499999999999993</v>
+        <v>13.42</v>
       </c>
       <c r="L8">
-        <v>787.34</v>
+        <v>791.81</v>
       </c>
       <c r="M8">
         <v>1.79</v>
@@ -9131,19 +9122,19 @@
         <v>21</v>
       </c>
       <c r="H9">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K9">
-        <v>7.68</v>
+        <v>11.51</v>
       </c>
       <c r="L9">
-        <v>675.49</v>
+        <v>679.32</v>
       </c>
       <c r="M9">
         <v>1.79</v>
@@ -9181,19 +9172,19 @@
         <v>21</v>
       </c>
       <c r="H10">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K10">
-        <v>10.37</v>
+        <v>15.55</v>
       </c>
       <c r="L10">
-        <v>912.44</v>
+        <v>917.62</v>
       </c>
       <c r="M10">
         <v>1.81</v>
@@ -9231,19 +9222,19 @@
         <v>21</v>
       </c>
       <c r="H11">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K11">
-        <v>10.01</v>
+        <v>15.02</v>
       </c>
       <c r="L11">
-        <v>880.95</v>
+        <v>885.96</v>
       </c>
       <c r="M11">
         <v>1.81</v>
@@ -9281,19 +9272,19 @@
         <v>21</v>
       </c>
       <c r="H12">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K12">
-        <v>7.8</v>
+        <v>11.7</v>
       </c>
       <c r="L12">
-        <v>686.4</v>
+        <v>690.3</v>
       </c>
       <c r="M12">
         <v>1.81</v>
@@ -9331,19 +9322,19 @@
         <v>21</v>
       </c>
       <c r="H13">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K13">
-        <v>9.49</v>
+        <v>14.24</v>
       </c>
       <c r="L13">
-        <v>821.03</v>
+        <v>825.77</v>
       </c>
       <c r="M13">
         <v>1.82</v>
@@ -9381,19 +9372,19 @@
         <v>21</v>
       </c>
       <c r="H14">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K14">
-        <v>10.33</v>
+        <v>15.49</v>
       </c>
       <c r="L14">
-        <v>893.53</v>
+        <v>898.69</v>
       </c>
       <c r="M14">
         <v>1.82</v>
@@ -9431,19 +9422,19 @@
         <v>21</v>
       </c>
       <c r="H15">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K15">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="L15">
-        <v>550.4</v>
+        <v>553.6</v>
       </c>
       <c r="M15">
         <v>1.82</v>
@@ -9481,19 +9472,19 @@
         <v>21</v>
       </c>
       <c r="H16">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K16">
-        <v>8.0500000000000007</v>
+        <v>12.08</v>
       </c>
       <c r="L16">
-        <v>692.51</v>
+        <v>696.53</v>
       </c>
       <c r="M16">
         <v>1.82</v>
@@ -10847,7 +10838,7 @@
         <v>21</v>
       </c>
       <c r="H2">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -10855,11 +10846,8 @@
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
-        <v>7.0000000000000007E-2</v>
-      </c>
       <c r="L2">
-        <v>37.03</v>
+        <v>38.6</v>
       </c>
       <c r="M2">
         <v>1.72</v>
@@ -10897,19 +10885,16 @@
         <v>21</v>
       </c>
       <c r="H3">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0.03</v>
-      </c>
-      <c r="K3">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>74.67</v>
+        <v>78.33</v>
       </c>
       <c r="M3">
         <v>1.5</v>
@@ -12324,7 +12309,7 @@
         <v>21</v>
       </c>
       <c r="H2">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -12332,11 +12317,8 @@
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
-        <v>1.23</v>
-      </c>
       <c r="L2">
-        <v>676.75</v>
+        <v>697.26</v>
       </c>
       <c r="M2">
         <v>1.7</v>
@@ -12374,7 +12356,7 @@
         <v>21</v>
       </c>
       <c r="H3">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -12382,11 +12364,8 @@
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
-        <v>1.17</v>
-      </c>
       <c r="L3">
-        <v>641.98</v>
+        <v>669.22</v>
       </c>
       <c r="M3">
         <v>1.72</v>
@@ -12424,7 +12403,7 @@
         <v>21</v>
       </c>
       <c r="H4">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -12432,11 +12411,8 @@
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
-        <v>1.55</v>
-      </c>
       <c r="L4">
-        <v>849.8</v>
+        <v>885.85</v>
       </c>
       <c r="M4">
         <v>1.72</v>
@@ -12474,7 +12450,7 @@
         <v>21</v>
       </c>
       <c r="H5">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -12482,11 +12458,8 @@
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5">
-        <v>2.04</v>
-      </c>
       <c r="L5">
-        <v>1122.05</v>
+        <v>1169.6500000000001</v>
       </c>
       <c r="M5">
         <v>1.72</v>
@@ -12524,7 +12497,7 @@
         <v>21</v>
       </c>
       <c r="H6">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -12532,11 +12505,8 @@
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6">
-        <v>1.2</v>
-      </c>
       <c r="L6">
-        <v>660.02</v>
+        <v>688.02</v>
       </c>
       <c r="M6">
         <v>1.72</v>
@@ -12684,19 +12654,16 @@
         <v>21</v>
       </c>
       <c r="H2">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="I2">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
-        <v>0.25</v>
-      </c>
       <c r="L2">
-        <v>135.30000000000001</v>
+        <v>138.58000000000001</v>
       </c>
       <c r="M2">
         <v>1.69</v>
@@ -12734,19 +12701,16 @@
         <v>21</v>
       </c>
       <c r="H3">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="I3">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
-        <v>0.05</v>
-      </c>
       <c r="L3">
-        <v>27.38</v>
+        <v>28.04</v>
       </c>
       <c r="M3">
         <v>1.69</v>
@@ -12784,19 +12748,16 @@
         <v>21</v>
       </c>
       <c r="H4">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="I4">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
-        <v>0.33</v>
-      </c>
       <c r="L4">
-        <v>42.42</v>
+        <v>43.44</v>
       </c>
       <c r="M4">
         <v>1.7</v>
@@ -12834,19 +12795,16 @@
         <v>21</v>
       </c>
       <c r="H5">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="I5">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5">
-        <v>0.77</v>
-      </c>
       <c r="L5">
-        <v>39.06</v>
+        <v>39.99</v>
       </c>
       <c r="M5">
         <v>1.72</v>
@@ -15490,7 +15448,7 @@
         <v>21</v>
       </c>
       <c r="H2">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -15498,11 +15456,8 @@
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
-        <v>7.0000000000000007E-2</v>
-      </c>
       <c r="L2">
-        <v>37.26</v>
+        <v>38.39</v>
       </c>
       <c r="M2">
         <v>1.7</v>
@@ -15540,7 +15495,7 @@
         <v>21</v>
       </c>
       <c r="H3">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -15548,11 +15503,8 @@
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
-        <v>0.06</v>
-      </c>
       <c r="L3">
-        <v>33.99</v>
+        <v>35.020000000000003</v>
       </c>
       <c r="M3">
         <v>1.7</v>
@@ -15590,7 +15542,7 @@
         <v>21</v>
       </c>
       <c r="H4">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -15598,11 +15550,8 @@
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
-        <v>0.12</v>
-      </c>
       <c r="L4">
-        <v>67.92</v>
+        <v>70.8</v>
       </c>
       <c r="M4">
         <v>1.72</v>
@@ -17331,19 +17280,16 @@
         <v>21</v>
       </c>
       <c r="H2">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0.03</v>
-      </c>
-      <c r="K2">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>56.76</v>
+        <v>58.74</v>
       </c>
       <c r="M2">
         <v>1.48</v>
@@ -17688,7 +17634,7 @@
         <v>21</v>
       </c>
       <c r="H2">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -17696,11 +17642,8 @@
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
-        <v>0.15</v>
-      </c>
       <c r="L2">
-        <v>80.62</v>
+        <v>83.06</v>
       </c>
       <c r="M2">
         <v>1.7</v>
@@ -18628,19 +18571,16 @@
         <v>21</v>
       </c>
       <c r="H2">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0.04</v>
-      </c>
-      <c r="K2">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>108.62</v>
+        <v>111.64</v>
       </c>
       <c r="M2">
         <v>1.48</v>
@@ -19875,7 +19815,7 @@
         <v>21</v>
       </c>
       <c r="H2">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -19883,11 +19823,8 @@
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
-        <v>0.09</v>
-      </c>
       <c r="L2">
-        <v>49.5</v>
+        <v>51</v>
       </c>
       <c r="M2">
         <v>1.7</v>
@@ -19925,7 +19862,7 @@
         <v>21</v>
       </c>
       <c r="H3">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -19933,11 +19870,8 @@
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
-        <v>0.16</v>
-      </c>
       <c r="L3">
-        <v>89.38</v>
+        <v>93.17</v>
       </c>
       <c r="M3">
         <v>1.72</v>
@@ -19975,7 +19909,7 @@
         <v>21</v>
       </c>
       <c r="H4">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -19983,11 +19917,8 @@
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
-        <v>0.06</v>
-      </c>
       <c r="L4">
-        <v>32.409999999999997</v>
+        <v>33.979999999999997</v>
       </c>
       <c r="M4">
         <v>1.73</v>
@@ -20025,7 +19956,7 @@
         <v>21</v>
       </c>
       <c r="H5">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -20033,11 +19964,8 @@
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5">
-        <v>0.43</v>
-      </c>
       <c r="L5">
-        <v>235.95</v>
+        <v>245.96</v>
       </c>
       <c r="M5">
         <v>1.72</v>
@@ -24911,7 +24839,7 @@
         <v>21</v>
       </c>
       <c r="H2">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -24919,11 +24847,8 @@
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
-        <v>0.11</v>
-      </c>
       <c r="L2">
-        <v>58.53</v>
+        <v>61.01</v>
       </c>
       <c r="M2">
         <v>1.72</v>
@@ -25547,24 +25472,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
   <dimension ref="A1:P17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.28515625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -27729,7 +27636,7 @@
         <v>21</v>
       </c>
       <c r="H2">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -27737,11 +27644,8 @@
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
-        <v>0.15</v>
-      </c>
       <c r="L2">
-        <v>80.37</v>
+        <v>82.32</v>
       </c>
       <c r="M2">
         <v>1.69</v>
@@ -28275,9 +28179,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2800-000000000000}">
   <dimension ref="A1:P72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -35560,19 +35461,16 @@
         <v>21</v>
       </c>
       <c r="H2">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0.04</v>
-      </c>
-      <c r="K2">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>92.22</v>
+        <v>94.78</v>
       </c>
       <c r="M2">
         <v>1.48</v>
@@ -36070,7 +35968,7 @@
         <v>21</v>
       </c>
       <c r="H2">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -36078,11 +35976,8 @@
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
-        <v>0.12</v>
-      </c>
       <c r="L2">
-        <v>66</v>
+        <v>67.599999999999994</v>
       </c>
       <c r="M2">
         <v>1.69</v>
@@ -36120,7 +36015,7 @@
         <v>21</v>
       </c>
       <c r="H3">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -36128,11 +36023,8 @@
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
-        <v>0.18</v>
-      </c>
       <c r="L3">
-        <v>97.28</v>
+        <v>99.64</v>
       </c>
       <c r="M3">
         <v>1.69</v>
@@ -36170,7 +36062,7 @@
         <v>21</v>
       </c>
       <c r="H4">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -36178,11 +36070,8 @@
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
-        <v>0.28999999999999998</v>
-      </c>
       <c r="L4">
-        <v>160.13999999999999</v>
+        <v>164.99</v>
       </c>
       <c r="M4">
         <v>1.7</v>
@@ -36220,7 +36109,7 @@
         <v>21</v>
       </c>
       <c r="H5">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -36228,11 +36117,8 @@
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5">
-        <v>0.17</v>
-      </c>
       <c r="L5">
-        <v>93.08</v>
+        <v>97.03</v>
       </c>
       <c r="M5">
         <v>1.72</v>
@@ -36270,7 +36156,7 @@
         <v>21</v>
       </c>
       <c r="H6">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -36278,11 +36164,8 @@
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6">
-        <v>0.09</v>
-      </c>
       <c r="L6">
-        <v>51.28</v>
+        <v>53.46</v>
       </c>
       <c r="M6">
         <v>1.72</v>
@@ -40184,7 +40067,7 @@
         <v>21</v>
       </c>
       <c r="H2">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -40192,11 +40075,8 @@
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
-        <v>0.19</v>
-      </c>
       <c r="L2">
-        <v>106.54</v>
+        <v>111.06</v>
       </c>
       <c r="M2">
         <v>1.72</v>
@@ -40344,19 +40224,16 @@
         <v>21</v>
       </c>
       <c r="H2">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0.03</v>
-      </c>
-      <c r="K2">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>39.44</v>
+        <v>41.09</v>
       </c>
       <c r="M2">
         <v>1.49</v>
@@ -40441,19 +40318,16 @@
         <v>21</v>
       </c>
       <c r="H4">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0.03</v>
-      </c>
-      <c r="K4">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>30.03</v>
+        <v>31.08</v>
       </c>
       <c r="M4">
         <v>1.48</v>
@@ -40491,19 +40365,16 @@
         <v>21</v>
       </c>
       <c r="H5">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0.03</v>
-      </c>
-      <c r="K5">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>50.83</v>
+        <v>52.61</v>
       </c>
       <c r="M5">
         <v>1.48</v>
@@ -42616,7 +42487,7 @@
         <v>21</v>
       </c>
       <c r="H2">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -42624,11 +42495,8 @@
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
-        <v>0.17</v>
-      </c>
       <c r="L2">
-        <v>91.46</v>
+        <v>93.68</v>
       </c>
       <c r="M2">
         <v>1.69</v>
@@ -42666,7 +42534,7 @@
         <v>21</v>
       </c>
       <c r="H3">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -42674,11 +42542,8 @@
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
-        <v>0.12</v>
-      </c>
       <c r="L3">
-        <v>65.55</v>
+        <v>67.14</v>
       </c>
       <c r="M3">
         <v>1.69</v>
@@ -42716,7 +42581,7 @@
         <v>21</v>
       </c>
       <c r="H4">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -42724,11 +42589,8 @@
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
-        <v>0.25</v>
-      </c>
       <c r="L4">
-        <v>135.13999999999999</v>
+        <v>139.22999999999999</v>
       </c>
       <c r="M4">
         <v>1.7</v>
@@ -42766,19 +42628,16 @@
         <v>21</v>
       </c>
       <c r="H5">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0.03</v>
-      </c>
-      <c r="K5">
-        <v>0.94</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>44.75</v>
+        <v>46.31</v>
       </c>
       <c r="M5">
         <v>1.48</v>
@@ -42816,7 +42675,7 @@
         <v>21</v>
       </c>
       <c r="H6">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -42824,11 +42683,8 @@
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6">
-        <v>0.16</v>
-      </c>
       <c r="L6">
-        <v>89.81</v>
+        <v>93.62</v>
       </c>
       <c r="M6">
         <v>1.72</v>
@@ -42866,7 +42722,7 @@
         <v>21</v>
       </c>
       <c r="H7">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -42874,11 +42730,8 @@
       <c r="J7">
         <v>0</v>
       </c>
-      <c r="K7">
-        <v>0.21</v>
-      </c>
       <c r="L7">
-        <v>115.5</v>
+        <v>120.4</v>
       </c>
       <c r="M7">
         <v>1.72</v>
@@ -46826,7 +46679,7 @@
         <v>21</v>
       </c>
       <c r="H2">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -46834,11 +46687,8 @@
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
-        <v>0.18</v>
-      </c>
       <c r="L2">
-        <v>101.36</v>
+        <v>105.66</v>
       </c>
       <c r="M2">
         <v>1.72</v>
@@ -47236,7 +47086,7 @@
         <v>21</v>
       </c>
       <c r="H2">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -47244,11 +47094,8 @@
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
-        <v>0.18</v>
-      </c>
       <c r="L2">
-        <v>97.53</v>
+        <v>99.9</v>
       </c>
       <c r="M2">
         <v>1.69</v>
@@ -47286,7 +47133,7 @@
         <v>21</v>
       </c>
       <c r="H3">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -47294,11 +47141,8 @@
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
-        <v>0.14000000000000001</v>
-      </c>
       <c r="L3">
-        <v>76.53</v>
+        <v>78.38</v>
       </c>
       <c r="M3">
         <v>1.69</v>
@@ -47336,7 +47180,7 @@
         <v>21</v>
       </c>
       <c r="H4">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -47344,11 +47188,8 @@
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
-        <v>0.17</v>
-      </c>
       <c r="L4">
-        <v>94.34</v>
+        <v>96.63</v>
       </c>
       <c r="M4">
         <v>1.69</v>
@@ -47386,7 +47227,7 @@
         <v>21</v>
       </c>
       <c r="H5">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -47394,11 +47235,8 @@
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5">
-        <v>0.18</v>
-      </c>
       <c r="L5">
-        <v>96.31</v>
+        <v>99.23</v>
       </c>
       <c r="M5">
         <v>1.7</v>
@@ -47436,7 +47274,7 @@
         <v>21</v>
       </c>
       <c r="H6">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -47444,11 +47282,8 @@
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6">
-        <v>0.14000000000000001</v>
-      </c>
       <c r="L6">
-        <v>75.52</v>
+        <v>77.81</v>
       </c>
       <c r="M6">
         <v>1.7</v>
@@ -47486,7 +47321,7 @@
         <v>21</v>
       </c>
       <c r="H7">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -47494,11 +47329,8 @@
       <c r="J7">
         <v>0</v>
       </c>
-      <c r="K7">
-        <v>0.22</v>
-      </c>
       <c r="L7">
-        <v>119.4</v>
+        <v>123.02</v>
       </c>
       <c r="M7">
         <v>1.7</v>
@@ -47536,7 +47368,7 @@
         <v>21</v>
       </c>
       <c r="H8">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -47544,11 +47376,8 @@
       <c r="J8">
         <v>0</v>
       </c>
-      <c r="K8">
-        <v>0.16</v>
-      </c>
       <c r="L8">
-        <v>89.05</v>
+        <v>91.75</v>
       </c>
       <c r="M8">
         <v>1.7</v>
@@ -47586,7 +47415,7 @@
         <v>21</v>
       </c>
       <c r="H9">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -47594,11 +47423,8 @@
       <c r="J9">
         <v>0</v>
       </c>
-      <c r="K9">
-        <v>0.21</v>
-      </c>
       <c r="L9">
-        <v>116.64</v>
+        <v>120.17</v>
       </c>
       <c r="M9">
         <v>1.7</v>
@@ -47636,19 +47462,16 @@
         <v>21</v>
       </c>
       <c r="H10">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0.03</v>
-      </c>
-      <c r="K10">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>45.12</v>
+        <v>47.01</v>
       </c>
       <c r="M10">
         <v>1.49</v>
@@ -53087,7 +52910,7 @@
         <v>21</v>
       </c>
       <c r="H2">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -53095,11 +52918,8 @@
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
-        <v>0.17</v>
-      </c>
       <c r="L2">
-        <v>92.59</v>
+        <v>95.4</v>
       </c>
       <c r="M2">
         <v>1.7</v>
@@ -53597,7 +53417,7 @@
         <v>21</v>
       </c>
       <c r="H2">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -53605,11 +53425,8 @@
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
-        <v>1.07</v>
-      </c>
       <c r="L2">
-        <v>588.15</v>
+        <v>602.41</v>
       </c>
       <c r="M2">
         <v>1.69</v>
@@ -53647,7 +53464,7 @@
         <v>21</v>
       </c>
       <c r="H3">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -53655,11 +53472,8 @@
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
-        <v>1.63</v>
-      </c>
       <c r="L3">
-        <v>897.36</v>
+        <v>919.11</v>
       </c>
       <c r="M3">
         <v>1.69</v>
@@ -54654,7 +54468,7 @@
         <v>21</v>
       </c>
       <c r="H2">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -54662,11 +54476,8 @@
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
-        <v>0.19</v>
-      </c>
       <c r="L2">
-        <v>104</v>
+        <v>107.15</v>
       </c>
       <c r="M2">
         <v>1.7</v>
@@ -54704,7 +54515,7 @@
         <v>21</v>
       </c>
       <c r="H3">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -54712,11 +54523,8 @@
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
-        <v>0.08</v>
-      </c>
       <c r="L3">
-        <v>45.05</v>
+        <v>46.14</v>
       </c>
       <c r="M3">
         <v>1.69</v>
@@ -54754,7 +54562,7 @@
         <v>21</v>
       </c>
       <c r="H4">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -54762,11 +54570,8 @@
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
-        <v>0.16</v>
-      </c>
       <c r="L4">
-        <v>85.37</v>
+        <v>87.44</v>
       </c>
       <c r="M4">
         <v>1.69</v>
@@ -54804,19 +54609,16 @@
         <v>21</v>
       </c>
       <c r="H5">
-        <v>1.74</v>
+        <v>1.94</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0.09</v>
-      </c>
-      <c r="K5">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="M5">
         <v>1.94</v>
@@ -54854,7 +54656,7 @@
         <v>21</v>
       </c>
       <c r="H6">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -54862,11 +54664,8 @@
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6">
-        <v>0.13</v>
-      </c>
       <c r="L6">
-        <v>71.61</v>
+        <v>73.349999999999994</v>
       </c>
       <c r="M6">
         <v>1.69</v>
@@ -54904,7 +54703,7 @@
         <v>21</v>
       </c>
       <c r="H7">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -54912,11 +54711,8 @@
       <c r="J7">
         <v>0</v>
       </c>
-      <c r="K7">
-        <v>0.12</v>
-      </c>
       <c r="L7">
-        <v>63.32</v>
+        <v>64.849999999999994</v>
       </c>
       <c r="M7">
         <v>1.69</v>
@@ -54954,7 +54750,7 @@
         <v>21</v>
       </c>
       <c r="H8">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -54962,11 +54758,8 @@
       <c r="J8">
         <v>0</v>
       </c>
-      <c r="K8">
-        <v>0.19</v>
-      </c>
       <c r="L8">
-        <v>106.86</v>
+        <v>110.75</v>
       </c>
       <c r="M8">
         <v>1.71</v>
@@ -55004,19 +54797,16 @@
         <v>21</v>
       </c>
       <c r="H9">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0.09</v>
-      </c>
-      <c r="K9">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>132.38999999999999</v>
+        <v>134.72999999999999</v>
       </c>
       <c r="M9">
         <v>1.73</v>
@@ -55054,7 +54844,7 @@
         <v>21</v>
       </c>
       <c r="H10">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -55062,11 +54852,8 @@
       <c r="J10">
         <v>0</v>
       </c>
-      <c r="K10">
-        <v>0.18</v>
-      </c>
       <c r="L10">
-        <v>101.62</v>
+        <v>104.7</v>
       </c>
       <c r="M10">
         <v>1.7</v>
@@ -55104,7 +54891,7 @@
         <v>21</v>
       </c>
       <c r="H11">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -55112,11 +54899,8 @@
       <c r="J11">
         <v>0</v>
       </c>
-      <c r="K11">
-        <v>0.12</v>
-      </c>
       <c r="L11">
-        <v>63.69</v>
+        <v>65.62</v>
       </c>
       <c r="M11">
         <v>1.7</v>
@@ -55154,7 +54938,7 @@
         <v>21</v>
       </c>
       <c r="H12">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -55162,11 +54946,8 @@
       <c r="J12">
         <v>0</v>
       </c>
-      <c r="K12">
-        <v>0.12</v>
-      </c>
       <c r="L12">
-        <v>68.73</v>
+        <v>70.81</v>
       </c>
       <c r="M12">
         <v>1.7</v>
@@ -55204,7 +54985,7 @@
         <v>21</v>
       </c>
       <c r="H13">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -55212,11 +54993,8 @@
       <c r="J13">
         <v>0</v>
       </c>
-      <c r="K13">
-        <v>0.13</v>
-      </c>
       <c r="L13">
-        <v>72.069999999999993</v>
+        <v>75.13</v>
       </c>
       <c r="M13">
         <v>1.72</v>
@@ -55254,19 +55032,16 @@
         <v>21</v>
       </c>
       <c r="H14">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0.09</v>
-      </c>
-      <c r="K14">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="L14">
-        <v>155.86000000000001</v>
+        <v>158.61000000000001</v>
       </c>
       <c r="M14">
         <v>1.73</v>
@@ -55304,7 +55079,7 @@
         <v>21</v>
       </c>
       <c r="H15">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -55312,11 +55087,8 @@
       <c r="J15">
         <v>0</v>
       </c>
-      <c r="K15">
-        <v>0.09</v>
-      </c>
       <c r="L15">
-        <v>49.3</v>
+        <v>51.39</v>
       </c>
       <c r="M15">
         <v>1.72</v>
@@ -55354,7 +55126,7 @@
         <v>21</v>
       </c>
       <c r="H16">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -55362,11 +55134,8 @@
       <c r="J16">
         <v>0</v>
       </c>
-      <c r="K16">
-        <v>0.13</v>
-      </c>
       <c r="L16">
-        <v>73.569999999999993</v>
+        <v>76.69</v>
       </c>
       <c r="M16">
         <v>1.72</v>
@@ -59905,19 +59674,16 @@
         <v>21</v>
       </c>
       <c r="H2">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0.03</v>
-      </c>
-      <c r="K2">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>59.59</v>
+        <v>61.67</v>
       </c>
       <c r="M2">
         <v>1.48</v>
@@ -60115,7 +59881,7 @@
         <v>21</v>
       </c>
       <c r="H2">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -60123,11 +59889,8 @@
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
-        <v>0.04</v>
-      </c>
       <c r="L2">
-        <v>19.52</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="M2">
         <v>1.69</v>
@@ -60875,7 +60638,7 @@
         <v>21</v>
       </c>
       <c r="H2">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -60883,11 +60646,8 @@
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
-        <v>0.19</v>
-      </c>
       <c r="L2">
-        <v>106.24</v>
+        <v>110.75</v>
       </c>
       <c r="M2">
         <v>1.72</v>
@@ -60925,7 +60685,7 @@
         <v>21</v>
       </c>
       <c r="H3">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -60933,11 +60693,8 @@
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
-        <v>0.1</v>
-      </c>
       <c r="L3">
-        <v>55.49</v>
+        <v>57.84</v>
       </c>
       <c r="M3">
         <v>1.72</v>
@@ -60975,7 +60732,7 @@
         <v>21</v>
       </c>
       <c r="H4">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -60983,11 +60740,8 @@
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
-        <v>0.85</v>
-      </c>
       <c r="L4">
-        <v>468.12</v>
+        <v>487.98</v>
       </c>
       <c r="M4">
         <v>1.72</v>
@@ -63414,19 +63168,16 @@
         <v>21</v>
       </c>
       <c r="H2">
-        <v>1.74</v>
+        <v>1.94</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0.09</v>
-      </c>
-      <c r="K2">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>51.54</v>
+        <v>57.46</v>
       </c>
       <c r="M2">
         <v>1.94</v>
@@ -63464,7 +63215,7 @@
         <v>21</v>
       </c>
       <c r="H3">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -63472,11 +63223,8 @@
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
-        <v>0.16</v>
-      </c>
       <c r="L3">
-        <v>90.75</v>
+        <v>92.95</v>
       </c>
       <c r="M3">
         <v>1.69</v>
@@ -63514,19 +63262,16 @@
         <v>21</v>
       </c>
       <c r="H4">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0.09</v>
-      </c>
-      <c r="K4">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>87.38</v>
+        <v>89.44</v>
       </c>
       <c r="M4">
         <v>1.74</v>
@@ -63564,19 +63309,16 @@
         <v>21</v>
       </c>
       <c r="H5">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0.09</v>
-      </c>
-      <c r="K5">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>39.83</v>
+        <v>40.770000000000003</v>
       </c>
       <c r="M5">
         <v>1.74</v>
@@ -63614,19 +63356,16 @@
         <v>21</v>
       </c>
       <c r="H6">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0.09</v>
-      </c>
-      <c r="K6">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>87.21</v>
+        <v>88.75</v>
       </c>
       <c r="M6">
         <v>1.73</v>
@@ -63758,19 +63497,16 @@
         <v>21</v>
       </c>
       <c r="H9">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0.03</v>
-      </c>
-      <c r="K9">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>42.83</v>
+        <v>44.63</v>
       </c>
       <c r="M9">
         <v>1.49</v>
@@ -63808,19 +63544,16 @@
         <v>21</v>
       </c>
       <c r="H10">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0.03</v>
-      </c>
-      <c r="K10">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>25.23</v>
+        <v>26.11</v>
       </c>
       <c r="M10">
         <v>1.48</v>
@@ -63858,19 +63591,16 @@
         <v>21</v>
       </c>
       <c r="H11">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0.09</v>
-      </c>
-      <c r="K11">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>30.76</v>
+        <v>31.48</v>
       </c>
       <c r="M11">
         <v>1.74</v>
@@ -63908,19 +63638,16 @@
         <v>21</v>
       </c>
       <c r="H12">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0.03</v>
-      </c>
-      <c r="K12">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="L12">
-        <v>16.84</v>
+        <v>17.55</v>
       </c>
       <c r="M12">
         <v>1.49</v>
@@ -63958,19 +63685,16 @@
         <v>21</v>
       </c>
       <c r="H13">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0.09</v>
-      </c>
-      <c r="K13">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="L13">
-        <v>52.77</v>
+        <v>53.7</v>
       </c>
       <c r="M13">
         <v>1.73</v>
